--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1561" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF53E938-EED5-4365-BCD1-FCDB49BBF05C}"/>
+  <xr:revisionPtr revIDLastSave="1563" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAF33CD9-A4CE-4C01-9A4F-AE59260DB564}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="36000" yWindow="420" windowWidth="21600" windowHeight="11295" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="36000" yWindow="420" windowWidth="21600" windowHeight="11295" firstSheet="12" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1636" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="866">
   <si>
     <t>Type</t>
   </si>
@@ -2182,6 +2182,12 @@
     <t>Mark to Find  HT Fan for chamber heater  or use external motor  as per Roys previous design.</t>
   </si>
   <si>
+    <t xml:space="preserve">mark </t>
+  </si>
+  <si>
+    <t xml:space="preserve">testing ROBO fan </t>
+  </si>
+  <si>
     <t xml:space="preserve">Electrical BOM  to be completed </t>
   </si>
   <si>
@@ -2207,9 +2213,6 @@
   </si>
   <si>
     <t>Do electrical drawings  load cell, Mains,  others</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mark </t>
   </si>
   <si>
     <t>done  untill controll borad confirmed</t>
@@ -3730,15 +3733,6 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="5" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3752,9 +3746,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3778,6 +3769,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -8276,32 +8279,32 @@
       <c r="A55" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B55" s="230" t="s">
+      <c r="B55" s="227" t="s">
         <v>139</v>
       </c>
-      <c r="C55" s="231"/>
-      <c r="D55" s="232">
+      <c r="C55" s="228"/>
+      <c r="D55" s="229">
         <v>1</v>
       </c>
       <c r="E55" s="73">
         <v>1</v>
       </c>
-      <c r="F55" s="233">
+      <c r="F55" s="230">
         <v>1.4</v>
       </c>
-      <c r="G55" s="234">
+      <c r="G55" s="231">
         <f>E55*F55</f>
         <v>1.4</v>
       </c>
-      <c r="H55" s="238" t="s">
+      <c r="H55" s="234" t="s">
         <v>140</v>
       </c>
-      <c r="I55" s="235" t="s">
+      <c r="I55" s="245" t="s">
         <v>55</v>
       </c>
       <c r="J55" s="157"/>
-      <c r="K55" s="236"/>
-      <c r="L55" s="237"/>
+      <c r="K55" s="232"/>
+      <c r="L55" s="233"/>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" s="33" t="s">
@@ -13737,12 +13740,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="227" t="s">
+      <c r="B1" s="242" t="s">
         <v>663</v>
       </c>
-      <c r="C1" s="228"/>
-      <c r="D1" s="228"/>
-      <c r="E1" s="229"/>
+      <c r="C1" s="243"/>
+      <c r="D1" s="243"/>
+      <c r="E1" s="244"/>
       <c r="F1" s="42"/>
     </row>
     <row r="2" spans="2:6">
@@ -14167,85 +14170,91 @@
       <c r="A6" t="s">
         <v>707</v>
       </c>
+      <c r="B6" t="s">
+        <v>708</v>
+      </c>
+      <c r="C6" t="s">
+        <v>709</v>
+      </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B7" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C9" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B10" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="C10" s="226" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="C11" s="242" t="s">
         <v>721</v>
+      </c>
+      <c r="C11" s="238" t="s">
+        <v>722</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C12" s="224" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="D12" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>726</v>
-      </c>
-      <c r="C13" s="242" t="s">
         <v>727</v>
+      </c>
+      <c r="C13" s="238" t="s">
+        <v>728</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>703</v>
@@ -14256,65 +14265,65 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B15" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D15" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B16" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C16" s="224" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D16" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B17" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B18" t="s">
         <v>703</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B20" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C20" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
   </sheetData>
@@ -14338,10 +14347,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C1" t="s">
         <v>366</v>
@@ -14352,126 +14361,126 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C2" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B3" s="223" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75" customHeight="1">
       <c r="A4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C6" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12" customHeight="1">
-      <c r="A7" s="239" t="s">
-        <v>759</v>
-      </c>
-      <c r="B7" s="240" t="s">
+      <c r="A7" s="235" t="s">
         <v>760</v>
       </c>
-      <c r="C7" s="239" t="s">
+      <c r="B7" s="236" t="s">
         <v>761</v>
       </c>
-      <c r="D7" s="241" t="s">
+      <c r="C7" s="235" t="s">
         <v>762</v>
+      </c>
+      <c r="D7" s="237" t="s">
+        <v>763</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C8" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C9" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C11" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C12" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -14494,7 +14503,7 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B19" s="155" t="s">
         <v>628</v>
@@ -14508,176 +14517,176 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C20" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="42" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="B22" s="42" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C22" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="42" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C23" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="42" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C24" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="42" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C25" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="244"/>
-      <c r="B26" s="245" t="s">
-        <v>791</v>
-      </c>
-      <c r="C26" s="244" t="s">
+      <c r="A26" s="240"/>
+      <c r="B26" s="241" t="s">
         <v>792</v>
       </c>
+      <c r="C26" s="240" t="s">
+        <v>793</v>
+      </c>
       <c r="D26" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="B27" s="42" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="C27" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C28" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="D28" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="42" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C29" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C30" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="B31" s="42" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C31" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="B32" s="42" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C32" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="B33" s="42" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C33" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C34" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D34" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="B35" s="42" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C35" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" s="42" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C36" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="B37" s="42" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C37" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="B38" s="42" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C38" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -14688,10 +14697,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B41" s="156" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C41" t="s">
         <v>366</v>
@@ -14699,68 +14708,68 @@
     </row>
     <row r="42" spans="1:4">
       <c r="B42" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C42" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="B43" t="s">
+        <v>827</v>
+      </c>
+      <c r="C43" t="s">
         <v>826</v>
-      </c>
-      <c r="C43" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="B44" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C44" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="B45" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C45" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="B47" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C47" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D47" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="D48" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="B49" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="B50" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B52" s="156" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C52" t="s">
         <v>366</v>
@@ -14768,82 +14777,82 @@
     </row>
     <row r="53" spans="1:3">
       <c r="B53" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C53" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="B54" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C54" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="B55" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C55" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="B56" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C56" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="B57" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C57" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="B58" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C58" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="B59" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C59" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="B60" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C60" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="B61" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C61" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="B62" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C62" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -14874,7 +14883,7 @@
         <v>365</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>366</v>
@@ -14883,83 +14892,83 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="C2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="E2" s="172" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="C3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" customHeight="1">
       <c r="A6" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C12" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -17059,7 +17068,7 @@
       <c r="E44" s="63"/>
     </row>
     <row r="46" spans="1:5">
-      <c r="B46" s="243" t="s">
+      <c r="B46" s="239" t="s">
         <v>487</v>
       </c>
     </row>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1563" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAF33CD9-A4CE-4C01-9A4F-AE59260DB564}"/>
+  <xr:revisionPtr revIDLastSave="1568" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3B3047C-F182-4CC7-9472-2DC737019940}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="36000" yWindow="420" windowWidth="21600" windowHeight="11295" firstSheet="12" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="36000" yWindow="420" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="866">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1639" uniqueCount="867">
   <si>
     <t>Type</t>
   </si>
@@ -1358,6 +1358,9 @@
   </si>
   <si>
     <t>Fan 24V  - CPAP  cooler 4010</t>
+  </si>
+  <si>
+    <t>need to ADD  CONNECTOR FOR CPAP FAN  PH4</t>
   </si>
   <si>
     <t>Fan Dual Ball Bearing 4010</t>
@@ -3263,7 +3266,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="247">
+  <cellXfs count="248">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
@@ -3778,6 +3781,9 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -8299,7 +8305,7 @@
       <c r="H55" s="234" t="s">
         <v>140</v>
       </c>
-      <c r="I55" s="245" t="s">
+      <c r="I55" s="246" t="s">
         <v>55</v>
       </c>
       <c r="J55" s="157"/>
@@ -10044,7 +10050,7 @@
         <v>251</v>
       </c>
       <c r="D106" s="76">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E106" s="73">
         <v>1</v>
@@ -11168,7 +11174,7 @@
       <c r="H139" s="100" t="s">
         <v>344</v>
       </c>
-      <c r="I139" s="246" t="s">
+      <c r="I139" s="247" t="s">
         <v>345</v>
       </c>
       <c r="J139" s="157"/>
@@ -11623,45 +11629,45 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="F1" s="171" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>415</v>
@@ -11682,7 +11688,7 @@
       </c>
       <c r="H2" s="175"/>
       <c r="J2" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="K2" s="1">
         <v>130</v>
@@ -11693,7 +11699,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B3" s="38" t="s">
         <v>416</v>
@@ -11712,7 +11718,7 @@
       </c>
       <c r="H3" s="175"/>
       <c r="J3" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="K3">
         <v>130</v>
@@ -11723,7 +11729,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>417</v>
@@ -11744,7 +11750,7 @@
       </c>
       <c r="H4" s="175"/>
       <c r="J4" s="1" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="K4" s="1">
         <v>155</v>
@@ -11755,7 +11761,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>418</v>
@@ -11776,7 +11782,7 @@
       </c>
       <c r="H5" s="175"/>
       <c r="J5" s="1" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="K5" s="1">
         <v>150</v>
@@ -11787,7 +11793,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B6" s="38" t="s">
         <v>419</v>
@@ -11812,7 +11818,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>420</v>
@@ -11837,7 +11843,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>421</v>
@@ -11858,12 +11864,12 @@
       </c>
       <c r="H8" s="175"/>
       <c r="J8" s="1" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>422</v>
@@ -11884,7 +11890,7 @@
       </c>
       <c r="H9" s="175"/>
       <c r="J9" s="185" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="K9" s="185">
         <v>3</v>
@@ -11892,7 +11898,7 @@
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B10" s="38" t="s">
         <v>423</v>
@@ -11911,7 +11917,7 @@
       </c>
       <c r="H10" s="175"/>
       <c r="J10" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="K10">
         <v>0.25</v>
@@ -11919,7 +11925,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B11" s="38" t="s">
         <v>424</v>
@@ -11938,7 +11944,7 @@
       </c>
       <c r="H11" s="175"/>
       <c r="J11" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="K11">
         <f>K9/K10</f>
@@ -11947,7 +11953,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B12" s="38" t="s">
         <v>425</v>
@@ -11966,7 +11972,7 @@
       </c>
       <c r="H12" s="175"/>
       <c r="J12" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="K12">
         <f>K9/K10</f>
@@ -11975,7 +11981,7 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B13" s="38" t="s">
         <v>426</v>
@@ -11994,7 +12000,7 @@
       </c>
       <c r="H13" s="175"/>
       <c r="J13" s="1" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="K13">
         <v>0.6</v>
@@ -12002,7 +12008,7 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>427</v>
@@ -12021,7 +12027,7 @@
       </c>
       <c r="H14" s="175"/>
       <c r="J14" s="1" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="K14" s="183">
         <f>K9/K13</f>
@@ -12030,7 +12036,7 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>428</v>
@@ -12049,7 +12055,7 @@
       </c>
       <c r="H15" s="175"/>
       <c r="J15" s="1" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="K15" s="184">
         <v>0.25</v>
@@ -12057,7 +12063,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B16" s="38" t="s">
         <v>429</v>
@@ -12076,15 +12082,15 @@
       </c>
       <c r="H16" s="175"/>
       <c r="J16" s="1" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B17" s="38" t="s">
         <v>430</v>
@@ -12105,10 +12111,10 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D18" s="183"/>
       <c r="E18" s="1">
@@ -12126,10 +12132,10 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D19" s="183"/>
       <c r="E19" s="1">
@@ -12147,10 +12153,10 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D20" s="183"/>
       <c r="E20" s="1">
@@ -12168,10 +12174,10 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="D21" s="183"/>
       <c r="E21" s="1">
@@ -12189,10 +12195,10 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D22" s="183"/>
       <c r="E22" s="1">
@@ -12210,10 +12216,10 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D23" s="183"/>
       <c r="E23" s="1">
@@ -12231,10 +12237,10 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D24" s="183"/>
       <c r="E24" s="1">
@@ -12252,10 +12258,10 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B25" s="38" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D25" s="183"/>
       <c r="E25" s="38">
@@ -12273,10 +12279,10 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D26" s="183"/>
       <c r="E26" s="1">
@@ -12294,10 +12300,10 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D27" s="183"/>
       <c r="E27" s="1">
@@ -12315,10 +12321,10 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B28" s="38" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D28" s="183"/>
       <c r="E28" s="38">
@@ -12336,10 +12342,10 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B29" s="38" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D29" s="183"/>
       <c r="E29" s="38">
@@ -12357,10 +12363,10 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B30" s="38" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D30" s="183"/>
       <c r="E30" s="38">
@@ -12378,10 +12384,10 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B31" s="38" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="D31" s="183"/>
       <c r="E31" s="38">
@@ -12399,10 +12405,10 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B32" s="38" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D32" s="183"/>
       <c r="E32" s="38">
@@ -12420,10 +12426,10 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B33" s="38" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D33" s="183"/>
       <c r="E33" s="38">
@@ -12441,10 +12447,10 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B34" s="38" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D34" s="183"/>
       <c r="E34" s="38">
@@ -12462,10 +12468,10 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B35" s="38" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D35" s="183"/>
       <c r="E35" s="38">
@@ -12483,10 +12489,10 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B36" s="38" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D36" s="183"/>
       <c r="E36" s="38">
@@ -12504,10 +12510,10 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B37" s="38" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D37" s="183"/>
       <c r="E37" s="38">
@@ -12525,10 +12531,10 @@
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B38" s="174" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="D38" s="183"/>
       <c r="E38" s="174">
@@ -12546,10 +12552,10 @@
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B39" s="38" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D39" s="183"/>
       <c r="E39" s="38">
@@ -12567,10 +12573,10 @@
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B40" s="38" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D40" s="183"/>
       <c r="E40" s="38">
@@ -12588,10 +12594,10 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B41" s="38" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D41" s="183"/>
       <c r="E41" s="38">
@@ -12609,10 +12615,10 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B42" s="38" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D42" s="183"/>
       <c r="E42" s="38">
@@ -12630,10 +12636,10 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B43" s="38" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D43" s="183"/>
       <c r="E43" s="38">
@@ -12651,10 +12657,10 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D44" s="183"/>
       <c r="E44" s="38">
@@ -12672,10 +12678,10 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B45" s="38" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D45" s="183"/>
       <c r="E45" s="38">
@@ -12693,10 +12699,10 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B46" s="38" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D46" s="183"/>
       <c r="E46" s="38">
@@ -12714,10 +12720,10 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B47" s="38" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D47" s="183"/>
       <c r="E47" s="38">
@@ -12735,10 +12741,10 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D48" s="183"/>
       <c r="E48" s="38">
@@ -12756,10 +12762,10 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D49" s="183"/>
       <c r="E49" s="38">
@@ -12777,10 +12783,10 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D50" s="183"/>
       <c r="E50" s="38">
@@ -12798,10 +12804,10 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D51" s="183"/>
       <c r="E51" s="38">
@@ -12819,10 +12825,10 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D52" s="183"/>
       <c r="E52" s="38">
@@ -12840,10 +12846,10 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D53" s="183"/>
       <c r="E53" s="38">
@@ -12861,10 +12867,10 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D54" s="183"/>
       <c r="E54" s="38">
@@ -12882,10 +12888,10 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D55" s="183"/>
       <c r="E55" s="1">
@@ -12903,10 +12909,10 @@
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D56" s="183"/>
       <c r="E56" s="1">
@@ -12924,10 +12930,10 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D57" s="183"/>
       <c r="E57" s="38">
@@ -12945,10 +12951,10 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="1" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D58" s="183"/>
       <c r="E58" s="38">
@@ -12966,7 +12972,7 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>392</v>
@@ -12991,7 +12997,7 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>394</v>
@@ -13012,7 +13018,7 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>396</v>
@@ -13035,7 +13041,7 @@
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="1" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>397</v>
@@ -13058,10 +13064,10 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D63" s="183"/>
       <c r="E63" s="1">
@@ -13079,10 +13085,10 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B64" s="45" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D64" s="183"/>
       <c r="E64" s="45">
@@ -13100,10 +13106,10 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B65" s="38" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D65" s="183"/>
       <c r="E65" s="38">
@@ -13121,10 +13127,10 @@
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="1" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B66" s="38" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D66" s="183"/>
       <c r="E66" s="38">
@@ -13142,10 +13148,10 @@
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B67" s="174" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D67" s="183"/>
       <c r="E67" s="174">
@@ -13163,10 +13169,10 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B68" s="69" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D68" s="183"/>
       <c r="E68" s="69">
@@ -13186,10 +13192,10 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B69" s="69" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D69" s="183">
         <v>2</v>
@@ -13209,10 +13215,10 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B70" s="69" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D70" s="183">
         <v>9</v>
@@ -13232,10 +13238,10 @@
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B71" s="69" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D71" s="183"/>
       <c r="E71" s="69">
@@ -13253,10 +13259,10 @@
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B72" s="69" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D72" s="183"/>
       <c r="E72" s="69">
@@ -13274,10 +13280,10 @@
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B73" s="69" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C73">
         <v>12.38</v>
@@ -13302,10 +13308,10 @@
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B74" s="38" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C74">
         <v>12.68</v>
@@ -13330,10 +13336,10 @@
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="1" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B75" s="69" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D75" s="183">
         <v>45</v>
@@ -13355,10 +13361,10 @@
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="1" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B76" s="38" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C76">
         <v>7.45</v>
@@ -13383,10 +13389,10 @@
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B77" s="38" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D77" s="183"/>
       <c r="E77" s="69">
@@ -13404,10 +13410,10 @@
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B78" s="38" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D78" s="183"/>
       <c r="E78" s="69">
@@ -13425,10 +13431,10 @@
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B79" s="38" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D79" s="183"/>
       <c r="E79" s="69">
@@ -13446,10 +13452,10 @@
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B80" s="38" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D80" s="183"/>
       <c r="E80" s="69">
@@ -13467,10 +13473,10 @@
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B81" s="38" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D81" s="183"/>
       <c r="E81" s="69">
@@ -13488,10 +13494,10 @@
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B82" s="38" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D82" s="183"/>
       <c r="E82" s="69">
@@ -13509,10 +13515,10 @@
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B83" s="38" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D83" s="183"/>
       <c r="E83" s="69">
@@ -13530,10 +13536,10 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B84" s="38" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D84" s="183"/>
       <c r="E84" s="69">
@@ -13551,10 +13557,10 @@
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B85" s="38" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D85" s="183"/>
       <c r="E85" s="69">
@@ -13572,10 +13578,10 @@
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B86" s="38" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D86" s="183"/>
       <c r="E86" s="69">
@@ -13593,10 +13599,10 @@
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B87" s="38" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D87" s="183"/>
       <c r="E87" s="69">
@@ -13614,10 +13620,10 @@
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B88" s="38" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D88" s="183"/>
       <c r="E88" s="69">
@@ -13635,10 +13641,10 @@
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B89" s="38" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D89" s="183"/>
       <c r="E89" s="69">
@@ -13656,10 +13662,10 @@
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B90" s="38" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D90" s="183"/>
       <c r="E90" s="69">
@@ -13677,10 +13683,10 @@
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="1" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B91" s="38" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D91" s="183"/>
       <c r="E91" s="69">
@@ -13741,7 +13747,7 @@
   <sheetData>
     <row r="1" spans="2:6">
       <c r="B1" s="242" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C1" s="243"/>
       <c r="D1" s="243"/>
@@ -13750,22 +13756,22 @@
     </row>
     <row r="2" spans="2:6">
       <c r="B2" s="40" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E2" s="136" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="F2" s="42"/>
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="40" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C3" s="42"/>
       <c r="E3" s="39"/>
@@ -13776,13 +13782,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E4" s="136" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="F4" s="42"/>
     </row>
@@ -13791,13 +13797,13 @@
         <v>2</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E5" s="136" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F5" s="42"/>
     </row>
@@ -13806,13 +13812,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E6" s="136" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="F6" s="42"/>
     </row>
@@ -13821,7 +13827,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D7" s="6"/>
       <c r="E7" s="136"/>
@@ -13843,7 +13849,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="B10" s="40" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C10" s="42"/>
       <c r="D10" s="6"/>
@@ -13856,10 +13862,10 @@
       </c>
       <c r="C11" s="42"/>
       <c r="D11" s="6" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E11" s="136" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F11" s="42"/>
     </row>
@@ -13869,10 +13875,10 @@
       </c>
       <c r="C12" s="42"/>
       <c r="D12" s="6" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="E12" s="136" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="F12" s="42"/>
     </row>
@@ -13882,10 +13888,10 @@
       </c>
       <c r="C13" s="42"/>
       <c r="D13" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E13" s="136" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F13" s="42"/>
     </row>
@@ -13895,10 +13901,10 @@
       </c>
       <c r="C14" s="42"/>
       <c r="D14" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E14" s="136" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="F14" s="42"/>
     </row>
@@ -13908,10 +13914,10 @@
       </c>
       <c r="C15" s="42"/>
       <c r="D15" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E15" s="136" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F15" s="42"/>
     </row>
@@ -13921,10 +13927,10 @@
       </c>
       <c r="C16" s="42"/>
       <c r="D16" s="6" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E16" s="136" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F16" s="42"/>
     </row>
@@ -13935,7 +13941,7 @@
       <c r="C17" s="42"/>
       <c r="D17" s="6"/>
       <c r="E17" s="41" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="F17" s="42"/>
     </row>
@@ -13946,7 +13952,7 @@
       <c r="C18" s="42"/>
       <c r="D18" s="6"/>
       <c r="E18" s="41" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="F18" s="42"/>
     </row>
@@ -13956,10 +13962,10 @@
       </c>
       <c r="C19" s="42"/>
       <c r="D19" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E19" s="136" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="F19" s="42"/>
     </row>
@@ -13969,10 +13975,10 @@
       </c>
       <c r="C20" s="42"/>
       <c r="D20" s="6" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E20" s="136" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="F20" s="42"/>
     </row>
@@ -13985,13 +13991,13 @@
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="40" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E22" s="136"/>
       <c r="F22" s="42"/>
@@ -14001,13 +14007,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="42" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E23" s="136" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F23" s="42"/>
     </row>
@@ -14016,13 +14022,13 @@
         <v>2</v>
       </c>
       <c r="C24" s="42" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E24" s="136" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F24" s="42"/>
     </row>
@@ -14031,13 +14037,13 @@
         <v>3</v>
       </c>
       <c r="C25" s="42" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="E25" s="136" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="F25" s="42"/>
     </row>
@@ -14046,7 +14052,7 @@
         <v>4</v>
       </c>
       <c r="C26" s="138" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D26" s="139"/>
       <c r="E26" s="140"/>
@@ -14103,227 +14109,227 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B1" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C1" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D1" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C2" s="225" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B3" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="D3" s="8"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C4" s="171" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="D4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1">
       <c r="A5" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C5" s="171" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B6" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C6" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B7" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D7" s="68" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C9" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B10" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C10" s="226" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D10" s="1"/>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C11" s="238" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C12" s="224" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="D12" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C13" s="238" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B15" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D15" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B16" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C16" s="224" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D16" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B17" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B18" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B20" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C20" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -14347,10 +14353,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B1" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C1" t="s">
         <v>366</v>
@@ -14361,126 +14367,126 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C2" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B3" s="223" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75" customHeight="1">
       <c r="A4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C6" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12" customHeight="1">
       <c r="A7" s="235" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B7" s="236" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C7" s="235" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D7" s="237" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B8" s="42" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C8" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C9" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C11" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C12" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -14503,10 +14509,10 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="B19" s="155" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C19" t="s">
         <v>366</v>
@@ -14517,176 +14523,176 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C20" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="42" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="B22" s="42" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C22" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="42" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C23" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="42" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C24" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="42" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="C25" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="240"/>
       <c r="B26" s="241" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C26" s="240" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D26" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="B27" s="42" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C27" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B28" s="42" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C28" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="D28" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="42" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C29" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B30" s="42" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C30" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="B31" s="42" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C31" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="B32" s="42" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C32" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="B33" s="42" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="C33" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="B34" s="42" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="C34" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="D34" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="B35" s="42" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C35" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" s="42" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C36" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="B37" s="42" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C37" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="B38" s="42" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C38" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -14697,10 +14703,10 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B41" s="156" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C41" t="s">
         <v>366</v>
@@ -14708,68 +14714,68 @@
     </row>
     <row r="42" spans="1:4">
       <c r="B42" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C42" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="B43" t="s">
+        <v>828</v>
+      </c>
+      <c r="C43" t="s">
         <v>827</v>
-      </c>
-      <c r="C43" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="B44" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C44" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="B45" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C45" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="B47" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="C47" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D47" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="D48" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="B49" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="B50" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B52" s="156" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C52" t="s">
         <v>366</v>
@@ -14777,82 +14783,82 @@
     </row>
     <row r="53" spans="1:3">
       <c r="B53" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C53" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="54" spans="1:3">
       <c r="B54" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="C54" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="B55" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C55" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="56" spans="1:3">
       <c r="B56" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="C56" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="B57" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C57" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="B58" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C58" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="59" spans="1:3">
       <c r="B59" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C59" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="60" spans="1:3">
       <c r="B60" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C60" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="B61" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C61" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="B62" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C62" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
   </sheetData>
@@ -14883,7 +14889,7 @@
         <v>365</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>366</v>
@@ -14892,83 +14898,83 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B2" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D2" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E2" s="172" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" customHeight="1">
       <c r="A6" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C12" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
   </sheetData>
@@ -16089,7 +16095,7 @@
     <tabColor rgb="FF00B050"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
@@ -16097,12 +16103,13 @@
     <col min="3" max="3" width="15" style="2" customWidth="1"/>
     <col min="4" max="4" width="10" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.7109375" style="2" customWidth="1"/>
-    <col min="6" max="16361" width="11.42578125" style="2"/>
+    <col min="6" max="6" width="54.5703125" style="2" customWidth="1"/>
+    <col min="7" max="16361" width="11.42578125" style="2"/>
     <col min="16362" max="16367" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="16368" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
+    <row r="1" spans="1:6" ht="30" customHeight="1">
       <c r="A1" s="53"/>
       <c r="B1" s="66" t="s">
         <v>365</v>
@@ -16115,7 +16122,7 @@
       </c>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="54" t="s">
         <v>368</v>
       </c>
@@ -16130,7 +16137,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" s="51" t="s">
         <v>372</v>
       </c>
@@ -16145,7 +16152,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" s="51" t="s">
         <v>375</v>
       </c>
@@ -16160,7 +16167,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="51" t="s">
         <v>378</v>
       </c>
@@ -16175,7 +16182,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="25"/>
       <c r="B6" s="28" t="s">
         <v>433</v>
@@ -16185,11 +16192,14 @@
         <v>1</v>
       </c>
       <c r="E6" s="56"/>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="245" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="25"/>
       <c r="B7" s="58" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C7"/>
       <c r="D7" s="15">
@@ -16197,10 +16207,10 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" s="25"/>
       <c r="B8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C8" s="67"/>
       <c r="D8" s="15">
@@ -16208,10 +16218,10 @@
       </c>
       <c r="E8" s="56"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="25"/>
       <c r="B9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C9"/>
       <c r="D9" s="15">
@@ -16219,10 +16229,10 @@
       </c>
       <c r="E9" s="56"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" s="25"/>
       <c r="B10" s="1" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="15">
@@ -16230,7 +16240,7 @@
       </c>
       <c r="E10" s="56"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11" s="25"/>
       <c r="B11" t="s">
         <v>177</v>
@@ -16241,12 +16251,12 @@
       </c>
       <c r="E11" s="56"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12" s="51" t="s">
         <v>389</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="15">
@@ -16254,10 +16264,10 @@
       </c>
       <c r="E12" s="56"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6">
       <c r="A13" s="25"/>
       <c r="B13" s="1" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="15">
@@ -16265,10 +16275,10 @@
       </c>
       <c r="E13" s="56"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6">
       <c r="A14" s="25"/>
       <c r="B14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="15">
@@ -16276,10 +16286,10 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:6">
       <c r="A15" s="25"/>
       <c r="B15" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="15">
@@ -16287,7 +16297,7 @@
       </c>
       <c r="E15" s="56"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:6">
       <c r="A16" s="25"/>
       <c r="B16" s="13" t="s">
         <v>254</v>
@@ -16301,7 +16311,7 @@
     <row r="17" spans="1:5">
       <c r="A17" s="25"/>
       <c r="B17" s="13" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C17" s="13"/>
       <c r="D17" s="15">
@@ -16312,10 +16322,10 @@
     <row r="18" spans="1:5">
       <c r="A18" s="25"/>
       <c r="B18" s="215" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C18" s="68" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D18" s="57">
         <v>1</v>
@@ -16325,7 +16335,7 @@
     <row r="19" spans="1:5">
       <c r="A19" s="25"/>
       <c r="B19" s="69" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C19" s="69"/>
       <c r="D19" s="15">
@@ -16336,7 +16346,7 @@
     <row r="20" spans="1:5">
       <c r="A20" s="25"/>
       <c r="B20" s="216" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C20" s="216"/>
       <c r="D20" s="15">
@@ -16347,7 +16357,7 @@
     <row r="21" spans="1:5">
       <c r="A21" s="25"/>
       <c r="B21" s="67" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C21" s="67"/>
       <c r="D21" s="15">
@@ -16358,7 +16368,7 @@
     <row r="22" spans="1:5">
       <c r="A22" s="25"/>
       <c r="B22" s="216" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C22" s="216"/>
       <c r="D22" s="15">
@@ -16369,7 +16379,7 @@
     <row r="23" spans="1:5">
       <c r="A23" s="25"/>
       <c r="B23" s="67" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C23" s="67"/>
       <c r="D23" s="15">
@@ -16380,7 +16390,7 @@
     <row r="24" spans="1:5">
       <c r="A24" s="25"/>
       <c r="B24" s="70" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C24" s="70"/>
       <c r="D24" s="15">
@@ -16391,7 +16401,7 @@
     <row r="25" spans="1:5">
       <c r="A25" s="25"/>
       <c r="B25" s="38" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C25" s="70"/>
       <c r="D25" s="15">
@@ -16402,7 +16412,7 @@
     <row r="26" spans="1:5">
       <c r="A26" s="25"/>
       <c r="B26" s="70" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C26" s="67"/>
       <c r="D26" s="15">
@@ -16420,7 +16430,7 @@
     <row r="28" spans="1:5" ht="18.75">
       <c r="A28" s="25"/>
       <c r="B28" s="21" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C28" s="22"/>
       <c r="D28" s="46"/>
@@ -16453,7 +16463,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="25"/>
       <c r="B31" s="20" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C31"/>
       <c r="D31" s="47">
@@ -16464,7 +16474,7 @@
     <row r="32" spans="1:5">
       <c r="A32" s="25"/>
       <c r="B32" s="20" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="47">
@@ -16475,7 +16485,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="25"/>
       <c r="B33" s="24" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C33" s="67"/>
       <c r="D33" s="47">
@@ -16530,7 +16540,7 @@
     <row r="38" spans="1:5">
       <c r="A38" s="25"/>
       <c r="B38" s="20" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="47">
@@ -16622,7 +16632,7 @@
         <v>372</v>
       </c>
       <c r="B3" s="196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C3" s="196"/>
       <c r="D3" s="15">
@@ -16678,10 +16688,10 @@
     <row r="7" spans="1:5">
       <c r="A7" s="25"/>
       <c r="B7" s="13" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C7" s="196" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D7" s="203">
         <v>28</v>
@@ -16691,7 +16701,7 @@
     <row r="8" spans="1:5">
       <c r="A8" s="25"/>
       <c r="B8" s="196" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C8" s="196"/>
       <c r="D8" s="15">
@@ -16702,7 +16712,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="25"/>
       <c r="B9" s="38" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="D9" s="15">
         <v>3</v>
@@ -16723,7 +16733,7 @@
     <row r="11" spans="1:5">
       <c r="A11" s="25"/>
       <c r="B11" s="192" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C11" s="196"/>
       <c r="D11" s="15">
@@ -16747,7 +16757,7 @@
     <row r="13" spans="1:5">
       <c r="A13" s="25"/>
       <c r="B13" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D13" s="15">
         <v>3</v>
@@ -16757,7 +16767,7 @@
     <row r="14" spans="1:5">
       <c r="A14" s="25"/>
       <c r="B14" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D14" s="15">
         <v>27</v>
@@ -16797,7 +16807,7 @@
     <row r="18" spans="1:5">
       <c r="A18" s="25"/>
       <c r="B18" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D18" s="15">
         <v>3</v>
@@ -16807,7 +16817,7 @@
     <row r="19" spans="1:5">
       <c r="A19" s="25"/>
       <c r="B19" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D19" s="15">
         <v>3</v>
@@ -16817,7 +16827,7 @@
     <row r="20" spans="1:5">
       <c r="A20" s="25"/>
       <c r="B20" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D20" s="15">
         <v>3</v>
@@ -16889,7 +16899,7 @@
     <row r="27" spans="1:5">
       <c r="A27" s="25"/>
       <c r="B27" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D27" s="15">
         <v>3</v>
@@ -16899,7 +16909,7 @@
     <row r="28" spans="1:5">
       <c r="A28" s="25"/>
       <c r="B28" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D28" s="15">
         <v>3</v>
@@ -16909,7 +16919,7 @@
     <row r="29" spans="1:5">
       <c r="A29" s="25"/>
       <c r="B29" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D29" s="15">
         <v>3</v>
@@ -16919,7 +16929,7 @@
     <row r="30" spans="1:5">
       <c r="A30" s="25"/>
       <c r="B30" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D30" s="15">
         <v>1</v>
@@ -16929,7 +16939,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="25"/>
       <c r="B31" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D31" s="15">
         <v>1</v>
@@ -16939,7 +16949,7 @@
     <row r="32" spans="1:5">
       <c r="A32" s="25"/>
       <c r="B32" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D32" s="15">
         <v>1</v>
@@ -16949,7 +16959,7 @@
     <row r="33" spans="1:5">
       <c r="A33" s="25"/>
       <c r="B33" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D33" s="15">
         <v>2</v>
@@ -16959,7 +16969,7 @@
     <row r="34" spans="1:5">
       <c r="A34" s="25"/>
       <c r="B34" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D34" s="15">
         <v>1</v>
@@ -16969,7 +16979,7 @@
     <row r="35" spans="1:5">
       <c r="A35" s="25"/>
       <c r="B35" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="D35" s="15">
         <v>1</v>
@@ -16979,7 +16989,7 @@
     <row r="36" spans="1:5">
       <c r="A36" s="25"/>
       <c r="B36" s="196" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C36" s="196"/>
       <c r="D36" s="15">
@@ -16990,7 +17000,7 @@
     <row r="37" spans="1:5">
       <c r="A37" s="25"/>
       <c r="B37" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D37" s="15">
         <v>1</v>
@@ -17000,7 +17010,7 @@
     <row r="38" spans="1:5">
       <c r="A38" s="25"/>
       <c r="B38" s="2" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D38" s="15">
         <v>1</v>
@@ -17010,7 +17020,7 @@
     <row r="39" spans="1:5">
       <c r="A39" s="25"/>
       <c r="B39" s="2" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D39" s="15">
         <v>1</v>
@@ -17020,7 +17030,7 @@
     <row r="40" spans="1:5">
       <c r="A40" s="25"/>
       <c r="B40" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D40" s="15">
         <v>1</v>
@@ -17030,7 +17040,7 @@
     <row r="41" spans="1:5">
       <c r="A41" s="25"/>
       <c r="B41" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D41" s="15">
         <v>3</v>
@@ -17040,7 +17050,7 @@
     <row r="42" spans="1:5">
       <c r="A42" s="25"/>
       <c r="B42" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D42" s="15">
         <v>1</v>
@@ -17050,7 +17060,7 @@
     <row r="43" spans="1:5">
       <c r="A43" s="25"/>
       <c r="B43" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D43" s="15">
         <v>1</v>
@@ -17060,7 +17070,7 @@
     <row r="44" spans="1:5" ht="15.75" thickBot="1">
       <c r="A44" s="61"/>
       <c r="B44" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D44" s="15">
         <v>1</v>
@@ -17069,7 +17079,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="B46" s="239" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
   </sheetData>
@@ -17145,7 +17155,7 @@
         <v>372</v>
       </c>
       <c r="B3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C3" s="196"/>
       <c r="D3" s="15">
@@ -17175,7 +17185,7 @@
         <v>378</v>
       </c>
       <c r="B5" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C5" s="196"/>
       <c r="D5" s="15">
@@ -17188,7 +17198,7 @@
     <row r="6" spans="1:5">
       <c r="A6" s="25"/>
       <c r="B6" s="196" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C6" s="196"/>
       <c r="D6" s="15">
@@ -17199,7 +17209,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="25"/>
       <c r="B7" s="196" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C7" s="196"/>
       <c r="D7" s="15">
@@ -17210,7 +17220,7 @@
     <row r="8" spans="1:5">
       <c r="A8" s="25"/>
       <c r="B8" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C8" s="196"/>
       <c r="D8" s="15">
@@ -17221,7 +17231,7 @@
     <row r="9" spans="1:5">
       <c r="A9" s="25"/>
       <c r="B9" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C9" s="196"/>
       <c r="D9" s="15">
@@ -17235,7 +17245,7 @@
         <v>317</v>
       </c>
       <c r="C10" s="198" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D10" s="15">
         <v>2</v>
@@ -17245,7 +17255,7 @@
     <row r="11" spans="1:5">
       <c r="A11" s="25"/>
       <c r="B11" s="13" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C11" s="196"/>
       <c r="D11" s="15">
@@ -17280,7 +17290,7 @@
     <row r="14" spans="1:5">
       <c r="A14" s="25"/>
       <c r="B14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="15">
@@ -17291,7 +17301,7 @@
     <row r="15" spans="1:5">
       <c r="A15" s="25"/>
       <c r="B15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="15">
@@ -17302,7 +17312,7 @@
     <row r="16" spans="1:5">
       <c r="A16" s="25"/>
       <c r="B16" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C16" s="196"/>
       <c r="D16" s="15">
@@ -17313,7 +17323,7 @@
     <row r="17" spans="1:5">
       <c r="A17" s="25"/>
       <c r="B17" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C17" s="196"/>
       <c r="D17" s="15">
@@ -17335,7 +17345,7 @@
     <row r="19" spans="1:5">
       <c r="A19" s="25"/>
       <c r="B19" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C19" s="196"/>
       <c r="D19" s="15">
@@ -17346,7 +17356,7 @@
     <row r="20" spans="1:5">
       <c r="A20" s="25"/>
       <c r="B20" s="196" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C20" s="196"/>
       <c r="D20" s="15">
@@ -17357,7 +17367,7 @@
     <row r="21" spans="1:5">
       <c r="A21" s="25"/>
       <c r="B21" s="196" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C21" s="196"/>
       <c r="D21" s="15">
@@ -17379,7 +17389,7 @@
     <row r="23" spans="1:5">
       <c r="A23" s="25"/>
       <c r="B23" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C23" s="196"/>
       <c r="D23" s="15">
@@ -17412,7 +17422,7 @@
     <row r="26" spans="1:5">
       <c r="A26" s="25"/>
       <c r="B26" s="196" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C26" s="196"/>
       <c r="D26" s="15">
@@ -17467,7 +17477,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="25"/>
       <c r="B31" s="196" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C31" s="196"/>
       <c r="D31" s="15">
@@ -17478,7 +17488,7 @@
     <row r="32" spans="1:5">
       <c r="A32" s="25"/>
       <c r="B32" s="196" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C32" s="196"/>
       <c r="D32" s="15">
@@ -17489,10 +17499,10 @@
     <row r="33" spans="1:5">
       <c r="A33" s="25"/>
       <c r="B33" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D33" s="15">
         <v>1</v>
@@ -17502,10 +17512,10 @@
     <row r="34" spans="1:5">
       <c r="A34" s="25"/>
       <c r="B34" s="196" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C34" s="196" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D34" s="15">
         <v>1</v>
@@ -17515,10 +17525,10 @@
     <row r="35" spans="1:5">
       <c r="A35" s="25"/>
       <c r="B35" s="196" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D35" s="15">
         <v>2</v>
@@ -17528,10 +17538,10 @@
     <row r="36" spans="1:5">
       <c r="A36" s="25"/>
       <c r="B36" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D36" s="15">
         <v>1</v>
@@ -17541,10 +17551,10 @@
     <row r="37" spans="1:5">
       <c r="A37" s="25"/>
       <c r="B37" s="2" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D37" s="15">
         <v>1</v>
@@ -17554,10 +17564,10 @@
     <row r="38" spans="1:5">
       <c r="A38" s="25"/>
       <c r="B38" s="215" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C38" s="215" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D38" s="57">
         <v>1</v>
@@ -17567,10 +17577,10 @@
     <row r="39" spans="1:5">
       <c r="A39" s="25"/>
       <c r="B39" s="2" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D39" s="15">
         <v>4</v>
@@ -17580,10 +17590,10 @@
     <row r="40" spans="1:5">
       <c r="A40" s="25"/>
       <c r="B40" s="196" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D40" s="15">
         <v>2</v>
@@ -17593,10 +17603,10 @@
     <row r="41" spans="1:5">
       <c r="A41" s="25"/>
       <c r="B41" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D41" s="15">
         <v>1</v>
@@ -17606,10 +17616,10 @@
     <row r="42" spans="1:5">
       <c r="A42" s="25"/>
       <c r="B42" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D42" s="15">
         <v>1</v>
@@ -17619,10 +17629,10 @@
     <row r="43" spans="1:5">
       <c r="A43" s="25"/>
       <c r="B43" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D43" s="15">
         <v>2</v>
@@ -17632,10 +17642,10 @@
     <row r="44" spans="1:5">
       <c r="A44" s="25"/>
       <c r="B44" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D44" s="15">
         <v>1</v>
@@ -17645,10 +17655,10 @@
     <row r="45" spans="1:5">
       <c r="A45" s="25"/>
       <c r="B45" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D45" s="15">
         <v>1</v>
@@ -17658,10 +17668,10 @@
     <row r="46" spans="1:5">
       <c r="A46" s="25"/>
       <c r="B46" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D46" s="15">
         <v>1</v>
@@ -17671,10 +17681,10 @@
     <row r="47" spans="1:5">
       <c r="A47" s="25"/>
       <c r="B47" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D47" s="15">
         <v>1</v>
@@ -17684,10 +17694,10 @@
     <row r="48" spans="1:5">
       <c r="A48" s="25"/>
       <c r="B48" s="196" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D48" s="15">
         <v>1</v>
@@ -17697,10 +17707,10 @@
     <row r="49" spans="1:5">
       <c r="A49" s="25"/>
       <c r="B49" s="196" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D49" s="15">
         <v>1</v>
@@ -17710,10 +17720,10 @@
     <row r="50" spans="1:5">
       <c r="A50" s="25"/>
       <c r="B50" s="196" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D50" s="15">
         <v>1</v>
@@ -17723,10 +17733,10 @@
     <row r="51" spans="1:5">
       <c r="A51" s="25"/>
       <c r="B51" s="196" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D51" s="15">
         <v>1</v>
@@ -17736,10 +17746,10 @@
     <row r="52" spans="1:5">
       <c r="A52" s="25"/>
       <c r="B52" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D52" s="15">
         <v>1</v>
@@ -17749,10 +17759,10 @@
     <row r="53" spans="1:5">
       <c r="A53" s="25"/>
       <c r="B53" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D53" s="15">
         <v>1</v>
@@ -17762,10 +17772,10 @@
     <row r="54" spans="1:5">
       <c r="A54" s="25"/>
       <c r="B54" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D54" s="15">
         <v>1</v>
@@ -17775,10 +17785,10 @@
     <row r="55" spans="1:5">
       <c r="A55" s="25"/>
       <c r="B55" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>530</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="D55" s="15">
         <v>1</v>
@@ -17788,10 +17798,10 @@
     <row r="56" spans="1:5">
       <c r="A56" s="25"/>
       <c r="B56" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D56" s="15">
         <v>1</v>
@@ -17801,10 +17811,10 @@
     <row r="57" spans="1:5">
       <c r="A57" s="25"/>
       <c r="B57" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D57" s="15">
         <v>1</v>
@@ -17814,10 +17824,10 @@
     <row r="58" spans="1:5">
       <c r="A58" s="25"/>
       <c r="B58" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D58" s="15">
         <v>1</v>
@@ -17827,10 +17837,10 @@
     <row r="59" spans="1:5">
       <c r="A59" s="25"/>
       <c r="B59" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="D59" s="15">
         <v>1</v>
@@ -17840,10 +17850,10 @@
     <row r="60" spans="1:5">
       <c r="A60" s="25"/>
       <c r="B60" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D60" s="15">
         <v>1</v>
@@ -17853,10 +17863,10 @@
     <row r="61" spans="1:5">
       <c r="A61" s="25"/>
       <c r="B61" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>536</v>
       </c>
       <c r="D61" s="15">
         <v>2</v>
@@ -17866,10 +17876,10 @@
     <row r="62" spans="1:5">
       <c r="A62" s="25"/>
       <c r="B62" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D62" s="15">
         <v>1</v>
@@ -17879,10 +17889,10 @@
     <row r="63" spans="1:5">
       <c r="A63" s="25"/>
       <c r="B63" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D63" s="15">
         <v>1</v>
@@ -17892,10 +17902,10 @@
     <row r="64" spans="1:5">
       <c r="A64" s="25"/>
       <c r="B64" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D64" s="15">
         <v>1</v>
@@ -17905,10 +17915,10 @@
     <row r="65" spans="1:5">
       <c r="A65" s="25"/>
       <c r="B65" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D65" s="15">
         <v>1</v>
@@ -17918,10 +17928,10 @@
     <row r="66" spans="1:5">
       <c r="A66" s="25"/>
       <c r="B66" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D66" s="15">
         <v>1</v>
@@ -17931,10 +17941,10 @@
     <row r="67" spans="1:5">
       <c r="A67" s="25"/>
       <c r="B67" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D67" s="15">
         <v>1</v>
@@ -17944,10 +17954,10 @@
     <row r="68" spans="1:5">
       <c r="A68" s="25"/>
       <c r="B68" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D68" s="15">
         <v>1</v>
@@ -17957,10 +17967,10 @@
     <row r="69" spans="1:5">
       <c r="A69" s="25"/>
       <c r="B69" s="196" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D69" s="15">
         <v>6</v>
@@ -17970,10 +17980,10 @@
     <row r="70" spans="1:5">
       <c r="A70" s="25"/>
       <c r="B70" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D70" s="15">
         <v>1</v>
@@ -17983,10 +17993,10 @@
     <row r="71" spans="1:5">
       <c r="A71" s="25"/>
       <c r="B71" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C71" s="196" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D71" s="15">
         <v>1</v>
@@ -17996,10 +18006,10 @@
     <row r="72" spans="1:5">
       <c r="A72" s="25"/>
       <c r="B72" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C72" s="196" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D72" s="15">
         <v>1</v>
@@ -18009,10 +18019,10 @@
     <row r="73" spans="1:5">
       <c r="A73" s="25"/>
       <c r="B73" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D73" s="15">
         <v>2</v>
@@ -18022,10 +18032,10 @@
     <row r="74" spans="1:5" ht="15.75" thickBot="1">
       <c r="A74" s="61"/>
       <c r="B74" s="52" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C74" s="52" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D74" s="62">
         <v>1</v>
@@ -18090,13 +18100,13 @@
         <v>368</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C2" s="217" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D2" s="219" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="E2" s="55" t="s">
         <v>371</v>
@@ -18110,7 +18120,7 @@
         <v>155</v>
       </c>
       <c r="C3" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D3" s="196">
         <v>1</v>
@@ -18124,10 +18134,10 @@
         <v>375</v>
       </c>
       <c r="B4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C4" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D4" s="196">
         <v>4</v>
@@ -18144,7 +18154,7 @@
         <v>321</v>
       </c>
       <c r="C5" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D5" s="196">
         <v>3</v>
@@ -18159,7 +18169,7 @@
         <v>336</v>
       </c>
       <c r="C6" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D6" s="196">
         <v>1</v>
@@ -18169,10 +18179,10 @@
     <row r="7" spans="1:5">
       <c r="A7" s="25"/>
       <c r="B7" s="196" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C7" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D7" s="2">
         <v>2</v>
@@ -18182,10 +18192,10 @@
     <row r="8" spans="1:5">
       <c r="A8" s="25"/>
       <c r="B8" s="196" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C8" s="196" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D8" s="196">
         <v>1</v>
@@ -18198,7 +18208,7 @@
         <v>58</v>
       </c>
       <c r="C9" s="196" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D9" s="196">
         <v>1</v>
@@ -18211,7 +18221,7 @@
         <v>53</v>
       </c>
       <c r="C10" s="196" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D10" s="196">
         <v>1</v>
@@ -18221,10 +18231,10 @@
     <row r="11" spans="1:5">
       <c r="A11" s="25"/>
       <c r="B11" s="28" t="s">
+        <v>558</v>
+      </c>
+      <c r="C11" s="196" t="s">
         <v>557</v>
-      </c>
-      <c r="C11" s="196" t="s">
-        <v>556</v>
       </c>
       <c r="D11" s="196">
         <v>1</v>
@@ -18239,7 +18249,7 @@
         <v>177</v>
       </c>
       <c r="C12" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D12" s="196">
         <v>10</v>
@@ -18252,7 +18262,7 @@
         <v>180</v>
       </c>
       <c r="C13" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D13" s="196">
         <v>1</v>
@@ -18262,10 +18272,10 @@
     <row r="14" spans="1:5">
       <c r="A14" s="25"/>
       <c r="B14" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C14" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D14" s="196">
         <v>2</v>
@@ -18275,10 +18285,10 @@
     <row r="15" spans="1:5">
       <c r="A15" s="25"/>
       <c r="B15" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C15" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D15" s="196">
         <v>7</v>
@@ -18291,7 +18301,7 @@
         <v>198</v>
       </c>
       <c r="C16" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D16" s="196">
         <v>3</v>
@@ -18301,10 +18311,10 @@
     <row r="17" spans="1:5">
       <c r="A17" s="25"/>
       <c r="B17" s="196" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C17" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D17" s="2">
         <v>2</v>
@@ -18317,7 +18327,7 @@
         <v>210</v>
       </c>
       <c r="C18" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D18" s="196">
         <v>1</v>
@@ -18327,10 +18337,10 @@
     <row r="19" spans="1:5">
       <c r="A19" s="25"/>
       <c r="B19" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C19" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D19" s="196">
         <v>2</v>
@@ -18340,10 +18350,10 @@
     <row r="20" spans="1:5">
       <c r="A20" s="25"/>
       <c r="B20" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C20" s="196" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D20" s="196">
         <v>2</v>
@@ -18353,10 +18363,10 @@
     <row r="21" spans="1:5">
       <c r="A21" s="25"/>
       <c r="B21" s="196" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C21" s="196" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="D21" s="2">
         <v>1</v>
@@ -18366,7 +18376,7 @@
     <row r="22" spans="1:5">
       <c r="A22" s="25"/>
       <c r="B22" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C22" s="196" t="s">
         <v>393</v>
@@ -18379,7 +18389,7 @@
     <row r="23" spans="1:5">
       <c r="A23" s="25"/>
       <c r="B23" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C23" s="196" t="s">
         <v>393</v>
@@ -18392,7 +18402,7 @@
     <row r="24" spans="1:5">
       <c r="A24" s="25"/>
       <c r="B24" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C24" s="196" t="s">
         <v>393</v>
@@ -18405,7 +18415,7 @@
     <row r="25" spans="1:5">
       <c r="A25" s="25"/>
       <c r="B25" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C25" s="196" t="s">
         <v>393</v>
@@ -18418,7 +18428,7 @@
     <row r="26" spans="1:5">
       <c r="A26" s="25"/>
       <c r="B26" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C26" s="196" t="s">
         <v>393</v>
@@ -18431,7 +18441,7 @@
     <row r="27" spans="1:5">
       <c r="A27" s="25"/>
       <c r="B27" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C27" s="196" t="s">
         <v>393</v>
@@ -18444,7 +18454,7 @@
     <row r="28" spans="1:5">
       <c r="A28" s="25"/>
       <c r="B28" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C28" s="196" t="s">
         <v>393</v>
@@ -18457,7 +18467,7 @@
     <row r="29" spans="1:5">
       <c r="A29" s="25"/>
       <c r="B29" s="196" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C29" s="196" t="s">
         <v>393</v>
@@ -18470,10 +18480,10 @@
     <row r="30" spans="1:5">
       <c r="A30" s="25"/>
       <c r="B30" s="196" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C30" s="196" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D30" s="2">
         <v>1</v>
@@ -18483,7 +18493,7 @@
     <row r="31" spans="1:5">
       <c r="A31" s="25"/>
       <c r="B31" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C31" s="196" t="s">
         <v>393</v>
@@ -18496,10 +18506,10 @@
     <row r="32" spans="1:5">
       <c r="A32" s="25"/>
       <c r="B32" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C32" s="196" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D32" s="196">
         <v>2</v>
@@ -18509,10 +18519,10 @@
     <row r="33" spans="1:5">
       <c r="A33" s="25"/>
       <c r="B33" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C33" s="196" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D33" s="196">
         <v>2</v>
@@ -18522,10 +18532,10 @@
     <row r="34" spans="1:5">
       <c r="A34" s="25"/>
       <c r="B34" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C34" s="196" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D34" s="196">
         <v>2</v>
@@ -18535,10 +18545,10 @@
     <row r="35" spans="1:5">
       <c r="A35" s="25"/>
       <c r="B35" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C35" s="196" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D35" s="196">
         <v>2</v>
@@ -18548,10 +18558,10 @@
     <row r="36" spans="1:5">
       <c r="A36" s="25"/>
       <c r="B36" s="196" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C36" s="196" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D36" s="196">
         <v>2</v>
@@ -18561,10 +18571,10 @@
     <row r="37" spans="1:5">
       <c r="A37" s="25"/>
       <c r="B37" s="196" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C37" s="196" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D37" s="196">
         <v>2</v>
@@ -18574,7 +18584,7 @@
     <row r="38" spans="1:5">
       <c r="A38" s="25"/>
       <c r="B38" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C38" s="196" t="s">
         <v>393</v>
@@ -18587,7 +18597,7 @@
     <row r="39" spans="1:5">
       <c r="A39" s="25"/>
       <c r="B39" s="196" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C39" s="196" t="s">
         <v>393</v>
@@ -18600,7 +18610,7 @@
     <row r="40" spans="1:5">
       <c r="A40" s="25"/>
       <c r="B40" s="196" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C40" s="196" t="s">
         <v>393</v>
@@ -18613,7 +18623,7 @@
     <row r="41" spans="1:5">
       <c r="A41" s="25"/>
       <c r="B41" s="196" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C41" s="196" t="s">
         <v>393</v>
@@ -18626,7 +18636,7 @@
     <row r="42" spans="1:5">
       <c r="A42" s="25"/>
       <c r="B42" s="196" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="C42" s="196" t="s">
         <v>393</v>
@@ -18639,7 +18649,7 @@
     <row r="43" spans="1:5">
       <c r="A43" s="25"/>
       <c r="B43" s="196" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C43" s="196" t="s">
         <v>393</v>
@@ -18652,7 +18662,7 @@
     <row r="44" spans="1:5" ht="15.75" thickBot="1">
       <c r="A44" s="61"/>
       <c r="B44" s="196" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C44" s="196" t="s">
         <v>393</v>
@@ -18723,7 +18733,7 @@
         <v>368</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C2" s="196"/>
       <c r="D2" s="196">
@@ -18752,7 +18762,7 @@
         <v>375</v>
       </c>
       <c r="B4" s="196" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C4" s="196"/>
       <c r="D4" s="196">
@@ -18780,7 +18790,7 @@
     <row r="6" spans="1:5">
       <c r="A6" s="25"/>
       <c r="B6" s="195" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="D6" s="196">
         <v>1</v>
@@ -18790,7 +18800,7 @@
     <row r="7" spans="1:5">
       <c r="A7" s="25"/>
       <c r="B7" s="196" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C7" s="196"/>
       <c r="D7" s="196">
@@ -18822,7 +18832,7 @@
     <row r="10" spans="1:5">
       <c r="A10" s="25"/>
       <c r="B10" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="D10" s="196">
         <v>4</v>
@@ -18832,7 +18842,7 @@
     <row r="11" spans="1:5">
       <c r="A11" s="25"/>
       <c r="B11" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D11" s="196">
         <v>4</v>
@@ -18874,7 +18884,7 @@
     <row r="15" spans="1:5">
       <c r="A15" s="25"/>
       <c r="B15" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D15" s="196">
         <v>1</v>
@@ -18884,7 +18894,7 @@
     <row r="16" spans="1:5">
       <c r="A16" s="25"/>
       <c r="B16" s="192" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D16" s="196">
         <v>1</v>
@@ -18894,7 +18904,7 @@
     <row r="17" spans="1:5">
       <c r="A17" s="25"/>
       <c r="B17" s="28" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D17" s="196">
         <v>1</v>
@@ -18904,7 +18914,7 @@
     <row r="18" spans="1:5" ht="15.75" thickBot="1">
       <c r="A18" s="61"/>
       <c r="B18" s="52" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C18" s="52"/>
       <c r="D18" s="220">
@@ -18971,10 +18981,10 @@
         <v>368</v>
       </c>
       <c r="B2" s="31" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D2" s="15">
         <v>1</v>
@@ -18988,10 +18998,10 @@
         <v>372</v>
       </c>
       <c r="B3" s="31" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="D3" s="15">
         <v>1</v>
@@ -19005,10 +19015,10 @@
         <v>375</v>
       </c>
       <c r="B4" s="31" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="D4" s="15">
         <v>1</v>
@@ -19022,10 +19032,10 @@
         <v>378</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C5" s="196" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D5" s="203">
         <v>2</v>
@@ -19037,10 +19047,10 @@
     <row r="6" spans="1:5">
       <c r="A6" s="25"/>
       <c r="B6" s="221" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C6" s="196" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D6" s="203">
         <v>5</v>
@@ -19050,10 +19060,10 @@
     <row r="7" spans="1:5">
       <c r="A7" s="25"/>
       <c r="B7" s="20" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C7" s="196" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D7" s="203">
         <v>2</v>
@@ -19063,10 +19073,10 @@
     <row r="8" spans="1:5">
       <c r="A8" s="25"/>
       <c r="B8" s="20" t="s">
+        <v>608</v>
+      </c>
+      <c r="C8" s="196" t="s">
         <v>607</v>
-      </c>
-      <c r="C8" s="196" t="s">
-        <v>606</v>
       </c>
       <c r="D8" s="15">
         <v>2</v>
@@ -19079,7 +19089,7 @@
         <v>144</v>
       </c>
       <c r="C9" s="196" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D9" s="15">
         <v>1</v>
@@ -19089,10 +19099,10 @@
     <row r="10" spans="1:5">
       <c r="A10" s="25"/>
       <c r="B10" s="30" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C10" s="196" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D10" s="203">
         <v>2</v>
@@ -19102,10 +19112,10 @@
     <row r="11" spans="1:5">
       <c r="A11" s="25"/>
       <c r="B11" s="30" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C11" s="196" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D11" s="15">
         <v>2</v>
@@ -19120,7 +19130,7 @@
         <v>113</v>
       </c>
       <c r="C12" s="196" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D12" s="15">
         <v>5</v>
@@ -19130,10 +19140,10 @@
     <row r="13" spans="1:5">
       <c r="A13" s="25"/>
       <c r="B13" s="30" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C13" s="196" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D13" s="203">
         <v>2</v>
@@ -19143,10 +19153,10 @@
     <row r="14" spans="1:5">
       <c r="A14" s="25"/>
       <c r="B14" s="30" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C14" s="196" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D14" s="203">
         <v>5</v>
@@ -19156,10 +19166,10 @@
     <row r="15" spans="1:5">
       <c r="A15" s="25"/>
       <c r="B15" s="222" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C15" s="196" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="D15" s="203">
         <v>5</v>
@@ -19169,10 +19179,10 @@
     <row r="16" spans="1:5">
       <c r="A16" s="25"/>
       <c r="B16" s="222" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C16" s="196" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D16" s="203">
         <v>5</v>
@@ -19182,10 +19192,10 @@
     <row r="17" spans="1:5">
       <c r="A17" s="25"/>
       <c r="B17" s="215" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C17" s="215" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D17" s="57"/>
       <c r="E17" s="56"/>
@@ -19196,7 +19206,7 @@
         <v>141</v>
       </c>
       <c r="C18" s="196" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="D18" s="196">
         <v>1</v>
@@ -19216,7 +19226,7 @@
     <row r="20" spans="1:5">
       <c r="A20" s="25"/>
       <c r="B20" s="58" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
@@ -19302,7 +19312,7 @@
     <row r="28" spans="1:5">
       <c r="A28" s="25"/>
       <c r="B28" s="18" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C28" s="28"/>
       <c r="D28">
@@ -19313,7 +19323,7 @@
     <row r="29" spans="1:5">
       <c r="A29" s="25"/>
       <c r="B29" s="18" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C29" s="28"/>
       <c r="D29">
@@ -19371,7 +19381,7 @@
         <v>46</v>
       </c>
       <c r="C34" s="196" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D34" s="15">
         <v>2</v>
@@ -19384,7 +19394,7 @@
         <v>49</v>
       </c>
       <c r="C35" s="196" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D35" s="15">
         <v>1</v>
@@ -19397,7 +19407,7 @@
         <v>51</v>
       </c>
       <c r="C36" s="196" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D36" s="15">
         <v>1</v>
@@ -19410,7 +19420,7 @@
         <v>91</v>
       </c>
       <c r="C37" s="196" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D37" s="15">
         <v>1</v>
@@ -19423,7 +19433,7 @@
         <v>70</v>
       </c>
       <c r="C38" s="196" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D38" s="196">
         <v>1</v>
@@ -19436,7 +19446,7 @@
         <v>128</v>
       </c>
       <c r="C39" s="196" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="D39" s="196">
         <v>1</v>
@@ -19449,7 +19459,7 @@
         <v>78</v>
       </c>
       <c r="C40" s="196" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="D40" s="15">
         <v>3</v>
@@ -19459,10 +19469,10 @@
     <row r="41" spans="1:5" ht="16.5" customHeight="1">
       <c r="A41" s="25"/>
       <c r="B41" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C41" s="196" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D41" s="15">
         <v>1</v>
@@ -19472,10 +19482,10 @@
     <row r="42" spans="1:5" ht="16.5" customHeight="1">
       <c r="A42" s="25"/>
       <c r="B42" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C42" s="196" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D42" s="15">
         <v>1</v>
@@ -19485,10 +19495,10 @@
     <row r="43" spans="1:5" ht="16.5" customHeight="1">
       <c r="A43" s="25"/>
       <c r="B43" s="196" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C43" s="196" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="D43" s="15">
         <v>2</v>
@@ -19498,10 +19508,10 @@
     <row r="44" spans="1:5" ht="16.5" customHeight="1" thickBot="1">
       <c r="A44" s="61"/>
       <c r="B44" s="49" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C44" s="220" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D44" s="62">
         <v>1</v>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1662" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CA28AA9-5D8E-4AFC-B12B-224A1452E8DD}"/>
+  <xr:revisionPtr revIDLastSave="1672" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5835FB84-AD85-44B1-A06D-38D91EE99EDE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="881">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1652" uniqueCount="874">
   <si>
     <t>Type</t>
   </si>
@@ -2212,7 +2212,7 @@
     <t>Mark/Roy</t>
   </si>
   <si>
-    <t>in Design WIP</t>
+    <t xml:space="preserve">done requires testing </t>
   </si>
   <si>
     <t>Cpap duct redesign</t>
@@ -2257,7 +2257,7 @@
     <t>make a basic config which boards ?</t>
   </si>
   <si>
-    <t>WIP needs testing</t>
+    <t>done on going tweeking</t>
   </si>
   <si>
     <t>Do electrical drawings load cell, Mains, others</t>
@@ -2290,9 +2290,6 @@
     <t>In Testing</t>
   </si>
   <si>
-    <t>Make V2 drawings</t>
-  </si>
-  <si>
     <t>need 2 x 10K resistors for the load cell and the cpap fan</t>
   </si>
   <si>
@@ -2302,31 +2299,13 @@
     <t>need to add to one of the BOM electrical ?</t>
   </si>
   <si>
-    <t>Create printed part to hold the 2 x 4 pin and 1 x 10 pin connector in the chamber</t>
-  </si>
-  <si>
-    <t>sample done need to put in V2 model</t>
-  </si>
-  <si>
     <t>workout a way to get esp32 programmed easierly</t>
   </si>
   <si>
     <t>Chris</t>
   </si>
   <si>
-    <t>is the gland done to feed to PTFE tube into the chamber from the buffer ?</t>
-  </si>
-  <si>
-    <t>Complete</t>
-  </si>
-  <si>
     <t>finally finish the Hardware BOM when all above done</t>
-  </si>
-  <si>
-    <t>Design cable clamp for bed</t>
-  </si>
-  <si>
-    <t>needs testing in folder</t>
   </si>
   <si>
     <t>Function</t>
@@ -2714,7 +2693,7 @@
     <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
   </numFmts>
-  <fonts count="42">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3311,7 +3290,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
@@ -3805,6 +3784,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3813,12 +3801,6 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="11">
@@ -3948,16 +3930,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -3977,10 +3963,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4112,9 +4094,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4131,6 +4110,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4189,9 +4171,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4208,6 +4187,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4266,9 +4248,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4285,6 +4264,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4343,9 +4325,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4362,6 +4341,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4420,9 +4402,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4439,6 +4418,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4497,9 +4479,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4516,6 +4495,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4590,9 +4572,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4609,6 +4588,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -4667,9 +4649,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -4686,6 +4665,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5088,13 +5070,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="medium">
           <color rgb="FF000000"/>
@@ -5113,6 +5088,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -6048,7 +6030,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M150" totalsRowShown="0" dataDxfId="93" headerRowBorderDxfId="91" tableBorderDxfId="92" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M150" totalsRowShown="0" dataDxfId="92" headerRowBorderDxfId="93" tableBorderDxfId="91" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:M150" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L150">
     <sortCondition ref="A1:A150"/>
@@ -6083,7 +6065,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="29" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="28" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="26" totalsRowDxfId="27" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="27" totalsRowDxfId="26" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6098,7 +6080,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="23" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="22" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="20" totalsRowDxfId="21" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6111,19 +6093,19 @@
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="17" totalsRowDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="15" totalsRowDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="18" totalsRowDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="16" totalsRowDxfId="15"/>
     <tableColumn id="3" xr3:uid="{6512942A-B4C3-4998-AA54-D3A429CF1394}" name="Meters"/>
     <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="14"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="12" totalsRowDxfId="13" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="10" totalsRowDxfId="11" dataCellStyle="Normal 7">
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="8" totalsRowDxfId="9">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="9" totalsRowDxfId="8">
       <calculatedColumnFormula>$K$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="6" totalsRowDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="7" totalsRowDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6233,7 +6215,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="65" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="64" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="62" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="63" totalsRowDxfId="62" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6248,7 +6230,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="58" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="56" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6263,7 +6245,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="52" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="50" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6278,7 +6260,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="46" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="44" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6293,7 +6275,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="40" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="38" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6308,7 +6290,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="34" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="32" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6517,7 +6499,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O152"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="12" customWidth="1"/>
     <col min="2" max="2" width="36.7109375" style="12" bestFit="1" customWidth="1"/>
@@ -6537,7 +6519,7 @@
     <col min="16" max="16384" width="8.7109375" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="44.25" customHeight="1">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="149" t="s">
         <v>0</v>
       </c>
@@ -6578,7 +6560,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="s">
         <v>13</v>
       </c>
@@ -6612,7 +6594,7 @@
       <c r="L2" s="75"/>
       <c r="M2" s="231"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>13</v>
       </c>
@@ -6646,7 +6628,7 @@
       <c r="L3" s="75"/>
       <c r="M3" s="231"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>13</v>
       </c>
@@ -6679,7 +6661,7 @@
       <c r="L4" s="78"/>
       <c r="M4" s="231"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>13</v>
       </c>
@@ -6713,7 +6695,7 @@
       <c r="L5" s="75"/>
       <c r="M5" s="231"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>13</v>
       </c>
@@ -6747,7 +6729,7 @@
       <c r="L6" s="75"/>
       <c r="M6" s="231"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>13</v>
       </c>
@@ -6781,7 +6763,7 @@
       <c r="L7" s="75"/>
       <c r="M7" s="231"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>13</v>
       </c>
@@ -6815,7 +6797,7 @@
       <c r="L8" s="75"/>
       <c r="M8" s="231"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>13</v>
       </c>
@@ -6849,7 +6831,7 @@
       <c r="L9" s="75"/>
       <c r="M9" s="231"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>13</v>
       </c>
@@ -6882,7 +6864,7 @@
       <c r="L10" s="78"/>
       <c r="M10" s="231"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
         <v>37</v>
       </c>
@@ -6916,7 +6898,7 @@
       <c r="L11" s="75"/>
       <c r="M11" s="231"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="33" t="s">
         <v>37</v>
       </c>
@@ -6950,7 +6932,7 @@
       <c r="L12" s="75"/>
       <c r="M12" s="231"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="33" t="s">
         <v>37</v>
       </c>
@@ -6984,7 +6966,7 @@
       <c r="L13" s="75"/>
       <c r="M13" s="231"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
         <v>37</v>
       </c>
@@ -7018,7 +7000,7 @@
       <c r="L14" s="75"/>
       <c r="M14" s="231"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="33" t="s">
         <v>37</v>
       </c>
@@ -7052,7 +7034,7 @@
       <c r="L15" s="75"/>
       <c r="M15" s="231"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="33" t="s">
         <v>37</v>
       </c>
@@ -7086,7 +7068,7 @@
       <c r="L16" s="75"/>
       <c r="M16" s="231"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="33" t="s">
         <v>37</v>
       </c>
@@ -7120,7 +7102,7 @@
       <c r="L17" s="75"/>
       <c r="M17" s="231"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="33" t="s">
         <v>37</v>
       </c>
@@ -7154,7 +7136,7 @@
       <c r="L18" s="75"/>
       <c r="M18" s="231"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="33" t="s">
         <v>37</v>
       </c>
@@ -7188,7 +7170,7 @@
       <c r="L19" s="75"/>
       <c r="M19" s="231"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
         <v>37</v>
       </c>
@@ -7222,7 +7204,7 @@
       <c r="L20" s="75"/>
       <c r="M20" s="231"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" s="33" t="s">
         <v>37</v>
       </c>
@@ -7258,7 +7240,7 @@
       <c r="L21" s="75"/>
       <c r="M21" s="231"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" s="33" t="s">
         <v>37</v>
       </c>
@@ -7291,7 +7273,7 @@
       <c r="L22" s="75"/>
       <c r="M22" s="231"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="33" t="s">
         <v>37</v>
       </c>
@@ -7324,7 +7306,7 @@
       <c r="L23" s="75"/>
       <c r="M23" s="231"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="33" t="s">
         <v>37</v>
       </c>
@@ -7345,7 +7327,7 @@
         <f t="shared" si="0"/>
         <v>13.59</v>
       </c>
-      <c r="H24" s="240" t="s">
+      <c r="H24" s="237" t="s">
         <v>71</v>
       </c>
       <c r="I24" s="109" t="s">
@@ -7358,7 +7340,7 @@
       <c r="L24" s="75"/>
       <c r="M24" s="231"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="33" t="s">
         <v>37</v>
       </c>
@@ -7392,7 +7374,7 @@
       <c r="L25" s="75"/>
       <c r="M25" s="231"/>
     </row>
-    <row r="26" spans="1:13" ht="15.75" customHeight="1">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
         <v>37</v>
       </c>
@@ -7426,7 +7408,7 @@
       <c r="L26" s="75"/>
       <c r="M26" s="231"/>
     </row>
-    <row r="27" spans="1:13" ht="16.5" customHeight="1">
+    <row r="27" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33" t="s">
         <v>37</v>
       </c>
@@ -7460,7 +7442,7 @@
       <c r="L27" s="75"/>
       <c r="M27" s="231"/>
     </row>
-    <row r="28" spans="1:13" ht="16.5" customHeight="1">
+    <row r="28" spans="1:13" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="33" t="s">
         <v>37</v>
       </c>
@@ -7494,7 +7476,7 @@
       <c r="L28" s="75"/>
       <c r="M28" s="231"/>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="33" t="s">
         <v>37</v>
       </c>
@@ -7528,7 +7510,7 @@
       <c r="L29" s="75"/>
       <c r="M29" s="231"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="33" t="s">
         <v>37</v>
       </c>
@@ -7562,7 +7544,7 @@
       <c r="L30" s="75"/>
       <c r="M30" s="231"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="33" t="s">
         <v>37</v>
       </c>
@@ -7596,7 +7578,7 @@
       <c r="L31" s="75"/>
       <c r="M31" s="231"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="33" t="s">
         <v>37</v>
       </c>
@@ -7630,7 +7612,7 @@
       <c r="L32" s="75"/>
       <c r="M32" s="231"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="33" t="s">
         <v>37</v>
       </c>
@@ -7664,7 +7646,7 @@
       <c r="L33" s="75"/>
       <c r="M33" s="231"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="33" t="s">
         <v>37</v>
       </c>
@@ -7698,7 +7680,7 @@
       <c r="L34" s="75"/>
       <c r="M34" s="231"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="33" t="s">
         <v>37</v>
       </c>
@@ -7732,7 +7714,7 @@
       <c r="L35" s="75"/>
       <c r="M35" s="231"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="33" t="s">
         <v>37</v>
       </c>
@@ -7766,7 +7748,7 @@
       <c r="L36" s="75"/>
       <c r="M36" s="231"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="33" t="s">
         <v>37</v>
       </c>
@@ -7800,7 +7782,7 @@
       <c r="L37" s="75"/>
       <c r="M37" s="231"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="33" t="s">
         <v>37</v>
       </c>
@@ -7834,7 +7816,7 @@
       <c r="L38" s="75"/>
       <c r="M38" s="231"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="33" t="s">
         <v>37</v>
       </c>
@@ -7868,7 +7850,7 @@
       <c r="L39" s="75"/>
       <c r="M39" s="231"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
         <v>37</v>
       </c>
@@ -7902,7 +7884,7 @@
       <c r="L40" s="75"/>
       <c r="M40" s="231"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="33" t="s">
         <v>37</v>
       </c>
@@ -7936,7 +7918,7 @@
       <c r="L41" s="75"/>
       <c r="M41" s="231"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="33" t="s">
         <v>37</v>
       </c>
@@ -7970,7 +7952,7 @@
       <c r="L42" s="75"/>
       <c r="M42" s="231"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="33" t="s">
         <v>37</v>
       </c>
@@ -8004,7 +7986,7 @@
       <c r="L43" s="75"/>
       <c r="M43" s="231"/>
     </row>
-    <row r="44" spans="1:13" ht="15.75" customHeight="1">
+    <row r="44" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="33" t="s">
         <v>37</v>
       </c>
@@ -8038,7 +8020,7 @@
       <c r="L44" s="75"/>
       <c r="M44" s="231"/>
     </row>
-    <row r="45" spans="1:13" ht="15.75" customHeight="1">
+    <row r="45" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="33" t="s">
         <v>37</v>
       </c>
@@ -8072,7 +8054,7 @@
       <c r="L45" s="75"/>
       <c r="M45" s="231"/>
     </row>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1">
+    <row r="46" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33" t="s">
         <v>37</v>
       </c>
@@ -8106,7 +8088,7 @@
       <c r="L46" s="75"/>
       <c r="M46" s="231"/>
     </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1">
+    <row r="47" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33" t="s">
         <v>37</v>
       </c>
@@ -8140,7 +8122,7 @@
       <c r="L47" s="75"/>
       <c r="M47" s="231"/>
     </row>
-    <row r="48" spans="1:13">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="33" t="s">
         <v>37</v>
       </c>
@@ -8174,7 +8156,7 @@
       <c r="L48" s="75"/>
       <c r="M48" s="231"/>
     </row>
-    <row r="49" spans="1:13">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="33" t="s">
         <v>37</v>
       </c>
@@ -8198,13 +8180,13 @@
       <c r="H49" s="187" t="s">
         <v>123</v>
       </c>
-      <c r="I49" s="241"/>
+      <c r="I49" s="239"/>
       <c r="J49" s="155"/>
       <c r="K49" s="12"/>
       <c r="L49" s="75"/>
       <c r="M49" s="231"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="33" t="s">
         <v>37</v>
       </c>
@@ -8228,13 +8210,13 @@
       <c r="H50" s="187" t="s">
         <v>123</v>
       </c>
-      <c r="I50" s="241"/>
+      <c r="I50" s="239"/>
       <c r="J50" s="155"/>
       <c r="K50" s="12"/>
       <c r="L50" s="75"/>
       <c r="M50" s="231"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="33" t="s">
         <v>37</v>
       </c>
@@ -8268,7 +8250,7 @@
       <c r="L51" s="75"/>
       <c r="M51" s="231"/>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="33" t="s">
         <v>37</v>
       </c>
@@ -8302,7 +8284,7 @@
       <c r="L52" s="75"/>
       <c r="M52" s="231"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A53" s="33" t="s">
         <v>37</v>
       </c>
@@ -8336,7 +8318,7 @@
       <c r="L53" s="75"/>
       <c r="M53" s="231"/>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="33" t="s">
         <v>37</v>
       </c>
@@ -8370,7 +8352,7 @@
       <c r="L54" s="75"/>
       <c r="M54" s="231"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
         <v>37</v>
       </c>
@@ -8404,7 +8386,7 @@
       <c r="L55" s="39"/>
       <c r="M55" s="231"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A56" s="33" t="s">
         <v>37</v>
       </c>
@@ -8438,7 +8420,7 @@
       <c r="L56" s="75"/>
       <c r="M56" s="231"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A57" s="33" t="s">
         <v>37</v>
       </c>
@@ -8470,7 +8452,7 @@
       <c r="L57" s="75"/>
       <c r="M57" s="231"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="33" t="s">
         <v>37</v>
       </c>
@@ -8504,7 +8486,7 @@
       <c r="L58" s="75"/>
       <c r="M58" s="231"/>
     </row>
-    <row r="59" spans="1:13" ht="17.25" customHeight="1">
+    <row r="59" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33" t="s">
         <v>37</v>
       </c>
@@ -8540,7 +8522,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="17.25" customHeight="1">
+    <row r="60" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="33" t="s">
         <v>37</v>
       </c>
@@ -8572,7 +8554,7 @@
       <c r="L60" s="75"/>
       <c r="M60" s="231"/>
     </row>
-    <row r="61" spans="1:13" ht="15.75">
+    <row r="61" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="33" t="s">
         <v>37</v>
       </c>
@@ -8592,7 +8574,7 @@
       <c r="H61" s="235" t="s">
         <v>153</v>
       </c>
-      <c r="I61" s="241"/>
+      <c r="I61" s="239"/>
       <c r="J61" s="155"/>
       <c r="K61" s="12"/>
       <c r="L61" s="75"/>
@@ -8600,7 +8582,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="62" spans="1:13">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="33" t="s">
         <v>37</v>
       </c>
@@ -8634,7 +8616,7 @@
       <c r="L62" s="75"/>
       <c r="M62" s="231"/>
     </row>
-    <row r="63" spans="1:13">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A63" s="33" t="s">
         <v>157</v>
       </c>
@@ -8667,7 +8649,7 @@
       <c r="L63" s="75"/>
       <c r="M63" s="231"/>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="33" t="s">
         <v>157</v>
       </c>
@@ -8700,7 +8682,7 @@
       <c r="L64" s="78"/>
       <c r="M64" s="231"/>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>157</v>
       </c>
@@ -8733,7 +8715,7 @@
       <c r="L65" s="75"/>
       <c r="M65" s="231"/>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="s">
         <v>157</v>
       </c>
@@ -8771,7 +8753,7 @@
       </c>
       <c r="M66" s="231"/>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>157</v>
       </c>
@@ -8809,7 +8791,7 @@
       </c>
       <c r="M67" s="231"/>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="s">
         <v>157</v>
       </c>
@@ -8845,7 +8827,7 @@
       <c r="L68" s="75"/>
       <c r="M68" s="231"/>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="33" t="s">
         <v>157</v>
       </c>
@@ -8880,7 +8862,7 @@
       <c r="L69" s="75"/>
       <c r="M69" s="231"/>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="33" t="s">
         <v>157</v>
       </c>
@@ -8916,7 +8898,7 @@
       <c r="L70" s="78"/>
       <c r="M70" s="231"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="33" t="s">
         <v>157</v>
       </c>
@@ -8952,7 +8934,7 @@
       <c r="L71" s="75"/>
       <c r="M71" s="231"/>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="33" t="s">
         <v>157</v>
       </c>
@@ -8987,7 +8969,7 @@
       <c r="L72" s="75"/>
       <c r="M72" s="231"/>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="33" t="s">
         <v>157</v>
       </c>
@@ -9023,7 +9005,7 @@
       <c r="L73" s="75"/>
       <c r="M73" s="231"/>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A74" s="33" t="s">
         <v>157</v>
       </c>
@@ -9059,7 +9041,7 @@
       </c>
       <c r="M74" s="231"/>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>157</v>
       </c>
@@ -9095,7 +9077,7 @@
       <c r="L75" s="75"/>
       <c r="M75" s="231"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A76" s="33" t="s">
         <v>157</v>
       </c>
@@ -9131,7 +9113,7 @@
       <c r="L76" s="75"/>
       <c r="M76" s="231"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>157</v>
       </c>
@@ -9167,7 +9149,7 @@
       <c r="L77" s="78"/>
       <c r="M77" s="231"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="s">
         <v>157</v>
       </c>
@@ -9201,7 +9183,7 @@
       <c r="L78" s="75"/>
       <c r="M78" s="231"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
         <v>157</v>
       </c>
@@ -9237,7 +9219,7 @@
       <c r="L79" s="75"/>
       <c r="M79" s="231"/>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="s">
         <v>157</v>
       </c>
@@ -9271,7 +9253,7 @@
       <c r="L80" s="75"/>
       <c r="M80" s="231"/>
     </row>
-    <row r="81" spans="1:13" ht="15.75" customHeight="1">
+    <row r="81" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
         <v>157</v>
       </c>
@@ -9309,7 +9291,7 @@
       </c>
       <c r="M81" s="231"/>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="33" t="s">
         <v>157</v>
       </c>
@@ -9344,7 +9326,7 @@
       <c r="L82" s="78"/>
       <c r="M82" s="231"/>
     </row>
-    <row r="83" spans="1:13">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="33" t="s">
         <v>157</v>
       </c>
@@ -9382,7 +9364,7 @@
       </c>
       <c r="M83" s="231"/>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="33" t="s">
         <v>157</v>
       </c>
@@ -9417,7 +9399,7 @@
       <c r="L84" s="78"/>
       <c r="M84" s="231"/>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
         <v>157</v>
       </c>
@@ -9451,7 +9433,7 @@
       <c r="L85" s="75"/>
       <c r="M85" s="231"/>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="33" t="s">
         <v>157</v>
       </c>
@@ -9487,7 +9469,7 @@
       <c r="L86" s="75"/>
       <c r="M86" s="231"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
         <v>157</v>
       </c>
@@ -9521,7 +9503,7 @@
       <c r="L87" s="75"/>
       <c r="M87" s="231"/>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="33" t="s">
         <v>157</v>
       </c>
@@ -9558,7 +9540,7 @@
       </c>
       <c r="M88" s="231"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A89" s="33" t="s">
         <v>157</v>
       </c>
@@ -9594,7 +9576,7 @@
       <c r="L89" s="78"/>
       <c r="M89" s="231"/>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="33" t="s">
         <v>157</v>
       </c>
@@ -9630,7 +9612,7 @@
       <c r="L90" s="78"/>
       <c r="M90" s="231"/>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="33" t="s">
         <v>157</v>
       </c>
@@ -9668,7 +9650,7 @@
       </c>
       <c r="M91" s="231"/>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="33" t="s">
         <v>157</v>
       </c>
@@ -9701,7 +9683,7 @@
       <c r="L92" s="75"/>
       <c r="M92" s="231"/>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="33" t="s">
         <v>157</v>
       </c>
@@ -9737,7 +9719,7 @@
       <c r="L93" s="78"/>
       <c r="M93" s="231"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="33" t="s">
         <v>157</v>
       </c>
@@ -9774,7 +9756,7 @@
       </c>
       <c r="M94" s="231"/>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="33" t="s">
         <v>157</v>
       </c>
@@ -9810,7 +9792,7 @@
       <c r="L95" s="75"/>
       <c r="M95" s="231"/>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="33" t="s">
         <v>157</v>
       </c>
@@ -9846,7 +9828,7 @@
       </c>
       <c r="M96" s="231"/>
     </row>
-    <row r="97" spans="1:15">
+    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="33" t="s">
         <v>157</v>
       </c>
@@ -9882,7 +9864,7 @@
       </c>
       <c r="M97" s="231"/>
     </row>
-    <row r="98" spans="1:15">
+    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="33" t="s">
         <v>157</v>
       </c>
@@ -9920,7 +9902,7 @@
       </c>
       <c r="M98" s="231"/>
     </row>
-    <row r="99" spans="1:15">
+    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="33" t="s">
         <v>157</v>
       </c>
@@ -9956,7 +9938,7 @@
       <c r="L99" s="75"/>
       <c r="M99" s="231"/>
     </row>
-    <row r="100" spans="1:15">
+    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="33" t="s">
         <v>157</v>
       </c>
@@ -9995,7 +9977,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="101" spans="1:15">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="33" t="s">
         <v>157</v>
       </c>
@@ -10031,7 +10013,7 @@
       <c r="L101" s="75"/>
       <c r="M101" s="231"/>
     </row>
-    <row r="102" spans="1:15">
+    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="33" t="s">
         <v>157</v>
       </c>
@@ -10067,7 +10049,7 @@
       <c r="L102" s="75"/>
       <c r="M102" s="231"/>
     </row>
-    <row r="103" spans="1:15">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="33" t="s">
         <v>157</v>
       </c>
@@ -10103,7 +10085,7 @@
       <c r="L103" s="75"/>
       <c r="M103" s="231"/>
     </row>
-    <row r="104" spans="1:15">
+    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="s">
         <v>157</v>
       </c>
@@ -10139,7 +10121,7 @@
       </c>
       <c r="M104" s="231"/>
     </row>
-    <row r="105" spans="1:15">
+    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
         <v>242</v>
       </c>
@@ -10173,7 +10155,7 @@
       <c r="L105" s="75"/>
       <c r="M105" s="231"/>
     </row>
-    <row r="106" spans="1:15">
+    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="s">
         <v>242</v>
       </c>
@@ -10207,7 +10189,7 @@
       <c r="L106" s="75"/>
       <c r="M106" s="231"/>
     </row>
-    <row r="107" spans="1:15">
+    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
         <v>242</v>
       </c>
@@ -10241,7 +10223,7 @@
       <c r="L107" s="75"/>
       <c r="M107" s="231"/>
     </row>
-    <row r="108" spans="1:15">
+    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="s">
         <v>242</v>
       </c>
@@ -10275,7 +10257,7 @@
       <c r="L108" s="75"/>
       <c r="M108" s="231"/>
     </row>
-    <row r="109" spans="1:15">
+    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
         <v>242</v>
       </c>
@@ -10309,7 +10291,7 @@
       <c r="L109" s="75"/>
       <c r="M109" s="231"/>
     </row>
-    <row r="110" spans="1:15">
+    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="s">
         <v>254</v>
       </c>
@@ -10343,7 +10325,7 @@
       <c r="L110" s="75"/>
       <c r="M110" s="231"/>
     </row>
-    <row r="111" spans="1:15">
+    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
         <v>254</v>
       </c>
@@ -10377,7 +10359,7 @@
       <c r="L111" s="75"/>
       <c r="M111" s="231"/>
     </row>
-    <row r="112" spans="1:15">
+    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="s">
         <v>254</v>
       </c>
@@ -10410,7 +10392,7 @@
       <c r="L112" s="75"/>
       <c r="M112" s="231"/>
     </row>
-    <row r="113" spans="1:13">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
         <v>254</v>
       </c>
@@ -10443,7 +10425,7 @@
       <c r="L113" s="75"/>
       <c r="M113" s="231"/>
     </row>
-    <row r="114" spans="1:13">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="33" t="s">
         <v>267</v>
       </c>
@@ -10477,7 +10459,7 @@
       <c r="L114" s="75"/>
       <c r="M114" s="231"/>
     </row>
-    <row r="115" spans="1:13">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="33" t="s">
         <v>267</v>
       </c>
@@ -10511,7 +10493,7 @@
       <c r="L115" s="75"/>
       <c r="M115" s="231"/>
     </row>
-    <row r="116" spans="1:13">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A116" s="33" t="s">
         <v>267</v>
       </c>
@@ -10545,7 +10527,7 @@
       <c r="L116" s="75"/>
       <c r="M116" s="231"/>
     </row>
-    <row r="117" spans="1:13">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
         <v>267</v>
       </c>
@@ -10579,7 +10561,7 @@
       <c r="L117" s="75"/>
       <c r="M117" s="231"/>
     </row>
-    <row r="118" spans="1:13">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="s">
         <v>267</v>
       </c>
@@ -10613,7 +10595,7 @@
       <c r="L118" s="75"/>
       <c r="M118" s="231"/>
     </row>
-    <row r="119" spans="1:13">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A119" s="33" t="s">
         <v>267</v>
       </c>
@@ -10647,7 +10629,7 @@
       <c r="L119" s="75"/>
       <c r="M119" s="231"/>
     </row>
-    <row r="120" spans="1:13">
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A120" s="33" t="s">
         <v>267</v>
       </c>
@@ -10681,7 +10663,7 @@
       <c r="L120" s="75"/>
       <c r="M120" s="231"/>
     </row>
-    <row r="121" spans="1:13">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A121" s="33" t="s">
         <v>267</v>
       </c>
@@ -10715,7 +10697,7 @@
       <c r="L121" s="75"/>
       <c r="M121" s="231"/>
     </row>
-    <row r="122" spans="1:13">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A122" s="33" t="s">
         <v>291</v>
       </c>
@@ -10751,7 +10733,7 @@
       <c r="L122" s="75"/>
       <c r="M122" s="231"/>
     </row>
-    <row r="123" spans="1:13">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A123" s="33" t="s">
         <v>291</v>
       </c>
@@ -10787,7 +10769,7 @@
       <c r="L123" s="75"/>
       <c r="M123" s="231"/>
     </row>
-    <row r="124" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="124" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="s">
         <v>291</v>
       </c>
@@ -10823,7 +10805,7 @@
       <c r="L124" s="75"/>
       <c r="M124" s="232"/>
     </row>
-    <row r="125" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="125" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="33" t="s">
         <v>291</v>
       </c>
@@ -10857,7 +10839,7 @@
       <c r="L125" s="75"/>
       <c r="M125" s="232"/>
     </row>
-    <row r="126" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="126" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="s">
         <v>291</v>
       </c>
@@ -10893,7 +10875,7 @@
       <c r="L126" s="75"/>
       <c r="M126" s="232"/>
     </row>
-    <row r="127" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="127" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
         <v>291</v>
       </c>
@@ -10929,7 +10911,7 @@
       <c r="L127" s="75"/>
       <c r="M127" s="232"/>
     </row>
-    <row r="128" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="128" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="s">
         <v>291</v>
       </c>
@@ -10965,7 +10947,7 @@
       <c r="L128" s="75"/>
       <c r="M128" s="232"/>
     </row>
-    <row r="129" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="129" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
         <v>291</v>
       </c>
@@ -11001,7 +10983,7 @@
       <c r="L129" s="75"/>
       <c r="M129" s="232"/>
     </row>
-    <row r="130" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="130" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="s">
         <v>291</v>
       </c>
@@ -11037,7 +11019,7 @@
       <c r="L130" s="75"/>
       <c r="M130" s="232"/>
     </row>
-    <row r="131" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="131" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
         <v>291</v>
       </c>
@@ -11073,7 +11055,7 @@
       <c r="L131" s="75"/>
       <c r="M131" s="232"/>
     </row>
-    <row r="132" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="132" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" s="33" t="s">
         <v>291</v>
       </c>
@@ -11107,7 +11089,7 @@
       <c r="L132" s="75"/>
       <c r="M132" s="232"/>
     </row>
-    <row r="133" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="133" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
         <v>291</v>
       </c>
@@ -11143,7 +11125,7 @@
       <c r="L133" s="75"/>
       <c r="M133" s="232"/>
     </row>
-    <row r="134" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="134" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="s">
         <v>291</v>
       </c>
@@ -11179,7 +11161,7 @@
       <c r="L134" s="75"/>
       <c r="M134" s="232"/>
     </row>
-    <row r="135" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="135" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
         <v>325</v>
       </c>
@@ -11213,7 +11195,7 @@
       <c r="L135" s="78"/>
       <c r="M135" s="232"/>
     </row>
-    <row r="136" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="136" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" s="33" t="s">
         <v>325</v>
       </c>
@@ -11247,7 +11229,7 @@
       <c r="L136" s="78"/>
       <c r="M136" s="232"/>
     </row>
-    <row r="137" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="137" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
         <v>325</v>
       </c>
@@ -11281,7 +11263,7 @@
       <c r="L137" s="78"/>
       <c r="M137" s="232"/>
     </row>
-    <row r="138" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="138" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" s="17" t="s">
         <v>325</v>
       </c>
@@ -11315,7 +11297,7 @@
       <c r="L138" s="78"/>
       <c r="M138" s="232"/>
     </row>
-    <row r="139" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="139" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
         <v>325</v>
       </c>
@@ -11349,7 +11331,7 @@
       <c r="L139" s="78"/>
       <c r="M139" s="232"/>
     </row>
-    <row r="140" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="140" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" s="17" t="s">
         <v>325</v>
       </c>
@@ -11385,7 +11367,7 @@
       <c r="L140" s="78"/>
       <c r="M140" s="232"/>
     </row>
-    <row r="141" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="141" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
         <v>340</v>
       </c>
@@ -11419,7 +11401,7 @@
       <c r="L141" s="75"/>
       <c r="M141" s="232"/>
     </row>
-    <row r="142" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="142" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" s="17" t="s">
         <v>344</v>
       </c>
@@ -11453,7 +11435,7 @@
       <c r="L142" s="75"/>
       <c r="M142" s="232"/>
     </row>
-    <row r="143" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="143" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
         <v>344</v>
       </c>
@@ -11485,7 +11467,7 @@
       <c r="L143" s="75"/>
       <c r="M143" s="232"/>
     </row>
-    <row r="144" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="144" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" s="17" t="s">
         <v>344</v>
       </c>
@@ -11519,7 +11501,7 @@
       <c r="L144" s="75"/>
       <c r="M144" s="232"/>
     </row>
-    <row r="145" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="145" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
         <v>344</v>
       </c>
@@ -11553,7 +11535,7 @@
       <c r="L145" s="75"/>
       <c r="M145" s="232"/>
     </row>
-    <row r="146" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="146" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" s="17" t="s">
         <v>344</v>
       </c>
@@ -11587,7 +11569,7 @@
       <c r="L146" s="75"/>
       <c r="M146" s="232"/>
     </row>
-    <row r="147" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="147" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
         <v>344</v>
       </c>
@@ -11621,7 +11603,7 @@
       <c r="L147" s="75"/>
       <c r="M147" s="232"/>
     </row>
-    <row r="148" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="148" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" s="17" t="s">
         <v>344</v>
       </c>
@@ -11655,7 +11637,7 @@
       <c r="L148" s="75"/>
       <c r="M148" s="232"/>
     </row>
-    <row r="149" spans="1:13" s="14" customFormat="1" ht="15.75">
+    <row r="149" spans="1:13" s="14" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
         <v>344</v>
       </c>
@@ -11689,7 +11671,7 @@
       <c r="L149" s="75"/>
       <c r="M149" s="232"/>
     </row>
-    <row r="150" spans="1:13">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A150" s="132" t="s">
         <v>344</v>
       </c>
@@ -11723,7 +11705,7 @@
       <c r="L150" s="95"/>
       <c r="M150" s="231"/>
     </row>
-    <row r="151" spans="1:13" ht="15.75">
+    <row r="151" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" s="34"/>
       <c r="B151" s="35" t="s">
         <v>368</v>
@@ -11744,7 +11726,7 @@
       <c r="K151" s="97"/>
       <c r="L151" s="98"/>
     </row>
-    <row r="152" spans="1:13">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
       <c r="G152" s="13"/>
       <c r="K152" s="214"/>
     </row>
@@ -11926,7 +11908,7 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A1:M92"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.85546875" customWidth="1"/>
     <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
@@ -11941,7 +11923,7 @@
     <col min="13" max="13" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>645</v>
       </c>
@@ -11979,7 +11961,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>656</v>
       </c>
@@ -12011,7 +11993,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>656</v>
       </c>
@@ -12041,7 +12023,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>656</v>
       </c>
@@ -12073,7 +12055,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>656</v>
       </c>
@@ -12105,7 +12087,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>656</v>
       </c>
@@ -12130,7 +12112,7 @@
       <c r="J6" s="1"/>
       <c r="M6" s="1"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>656</v>
       </c>
@@ -12155,7 +12137,7 @@
         <v>0.29166666666666669</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>656</v>
       </c>
@@ -12181,7 +12163,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>656</v>
       </c>
@@ -12210,7 +12192,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>656</v>
       </c>
@@ -12237,7 +12219,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>656</v>
       </c>
@@ -12265,7 +12247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>656</v>
       </c>
@@ -12293,7 +12275,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>656</v>
       </c>
@@ -12320,7 +12302,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>656</v>
       </c>
@@ -12348,7 +12330,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>656</v>
       </c>
@@ -12375,7 +12357,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>656</v>
       </c>
@@ -12402,7 +12384,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>656</v>
       </c>
@@ -12423,7 +12405,7 @@
       </c>
       <c r="H17" s="173"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>671</v>
       </c>
@@ -12444,7 +12426,7 @@
       </c>
       <c r="H18" s="173"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>671</v>
       </c>
@@ -12465,7 +12447,7 @@
       </c>
       <c r="H19" s="173"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>671</v>
       </c>
@@ -12486,7 +12468,7 @@
       </c>
       <c r="H20" s="173"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>671</v>
       </c>
@@ -12507,7 +12489,7 @@
       </c>
       <c r="H21" s="173"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>671</v>
       </c>
@@ -12528,7 +12510,7 @@
       </c>
       <c r="H22" s="173"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>671</v>
       </c>
@@ -12549,7 +12531,7 @@
       </c>
       <c r="H23" s="173"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>671</v>
       </c>
@@ -12570,7 +12552,7 @@
       </c>
       <c r="H24" s="173"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>671</v>
       </c>
@@ -12591,7 +12573,7 @@
       </c>
       <c r="H25" s="173"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>671</v>
       </c>
@@ -12612,7 +12594,7 @@
       </c>
       <c r="H26" s="173"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>671</v>
       </c>
@@ -12633,7 +12615,7 @@
       </c>
       <c r="H27" s="173"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>671</v>
       </c>
@@ -12654,7 +12636,7 @@
       </c>
       <c r="H28" s="173"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>671</v>
       </c>
@@ -12675,7 +12657,7 @@
       </c>
       <c r="H29" s="173"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>671</v>
       </c>
@@ -12696,7 +12678,7 @@
       </c>
       <c r="H30" s="173"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>671</v>
       </c>
@@ -12717,7 +12699,7 @@
       </c>
       <c r="H31" s="173"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>671</v>
       </c>
@@ -12738,7 +12720,7 @@
       </c>
       <c r="H32" s="173"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>671</v>
       </c>
@@ -12759,7 +12741,7 @@
       </c>
       <c r="H33" s="173"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>672</v>
       </c>
@@ -12780,7 +12762,7 @@
       </c>
       <c r="H34" s="173"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>672</v>
       </c>
@@ -12801,7 +12783,7 @@
       </c>
       <c r="H35" s="173"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>672</v>
       </c>
@@ -12822,7 +12804,7 @@
       </c>
       <c r="H36" s="173"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>672</v>
       </c>
@@ -12843,7 +12825,7 @@
       </c>
       <c r="H37" s="173"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>672</v>
       </c>
@@ -12864,7 +12846,7 @@
       </c>
       <c r="H38" s="173"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>672</v>
       </c>
@@ -12885,7 +12867,7 @@
       </c>
       <c r="H39" s="173"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>672</v>
       </c>
@@ -12906,7 +12888,7 @@
       </c>
       <c r="H40" s="173"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>672</v>
       </c>
@@ -12927,7 +12909,7 @@
       </c>
       <c r="H41" s="173"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>672</v>
       </c>
@@ -12948,7 +12930,7 @@
       </c>
       <c r="H42" s="173"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>672</v>
       </c>
@@ -12969,7 +12951,7 @@
       </c>
       <c r="H43" s="173"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>672</v>
       </c>
@@ -12990,7 +12972,7 @@
       </c>
       <c r="H44" s="173"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>672</v>
       </c>
@@ -13011,7 +12993,7 @@
       </c>
       <c r="H45" s="173"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>672</v>
       </c>
@@ -13032,7 +13014,7 @@
       </c>
       <c r="H46" s="173"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>672</v>
       </c>
@@ -13053,7 +13035,7 @@
       </c>
       <c r="H47" s="173"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>672</v>
       </c>
@@ -13074,7 +13056,7 @@
       </c>
       <c r="H48" s="173"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>672</v>
       </c>
@@ -13095,7 +13077,7 @@
       </c>
       <c r="H49" s="173"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>672</v>
       </c>
@@ -13116,7 +13098,7 @@
       </c>
       <c r="H50" s="173"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>672</v>
       </c>
@@ -13137,7 +13119,7 @@
       </c>
       <c r="H51" s="173"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>672</v>
       </c>
@@ -13158,7 +13140,7 @@
       </c>
       <c r="H52" s="173"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>672</v>
       </c>
@@ -13179,7 +13161,7 @@
       </c>
       <c r="H53" s="173"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>672</v>
       </c>
@@ -13200,7 +13182,7 @@
       </c>
       <c r="H54" s="173"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>672</v>
       </c>
@@ -13221,7 +13203,7 @@
       </c>
       <c r="H55" s="173"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>672</v>
       </c>
@@ -13242,7 +13224,7 @@
       </c>
       <c r="H56" s="173"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>672</v>
       </c>
@@ -13263,7 +13245,7 @@
       </c>
       <c r="H57" s="173"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>672</v>
       </c>
@@ -13284,7 +13266,7 @@
       </c>
       <c r="H58" s="173"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>673</v>
       </c>
@@ -13309,7 +13291,7 @@
         <v>1.7361111111111112E-2</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>673</v>
       </c>
@@ -13330,7 +13312,7 @@
       </c>
       <c r="H60" s="173"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>673</v>
       </c>
@@ -13353,7 +13335,7 @@
       </c>
       <c r="H61" s="173"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>673</v>
       </c>
@@ -13376,7 +13358,7 @@
       </c>
       <c r="H62" s="173"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>674</v>
       </c>
@@ -13397,7 +13379,7 @@
       </c>
       <c r="H63" s="173"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>674</v>
       </c>
@@ -13418,7 +13400,7 @@
       </c>
       <c r="H64" s="173"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>674</v>
       </c>
@@ -13439,7 +13421,7 @@
       </c>
       <c r="H65" s="173"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>674</v>
       </c>
@@ -13460,7 +13442,7 @@
       </c>
       <c r="H66" s="173"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>676</v>
       </c>
@@ -13481,7 +13463,7 @@
       </c>
       <c r="H67" s="173"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>676</v>
       </c>
@@ -13504,7 +13486,7 @@
         <v>1.1111111111111112E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>676</v>
       </c>
@@ -13527,7 +13509,7 @@
       </c>
       <c r="H69" s="173"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>676</v>
       </c>
@@ -13550,7 +13532,7 @@
       </c>
       <c r="H70" s="173"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>676</v>
       </c>
@@ -13571,7 +13553,7 @@
       </c>
       <c r="H71" s="173"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>676</v>
       </c>
@@ -13592,7 +13574,7 @@
       </c>
       <c r="H72" s="173"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>676</v>
       </c>
@@ -13620,7 +13602,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>676</v>
       </c>
@@ -13648,7 +13630,7 @@
         <v>8.3333333333333329E-2</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>676</v>
       </c>
@@ -13673,7 +13655,7 @@
         <v>0.6069444444444444</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>677</v>
       </c>
@@ -13701,7 +13683,7 @@
         <v>4.027777777777778E-2</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>679</v>
       </c>
@@ -13722,7 +13704,7 @@
       </c>
       <c r="H77" s="173"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>679</v>
       </c>
@@ -13743,7 +13725,7 @@
       </c>
       <c r="H78" s="173"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>679</v>
       </c>
@@ -13764,7 +13746,7 @@
       </c>
       <c r="H79" s="173"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>679</v>
       </c>
@@ -13785,7 +13767,7 @@
       </c>
       <c r="H80" s="173"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>679</v>
       </c>
@@ -13806,7 +13788,7 @@
       </c>
       <c r="H81" s="173"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>679</v>
       </c>
@@ -13827,7 +13809,7 @@
       </c>
       <c r="H82" s="173"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>679</v>
       </c>
@@ -13848,7 +13830,7 @@
       </c>
       <c r="H83" s="173"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>679</v>
       </c>
@@ -13869,7 +13851,7 @@
       </c>
       <c r="H84" s="173"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>679</v>
       </c>
@@ -13890,7 +13872,7 @@
       </c>
       <c r="H85" s="173"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>679</v>
       </c>
@@ -13911,7 +13893,7 @@
       </c>
       <c r="H86" s="173"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>679</v>
       </c>
@@ -13932,7 +13914,7 @@
       </c>
       <c r="H87" s="173"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>679</v>
       </c>
@@ -13953,7 +13935,7 @@
       </c>
       <c r="H88" s="173"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>679</v>
       </c>
@@ -13974,7 +13956,7 @@
       </c>
       <c r="H89" s="173"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>679</v>
       </c>
@@ -13995,7 +13977,7 @@
       </c>
       <c r="H90" s="173"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>679</v>
       </c>
@@ -14016,7 +13998,7 @@
       </c>
       <c r="H91" s="173"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="E92" s="1">
@@ -14050,7 +14032,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:F29"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
     <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
@@ -14059,16 +14041,16 @@
     <col min="6" max="6" width="57.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:6">
-      <c r="B1" s="237" t="s">
+    <row r="1" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="240" t="s">
         <v>680</v>
       </c>
-      <c r="C1" s="238"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="239"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="242"/>
       <c r="F1" s="42"/>
     </row>
-    <row r="2" spans="2:6">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="40" t="s">
         <v>681</v>
       </c>
@@ -14083,7 +14065,7 @@
       </c>
       <c r="F2" s="42"/>
     </row>
-    <row r="3" spans="2:6">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="40" t="s">
         <v>685</v>
       </c>
@@ -14091,7 +14073,7 @@
       <c r="E3" s="39"/>
       <c r="F3" s="9"/>
     </row>
-    <row r="4" spans="2:6">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="40">
         <v>1</v>
       </c>
@@ -14106,7 +14088,7 @@
       </c>
       <c r="F4" s="42"/>
     </row>
-    <row r="5" spans="2:6">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="40">
         <v>2</v>
       </c>
@@ -14121,7 +14103,7 @@
       </c>
       <c r="F5" s="42"/>
     </row>
-    <row r="6" spans="2:6">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="40">
         <v>3</v>
       </c>
@@ -14136,7 +14118,7 @@
       </c>
       <c r="F6" s="42"/>
     </row>
-    <row r="7" spans="2:6">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="40">
         <v>4</v>
       </c>
@@ -14147,21 +14129,21 @@
       <c r="E7" s="135"/>
       <c r="F7" s="42"/>
     </row>
-    <row r="8" spans="2:6">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="40"/>
       <c r="C8" s="42"/>
       <c r="D8" s="6"/>
       <c r="E8" s="135"/>
       <c r="F8" s="42"/>
     </row>
-    <row r="9" spans="2:6">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="40"/>
       <c r="C9" s="42"/>
       <c r="D9" s="6"/>
       <c r="E9" s="135"/>
       <c r="F9" s="42"/>
     </row>
-    <row r="10" spans="2:6">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="40" t="s">
         <v>694</v>
       </c>
@@ -14170,7 +14152,7 @@
       <c r="E10" s="135"/>
       <c r="F10" s="42"/>
     </row>
-    <row r="11" spans="2:6">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="40">
         <v>1</v>
       </c>
@@ -14183,7 +14165,7 @@
       </c>
       <c r="F11" s="42"/>
     </row>
-    <row r="12" spans="2:6">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="40">
         <v>2</v>
       </c>
@@ -14196,7 +14178,7 @@
       </c>
       <c r="F12" s="42"/>
     </row>
-    <row r="13" spans="2:6">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="40">
         <v>3</v>
       </c>
@@ -14209,7 +14191,7 @@
       </c>
       <c r="F13" s="42"/>
     </row>
-    <row r="14" spans="2:6">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="40">
         <v>4</v>
       </c>
@@ -14222,7 +14204,7 @@
       </c>
       <c r="F14" s="42"/>
     </row>
-    <row r="15" spans="2:6">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="40">
         <v>5</v>
       </c>
@@ -14235,7 +14217,7 @@
       </c>
       <c r="F15" s="42"/>
     </row>
-    <row r="16" spans="2:6">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="40">
         <v>6</v>
       </c>
@@ -14248,7 +14230,7 @@
       </c>
       <c r="F16" s="42"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="40">
         <v>7</v>
       </c>
@@ -14259,7 +14241,7 @@
       </c>
       <c r="F17" s="42"/>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="40">
         <v>8</v>
       </c>
@@ -14270,7 +14252,7 @@
       </c>
       <c r="F18" s="42"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="40">
         <v>9</v>
       </c>
@@ -14283,7 +14265,7 @@
       </c>
       <c r="F19" s="42"/>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="40">
         <v>10</v>
       </c>
@@ -14296,14 +14278,14 @@
       </c>
       <c r="F20" s="42"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="40"/>
       <c r="C21" s="42"/>
       <c r="D21" s="6"/>
       <c r="E21" s="135"/>
       <c r="F21" s="42"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="40" t="s">
         <v>685</v>
       </c>
@@ -14316,7 +14298,7 @@
       <c r="E22" s="135"/>
       <c r="F22" s="42"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="40">
         <v>1</v>
       </c>
@@ -14331,7 +14313,7 @@
       </c>
       <c r="F23" s="42"/>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="40">
         <v>2</v>
       </c>
@@ -14346,7 +14328,7 @@
       </c>
       <c r="F24" s="42"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="40">
         <v>3</v>
       </c>
@@ -14361,7 +14343,7 @@
       </c>
       <c r="F25" s="42"/>
     </row>
-    <row r="26" spans="2:6" ht="15.75" thickBot="1">
+    <row r="26" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B26" s="136">
         <v>4</v>
       </c>
@@ -14372,21 +14354,21 @@
       <c r="E26" s="139"/>
       <c r="F26" s="42"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="42"/>
       <c r="C27" s="42"/>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="42"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="42"/>
       <c r="C28" s="42"/>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="42"/>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
       <c r="F29" s="42"/>
@@ -14412,8 +14394,8 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="83.140625" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -14421,7 +14403,7 @@
     <col min="4" max="4" width="70.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
+    <row r="1" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>708</v>
       </c>
@@ -14435,7 +14417,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="20.25" customHeight="1">
+    <row r="2" spans="1:4" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>712</v>
       </c>
@@ -14449,19 +14431,19 @@
         <v>715</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>716</v>
       </c>
       <c r="B3" t="s">
         <v>717</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="238" t="s">
         <v>718</v>
       </c>
       <c r="D3" s="8"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>719</v>
       </c>
@@ -14475,7 +14457,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="14.25" customHeight="1">
+    <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>723</v>
       </c>
@@ -14486,7 +14468,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>724</v>
       </c>
@@ -14497,7 +14479,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>727</v>
       </c>
@@ -14511,7 +14493,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>730</v>
       </c>
@@ -14519,15 +14501,15 @@
         <v>731</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="7" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>734</v>
       </c>
@@ -14539,7 +14521,7 @@
       </c>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>736</v>
       </c>
@@ -14550,7 +14532,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>738</v>
       </c>
@@ -14561,7 +14543,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>741</v>
       </c>
@@ -14572,78 +14554,31 @@
         <v>743</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>744</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="B14" t="s">
+        <v>725</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="D14" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="B15" t="s">
-        <v>725</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="D15" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>748</v>
-      </c>
-      <c r="B16" t="s">
-        <v>725</v>
-      </c>
-      <c r="C16" s="184" t="s">
         <v>749</v>
-      </c>
-      <c r="D16" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>750</v>
-      </c>
-      <c r="B17" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>752</v>
-      </c>
-      <c r="B18" t="s">
-        <v>720</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>755</v>
-      </c>
-      <c r="B20" t="s">
-        <v>725</v>
-      </c>
-      <c r="C20" t="s">
-        <v>756</v>
       </c>
     </row>
   </sheetData>
@@ -14657,7 +14592,7 @@
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="54" customWidth="1"/>
@@ -14665,12 +14600,12 @@
     <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="B1" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="C1" t="s">
         <v>371</v>
@@ -14679,151 +14614,151 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>753</v>
+      </c>
+      <c r="C2" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>755</v>
+      </c>
+      <c r="B3" s="58" t="s">
+        <v>756</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>758</v>
+      </c>
+      <c r="B4" s="42" t="s">
         <v>759</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="C4" s="4" t="s">
         <v>760</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>761</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1">
-      <c r="A3" t="s">
+      <c r="B5" s="42" t="s">
         <v>762</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="C5" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="C3" s="4" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>764</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A4" t="s">
+      <c r="B6" s="42" t="s">
         <v>765</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="C6" t="s">
         <v>766</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="7" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>767</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+      <c r="B7" s="42" t="s">
         <v>768</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="C7" t="s">
         <v>769</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>770</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>771</v>
       </c>
-      <c r="B6" s="42" t="s">
+      <c r="B8" s="42" t="s">
         <v>772</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C8" t="s">
         <v>773</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="12" customHeight="1">
-      <c r="A7" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>774</v>
       </c>
-      <c r="B7" s="42" t="s">
+      <c r="B9" s="42" t="s">
         <v>775</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>776</v>
       </c>
-      <c r="D7" s="4" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
+      <c r="B10" s="42" t="s">
         <v>778</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="C10" t="s">
         <v>779</v>
       </c>
-      <c r="C8" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+      <c r="B11" s="42" t="s">
         <v>781</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="C11" t="s">
         <v>782</v>
       </c>
-      <c r="C9" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+      <c r="B12" s="42" t="s">
         <v>784</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="C12" t="s">
         <v>785</v>
       </c>
-      <c r="C10" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>787</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>788</v>
-      </c>
-      <c r="C11" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>790</v>
-      </c>
-      <c r="B12" s="42" t="s">
-        <v>791</v>
-      </c>
-      <c r="C12" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B13" s="42"/>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B14" s="42"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B15" s="42"/>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B16" s="42"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B17" s="42"/>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B18" s="42"/>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="B19" s="154" t="s">
         <v>645</v>
@@ -14835,344 +14770,344 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>786</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>787</v>
+      </c>
+      <c r="C20" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="42" t="s">
+        <v>789</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="42" t="s">
+        <v>791</v>
+      </c>
+      <c r="C22" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="42" t="s">
         <v>793</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="C23" t="s">
         <v>794</v>
       </c>
-      <c r="C20" t="s">
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="42" t="s">
         <v>795</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="B21" s="42" t="s">
+      <c r="C24" t="s">
         <v>796</v>
       </c>
-      <c r="C21" s="4" t="s">
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="42" t="s">
         <v>797</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="B22" s="42" t="s">
+      <c r="C25" t="s">
         <v>798</v>
       </c>
-      <c r="C22" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="B23" s="42" t="s">
-        <v>800</v>
-      </c>
-      <c r="C23" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="B24" s="42" t="s">
-        <v>802</v>
-      </c>
-      <c r="C24" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="B25" s="42" t="s">
-        <v>804</v>
-      </c>
-      <c r="C25" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="190"/>
       <c r="B26" s="191" t="s">
+        <v>799</v>
+      </c>
+      <c r="C26" s="190" t="s">
+        <v>800</v>
+      </c>
+      <c r="D26" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="42" t="s">
+        <v>802</v>
+      </c>
+      <c r="C27" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>804</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>805</v>
+      </c>
+      <c r="C28" t="s">
         <v>806</v>
       </c>
-      <c r="C26" s="190" t="s">
+      <c r="D28" t="s">
         <v>807</v>
       </c>
-      <c r="D26" t="s">
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="42" t="s">
         <v>808</v>
       </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="B27" s="42" t="s">
+      <c r="C29" t="s">
         <v>809</v>
       </c>
-      <c r="C27" t="s">
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>810</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
+      <c r="B30" s="42" t="s">
         <v>811</v>
       </c>
-      <c r="B28" s="42" t="s">
+      <c r="C30" t="s">
         <v>812</v>
       </c>
-      <c r="C28" t="s">
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="42" t="s">
         <v>813</v>
       </c>
-      <c r="D28" t="s">
+      <c r="C31" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="B29" s="42" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="42" t="s">
         <v>815</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C32" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="42" t="s">
         <v>817</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="C33" t="s">
         <v>818</v>
       </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>754</v>
+      </c>
+      <c r="B34" s="42" t="s">
         <v>819</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="B31" s="42" t="s">
+      <c r="C34" t="s">
         <v>820</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D34" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="B32" s="42" t="s">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="42" t="s">
         <v>822</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C35" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
-      <c r="B33" s="42" t="s">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="42" t="s">
         <v>824</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C36" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>761</v>
-      </c>
-      <c r="B34" s="42" t="s">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="42" t="s">
         <v>826</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C37" t="s">
         <v>827</v>
       </c>
-      <c r="D34" t="s">
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="42" t="s">
         <v>828</v>
       </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="B35" s="42" t="s">
+      <c r="C38" t="s">
         <v>829</v>
       </c>
-      <c r="C35" t="s">
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="42"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="42"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>830</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="B36" s="42" t="s">
+      <c r="B41" s="64" t="s">
         <v>831</v>
-      </c>
-      <c r="C36" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="B37" s="42" t="s">
-        <v>833</v>
-      </c>
-      <c r="C37" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="B38" s="42" t="s">
-        <v>835</v>
-      </c>
-      <c r="C38" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="B39" s="42"/>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="B40" s="42"/>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>837</v>
-      </c>
-      <c r="B41" s="64" t="s">
-        <v>838</v>
       </c>
       <c r="C41" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
+        <v>832</v>
+      </c>
+      <c r="C42" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
+        <v>834</v>
+      </c>
+      <c r="C43" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
+        <v>835</v>
+      </c>
+      <c r="C44" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>836</v>
+      </c>
+      <c r="C45" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>837</v>
+      </c>
+      <c r="C47" t="s">
+        <v>833</v>
+      </c>
+      <c r="D47" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D48" t="s">
         <v>839</v>
       </c>
-      <c r="C42" t="s">
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
-      <c r="B43" t="s">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
         <v>841</v>
       </c>
-      <c r="C43" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="B44" t="s">
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>830</v>
+      </c>
+      <c r="B52" s="64" t="s">
         <v>842</v>
-      </c>
-      <c r="C44" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="B45" t="s">
-        <v>843</v>
-      </c>
-      <c r="C45" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="B47" t="s">
-        <v>844</v>
-      </c>
-      <c r="C47" t="s">
-        <v>840</v>
-      </c>
-      <c r="D47" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="D48" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="B49" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="B50" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>837</v>
-      </c>
-      <c r="B52" s="64" t="s">
-        <v>849</v>
       </c>
       <c r="C52" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
+        <v>843</v>
+      </c>
+      <c r="C53" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>844</v>
+      </c>
+      <c r="C54" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>845</v>
+      </c>
+      <c r="C55" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>846</v>
+      </c>
+      <c r="C56" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>847</v>
+      </c>
+      <c r="C57" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>848</v>
+      </c>
+      <c r="C58" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>849</v>
+      </c>
+      <c r="C59" t="s">
         <v>850</v>
       </c>
-      <c r="C53" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="B54" t="s">
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
         <v>851</v>
       </c>
-      <c r="C54" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
-      <c r="B55" t="s">
+      <c r="C60" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
         <v>852</v>
       </c>
-      <c r="C55" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
-      <c r="B56" t="s">
+      <c r="C61" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
         <v>853</v>
       </c>
-      <c r="C56" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
-      <c r="B57" t="s">
-        <v>854</v>
-      </c>
-      <c r="C57" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
-      <c r="B58" t="s">
-        <v>855</v>
-      </c>
-      <c r="C58" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
-      <c r="B59" t="s">
-        <v>856</v>
-      </c>
-      <c r="C59" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
-      <c r="B60" t="s">
-        <v>858</v>
-      </c>
-      <c r="C60" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
-      <c r="B61" t="s">
-        <v>859</v>
-      </c>
-      <c r="C61" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
-      <c r="B62" t="s">
-        <v>860</v>
-      </c>
       <c r="C62" t="s">
-        <v>840</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>
@@ -15189,7 +15124,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617F1214-FEDF-4959-B6B1-8C60CA48A0FC}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
@@ -15198,12 +15133,12 @@
     <col min="5" max="5" width="34.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>370</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>371</v>
@@ -15212,83 +15147,83 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>856</v>
+      </c>
+      <c r="B2" t="s">
+        <v>857</v>
+      </c>
+      <c r="C2" t="s">
+        <v>858</v>
+      </c>
+      <c r="D2" t="s">
+        <v>859</v>
+      </c>
+      <c r="E2" s="170" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>861</v>
+      </c>
+      <c r="C3" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>863</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>864</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>865</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C6" s="4" t="s">
         <v>866</v>
       </c>
-      <c r="E2" s="170" t="s">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>868</v>
       </c>
-      <c r="C3" t="s">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A6" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>872</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C12" t="s">
         <v>873</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>879</v>
-      </c>
-      <c r="C12" t="s">
-        <v>880</v>
       </c>
     </row>
   </sheetData>
@@ -15303,7 +15238,7 @@
     <tabColor rgb="FF00B050"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="11" customWidth="1"/>
@@ -15316,7 +15251,7 @@
     <col min="9" max="16384" width="11" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" ht="30">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="53"/>
       <c r="B1" s="19" t="s">
         <v>370</v>
@@ -15332,7 +15267,7 @@
       </c>
       <c r="F1" s="140"/>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>373</v>
       </c>
@@ -15356,7 +15291,7 @@
       <c r="I2" s="216"/>
       <c r="J2" s="216"/>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>377</v>
       </c>
@@ -15380,7 +15315,7 @@
       <c r="I3" s="216"/>
       <c r="J3" s="216"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>380</v>
       </c>
@@ -15404,7 +15339,7 @@
       <c r="I4" s="216"/>
       <c r="J4" s="216"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>383</v>
       </c>
@@ -15428,7 +15363,7 @@
       <c r="I5" s="216"/>
       <c r="J5" s="216"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="20" t="s">
         <v>384</v>
@@ -15448,7 +15383,7 @@
       <c r="I6" s="216"/>
       <c r="J6" s="216"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="20" t="s">
         <v>384</v>
@@ -15468,7 +15403,7 @@
       <c r="I7" s="216"/>
       <c r="J7" s="216"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" s="20" t="s">
         <v>389</v>
@@ -15486,7 +15421,7 @@
       <c r="I8" s="216"/>
       <c r="J8" s="216"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
       <c r="B9" s="20" t="s">
         <v>391</v>
@@ -15504,7 +15439,7 @@
       <c r="I9" s="216"/>
       <c r="J9" s="216"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="25"/>
       <c r="B10" s="20" t="s">
         <v>393</v>
@@ -15522,7 +15457,7 @@
       <c r="I10" s="216"/>
       <c r="J10" s="216"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
       <c r="B11" s="20" t="s">
         <v>222</v>
@@ -15540,7 +15475,7 @@
       <c r="I11" s="216"/>
       <c r="J11" s="216"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>394</v>
       </c>
@@ -15560,7 +15495,7 @@
       <c r="I12" s="216"/>
       <c r="J12" s="216"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="20" t="s">
         <v>226</v>
@@ -15578,7 +15513,7 @@
       <c r="I13" s="216"/>
       <c r="J13" s="216"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="20" t="s">
         <v>233</v>
@@ -15596,7 +15531,7 @@
       <c r="I14" s="216"/>
       <c r="J14" s="216"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" s="20" t="s">
         <v>240</v>
@@ -15614,7 +15549,7 @@
       <c r="I15" s="216"/>
       <c r="J15" s="216"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="151" t="s">
         <v>396</v>
       </c>
@@ -15634,7 +15569,7 @@
       <c r="I16" s="216"/>
       <c r="J16" s="216"/>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="20" t="s">
         <v>399</v>
@@ -15649,7 +15584,7 @@
       <c r="F17" s="146"/>
       <c r="G17" s="216"/>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
       <c r="B18" s="20" t="s">
         <v>401</v>
@@ -15664,7 +15599,7 @@
       <c r="F18" s="146"/>
       <c r="G18" s="216"/>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="61"/>
       <c r="B19" s="43" t="s">
         <v>402</v>
@@ -15679,7 +15614,7 @@
       <c r="F19" s="148"/>
       <c r="G19" s="216"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B20" s="216"/>
       <c r="C20" s="216"/>
       <c r="E20" s="216"/>
@@ -15714,7 +15649,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="2" customWidth="1"/>
@@ -15728,7 +15663,7 @@
     <col min="16356" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="157"/>
       <c r="B1" s="158" t="s">
         <v>370</v>
@@ -15743,7 +15678,7 @@
       <c r="G1"/>
       <c r="H1"/>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="160" t="s">
         <v>373</v>
       </c>
@@ -15760,7 +15695,7 @@
       <c r="G2"/>
       <c r="H2"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="162" t="s">
         <v>377</v>
       </c>
@@ -15777,7 +15712,7 @@
       <c r="G3"/>
       <c r="H3"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="162" t="s">
         <v>380</v>
       </c>
@@ -15794,7 +15729,7 @@
       <c r="G4"/>
       <c r="H4"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="162" t="s">
         <v>383</v>
       </c>
@@ -15811,7 +15746,7 @@
       <c r="G5"/>
       <c r="H5"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="163"/>
       <c r="B6" s="203" t="s">
         <v>331</v>
@@ -15824,7 +15759,7 @@
       <c r="G6" s="1"/>
       <c r="H6"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="163"/>
       <c r="B7" s="203" t="s">
         <v>333</v>
@@ -15837,7 +15772,7 @@
       <c r="G7" s="1"/>
       <c r="H7"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="163"/>
       <c r="B8" s="203" t="s">
         <v>404</v>
@@ -15850,7 +15785,7 @@
       <c r="G8"/>
       <c r="H8"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="163"/>
       <c r="B9" t="s">
         <v>405</v>
@@ -15863,7 +15798,7 @@
       <c r="G9"/>
       <c r="H9"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="163"/>
       <c r="B10" t="s">
         <v>406</v>
@@ -15876,7 +15811,7 @@
       <c r="G10"/>
       <c r="H10"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="163"/>
       <c r="B11" s="1" t="s">
         <v>407</v>
@@ -15889,7 +15824,7 @@
       <c r="G11" s="1"/>
       <c r="H11"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="162" t="s">
         <v>394</v>
       </c>
@@ -15906,7 +15841,7 @@
       <c r="G12"/>
       <c r="H12"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="163"/>
       <c r="B13" s="203" t="s">
         <v>409</v>
@@ -15921,7 +15856,7 @@
       <c r="G13"/>
       <c r="H13"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="163"/>
       <c r="B14" s="203" t="s">
         <v>411</v>
@@ -15934,7 +15869,7 @@
       <c r="G14"/>
       <c r="H14"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="163"/>
       <c r="B15" s="2" t="s">
         <v>183</v>
@@ -15947,7 +15882,7 @@
       <c r="G15"/>
       <c r="H15"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="163"/>
       <c r="B16" s="2" t="s">
         <v>186</v>
@@ -15960,7 +15895,7 @@
       <c r="G16"/>
       <c r="H16"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="163"/>
       <c r="B17" s="2" t="s">
         <v>188</v>
@@ -15973,7 +15908,7 @@
       <c r="G17"/>
       <c r="H17"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="163"/>
       <c r="B18" t="s">
         <v>412</v>
@@ -15986,7 +15921,7 @@
       <c r="G18"/>
       <c r="H18"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="163"/>
       <c r="B19" s="2" t="s">
         <v>413</v>
@@ -15999,7 +15934,7 @@
       <c r="G19"/>
       <c r="H19"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="163"/>
       <c r="B20" s="2" t="s">
         <v>414</v>
@@ -16012,7 +15947,7 @@
       <c r="G20"/>
       <c r="H20"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="163"/>
       <c r="B21" s="2" t="s">
         <v>393</v>
@@ -16025,7 +15960,7 @@
       <c r="G21"/>
       <c r="H21"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="163"/>
       <c r="B22" s="2" t="s">
         <v>395</v>
@@ -16038,7 +15973,7 @@
       <c r="G22"/>
       <c r="H22"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="163"/>
       <c r="B23" s="2" t="s">
         <v>226</v>
@@ -16051,7 +15986,7 @@
       <c r="G23"/>
       <c r="H23"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="163"/>
       <c r="B24" s="2" t="s">
         <v>230</v>
@@ -16064,7 +15999,7 @@
       <c r="G24"/>
       <c r="H24"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="163"/>
       <c r="B25" s="2" t="s">
         <v>235</v>
@@ -16077,7 +16012,7 @@
       <c r="G25"/>
       <c r="H25"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="163"/>
       <c r="B26" s="203" t="s">
         <v>415</v>
@@ -16092,7 +16027,7 @@
       <c r="G26"/>
       <c r="H26"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="163"/>
       <c r="B27" s="203" t="s">
         <v>417</v>
@@ -16107,7 +16042,7 @@
       <c r="G27"/>
       <c r="H27"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="163"/>
       <c r="B28" s="203" t="s">
         <v>419</v>
@@ -16120,7 +16055,7 @@
       <c r="G28"/>
       <c r="H28"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="163"/>
       <c r="B29" s="38" t="s">
         <v>420</v>
@@ -16136,7 +16071,7 @@
       <c r="G29"/>
       <c r="H29"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="163"/>
       <c r="B30" s="38" t="s">
         <v>421</v>
@@ -16152,7 +16087,7 @@
       <c r="G30"/>
       <c r="H30"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="163"/>
       <c r="B31" t="s">
         <v>422</v>
@@ -16168,7 +16103,7 @@
       <c r="G31" s="203"/>
       <c r="H31"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="163"/>
       <c r="B32" t="s">
         <v>423</v>
@@ -16184,7 +16119,7 @@
       <c r="G32"/>
       <c r="H32"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="163"/>
       <c r="B33" s="38" t="s">
         <v>424</v>
@@ -16200,7 +16135,7 @@
       <c r="G33"/>
       <c r="H33"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="163"/>
       <c r="B34" t="s">
         <v>425</v>
@@ -16216,7 +16151,7 @@
       <c r="G34"/>
       <c r="H34"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="163"/>
       <c r="B35" s="1" t="s">
         <v>426</v>
@@ -16232,7 +16167,7 @@
       <c r="G35"/>
       <c r="H35"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="163"/>
       <c r="B36" s="1" t="s">
         <v>427</v>
@@ -16248,7 +16183,7 @@
       <c r="G36"/>
       <c r="H36"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="163"/>
       <c r="B37" s="38" t="s">
         <v>428</v>
@@ -16264,7 +16199,7 @@
       <c r="G37"/>
       <c r="H37"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="163"/>
       <c r="B38" s="38" t="s">
         <v>429</v>
@@ -16280,7 +16215,7 @@
       <c r="G38" s="1"/>
       <c r="H38"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="163"/>
       <c r="B39" s="38" t="s">
         <v>430</v>
@@ -16296,7 +16231,7 @@
       <c r="G39"/>
       <c r="H39"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="163"/>
       <c r="B40" s="38" t="s">
         <v>431</v>
@@ -16312,7 +16247,7 @@
       <c r="G40"/>
       <c r="H40"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="163"/>
       <c r="B41" s="1" t="s">
         <v>432</v>
@@ -16328,7 +16263,7 @@
       <c r="G41"/>
       <c r="H41"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="163"/>
       <c r="B42" s="1" t="s">
         <v>433</v>
@@ -16344,7 +16279,7 @@
       <c r="G42"/>
       <c r="H42"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="163"/>
       <c r="B43" s="38" t="s">
         <v>434</v>
@@ -16360,7 +16295,7 @@
       <c r="G43"/>
       <c r="H43"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="166"/>
       <c r="B44" s="38" t="s">
         <v>435</v>
@@ -16376,7 +16311,7 @@
       <c r="G44"/>
       <c r="H44"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="F45" s="203"/>
     </row>
   </sheetData>
@@ -16410,7 +16345,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="2" customWidth="1"/>
@@ -16423,7 +16358,7 @@
     <col min="16368" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1">
+    <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="53"/>
       <c r="B1" s="66" t="s">
         <v>370</v>
@@ -16436,7 +16371,7 @@
       </c>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>373</v>
       </c>
@@ -16451,7 +16386,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>377</v>
       </c>
@@ -16466,7 +16401,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>380</v>
       </c>
@@ -16481,7 +16416,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>383</v>
       </c>
@@ -16496,7 +16431,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="28" t="s">
         <v>438</v>
@@ -16510,7 +16445,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="58" t="s">
         <v>75</v>
@@ -16521,7 +16456,7 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" t="s">
         <v>440</v>
@@ -16532,7 +16467,7 @@
       </c>
       <c r="E8" s="56"/>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
       <c r="B9" t="s">
         <v>441</v>
@@ -16543,7 +16478,7 @@
       </c>
       <c r="E9" s="56"/>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="25"/>
       <c r="B10" s="1" t="s">
         <v>442</v>
@@ -16554,7 +16489,7 @@
       </c>
       <c r="E10" s="56"/>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
       <c r="B11" t="s">
         <v>185</v>
@@ -16565,7 +16500,7 @@
       </c>
       <c r="E11" s="56"/>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>394</v>
       </c>
@@ -16578,7 +16513,7 @@
       </c>
       <c r="E12" s="56"/>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="1" t="s">
         <v>444</v>
@@ -16589,7 +16524,7 @@
       </c>
       <c r="E13" s="56"/>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" t="s">
         <v>445</v>
@@ -16600,7 +16535,7 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" s="1" t="s">
         <v>446</v>
@@ -16611,7 +16546,7 @@
       </c>
       <c r="E15" s="56"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
       <c r="B16" s="13" t="s">
         <v>259</v>
@@ -16622,7 +16557,7 @@
       </c>
       <c r="E16" s="56"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="13" t="s">
         <v>447</v>
@@ -16633,7 +16568,7 @@
       </c>
       <c r="E17" s="56"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
       <c r="B18" s="223" t="s">
         <v>448</v>
@@ -16646,7 +16581,7 @@
       </c>
       <c r="E18" s="56"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="25"/>
       <c r="B19" s="69" t="s">
         <v>450</v>
@@ -16657,7 +16592,7 @@
       </c>
       <c r="E19" s="56"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="224" t="s">
         <v>451</v>
@@ -16668,7 +16603,7 @@
       </c>
       <c r="E20" s="56"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="67" t="s">
         <v>452</v>
@@ -16679,7 +16614,7 @@
       </c>
       <c r="E21" s="56"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="25"/>
       <c r="B22" s="224" t="s">
         <v>453</v>
@@ -16690,7 +16625,7 @@
       </c>
       <c r="E22" s="56"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="25"/>
       <c r="B23" s="67" t="s">
         <v>454</v>
@@ -16701,7 +16636,7 @@
       </c>
       <c r="E23" s="56"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="25"/>
       <c r="B24" s="70" t="s">
         <v>455</v>
@@ -16712,7 +16647,7 @@
       </c>
       <c r="E24" s="56"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
       <c r="B25" s="38" t="s">
         <v>456</v>
@@ -16723,7 +16658,7 @@
       </c>
       <c r="E25" s="56"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
       <c r="B26" s="70" t="s">
         <v>457</v>
@@ -16734,14 +16669,14 @@
       </c>
       <c r="E26" s="56"/>
     </row>
-    <row r="27" spans="1:5" ht="15.75" thickBot="1">
+    <row r="27" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="25"/>
       <c r="B27" s="64"/>
       <c r="C27" s="64"/>
       <c r="D27" s="216"/>
       <c r="E27" s="56"/>
     </row>
-    <row r="28" spans="1:5" ht="18.75">
+    <row r="28" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="25"/>
       <c r="B28" s="21" t="s">
         <v>458</v>
@@ -16750,7 +16685,7 @@
       <c r="D28" s="46"/>
       <c r="E28" s="56"/>
     </row>
-    <row r="29" spans="1:5" ht="30" customHeight="1">
+    <row r="29" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
       <c r="B29" s="23" t="s">
         <v>370</v>
@@ -16763,7 +16698,7 @@
       </c>
       <c r="E29" s="56"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
       <c r="B30" s="20" t="s">
         <v>354</v>
@@ -16774,7 +16709,7 @@
       </c>
       <c r="E30" s="56"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
       <c r="B31" s="20" t="s">
         <v>459</v>
@@ -16785,7 +16720,7 @@
       </c>
       <c r="E31" s="56"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="25"/>
       <c r="B32" s="20" t="s">
         <v>460</v>
@@ -16796,7 +16731,7 @@
       </c>
       <c r="E32" s="56"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="25"/>
       <c r="B33" s="24" t="s">
         <v>461</v>
@@ -16807,7 +16742,7 @@
       </c>
       <c r="E33" s="56"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
       <c r="B34" s="17" t="s">
         <v>362</v>
@@ -16818,7 +16753,7 @@
       </c>
       <c r="E34" s="56"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
       <c r="B35" s="26" t="s">
         <v>356</v>
@@ -16829,7 +16764,7 @@
       </c>
       <c r="E35" s="56"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="25"/>
       <c r="B36" s="27" t="s">
         <v>358</v>
@@ -16840,7 +16775,7 @@
       </c>
       <c r="E36" s="56"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="25"/>
       <c r="B37" s="17" t="s">
         <v>360</v>
@@ -16851,7 +16786,7 @@
       </c>
       <c r="E37" s="56"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="25"/>
       <c r="B38" s="20" t="s">
         <v>462</v>
@@ -16862,7 +16797,7 @@
       </c>
       <c r="E38" s="56"/>
     </row>
-    <row r="39" spans="1:5" ht="15.75" thickBot="1">
+    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="61"/>
       <c r="B39" s="43" t="s">
         <v>351</v>
@@ -16902,7 +16837,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="2" customWidth="1"/>
@@ -16914,7 +16849,7 @@
     <col min="16368" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="53"/>
       <c r="B1" s="10" t="s">
         <v>370</v>
@@ -16927,7 +16862,7 @@
       </c>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1">
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>373</v>
       </c>
@@ -16941,7 +16876,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1">
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>377</v>
       </c>
@@ -16956,7 +16891,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>380</v>
       </c>
@@ -16971,7 +16906,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>383</v>
       </c>
@@ -16986,7 +16921,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="45" t="s">
         <v>318</v>
@@ -16999,7 +16934,7 @@
       </c>
       <c r="E6" s="56"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="13" t="s">
         <v>464</v>
@@ -17012,7 +16947,7 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" s="203" t="s">
         <v>466</v>
@@ -17023,7 +16958,7 @@
       </c>
       <c r="E8" s="56"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
       <c r="B9" s="38" t="s">
         <v>467</v>
@@ -17033,7 +16968,7 @@
       </c>
       <c r="E9" s="56"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="25"/>
       <c r="B10" s="203" t="s">
         <v>250</v>
@@ -17044,7 +16979,7 @@
       </c>
       <c r="E10" s="56"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
       <c r="B11" s="199" t="s">
         <v>468</v>
@@ -17055,7 +16990,7 @@
       </c>
       <c r="E11" s="56"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>394</v>
       </c>
@@ -17068,7 +17003,7 @@
       </c>
       <c r="E12" s="56"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="2" t="s">
         <v>469</v>
@@ -17078,7 +17013,7 @@
       </c>
       <c r="E13" s="56"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="2" t="s">
         <v>470</v>
@@ -17088,7 +17023,7 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" s="2" t="s">
         <v>186</v>
@@ -17098,7 +17033,7 @@
       </c>
       <c r="E15" s="56"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
       <c r="B16" s="2" t="s">
         <v>188</v>
@@ -17108,7 +17043,7 @@
       </c>
       <c r="E16" s="56"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="2" t="s">
         <v>412</v>
@@ -17118,7 +17053,7 @@
       </c>
       <c r="E17" s="56"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
       <c r="B18" s="2" t="s">
         <v>471</v>
@@ -17128,7 +17063,7 @@
       </c>
       <c r="E18" s="56"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="25"/>
       <c r="B19" s="2" t="s">
         <v>472</v>
@@ -17138,7 +17073,7 @@
       </c>
       <c r="E19" s="56"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="2" t="s">
         <v>473</v>
@@ -17148,7 +17083,7 @@
       </c>
       <c r="E20" s="56"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="2" t="s">
         <v>212</v>
@@ -17158,7 +17093,7 @@
       </c>
       <c r="E21" s="56"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="25"/>
       <c r="B22" s="2" t="s">
         <v>413</v>
@@ -17168,7 +17103,7 @@
       </c>
       <c r="E22" s="56"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="25"/>
       <c r="B23" s="2" t="s">
         <v>393</v>
@@ -17178,7 +17113,7 @@
       </c>
       <c r="E23" s="56"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="25"/>
       <c r="B24" s="203" t="s">
         <v>395</v>
@@ -17189,7 +17124,7 @@
       </c>
       <c r="E24" s="56"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
       <c r="B25" s="203" t="s">
         <v>226</v>
@@ -17200,7 +17135,7 @@
       </c>
       <c r="E25" s="56"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
       <c r="B26" s="2" t="s">
         <v>228</v>
@@ -17210,7 +17145,7 @@
       </c>
       <c r="E26" s="56"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
       <c r="B27" s="2" t="s">
         <v>474</v>
@@ -17220,7 +17155,7 @@
       </c>
       <c r="E27" s="56"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
       <c r="B28" s="2" t="s">
         <v>475</v>
@@ -17230,7 +17165,7 @@
       </c>
       <c r="E28" s="56"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
       <c r="B29" s="2" t="s">
         <v>476</v>
@@ -17240,7 +17175,7 @@
       </c>
       <c r="E29" s="56"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
       <c r="B30" s="2" t="s">
         <v>477</v>
@@ -17250,7 +17185,7 @@
       </c>
       <c r="E30" s="56"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
       <c r="B31" s="2" t="s">
         <v>478</v>
@@ -17260,7 +17195,7 @@
       </c>
       <c r="E31" s="56"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="25"/>
       <c r="B32" s="2" t="s">
         <v>479</v>
@@ -17270,7 +17205,7 @@
       </c>
       <c r="E32" s="56"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="25"/>
       <c r="B33" s="2" t="s">
         <v>480</v>
@@ -17280,7 +17215,7 @@
       </c>
       <c r="E33" s="56"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
       <c r="B34" s="2" t="s">
         <v>481</v>
@@ -17290,7 +17225,7 @@
       </c>
       <c r="E34" s="56"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
       <c r="B35" s="2" t="s">
         <v>482</v>
@@ -17300,7 +17235,7 @@
       </c>
       <c r="E35" s="56"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="25"/>
       <c r="B36" s="203" t="s">
         <v>483</v>
@@ -17311,7 +17246,7 @@
       </c>
       <c r="E36" s="56"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="25"/>
       <c r="B37" s="2" t="s">
         <v>484</v>
@@ -17321,7 +17256,7 @@
       </c>
       <c r="E37" s="56"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="25"/>
       <c r="B38" s="2" t="s">
         <v>485</v>
@@ -17331,7 +17266,7 @@
       </c>
       <c r="E38" s="56"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="25"/>
       <c r="B39" s="2" t="s">
         <v>486</v>
@@ -17341,7 +17276,7 @@
       </c>
       <c r="E39" s="56"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="25"/>
       <c r="B40" s="2" t="s">
         <v>487</v>
@@ -17351,7 +17286,7 @@
       </c>
       <c r="E40" s="56"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="25"/>
       <c r="B41" s="2" t="s">
         <v>488</v>
@@ -17361,7 +17296,7 @@
       </c>
       <c r="E41" s="56"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="25"/>
       <c r="B42" s="2" t="s">
         <v>489</v>
@@ -17371,7 +17306,7 @@
       </c>
       <c r="E42" s="56"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="25"/>
       <c r="B43" s="2" t="s">
         <v>490</v>
@@ -17381,7 +17316,7 @@
       </c>
       <c r="E43" s="56"/>
     </row>
-    <row r="44" spans="1:5" ht="15.75" thickBot="1">
+    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="61"/>
       <c r="B44" s="2" t="s">
         <v>491</v>
@@ -17391,7 +17326,7 @@
       </c>
       <c r="E44" s="63"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B46" s="189" t="s">
         <v>492</v>
       </c>
@@ -17424,7 +17359,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E74"/>
-  <sheetFormatPr defaultColWidth="3.7109375" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="3.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="2" customWidth="1"/>
@@ -17436,7 +17371,7 @@
     <col min="16345" max="16384" width="3.7109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="53"/>
       <c r="B1" s="66" t="s">
         <v>370</v>
@@ -17449,7 +17384,7 @@
       </c>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>373</v>
       </c>
@@ -17464,7 +17399,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>377</v>
       </c>
@@ -17479,7 +17414,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>380</v>
       </c>
@@ -17494,7 +17429,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>383</v>
       </c>
@@ -17509,7 +17444,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="203" t="s">
         <v>495</v>
@@ -17520,7 +17455,7 @@
       </c>
       <c r="E6" s="56"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="203" t="s">
         <v>496</v>
@@ -17531,7 +17466,7 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" s="1" t="s">
         <v>497</v>
@@ -17542,7 +17477,7 @@
       </c>
       <c r="E8" s="56"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
       <c r="B9" s="1" t="s">
         <v>498</v>
@@ -17553,7 +17488,7 @@
       </c>
       <c r="E9" s="56"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="25"/>
       <c r="B10" s="13" t="s">
         <v>322</v>
@@ -17566,7 +17501,7 @@
       </c>
       <c r="E10" s="56"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
       <c r="B11" s="13" t="s">
         <v>500</v>
@@ -17577,7 +17512,7 @@
       </c>
       <c r="E11" s="56"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="25"/>
       <c r="B12" s="203" t="s">
         <v>65</v>
@@ -17588,7 +17523,7 @@
       </c>
       <c r="E12" s="56"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="51" t="s">
         <v>394</v>
       </c>
@@ -17601,7 +17536,7 @@
       </c>
       <c r="E13" s="56"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" t="s">
         <v>440</v>
@@ -17612,7 +17547,7 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" t="s">
         <v>501</v>
@@ -17623,7 +17558,7 @@
       </c>
       <c r="E15" s="56"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
       <c r="B16" t="s">
         <v>502</v>
@@ -17634,7 +17569,7 @@
       </c>
       <c r="E16" s="56"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="2" t="s">
         <v>443</v>
@@ -17645,7 +17580,7 @@
       </c>
       <c r="E17" s="56"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
       <c r="B18" s="65" t="s">
         <v>190</v>
@@ -17656,7 +17591,7 @@
       </c>
       <c r="E18" s="56"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="25"/>
       <c r="B19" s="2" t="s">
         <v>472</v>
@@ -17667,7 +17602,7 @@
       </c>
       <c r="E19" s="56"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="203" t="s">
         <v>503</v>
@@ -17678,7 +17613,7 @@
       </c>
       <c r="E20" s="56"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="203" t="s">
         <v>504</v>
@@ -17689,7 +17624,7 @@
       </c>
       <c r="E21" s="56"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="25"/>
       <c r="B22" s="28" t="s">
         <v>204</v>
@@ -17700,7 +17635,7 @@
       </c>
       <c r="E22" s="56"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="25"/>
       <c r="B23" t="s">
         <v>505</v>
@@ -17711,7 +17646,7 @@
       </c>
       <c r="E23" s="56"/>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="25"/>
       <c r="B24" s="28" t="s">
         <v>210</v>
@@ -17722,7 +17657,7 @@
       </c>
       <c r="E24" s="56"/>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
       <c r="B25" s="28" t="s">
         <v>216</v>
@@ -17733,7 +17668,7 @@
       </c>
       <c r="E25" s="56"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
       <c r="B26" s="203" t="s">
         <v>506</v>
@@ -17744,7 +17679,7 @@
       </c>
       <c r="E26" s="56"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
       <c r="B27" s="203" t="s">
         <v>220</v>
@@ -17755,7 +17690,7 @@
       </c>
       <c r="E27" s="56"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
       <c r="B28" s="2" t="s">
         <v>393</v>
@@ -17766,7 +17701,7 @@
       </c>
       <c r="E28" s="56"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
       <c r="B29" s="2" t="s">
         <v>395</v>
@@ -17777,7 +17712,7 @@
       </c>
       <c r="E29" s="56"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
       <c r="B30" s="2" t="s">
         <v>226</v>
@@ -17788,7 +17723,7 @@
       </c>
       <c r="E30" s="56"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
       <c r="B31" s="203" t="s">
         <v>507</v>
@@ -17799,7 +17734,7 @@
       </c>
       <c r="E31" s="56"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="25"/>
       <c r="B32" s="203" t="s">
         <v>508</v>
@@ -17810,7 +17745,7 @@
       </c>
       <c r="E32" s="56"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="25"/>
       <c r="B33" s="2" t="s">
         <v>509</v>
@@ -17823,7 +17758,7 @@
       </c>
       <c r="E33" s="56"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
       <c r="B34" s="203" t="s">
         <v>511</v>
@@ -17836,7 +17771,7 @@
       </c>
       <c r="E34" s="56"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
       <c r="B35" s="203" t="s">
         <v>513</v>
@@ -17849,7 +17784,7 @@
       </c>
       <c r="E35" s="56"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="25"/>
       <c r="B36" s="2" t="s">
         <v>514</v>
@@ -17862,7 +17797,7 @@
       </c>
       <c r="E36" s="56"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="25"/>
       <c r="B37" s="2" t="s">
         <v>515</v>
@@ -17875,7 +17810,7 @@
       </c>
       <c r="E37" s="56"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="25"/>
       <c r="B38" s="223" t="s">
         <v>516</v>
@@ -17888,7 +17823,7 @@
       </c>
       <c r="E38" s="56"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="25"/>
       <c r="B39" s="2" t="s">
         <v>518</v>
@@ -17901,7 +17836,7 @@
       </c>
       <c r="E39" s="56"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="25"/>
       <c r="B40" s="203" t="s">
         <v>519</v>
@@ -17914,7 +17849,7 @@
       </c>
       <c r="E40" s="56"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="25"/>
       <c r="B41" s="2" t="s">
         <v>520</v>
@@ -17927,7 +17862,7 @@
       </c>
       <c r="E41" s="56"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="25"/>
       <c r="B42" s="2" t="s">
         <v>521</v>
@@ -17940,7 +17875,7 @@
       </c>
       <c r="E42" s="56"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="25"/>
       <c r="B43" s="2" t="s">
         <v>522</v>
@@ -17953,7 +17888,7 @@
       </c>
       <c r="E43" s="56"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="25"/>
       <c r="B44" s="2" t="s">
         <v>523</v>
@@ -17966,7 +17901,7 @@
       </c>
       <c r="E44" s="56"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="25"/>
       <c r="B45" s="2" t="s">
         <v>524</v>
@@ -17979,7 +17914,7 @@
       </c>
       <c r="E45" s="56"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="25"/>
       <c r="B46" s="2" t="s">
         <v>525</v>
@@ -17992,7 +17927,7 @@
       </c>
       <c r="E46" s="56"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="25"/>
       <c r="B47" s="2" t="s">
         <v>526</v>
@@ -18005,7 +17940,7 @@
       </c>
       <c r="E47" s="56"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="25"/>
       <c r="B48" s="203" t="s">
         <v>527</v>
@@ -18018,7 +17953,7 @@
       </c>
       <c r="E48" s="56"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="25"/>
       <c r="B49" s="203" t="s">
         <v>528</v>
@@ -18031,7 +17966,7 @@
       </c>
       <c r="E49" s="56"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="25"/>
       <c r="B50" s="203" t="s">
         <v>529</v>
@@ -18044,7 +17979,7 @@
       </c>
       <c r="E50" s="56"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="25"/>
       <c r="B51" s="203" t="s">
         <v>530</v>
@@ -18057,7 +17992,7 @@
       </c>
       <c r="E51" s="56"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="25"/>
       <c r="B52" s="2" t="s">
         <v>531</v>
@@ -18070,7 +18005,7 @@
       </c>
       <c r="E52" s="56"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="25"/>
       <c r="B53" s="2" t="s">
         <v>532</v>
@@ -18083,7 +18018,7 @@
       </c>
       <c r="E53" s="56"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="25"/>
       <c r="B54" s="2" t="s">
         <v>533</v>
@@ -18096,7 +18031,7 @@
       </c>
       <c r="E54" s="56"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="25"/>
       <c r="B55" s="2" t="s">
         <v>535</v>
@@ -18109,7 +18044,7 @@
       </c>
       <c r="E55" s="56"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="25"/>
       <c r="B56" s="2" t="s">
         <v>536</v>
@@ -18122,7 +18057,7 @@
       </c>
       <c r="E56" s="56"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="25"/>
       <c r="B57" s="2" t="s">
         <v>537</v>
@@ -18135,7 +18070,7 @@
       </c>
       <c r="E57" s="56"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="25"/>
       <c r="B58" s="2" t="s">
         <v>538</v>
@@ -18148,7 +18083,7 @@
       </c>
       <c r="E58" s="56"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="25"/>
       <c r="B59" s="2" t="s">
         <v>539</v>
@@ -18161,7 +18096,7 @@
       </c>
       <c r="E59" s="56"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="25"/>
       <c r="B60" s="2" t="s">
         <v>540</v>
@@ -18174,7 +18109,7 @@
       </c>
       <c r="E60" s="56"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="25"/>
       <c r="B61" s="2" t="s">
         <v>542</v>
@@ -18187,7 +18122,7 @@
       </c>
       <c r="E61" s="56"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="25"/>
       <c r="B62" s="2" t="s">
         <v>543</v>
@@ -18200,7 +18135,7 @@
       </c>
       <c r="E62" s="56"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="25"/>
       <c r="B63" s="2" t="s">
         <v>544</v>
@@ -18213,7 +18148,7 @@
       </c>
       <c r="E63" s="56"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="25"/>
       <c r="B64" s="2" t="s">
         <v>545</v>
@@ -18226,7 +18161,7 @@
       </c>
       <c r="E64" s="56"/>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="25"/>
       <c r="B65" s="2" t="s">
         <v>546</v>
@@ -18239,7 +18174,7 @@
       </c>
       <c r="E65" s="56"/>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="25"/>
       <c r="B66" s="2" t="s">
         <v>547</v>
@@ -18252,7 +18187,7 @@
       </c>
       <c r="E66" s="56"/>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="25"/>
       <c r="B67" s="2" t="s">
         <v>548</v>
@@ -18265,7 +18200,7 @@
       </c>
       <c r="E67" s="56"/>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="25"/>
       <c r="B68" s="2" t="s">
         <v>549</v>
@@ -18278,7 +18213,7 @@
       </c>
       <c r="E68" s="56"/>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="25"/>
       <c r="B69" s="203" t="s">
         <v>550</v>
@@ -18291,7 +18226,7 @@
       </c>
       <c r="E69" s="56"/>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="25"/>
       <c r="B70" s="2" t="s">
         <v>551</v>
@@ -18304,7 +18239,7 @@
       </c>
       <c r="E70" s="56"/>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="25"/>
       <c r="B71" s="1" t="s">
         <v>552</v>
@@ -18317,7 +18252,7 @@
       </c>
       <c r="E71" s="56"/>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="25"/>
       <c r="B72" t="s">
         <v>553</v>
@@ -18330,7 +18265,7 @@
       </c>
       <c r="E72" s="56"/>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="25"/>
       <c r="B73" s="2" t="s">
         <v>554</v>
@@ -18343,7 +18278,7 @@
       </c>
       <c r="E73" s="56"/>
     </row>
-    <row r="74" spans="1:5" ht="15.75" thickBot="1">
+    <row r="74" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="61"/>
       <c r="B74" s="52" t="s">
         <v>555</v>
@@ -18384,7 +18319,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F46"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="2" customWidth="1"/>
@@ -18396,7 +18331,7 @@
     <col min="16366" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="53"/>
       <c r="B1" s="10" t="s">
         <v>370</v>
@@ -18409,7 +18344,7 @@
       </c>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>373</v>
       </c>
@@ -18426,7 +18361,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>377</v>
       </c>
@@ -18443,7 +18378,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>380</v>
       </c>
@@ -18460,7 +18395,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>383</v>
       </c>
@@ -18477,7 +18412,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="13" t="s">
         <v>559</v>
@@ -18490,7 +18425,7 @@
       </c>
       <c r="E6" s="56"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="203" t="s">
         <v>560</v>
@@ -18503,7 +18438,7 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" s="203" t="s">
         <v>561</v>
@@ -18516,7 +18451,7 @@
       </c>
       <c r="E8" s="56"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
       <c r="B9" s="208" t="s">
         <v>58</v>
@@ -18529,7 +18464,7 @@
       </c>
       <c r="E9" s="56"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="25"/>
       <c r="B10" s="2" t="s">
         <v>54</v>
@@ -18542,7 +18477,7 @@
       </c>
       <c r="E10" s="56"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
       <c r="B11" s="28" t="s">
         <v>563</v>
@@ -18555,7 +18490,7 @@
       </c>
       <c r="E11" s="56"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>394</v>
       </c>
@@ -18570,7 +18505,7 @@
       </c>
       <c r="E12" s="56"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="203" t="s">
         <v>188</v>
@@ -18583,7 +18518,7 @@
       </c>
       <c r="E13" s="56"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="2" t="s">
         <v>564</v>
@@ -18596,7 +18531,7 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" s="2" t="s">
         <v>565</v>
@@ -18609,7 +18544,7 @@
       </c>
       <c r="E15" s="56"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
       <c r="B16" s="2" t="s">
         <v>206</v>
@@ -18622,7 +18557,7 @@
       </c>
       <c r="E16" s="56"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="203" t="s">
         <v>566</v>
@@ -18635,7 +18570,7 @@
       </c>
       <c r="E17" s="56"/>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
       <c r="B18" s="203" t="s">
         <v>218</v>
@@ -18648,7 +18583,7 @@
       </c>
       <c r="E18" s="56"/>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="25"/>
       <c r="B19" t="s">
         <v>567</v>
@@ -18661,7 +18596,7 @@
       </c>
       <c r="E19" s="56"/>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" t="s">
         <v>568</v>
@@ -18674,7 +18609,7 @@
       </c>
       <c r="E20" s="56"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="203" t="s">
         <v>569</v>
@@ -18690,7 +18625,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="25"/>
       <c r="B22" t="s">
         <v>571</v>
@@ -18703,7 +18638,7 @@
       </c>
       <c r="E22" s="56"/>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="25"/>
       <c r="B23" t="s">
         <v>572</v>
@@ -18716,7 +18651,7 @@
       </c>
       <c r="E23" s="56"/>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="25"/>
       <c r="B24" t="s">
         <v>573</v>
@@ -18729,7 +18664,7 @@
       </c>
       <c r="E24" s="56"/>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
       <c r="B25" t="s">
         <v>574</v>
@@ -18742,7 +18677,7 @@
       </c>
       <c r="E25" s="56"/>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
       <c r="B26" t="s">
         <v>575</v>
@@ -18755,7 +18690,7 @@
       </c>
       <c r="E26" s="56"/>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
       <c r="B27" t="s">
         <v>576</v>
@@ -18768,7 +18703,7 @@
       </c>
       <c r="E27" s="56"/>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
       <c r="B28" s="1" t="s">
         <v>577</v>
@@ -18781,7 +18716,7 @@
       </c>
       <c r="E28" s="56"/>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
       <c r="B29" s="203" t="s">
         <v>578</v>
@@ -18794,7 +18729,7 @@
       </c>
       <c r="E29" s="56"/>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
       <c r="B30" s="203" t="s">
         <v>579</v>
@@ -18807,7 +18742,7 @@
       </c>
       <c r="E30" s="56"/>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
       <c r="B31" t="s">
         <v>580</v>
@@ -18820,7 +18755,7 @@
       </c>
       <c r="E31" s="56"/>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="25"/>
       <c r="B32" s="1" t="s">
         <v>581</v>
@@ -18833,7 +18768,7 @@
       </c>
       <c r="E32" s="56"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="25"/>
       <c r="B33" t="s">
         <v>583</v>
@@ -18846,7 +18781,7 @@
       </c>
       <c r="E33" s="56"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
       <c r="B34" s="1" t="s">
         <v>585</v>
@@ -18859,7 +18794,7 @@
       </c>
       <c r="E34" s="56"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
       <c r="B35" s="1" t="s">
         <v>587</v>
@@ -18872,7 +18807,7 @@
       </c>
       <c r="E35" s="56"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="25"/>
       <c r="B36" s="203" t="s">
         <v>588</v>
@@ -18885,7 +18820,7 @@
       </c>
       <c r="E36" s="56"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="25"/>
       <c r="B37" s="203" t="s">
         <v>590</v>
@@ -18898,7 +18833,7 @@
       </c>
       <c r="E37" s="56"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="25"/>
       <c r="B38" s="1" t="s">
         <v>591</v>
@@ -18911,7 +18846,7 @@
       </c>
       <c r="E38" s="56"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="25"/>
       <c r="B39" s="203" t="s">
         <v>592</v>
@@ -18924,7 +18859,7 @@
       </c>
       <c r="E39" s="56"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="25"/>
       <c r="B40" s="203" t="s">
         <v>593</v>
@@ -18937,7 +18872,7 @@
       </c>
       <c r="E40" s="56"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="25"/>
       <c r="B41" s="203" t="s">
         <v>594</v>
@@ -18950,7 +18885,7 @@
       </c>
       <c r="E41" s="56"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="25"/>
       <c r="B42" s="203" t="s">
         <v>595</v>
@@ -18963,7 +18898,7 @@
       </c>
       <c r="E42" s="56"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="25"/>
       <c r="B43" s="203" t="s">
         <v>596</v>
@@ -18976,7 +18911,7 @@
       </c>
       <c r="E43" s="56"/>
     </row>
-    <row r="44" spans="1:5" ht="15.75" thickBot="1">
+    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="61"/>
       <c r="B44" s="203" t="s">
         <v>597</v>
@@ -18989,10 +18924,10 @@
       </c>
       <c r="E44" s="63"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C45" s="216"/>
     </row>
-    <row r="46" spans="1:5" ht="30">
+    <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="B46" s="230" t="s">
         <v>598</v>
       </c>
@@ -19025,7 +18960,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="2" customWidth="1"/>
@@ -19037,7 +18972,7 @@
     <col min="16362" max="16384" width="11.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="53"/>
       <c r="B1" s="66" t="s">
         <v>370</v>
@@ -19050,7 +18985,7 @@
       </c>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>373</v>
       </c>
@@ -19065,7 +19000,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>377</v>
       </c>
@@ -19079,7 +19014,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>380</v>
       </c>
@@ -19094,7 +19029,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>383</v>
       </c>
@@ -19109,7 +19044,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="202" t="s">
         <v>601</v>
@@ -19119,7 +19054,7 @@
       </c>
       <c r="E6" s="56"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="203" t="s">
         <v>602</v>
@@ -19130,7 +19065,7 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" t="s">
         <v>173</v>
@@ -19141,7 +19076,7 @@
       </c>
       <c r="E8" s="56"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
       <c r="B9" t="s">
         <v>177</v>
@@ -19151,7 +19086,7 @@
       </c>
       <c r="E9" s="56"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="25"/>
       <c r="B10" t="s">
         <v>603</v>
@@ -19161,7 +19096,7 @@
       </c>
       <c r="E10" s="56"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
       <c r="B11" t="s">
         <v>444</v>
@@ -19171,7 +19106,7 @@
       </c>
       <c r="E11" s="56"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>394</v>
       </c>
@@ -19183,7 +19118,7 @@
       </c>
       <c r="E12" s="56"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="1" t="s">
         <v>395</v>
@@ -19193,7 +19128,7 @@
       </c>
       <c r="E13" s="56"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="2" t="s">
         <v>226</v>
@@ -19203,7 +19138,7 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" t="s">
         <v>604</v>
@@ -19213,7 +19148,7 @@
       </c>
       <c r="E15" s="56"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
       <c r="B16" s="199" t="s">
         <v>605</v>
@@ -19223,7 +19158,7 @@
       </c>
       <c r="E16" s="56"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="28" t="s">
         <v>606</v>
@@ -19233,7 +19168,7 @@
       </c>
       <c r="E17" s="56"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" thickBot="1">
+    <row r="18" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="61"/>
       <c r="B18" s="52" t="s">
         <v>607</v>
@@ -19273,7 +19208,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E49"/>
-  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
     <col min="2" max="2" width="34.140625" style="2" customWidth="1"/>
@@ -19285,7 +19220,7 @@
     <col min="16240" max="16384" width="10.28515625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="53"/>
       <c r="B1" s="19" t="s">
         <v>370</v>
@@ -19298,7 +19233,7 @@
       </c>
       <c r="E1" s="50"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="54" t="s">
         <v>373</v>
       </c>
@@ -19315,7 +19250,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="51" t="s">
         <v>377</v>
       </c>
@@ -19332,7 +19267,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="51" t="s">
         <v>380</v>
       </c>
@@ -19349,7 +19284,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="51" t="s">
         <v>383</v>
       </c>
@@ -19366,7 +19301,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="211" t="s">
         <v>612</v>
@@ -19379,7 +19314,7 @@
       </c>
       <c r="E6" s="56"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="20" t="s">
         <v>615</v>
@@ -19392,7 +19327,7 @@
       </c>
       <c r="E7" s="56"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="25"/>
       <c r="B8" s="20" t="s">
         <v>615</v>
@@ -19405,7 +19340,7 @@
       </c>
       <c r="E8" s="56"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="25"/>
       <c r="B9" s="229" t="s">
         <v>146</v>
@@ -19418,7 +19353,7 @@
       </c>
       <c r="E9" s="56"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="25"/>
       <c r="B10" s="30" t="s">
         <v>617</v>
@@ -19431,7 +19366,7 @@
       </c>
       <c r="E10" s="56"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="25"/>
       <c r="B11" s="30" t="s">
         <v>617</v>
@@ -19444,7 +19379,7 @@
       </c>
       <c r="E11" s="56"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="51" t="s">
         <v>394</v>
       </c>
@@ -19459,7 +19394,7 @@
       </c>
       <c r="E12" s="56"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="30" t="s">
         <v>620</v>
@@ -19472,7 +19407,7 @@
       </c>
       <c r="E13" s="56"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="25"/>
       <c r="B14" s="30" t="s">
         <v>620</v>
@@ -19485,7 +19420,7 @@
       </c>
       <c r="E14" s="56"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="25"/>
       <c r="B15" s="229" t="s">
         <v>621</v>
@@ -19498,7 +19433,7 @@
       </c>
       <c r="E15" s="56"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="25"/>
       <c r="B16" s="229" t="s">
         <v>621</v>
@@ -19511,7 +19446,7 @@
       </c>
       <c r="E16" s="56"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="25"/>
       <c r="B17" s="30" t="s">
         <v>620</v>
@@ -19524,7 +19459,7 @@
       </c>
       <c r="E17" s="56"/>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="25"/>
       <c r="B18" s="211" t="s">
         <v>612</v>
@@ -19537,7 +19472,7 @@
       </c>
       <c r="E18" s="56"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="25"/>
       <c r="B19" s="223" t="s">
         <v>624</v>
@@ -19548,7 +19483,7 @@
       <c r="D19" s="57"/>
       <c r="E19" s="56"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="25"/>
       <c r="B20" s="203" t="s">
         <v>143</v>
@@ -19561,7 +19496,7 @@
       </c>
       <c r="E20" s="56"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="25"/>
       <c r="B21" s="203" t="s">
         <v>626</v>
@@ -19571,7 +19506,7 @@
       </c>
       <c r="E21" s="56"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="25"/>
       <c r="B22" s="58" t="s">
         <v>75</v>
@@ -19581,7 +19516,7 @@
       </c>
       <c r="E22" s="56"/>
     </row>
-    <row r="23" spans="1:5" ht="14.25" customHeight="1">
+    <row r="23" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="25"/>
       <c r="B23" s="59" t="s">
         <v>82</v>
@@ -19592,7 +19527,7 @@
       </c>
       <c r="E23" s="56"/>
     </row>
-    <row r="24" spans="1:5" ht="15.75" customHeight="1">
+    <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="25"/>
       <c r="B24" s="59" t="s">
         <v>85</v>
@@ -19603,7 +19538,7 @@
       </c>
       <c r="E24" s="56"/>
     </row>
-    <row r="25" spans="1:5" ht="15" customHeight="1">
+    <row r="25" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="25"/>
       <c r="B25" s="59" t="s">
         <v>87</v>
@@ -19614,7 +19549,7 @@
       </c>
       <c r="E25" s="56"/>
     </row>
-    <row r="26" spans="1:5" ht="14.25" customHeight="1">
+    <row r="26" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
       <c r="B26" s="59" t="s">
         <v>89</v>
@@ -19625,7 +19560,7 @@
       </c>
       <c r="E26" s="56"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="25"/>
       <c r="B27" s="202" t="s">
         <v>44</v>
@@ -19635,7 +19570,7 @@
       </c>
       <c r="E27" s="56"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
       <c r="B28" t="s">
         <v>173</v>
@@ -19646,7 +19581,7 @@
       </c>
       <c r="E28" s="56"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="25"/>
       <c r="B29" t="s">
         <v>177</v>
@@ -19657,7 +19592,7 @@
       </c>
       <c r="E29" s="56"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="25"/>
       <c r="B30" s="18" t="s">
         <v>603</v>
@@ -19668,7 +19603,7 @@
       </c>
       <c r="E30" s="56"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="25"/>
       <c r="B31" s="18" t="s">
         <v>444</v>
@@ -19679,7 +19614,7 @@
       </c>
       <c r="E31" s="56"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="25"/>
       <c r="B32" s="18" t="s">
         <v>220</v>
@@ -19690,7 +19625,7 @@
       </c>
       <c r="E32" s="56"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="25"/>
       <c r="B33" s="18" t="s">
         <v>393</v>
@@ -19701,7 +19636,7 @@
       </c>
       <c r="E33" s="56"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="25"/>
       <c r="B34" s="18" t="s">
         <v>395</v>
@@ -19712,7 +19647,7 @@
       </c>
       <c r="E34" s="56"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="25"/>
       <c r="B35" s="18" t="s">
         <v>226</v>
@@ -19723,7 +19658,7 @@
       </c>
       <c r="E35" s="56"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="25"/>
       <c r="B36" s="229" t="s">
         <v>47</v>
@@ -19736,7 +19671,7 @@
       </c>
       <c r="E36" s="56"/>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1">
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="25"/>
       <c r="B37" s="229" t="s">
         <v>50</v>
@@ -19749,7 +19684,7 @@
       </c>
       <c r="E37" s="56"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="25"/>
       <c r="B38" s="25" t="s">
         <v>628</v>
@@ -19762,7 +19697,7 @@
       </c>
       <c r="E38" s="56"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="25"/>
       <c r="B39" s="229" t="s">
         <v>91</v>
@@ -19775,7 +19710,7 @@
       </c>
       <c r="E39" s="56"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="25"/>
       <c r="B40" s="17" t="s">
         <v>630</v>
@@ -19788,7 +19723,7 @@
       </c>
       <c r="E40" s="56"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="25"/>
       <c r="B41" s="229" t="s">
         <v>130</v>
@@ -19801,7 +19736,7 @@
       </c>
       <c r="E41" s="56"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="25"/>
       <c r="B42" s="2" t="s">
         <v>78</v>
@@ -19814,7 +19749,7 @@
       </c>
       <c r="E42" s="56"/>
     </row>
-    <row r="43" spans="1:5" ht="16.5" customHeight="1">
+    <row r="43" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="25"/>
       <c r="B43" t="s">
         <v>634</v>
@@ -19827,7 +19762,7 @@
       </c>
       <c r="E43" s="56"/>
     </row>
-    <row r="44" spans="1:5" ht="16.5" customHeight="1">
+    <row r="44" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="25"/>
       <c r="B44" t="s">
         <v>636</v>
@@ -19840,7 +19775,7 @@
       </c>
       <c r="E44" s="56"/>
     </row>
-    <row r="45" spans="1:5" ht="16.5" customHeight="1">
+    <row r="45" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="25"/>
       <c r="B45" s="203" t="s">
         <v>638</v>
@@ -19853,7 +19788,7 @@
       </c>
       <c r="E45" s="56"/>
     </row>
-    <row r="46" spans="1:5" ht="16.5" customHeight="1" thickBot="1">
+    <row r="46" spans="1:5" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="61"/>
       <c r="B46" s="49" t="s">
         <v>640</v>
@@ -19866,7 +19801,7 @@
       </c>
       <c r="E46" s="63"/>
     </row>
-    <row r="48" spans="1:5" ht="60">
+    <row r="48" spans="1:5" ht="60" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
         <v>641</v>
       </c>
@@ -19877,7 +19812,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="2" t="s">
         <v>644</v>
       </c>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1845" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{21D22F4F-3B6A-4970-94E5-DE7CA83335BD}"/>
+  <xr:revisionPtr revIDLastSave="1877" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FBC7149C-F2B3-427F-8F05-5BCD2749B10E}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="885">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1682" uniqueCount="897">
   <si>
     <t>Type</t>
   </si>
@@ -2347,6 +2347,9 @@
     <t>Macro</t>
   </si>
   <si>
+    <t>notes</t>
+  </si>
+  <si>
     <t>Bed mesh compensation</t>
   </si>
   <si>
@@ -2356,6 +2359,18 @@
     <t>G29</t>
   </si>
   <si>
+    <t xml:space="preserve">Adaptive bed mesh </t>
+  </si>
+  <si>
+    <t>adaptive_mesh</t>
+  </si>
+  <si>
+    <t>G29 but will just bed mesh around the part thats being printed</t>
+  </si>
+  <si>
+    <t>add "adaptive mesh settings" from the  gcode.text  file in config</t>
+  </si>
+  <si>
     <t xml:space="preserve">filament change  </t>
   </si>
   <si>
@@ -2377,7 +2392,7 @@
     <t>Homing startup</t>
   </si>
   <si>
-    <t>home_startup</t>
+    <t>startup_sequence</t>
   </si>
   <si>
     <t xml:space="preserve">Initial  setup at machine turn on, Home X,Y, ask if you want to home Z  </t>
@@ -2413,7 +2428,10 @@
     <t>Clean tne nozzle by wiping over silicon wafer</t>
   </si>
   <si>
-    <t>Z homing high</t>
+    <t>already don in nozzle_brush</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z homing at bottom of printer </t>
   </si>
   <si>
     <t>z_home_max</t>
@@ -2447,6 +2465,24 @@
   </si>
   <si>
     <t>Drop off the flint zone probe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">move nozzel  over bucket </t>
+  </si>
+  <si>
+    <t>park_bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">park nozzle over bucket </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Measure distance between probe and nozzel tip </t>
+  </si>
+  <si>
+    <t>AnvilZoffset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculates offset </t>
   </si>
   <si>
     <t>G32</t>
@@ -2726,7 +2762,7 @@
     <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
   </numFmts>
-  <fonts count="43">
+  <fonts count="44">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3014,6 +3050,12 @@
       <sz val="11"/>
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -3337,7 +3379,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="299">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
@@ -3966,15 +4008,6 @@
     <xf numFmtId="0" fontId="29" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -3988,6 +4021,19 @@
     <xf numFmtId="1" fontId="14" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -6288,26 +6334,26 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{08A74962-DE02-40B7-84D1-EBA03C7907E7}" name="Table3" displayName="Table3" ref="A1:D13" totalsRowShown="0">
-  <autoFilter ref="A1:D13" xr:uid="{08A74962-DE02-40B7-84D1-EBA03C7907E7}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C13">
-    <sortCondition ref="A1:A13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{08A74962-DE02-40B7-84D1-EBA03C7907E7}" name="Table3" displayName="Table3" ref="A1:D15" totalsRowShown="0">
+  <autoFilter ref="A1:D15" xr:uid="{08A74962-DE02-40B7-84D1-EBA03C7907E7}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C15">
+    <sortCondition ref="A1:A15"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{E1FF070C-6993-4332-802B-B4D29E1606E7}" name="Function"/>
     <tableColumn id="2" xr3:uid="{54776E09-074A-46D8-A8AF-0675792CABF2}" name="Macro" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{8FBB1689-4854-43C5-AC93-F6E571CF242D}" name="Description"/>
-    <tableColumn id="4" xr3:uid="{8BF21A82-1921-4BE2-9EDE-151E7264E122}" name="Column1"/>
+    <tableColumn id="4" xr3:uid="{8BF21A82-1921-4BE2-9EDE-151E7264E122}" name="notes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{22CC0901-A1E8-42BF-83D2-CD8909D9E84D}" name="Table4" displayName="Table4" ref="A19:D39" totalsRowShown="0">
-  <autoFilter ref="A19:D39" xr:uid="{22CC0901-A1E8-42BF-83D2-CD8909D9E84D}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A20:C39">
-    <sortCondition ref="B19:B39"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{22CC0901-A1E8-42BF-83D2-CD8909D9E84D}" name="Table4" displayName="Table4" ref="A21:D41" totalsRowShown="0">
+  <autoFilter ref="A21:D41" xr:uid="{22CC0901-A1E8-42BF-83D2-CD8909D9E84D}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A22:C41">
+    <sortCondition ref="B21:B41"/>
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{72FB4F94-B23A-4D8C-9115-4A4A22828CD8}" name="Function"/>
@@ -6320,8 +6366,8 @@
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{65AAB1FE-3FF5-4932-83DF-59F4C29F97F6}" name="Table5" displayName="Table5" ref="A41:C47" totalsRowShown="0">
-  <autoFilter ref="A41:C47" xr:uid="{65AAB1FE-3FF5-4932-83DF-59F4C29F97F6}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{65AAB1FE-3FF5-4932-83DF-59F4C29F97F6}" name="Table5" displayName="Table5" ref="A43:C49" totalsRowShown="0">
+  <autoFilter ref="A43:C49" xr:uid="{65AAB1FE-3FF5-4932-83DF-59F4C29F97F6}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E54889A3-633F-4685-B8E1-B4DB7E01A94A}" name="Printer code"/>
     <tableColumn id="2" xr3:uid="{9B5CA5FD-9D48-460B-8000-5A3DECA0A58C}" name="Machine Gcode"/>
@@ -6332,8 +6378,8 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{255B9BA2-9874-4909-AB93-96FB850EFBDB}" name="Table58" displayName="Table58" ref="A52:C62" totalsRowShown="0">
-  <autoFilter ref="A52:C62" xr:uid="{255B9BA2-9874-4909-AB93-96FB850EFBDB}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{255B9BA2-9874-4909-AB93-96FB850EFBDB}" name="Table58" displayName="Table58" ref="A54:C64" totalsRowShown="0">
+  <autoFilter ref="A54:C64" xr:uid="{255B9BA2-9874-4909-AB93-96FB850EFBDB}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D1A0D768-AEE9-4B9C-AC96-95895F8F742C}" name="Printer code"/>
     <tableColumn id="2" xr3:uid="{646EABC4-F408-4AD0-8ED9-44B19D7B9F30}" name="Filaments"/>
@@ -7238,27 +7284,27 @@
       <c r="M16" s="141"/>
     </row>
     <row r="17" spans="1:13">
-      <c r="A17" s="293" t="s">
+      <c r="A17" s="290" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="296" t="s">
+      <c r="B17" s="293" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="287"/>
-      <c r="D17" s="294">
+      <c r="D17" s="291">
         <v>1</v>
       </c>
       <c r="E17" s="160">
         <v>1</v>
       </c>
-      <c r="F17" s="295">
+      <c r="F17" s="292">
         <v>3.9</v>
       </c>
       <c r="G17" s="206">
         <f>E17*F17</f>
         <v>3.9</v>
       </c>
-      <c r="H17" s="297" t="s">
+      <c r="H17" s="294" t="s">
         <v>53</v>
       </c>
       <c r="I17" s="255" t="s">
@@ -8417,7 +8463,7 @@
       <c r="H51" s="175" t="s">
         <v>126</v>
       </c>
-      <c r="I51" s="298"/>
+      <c r="I51" s="300"/>
       <c r="J51" s="103"/>
       <c r="K51" s="12"/>
       <c r="L51" s="72"/>
@@ -8447,7 +8493,7 @@
       <c r="H52" s="175" t="s">
         <v>127</v>
       </c>
-      <c r="I52" s="298"/>
+      <c r="I52" s="300"/>
       <c r="J52" s="103"/>
       <c r="K52" s="12"/>
       <c r="L52" s="72"/>
@@ -8811,7 +8857,7 @@
       <c r="H63" s="145" t="s">
         <v>156</v>
       </c>
-      <c r="I63" s="298"/>
+      <c r="I63" s="300"/>
       <c r="J63" s="103"/>
       <c r="K63" s="12"/>
       <c r="L63" s="72"/>
@@ -14287,12 +14333,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6">
-      <c r="B1" s="290" t="s">
+      <c r="B1" s="295" t="s">
         <v>691</v>
       </c>
-      <c r="C1" s="291"/>
-      <c r="D1" s="291"/>
-      <c r="E1" s="292"/>
+      <c r="C1" s="296"/>
+      <c r="D1" s="296"/>
+      <c r="E1" s="297"/>
       <c r="F1" s="42"/>
     </row>
     <row r="2" spans="2:6">
@@ -14836,13 +14882,13 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="27" customWidth="1"/>
+    <col min="1" max="1" width="44.28515625" customWidth="1"/>
     <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="83.42578125" customWidth="1"/>
-    <col min="4" max="4" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -14856,141 +14902,171 @@
         <v>374</v>
       </c>
       <c r="D1" t="s">
-        <v>12</v>
+        <v>763</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B2" s="42" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C2" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>766</v>
-      </c>
-      <c r="B3" s="58" t="s">
         <v>767</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="42" t="s">
         <v>768</v>
+      </c>
+      <c r="C3" t="s">
+        <v>769</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>770</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18.75" customHeight="1">
       <c r="A4" t="s">
-        <v>769</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>770</v>
+        <v>771</v>
+      </c>
+      <c r="B4" s="58" t="s">
+        <v>772</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B5" s="42" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B6" s="42" t="s">
-        <v>776</v>
-      </c>
-      <c r="C6" t="s">
-        <v>777</v>
+        <v>778</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="12" customHeight="1">
       <c r="A7" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B7" s="42" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C7" t="s">
-        <v>780</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
         <v>782</v>
       </c>
-      <c r="B8" s="42" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="12.75" customHeight="1">
+      <c r="A8" s="137" t="s">
         <v>783</v>
       </c>
-      <c r="C8" t="s">
+      <c r="B8" s="138" t="s">
         <v>784</v>
       </c>
+      <c r="C8" s="137" t="s">
+        <v>785</v>
+      </c>
+      <c r="D8" s="298" t="s">
+        <v>786</v>
+      </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>785</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>786</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="A9" s="137" t="s">
         <v>787</v>
+      </c>
+      <c r="B9" s="138" t="s">
+        <v>788</v>
+      </c>
+      <c r="C9" s="137" t="s">
+        <v>789</v>
+      </c>
+      <c r="D9" t="s">
+        <v>790</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B10" s="42" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C10" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B11" s="42" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C11" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="B12" s="42" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C12" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="B13" s="42"/>
+      <c r="A13" t="s">
+        <v>800</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>801</v>
+      </c>
+      <c r="C13" t="s">
+        <v>802</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="B14" s="42"/>
+      <c r="A14" t="s">
+        <v>803</v>
+      </c>
+      <c r="B14" s="299" t="s">
+        <v>804</v>
+      </c>
+      <c r="C14" t="s">
+        <v>805</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="B15" s="42"/>
+      <c r="A15" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="B15" s="42" t="s">
+        <v>807</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>808</v>
+      </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="42"/>
@@ -15002,357 +15078,363 @@
       <c r="B18" s="42"/>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" t="s">
+      <c r="B19" s="42"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="B20" s="42"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
         <v>761</v>
       </c>
-      <c r="B19" s="102" t="s">
+      <c r="B21" s="102" t="s">
         <v>656</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C21" t="s">
         <v>374</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D21" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>797</v>
-      </c>
-      <c r="B20" s="42" t="s">
-        <v>798</v>
-      </c>
-      <c r="C20" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="B21" s="42" t="s">
-        <v>800</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>801</v>
-      </c>
-    </row>
     <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>809</v>
+      </c>
       <c r="B22" s="42" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="C22" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="42" t="s">
-        <v>804</v>
-      </c>
-      <c r="C23" t="s">
-        <v>805</v>
+        <v>812</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>813</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="42" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="C24" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="42" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="C25" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="137"/>
-      <c r="B26" s="138" t="s">
-        <v>810</v>
-      </c>
-      <c r="C26" s="137" t="s">
-        <v>811</v>
-      </c>
-      <c r="D26" t="s">
-        <v>812</v>
+      <c r="B26" s="42" t="s">
+        <v>818</v>
+      </c>
+      <c r="C26" t="s">
+        <v>819</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="B27" s="42" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="C27" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>815</v>
-      </c>
-      <c r="B28" s="42" t="s">
-        <v>816</v>
-      </c>
-      <c r="C28" t="s">
-        <v>817</v>
+      <c r="A28" s="137"/>
+      <c r="B28" s="138" t="s">
+        <v>822</v>
+      </c>
+      <c r="C28" s="137" t="s">
+        <v>823</v>
       </c>
       <c r="D28" t="s">
-        <v>818</v>
+        <v>824</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="42" t="s">
-        <v>819</v>
+        <v>825</v>
       </c>
       <c r="C29" t="s">
-        <v>820</v>
+        <v>826</v>
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>821</v>
-      </c>
-      <c r="B30" s="42" t="s">
-        <v>822</v>
-      </c>
-      <c r="C30" t="s">
-        <v>823</v>
+      <c r="A30" s="137" t="s">
+        <v>827</v>
+      </c>
+      <c r="B30" s="138" t="s">
+        <v>828</v>
+      </c>
+      <c r="C30" s="137" t="s">
+        <v>829</v>
+      </c>
+      <c r="D30" s="137" t="s">
+        <v>830</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="B31" s="42" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="C31" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
     </row>
     <row r="32" spans="1:4">
+      <c r="A32" t="s">
+        <v>833</v>
+      </c>
       <c r="B32" s="42" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="C32" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="B33" s="42" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="C33" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>765</v>
-      </c>
       <c r="B34" s="42" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="C34" t="s">
-        <v>831</v>
-      </c>
-      <c r="D34" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="B35" s="42" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="C35" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
     </row>
     <row r="36" spans="1:4">
+      <c r="A36" t="s">
+        <v>766</v>
+      </c>
       <c r="B36" s="42" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="C36" t="s">
-        <v>836</v>
+        <v>843</v>
+      </c>
+      <c r="D36" t="s">
+        <v>844</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="B37" s="42" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="C37" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="B38" s="42" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="C38" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="B39" s="42"/>
+      <c r="B39" s="42" t="s">
+        <v>849</v>
+      </c>
+      <c r="C39" t="s">
+        <v>850</v>
+      </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="B40" s="42"/>
+      <c r="B40" s="42" t="s">
+        <v>851</v>
+      </c>
+      <c r="C40" t="s">
+        <v>852</v>
+      </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>841</v>
-      </c>
-      <c r="B41" s="64" t="s">
-        <v>842</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B41" s="42"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="B42" s="42"/>
+    </row>
+    <row r="43" spans="1:4">
+      <c r="A43" t="s">
+        <v>853</v>
+      </c>
+      <c r="B43" s="64" t="s">
+        <v>854</v>
+      </c>
+      <c r="C43" t="s">
         <v>374</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="B42" t="s">
-        <v>843</v>
-      </c>
-      <c r="C42" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="B43" t="s">
-        <v>845</v>
-      </c>
-      <c r="C43" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="B44" t="s">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="C44" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="B45" t="s">
-        <v>847</v>
+        <v>857</v>
       </c>
       <c r="C45" t="s">
-        <v>844</v>
+        <v>856</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
+      <c r="B46" t="s">
+        <v>858</v>
+      </c>
+      <c r="C46" t="s">
+        <v>856</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="B47" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="C47" t="s">
-        <v>844</v>
-      </c>
-      <c r="D47" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="D48" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="B49" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="B50" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
-      <c r="A52" t="s">
-        <v>841</v>
-      </c>
-      <c r="B52" s="64" t="s">
+        <v>860</v>
+      </c>
+      <c r="C49" t="s">
+        <v>856</v>
+      </c>
+      <c r="D49" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
+      <c r="D50" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="B51" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="B52" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
         <v>853</v>
       </c>
-      <c r="C52" t="s">
+      <c r="B54" s="64" t="s">
+        <v>865</v>
+      </c>
+      <c r="C54" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="53" spans="1:3">
-      <c r="B53" t="s">
-        <v>854</v>
-      </c>
-      <c r="C53" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
-      <c r="B54" t="s">
-        <v>855</v>
-      </c>
-      <c r="C54" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+    <row r="55" spans="1:4">
       <c r="B55" t="s">
+        <v>866</v>
+      </c>
+      <c r="C55" t="s">
         <v>856</v>
       </c>
-      <c r="C55" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+    </row>
+    <row r="56" spans="1:4">
       <c r="B56" t="s">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="C56" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="B57" t="s">
-        <v>858</v>
+        <v>868</v>
       </c>
       <c r="C57" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="B58" t="s">
-        <v>859</v>
+        <v>869</v>
       </c>
       <c r="C58" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="B59" t="s">
-        <v>860</v>
+        <v>870</v>
       </c>
       <c r="C59" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="B60" t="s">
-        <v>862</v>
+        <v>871</v>
       </c>
       <c r="C60" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="B61" t="s">
-        <v>863</v>
+        <v>872</v>
       </c>
       <c r="C61" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="B62" t="s">
-        <v>864</v>
+        <v>874</v>
       </c>
       <c r="C62" t="s">
-        <v>844</v>
+        <v>856</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="B63" t="s">
+        <v>875</v>
+      </c>
+      <c r="C63" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="B64" t="s">
+        <v>876</v>
+      </c>
+      <c r="C64" t="s">
+        <v>856</v>
       </c>
     </row>
   </sheetData>
@@ -15383,7 +15465,7 @@
         <v>373</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>374</v>
@@ -15392,83 +15474,83 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
       <c r="B2" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
       <c r="C2" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
       <c r="D2" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
       <c r="E2" s="118" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
       <c r="C3" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" customHeight="1">
       <c r="A6" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
       <c r="C12" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
     </row>
   </sheetData>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30015"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3117" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51833C24-4B78-4AE7-8DBA-B4EBCFA16725}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -3361,14 +3361,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
-    <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="169" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+    <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
   </numFmts>
   <fonts count="66">
     <font>
@@ -4142,7 +4142,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="303">
+  <cellXfs count="301">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2"/>
@@ -4169,7 +4169,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4209,10 +4209,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -4279,13 +4279,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4345,9 +4345,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4358,7 +4358,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4409,7 +4409,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4497,7 +4497,7 @@
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4530,7 +4530,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="8" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
@@ -4552,7 +4552,7 @@
     <xf numFmtId="3" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="21" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
@@ -4568,7 +4568,7 @@
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4696,7 +4696,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="6" fontId="2" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12" applyProtection="1">
@@ -4785,30 +4785,26 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="12"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5129,13 +5125,6 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -5177,6 +5166,13 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5204,54 +5200,20 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5271,10 +5233,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5406,9 +5364,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5425,6 +5380,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5483,9 +5441,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5502,6 +5457,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5560,9 +5518,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5579,6 +5534,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5637,9 +5595,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5656,6 +5611,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5714,9 +5672,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5733,6 +5688,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5791,9 +5749,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5810,6 +5765,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5884,9 +5842,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5903,6 +5858,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5961,9 +5919,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5980,6 +5935,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6273,7 +6231,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6298,7 +6256,7 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6373,13 +6331,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="medium">
           <color rgb="FF000000"/>
@@ -6398,6 +6349,51 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border>
@@ -7400,67 +7396,67 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M152" totalsRowShown="0" dataDxfId="102" headerRowBorderDxfId="100" tableBorderDxfId="101" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M152" totalsRowShown="0" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:M152" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L152">
     <sortCondition ref="A1:A152"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="99"/>
-    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="98"/>
-    <tableColumn id="1" xr3:uid="{277C1F1F-DAAE-4C91-9EDC-C8D501677DE9}" name="Cut length" dataDxfId="97" dataCellStyle="Normal 7"/>
-    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="96"/>
-    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="95"/>
-    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="94"/>
-    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="93">
+    <tableColumn id="3" xr3:uid="{E596F2F7-CDFF-486E-86F5-053FDD2A2A5C}" name="Type" dataDxfId="97"/>
+    <tableColumn id="4" xr3:uid="{21BB2F02-45DC-4E39-9123-FC046A8DFC11}" name="Part" dataDxfId="96"/>
+    <tableColumn id="1" xr3:uid="{277C1F1F-DAAE-4C91-9EDC-C8D501677DE9}" name="Cut length" dataDxfId="95" dataCellStyle="Normal 7"/>
+    <tableColumn id="7" xr3:uid="{47852F97-FC81-4943-BFF5-71D7E867A237}" name="Qty Required" dataDxfId="94"/>
+    <tableColumn id="5" xr3:uid="{5C2A44A8-DE4F-4B5A-930C-443716E7E898}" name="Pack Order Qty" dataDxfId="93"/>
+    <tableColumn id="8" xr3:uid="{07FAA242-B582-4790-9720-A5DC124D6B2D}" name="Pack Price $USD" dataDxfId="92"/>
+    <tableColumn id="10" xr3:uid="{B3F33643-2531-4917-B84D-BE4983A99A8C}" name="*Cost Price $USD" dataDxfId="91">
       <calculatedColumnFormula>E2*F2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="92" dataCellStyle="Hyperlink"/>
-    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="91"/>
-    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Qty in a Pack" dataDxfId="90" dataCellStyle="Hyperlink"/>
-    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN" dataDxfId="89"/>
-    <tableColumn id="14" xr3:uid="{63E8BC06-DC55-407C-B167-F3CA5B6EBA86}" name="ISO" dataDxfId="88"/>
-    <tableColumn id="6" xr3:uid="{20868F13-EF4A-4C62-958A-6FEB2EB595D7}" name="Column1" dataDxfId="87"/>
+    <tableColumn id="2" xr3:uid="{2B3304EF-95F3-4EA3-9A24-E520BCF247B0}" name="Order Link" dataDxfId="90" dataCellStyle="Hyperlink"/>
+    <tableColumn id="12" xr3:uid="{53A14610-D497-4DD1-8CFF-F20E191D3317}" name="Supplier" dataDxfId="89"/>
+    <tableColumn id="11" xr3:uid="{A7F10A10-A127-43E0-B65C-9F538B8DD15E}" name="Qty in a Pack" dataDxfId="88" dataCellStyle="Hyperlink"/>
+    <tableColumn id="13" xr3:uid="{DE4564AA-6825-49A5-B67A-A550AFECDCA7}" name="DIN" dataDxfId="87"/>
+    <tableColumn id="14" xr3:uid="{63E8BC06-DC55-407C-B167-F3CA5B6EBA86}" name="ISO" dataDxfId="86"/>
+    <tableColumn id="6" xr3:uid="{20868F13-EF4A-4C62-958A-6FEB2EB595D7}" name="Column1" dataDxfId="85"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D51" totalsRowShown="0" headerRowDxfId="37" tableBorderDxfId="36" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{604B429D-E2E1-4265-83DF-FBAD19483C12}" name="Table91317181920" displayName="Table91317181920" ref="B1:D51" totalsRowShown="0" headerRowDxfId="35" tableBorderDxfId="34" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D51" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D51">
     <sortCondition ref="B1:B51"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="34" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="32" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="32" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="31" totalsRowDxfId="30" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:H92" totalsRowCount="1" headerRowDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}" name="Table6" displayName="Table6" ref="A1:H92" totalsRowCount="1" headerRowDxfId="29">
   <autoFilter ref="A1:H91" xr:uid="{02B4D57F-6E20-42C2-A7CF-65378FC03170}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H91">
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="29" totalsRowDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="27" totalsRowDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="26" totalsRowDxfId="25"/>
     <tableColumn id="3" xr3:uid="{6512942A-B4C3-4998-AA54-D3A429CF1394}" name="Meters"/>
-    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="25" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="23" dataCellStyle="Normal 7">
+    <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="24"/>
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="20" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="21">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18">
       <calculatedColumnFormula>$K$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7474,7 +7470,7 @@
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{E1FF070C-6993-4332-802B-B4D29E1606E7}" name="Function"/>
-    <tableColumn id="2" xr3:uid="{54776E09-074A-46D8-A8AF-0675792CABF2}" name="Macro" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{54776E09-074A-46D8-A8AF-0675792CABF2}" name="Macro" dataDxfId="102"/>
     <tableColumn id="3" xr3:uid="{8FBB1689-4854-43C5-AC93-F6E571CF242D}" name="Description"/>
     <tableColumn id="4" xr3:uid="{8BF21A82-1921-4BE2-9EDE-151E7264E122}" name="notes"/>
   </tableColumns>
@@ -7490,7 +7486,7 @@
   </sortState>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{72FB4F94-B23A-4D8C-9115-4A4A22828CD8}" name="Function"/>
-    <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{72E39D2F-151A-44B2-BA84-B7F34C14C282}" name="System" dataDxfId="101"/>
     <tableColumn id="3" xr3:uid="{5B376876-1002-41A2-9B1B-97FBB74534E9}" name="Description"/>
     <tableColumn id="4" xr3:uid="{B8821D9B-B31B-482C-A94B-3E00C4020734}" name="Column1"/>
   </tableColumns>
@@ -7523,7 +7519,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
   <autoFilter ref="A4:L37" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7560,121 +7556,121 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="86" dataDxfId="85" tableBorderDxfId="84" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}" name="Table112" displayName="Table112" ref="B1:E19" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83" tableBorderDxfId="82" headerRowCellStyle="Normal 2">
   <autoFilter ref="B1:E19" xr:uid="{9FCF4A79-156B-41FF-A555-9328C94776F1}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E19">
     <sortCondition ref="B1:B19"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="83"/>
-    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="82"/>
-    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Cut length" dataDxfId="81" dataCellStyle="Normal 8"/>
-    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="BOM Quantity" dataDxfId="80"/>
+    <tableColumn id="1" xr3:uid="{12342F44-8220-45C2-AC30-328741D516AB}" name="Part name" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{2385B826-F8C8-4362-89A6-95A38D685D6B}" name="Description" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{0FBBE615-D864-4E30-B741-3BE35C30458E}" name="Cut length" dataDxfId="79" dataCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{59176566-F320-409F-9AA9-17486015A49A}" name="BOM Quantity" dataDxfId="78"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="79" tableBorderDxfId="78" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}" name="Table9" displayName="Table9" ref="B1:D44" totalsRowShown="0" headerRowDxfId="77" tableBorderDxfId="76" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D44" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D44">
     <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="76" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="74" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="74" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="73" totalsRowDxfId="72" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D26" totalsRowShown="0" headerRowDxfId="73" tableBorderDxfId="72" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{0D081A3B-5ADC-4D38-A88B-EBE88E8EC051}" name="Table916" displayName="Table916" ref="B1:D26" totalsRowShown="0" headerRowDxfId="71" tableBorderDxfId="70" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D26" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D26">
     <sortCondition ref="B1:B26"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="71" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="70" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="68" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="68" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="67" totalsRowDxfId="66" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B29:D39" totalsRowShown="0" headerRowDxfId="67" tableBorderDxfId="66" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}" name="Table91629" displayName="Table91629" ref="B29:D39" totalsRowShown="0" headerRowDxfId="65" tableBorderDxfId="64" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B29:D39" xr:uid="{DA456747-D398-4471-8B86-AB700DA339AD}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B30:D39">
     <sortCondition ref="B29:B39"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="65" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="64" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="62" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="62" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="61" totalsRowDxfId="60" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D45" totalsRowShown="0" headerRowDxfId="61" tableBorderDxfId="60" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{5A485C34-0DBE-4411-B49C-86BFD99B3F62}" name="Table913" displayName="Table913" ref="B1:D45" totalsRowShown="0" headerRowDxfId="59" tableBorderDxfId="58" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D45" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D45">
     <sortCondition ref="B1:B45"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="58" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="56" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="56" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="55" totalsRowDxfId="54" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D74" totalsRowShown="0" headerRowDxfId="55" tableBorderDxfId="54" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{0A9E0A99-CDD4-4F70-BA5B-784249346C24}" name="Table91317" displayName="Table91317" ref="B1:D74" totalsRowShown="0" headerRowDxfId="53" tableBorderDxfId="52" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D74" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D74">
     <sortCondition ref="B1:B74"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="52" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="50" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="50" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="49" totalsRowDxfId="48" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D44" totalsRowShown="0" headerRowDxfId="49" tableBorderDxfId="48" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{80146AFF-010D-476D-80AD-DFB7130CCD89}" name="Table9131718" displayName="Table9131718" ref="B1:D44" totalsRowShown="0" headerRowDxfId="47" tableBorderDxfId="46" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D44" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D44">
     <sortCondition ref="B1:B44"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="46" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="44" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="44" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="43" totalsRowDxfId="42" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D18" totalsRowShown="0" headerRowDxfId="43" tableBorderDxfId="42" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{AC31348F-CB75-44A7-A48C-4BBEA19837B3}" name="Table913171819" displayName="Table913171819" ref="B1:D18" totalsRowShown="0" headerRowDxfId="41" tableBorderDxfId="40" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <autoFilter ref="B1:D18" xr:uid="{BAD2131D-41B2-42EA-A67B-FBB781AD12E7}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:D18">
     <sortCondition ref="B1:B18"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="40" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="38" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="38" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="37" totalsRowDxfId="36" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9629,7 +9625,7 @@
       <c r="H51" s="153" t="s">
         <v>126</v>
       </c>
-      <c r="I51" s="301"/>
+      <c r="I51" s="295"/>
       <c r="J51" s="94"/>
       <c r="K51" s="10"/>
       <c r="L51" s="68"/>
@@ -9659,7 +9655,7 @@
       <c r="H52" s="153" t="s">
         <v>127</v>
       </c>
-      <c r="I52" s="301"/>
+      <c r="I52" s="295"/>
       <c r="J52" s="94"/>
       <c r="K52" s="10"/>
       <c r="L52" s="68"/>
@@ -10023,7 +10019,7 @@
       <c r="H63" s="134" t="s">
         <v>156</v>
       </c>
-      <c r="I63" s="301"/>
+      <c r="I63" s="295"/>
       <c r="J63" s="94"/>
       <c r="K63" s="10"/>
       <c r="L63" s="68"/>
@@ -15759,7 +15755,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="296" t="s">
+      <c r="A12" s="294" t="s">
         <v>756</v>
       </c>
       <c r="B12" s="38" t="s">
@@ -15844,7 +15840,7 @@
       <c r="C21" t="s">
         <v>773</v>
       </c>
-      <c r="D21" s="295" t="s">
+      <c r="D21" s="293" t="s">
         <v>774</v>
       </c>
     </row>
@@ -17238,33 +17234,15 @@
       <c r="A1" s="261" t="s">
         <v>1014</v>
       </c>
-      <c r="B1" s="293"/>
-      <c r="C1" s="293"/>
-      <c r="D1" s="293"/>
-      <c r="E1" s="293"/>
-      <c r="F1" s="293"/>
-      <c r="G1" s="293"/>
-      <c r="H1" s="293"/>
-      <c r="I1" s="293"/>
-      <c r="J1" s="293"/>
-      <c r="K1" s="293"/>
-      <c r="L1" s="293"/>
+      <c r="B1" s="221"/>
+      <c r="C1" s="221"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="262" t="s">
         <v>1015</v>
       </c>
-      <c r="B2" s="293"/>
-      <c r="C2" s="293"/>
-      <c r="D2" s="293"/>
-      <c r="E2" s="293"/>
-      <c r="F2" s="293"/>
-      <c r="G2" s="293"/>
-      <c r="H2" s="293"/>
-      <c r="I2" s="293"/>
-      <c r="J2" s="293"/>
-      <c r="K2" s="293"/>
-      <c r="L2" s="293"/>
+      <c r="B2" s="221"/>
+      <c r="C2" s="221"/>
     </row>
     <row r="3" spans="1:12" s="260" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="285"/>
@@ -18421,7 +18399,6 @@
       <c r="L33" s="278">
         <v>2540</v>
       </c>
-      <c r="M33" s="292"/>
     </row>
     <row r="34" spans="1:13" s="260" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="287" t="s">
@@ -18460,7 +18437,6 @@
       <c r="L34" s="278">
         <v>1600</v>
       </c>
-      <c r="M34" s="292"/>
     </row>
     <row r="35" spans="1:13" s="260" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="287" t="s">
@@ -18499,7 +18475,6 @@
       <c r="L35" s="278">
         <v>1900</v>
       </c>
-      <c r="M35" s="292"/>
     </row>
     <row r="36" spans="1:13" s="260" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="287" t="s">
@@ -18538,7 +18513,6 @@
       <c r="L36" s="278">
         <v>1600</v>
       </c>
-      <c r="M36" s="292"/>
     </row>
     <row r="37" spans="1:13" s="260" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="287" t="s">
@@ -18577,7 +18551,6 @@
       <c r="L37" s="278">
         <v>3500</v>
       </c>
-      <c r="M37" s="292"/>
     </row>
     <row r="38" spans="1:13" s="260" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="265"/>
@@ -18598,29 +18571,15 @@
       <c r="A39" s="263" t="s">
         <v>1069</v>
       </c>
-      <c r="B39" s="294"/>
-      <c r="C39" s="294"/>
-      <c r="D39" s="293"/>
-      <c r="E39" s="293"/>
-      <c r="F39" s="293"/>
-      <c r="G39" s="293"/>
-      <c r="H39" s="293"/>
-      <c r="I39" s="293"/>
-      <c r="J39" s="293"/>
+      <c r="B39" s="292"/>
+      <c r="C39" s="292"/>
       <c r="K39" s="269"/>
       <c r="L39" s="269"/>
       <c r="M39" s="270"/>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1">
-      <c r="B40" s="294"/>
-      <c r="C40" s="294"/>
-      <c r="D40" s="293"/>
-      <c r="E40" s="293"/>
-      <c r="F40" s="293"/>
-      <c r="G40" s="293"/>
-      <c r="H40" s="293"/>
-      <c r="I40" s="293"/>
-      <c r="J40" s="293"/>
+      <c r="B40" s="292"/>
+      <c r="C40" s="292"/>
       <c r="K40" s="269"/>
       <c r="L40" s="269"/>
       <c r="M40" s="270"/>
@@ -18639,92 +18598,50 @@
       <c r="I41" s="300"/>
       <c r="J41" s="300"/>
       <c r="K41" s="300"/>
-      <c r="L41" s="293"/>
       <c r="M41" s="270"/>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A42" s="294" t="s">
+      <c r="A42" s="292" t="s">
         <v>1071</v>
       </c>
-      <c r="B42" s="293"/>
-      <c r="C42" s="293"/>
-      <c r="D42" s="293"/>
-      <c r="E42" s="293"/>
-      <c r="F42" s="293"/>
-      <c r="G42" s="293"/>
-      <c r="H42" s="293"/>
-      <c r="I42" s="293"/>
+      <c r="B42" s="221"/>
+      <c r="C42" s="221"/>
       <c r="J42" s="269"/>
-      <c r="K42" s="293"/>
-      <c r="L42" s="293"/>
       <c r="M42" s="270"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A43" s="294" t="s">
+      <c r="A43" s="292" t="s">
         <v>1072</v>
       </c>
-      <c r="B43" s="293"/>
-      <c r="C43" s="293"/>
-      <c r="D43" s="293"/>
-      <c r="E43" s="293"/>
-      <c r="F43" s="293"/>
-      <c r="G43" s="293"/>
-      <c r="H43" s="293"/>
-      <c r="I43" s="293"/>
+      <c r="B43" s="221"/>
+      <c r="C43" s="221"/>
       <c r="J43" s="269"/>
-      <c r="K43" s="293"/>
-      <c r="L43" s="293"/>
       <c r="M43" s="270"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A44" s="294" t="s">
+      <c r="A44" s="292" t="s">
         <v>1073</v>
       </c>
-      <c r="B44" s="293"/>
-      <c r="C44" s="293"/>
-      <c r="D44" s="293"/>
-      <c r="E44" s="293"/>
-      <c r="F44" s="293"/>
-      <c r="G44" s="293"/>
-      <c r="H44" s="293"/>
-      <c r="I44" s="293"/>
-      <c r="J44" s="293"/>
-      <c r="K44" s="293"/>
-      <c r="L44" s="293"/>
+      <c r="B44" s="221"/>
+      <c r="C44" s="221"/>
       <c r="M44" s="270"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A45" s="294" t="s">
+      <c r="A45" s="292" t="s">
         <v>1074</v>
       </c>
-      <c r="B45" s="293"/>
-      <c r="C45" s="293"/>
-      <c r="D45" s="293"/>
-      <c r="E45" s="293"/>
-      <c r="F45" s="293"/>
-      <c r="G45" s="293"/>
-      <c r="H45" s="293"/>
-      <c r="I45" s="293"/>
-      <c r="J45" s="293"/>
-      <c r="K45" s="293"/>
-      <c r="L45" s="293"/>
+      <c r="B45" s="221"/>
+      <c r="C45" s="221"/>
       <c r="M45" s="270"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A46" s="294" t="s">
+      <c r="A46" s="292" t="s">
         <v>1075</v>
       </c>
-      <c r="B46" s="293"/>
-      <c r="C46" s="293"/>
-      <c r="D46" s="293"/>
-      <c r="E46" s="293"/>
-      <c r="F46" s="293"/>
-      <c r="G46" s="293"/>
-      <c r="H46" s="293"/>
+      <c r="B46" s="221"/>
+      <c r="C46" s="221"/>
       <c r="I46" s="269"/>
       <c r="J46" s="269"/>
-      <c r="K46" s="293"/>
-      <c r="L46" s="293"/>
       <c r="M46" s="270"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
@@ -18740,12 +18657,9 @@
       <c r="H47" s="271"/>
       <c r="I47" s="271"/>
       <c r="J47" s="271"/>
-      <c r="K47" s="293"/>
-      <c r="L47" s="293"/>
       <c r="M47" s="270"/>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D48" s="293"/>
       <c r="E48" s="275"/>
       <c r="F48" s="275"/>
       <c r="G48" s="275"/>
@@ -18760,7 +18674,6 @@
       <c r="A49" s="289" t="s">
         <v>1077</v>
       </c>
-      <c r="D49" s="293"/>
       <c r="E49" s="275"/>
       <c r="F49" s="275"/>
       <c r="G49" s="275"/>
@@ -18775,7 +18688,6 @@
       <c r="A50" s="289" t="s">
         <v>1078</v>
       </c>
-      <c r="D50" s="293"/>
       <c r="E50" s="275"/>
       <c r="F50" s="275"/>
       <c r="G50" s="275"/>
@@ -18787,8 +18699,7 @@
       <c r="M50" s="270"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A51" s="302"/>
-      <c r="D51" s="293"/>
+      <c r="A51" s="296"/>
       <c r="E51" s="275"/>
       <c r="F51" s="275"/>
       <c r="G51" s="275"/>
@@ -18801,7 +18712,6 @@
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1">
       <c r="A52" s="290"/>
-      <c r="D52" s="293"/>
       <c r="E52" s="275"/>
       <c r="F52" s="275"/>
       <c r="G52" s="275"/>
@@ -18813,7 +18723,6 @@
       <c r="M52" s="270"/>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D53" s="293"/>
       <c r="E53" s="275"/>
       <c r="F53" s="275"/>
       <c r="G53" s="275"/>
@@ -18825,7 +18734,6 @@
       <c r="M53" s="270"/>
     </row>
     <row r="54" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D54" s="293"/>
       <c r="E54" s="275"/>
       <c r="F54" s="275"/>
       <c r="G54" s="275"/>
@@ -18837,7 +18745,6 @@
       <c r="M54" s="270"/>
     </row>
     <row r="55" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D55" s="293"/>
       <c r="E55" s="275"/>
       <c r="F55" s="275"/>
       <c r="G55" s="275"/>
@@ -18849,7 +18756,6 @@
       <c r="M55" s="270"/>
     </row>
     <row r="56" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D56" s="293"/>
       <c r="E56" s="275"/>
       <c r="F56" s="275"/>
       <c r="G56" s="275"/>
@@ -18861,7 +18767,6 @@
       <c r="M56" s="270"/>
     </row>
     <row r="57" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D57" s="293"/>
       <c r="E57" s="275"/>
       <c r="F57" s="275"/>
       <c r="G57" s="275"/>
@@ -18873,7 +18778,6 @@
       <c r="M57" s="270"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D58" s="293"/>
       <c r="E58" s="275"/>
       <c r="F58" s="275"/>
       <c r="G58" s="275"/>
@@ -18885,7 +18789,6 @@
       <c r="M58" s="270"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D59" s="293"/>
       <c r="E59" s="275"/>
       <c r="F59" s="275"/>
       <c r="G59" s="275"/>
@@ -18897,7 +18800,6 @@
       <c r="M59" s="270"/>
     </row>
     <row r="60" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D60" s="293"/>
       <c r="E60" s="275"/>
       <c r="F60" s="275"/>
       <c r="G60" s="275"/>
@@ -18909,7 +18811,6 @@
       <c r="M60" s="270"/>
     </row>
     <row r="61" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D61" s="293"/>
       <c r="E61" s="275"/>
       <c r="F61" s="275"/>
       <c r="G61" s="275"/>
@@ -18921,7 +18822,6 @@
       <c r="M61" s="270"/>
     </row>
     <row r="62" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D62" s="293"/>
       <c r="E62" s="275"/>
       <c r="F62" s="275"/>
       <c r="G62" s="275"/>
@@ -18933,7 +18833,6 @@
       <c r="M62" s="270"/>
     </row>
     <row r="63" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D63" s="293"/>
       <c r="E63" s="275"/>
       <c r="F63" s="275"/>
       <c r="G63" s="275"/>
@@ -18945,7 +18844,6 @@
       <c r="M63" s="270"/>
     </row>
     <row r="64" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D64" s="293"/>
       <c r="E64" s="275"/>
       <c r="F64" s="275"/>
       <c r="G64" s="275"/>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3252" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F99FD26D-7191-4B2D-B9F6-AC93C57F5633}"/>
+  <xr:revisionPtr revIDLastSave="3256" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2C6D273-7624-4785-ACA5-3D7990623CFD}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3277" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29DE1207-3A92-44B3-A4BC-2D535B79722E}"/>
+  <xr:revisionPtr revIDLastSave="3293" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D10C75D7-64A4-4750-9268-7262A9680685}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="1094">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="1101">
   <si>
     <t>Type</t>
   </si>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">calipers </t>
   </si>
   <si>
-    <t xml:space="preserve">Good choice Shahe </t>
+    <t xml:space="preserve">Recomend Shahe </t>
   </si>
   <si>
     <t>Allen Key short shank 2.5mmfor moth end</t>
@@ -2628,6 +2628,18 @@
   </si>
   <si>
     <t>https://www.aliexpress.com/item/1005002948629438.html?spm=a2g0o.order_list.order_list_main.192.45b518027U4htK</t>
+  </si>
+  <si>
+    <t>Philips No. 2   ( screws in GX20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good wire strippers  for the High temperature cable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead/Tin Sloder 60/40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This will make the soldering much easier </t>
   </si>
   <si>
     <t>New  features and upgrades on the Valkyrie V2  HT 100+</t>
@@ -3401,20 +3413,29 @@
       <t> to reach the high HDT values listed. Without annealing, these parts will soften significantly at much lower temperatures.</t>
     </r>
   </si>
+  <si>
+    <t>make scrafitial layers in the gearbox</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>adapt the PSU 350 buddy to the LRS-350</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="8">
-    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
-    <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="169" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+    <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
   </numFmts>
   <fonts count="69">
     <font>
@@ -4207,7 +4228,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="330">
+  <cellXfs count="318">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
@@ -4234,7 +4255,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4274,10 +4295,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -4344,13 +4365,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="36" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="36" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4410,9 +4431,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4423,7 +4444,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4471,7 +4492,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4559,7 +4580,7 @@
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4592,7 +4613,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
@@ -4614,7 +4635,7 @@
     <xf numFmtId="3" fontId="22" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="22" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
@@ -4630,7 +4651,7 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4677,7 +4698,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12"/>
-    <xf numFmtId="6" fontId="3" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyProtection="1">
@@ -4765,10 +4786,6 @@
     </xf>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4862,7 +4879,6 @@
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4875,7 +4891,7 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4899,33 +4915,7 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1"/>
     <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -4937,6 +4927,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5257,13 +5258,6 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -5303,6 +5297,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -5370,16 +5371,20 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+      <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
+      <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5399,10 +5404,6 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5534,9 +5535,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5553,6 +5551,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5611,9 +5612,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5630,6 +5628,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5688,9 +5689,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5707,6 +5705,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5765,9 +5766,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5784,6 +5782,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5842,9 +5843,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5861,6 +5859,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5919,9 +5920,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5938,6 +5936,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6012,9 +6013,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6031,6 +6029,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6089,9 +6090,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6108,6 +6106,9 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6401,7 +6402,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6426,7 +6427,7 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6501,13 +6502,6 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <border outline="0">
         <top style="medium">
           <color rgb="FF000000"/>
@@ -6526,6 +6520,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <border>
@@ -7528,7 +7529,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M152" totalsRowShown="0" dataDxfId="102" headerRowBorderDxfId="100" tableBorderDxfId="101" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M152" totalsRowShown="0" dataDxfId="101" headerRowBorderDxfId="102" tableBorderDxfId="100" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:M152" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L152">
     <sortCondition ref="A1:A152"/>
@@ -7563,7 +7564,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="34" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="32" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7576,19 +7577,19 @@
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="29" totalsRowDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="27" totalsRowDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="28" totalsRowDxfId="27"/>
     <tableColumn id="3" xr3:uid="{6512942A-B4C3-4998-AA54-D3A429CF1394}" name="Meters"/>
     <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="25" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="23" dataCellStyle="Normal 7">
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="21">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="20">
       <calculatedColumnFormula>$K$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7651,7 +7652,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
   <autoFilter ref="A4:L37" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7712,7 +7713,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="76" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="74" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="75" totalsRowDxfId="74" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7727,7 +7728,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="71" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="70" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="68" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="69" totalsRowDxfId="68" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7742,7 +7743,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="65" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="64" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="62" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="63" totalsRowDxfId="62" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7757,7 +7758,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="58" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="56" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7772,7 +7773,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="52" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="50" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7787,7 +7788,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="46" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="44" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7802,7 +7803,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="40" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="38" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8034,31 +8035,31 @@
       <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="259" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="260" t="s">
+      <c r="B1" s="257" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="258" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="259" t="s">
+      <c r="D1" s="257" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="259" t="s">
+      <c r="E1" s="257" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="259" t="s">
+      <c r="F1" s="257" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="259" t="s">
+      <c r="G1" s="257" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="261" t="s">
+      <c r="H1" s="259" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="262" t="s">
+      <c r="I1" s="260" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="263" t="s">
+      <c r="J1" s="261" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="67" t="s">
@@ -8176,7 +8177,7 @@
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="264" t="s">
+      <c r="B5" s="262" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="139"/>
@@ -8210,7 +8211,7 @@
       <c r="A6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="257" t="s">
+      <c r="B6" s="255" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="156"/>
@@ -8244,7 +8245,7 @@
       <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="257" t="s">
+      <c r="B7" s="255" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="156"/>
@@ -8278,7 +8279,7 @@
       <c r="A8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="265" t="s">
+      <c r="B8" s="263" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="139"/>
@@ -8312,7 +8313,7 @@
       <c r="A9" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="264" t="s">
+      <c r="B9" s="262" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="139"/>
@@ -8332,7 +8333,7 @@
       <c r="H9" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="258" t="s">
+      <c r="I9" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J9" s="27">
@@ -8365,7 +8366,7 @@
       <c r="H10" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="258" t="s">
+      <c r="I10" s="256" t="s">
         <v>36</v>
       </c>
       <c r="J10" s="27">
@@ -8399,7 +8400,7 @@
       <c r="H11" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="266" t="s">
+      <c r="I11" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J11" s="27">
@@ -8433,7 +8434,7 @@
       <c r="H12" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="266" t="s">
+      <c r="I12" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J12" s="27">
@@ -8467,7 +8468,7 @@
       <c r="H13" s="152" t="s">
         <v>43</v>
       </c>
-      <c r="I13" s="266" t="s">
+      <c r="I13" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J13" s="27">
@@ -8481,11 +8482,11 @@
       <c r="A14" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="267" t="s">
+      <c r="B14" s="265" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="160"/>
-      <c r="D14" s="268">
+      <c r="D14" s="266">
         <v>1</v>
       </c>
       <c r="E14" s="140">
@@ -8501,7 +8502,7 @@
       <c r="H14" s="152" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="266" t="s">
+      <c r="I14" s="264" t="s">
         <v>46</v>
       </c>
       <c r="J14" s="27">
@@ -8515,17 +8516,17 @@
       <c r="A15" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="268" t="s">
+      <c r="B15" s="266" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="269"/>
+      <c r="C15" s="267"/>
       <c r="D15" s="13">
         <v>2</v>
       </c>
       <c r="E15" s="140">
         <v>1</v>
       </c>
-      <c r="F15" s="268">
+      <c r="F15" s="266">
         <v>2.3199999999999998</v>
       </c>
       <c r="G15" s="141">
@@ -8535,7 +8536,7 @@
       <c r="H15" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="266" t="s">
+      <c r="I15" s="264" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="27">
@@ -8549,17 +8550,17 @@
       <c r="A16" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="268" t="s">
+      <c r="B16" s="266" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="269"/>
+      <c r="C16" s="267"/>
       <c r="D16" s="13">
         <v>1</v>
       </c>
       <c r="E16" s="140">
         <v>1</v>
       </c>
-      <c r="F16" s="270">
+      <c r="F16" s="268">
         <v>4.82</v>
       </c>
       <c r="G16" s="141">
@@ -8569,7 +8570,7 @@
       <c r="H16" s="152" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="271" t="s">
+      <c r="I16" s="269" t="s">
         <v>49</v>
       </c>
       <c r="J16" s="27">
@@ -8603,7 +8604,7 @@
       <c r="H17" s="202" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="271" t="s">
+      <c r="I17" s="269" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="94">
@@ -8620,14 +8621,14 @@
       <c r="B18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="269"/>
+      <c r="C18" s="267"/>
       <c r="D18" s="13">
         <v>1</v>
       </c>
       <c r="E18" s="140">
         <v>1</v>
       </c>
-      <c r="F18" s="270"/>
+      <c r="F18" s="268"/>
       <c r="G18" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8635,7 +8636,7 @@
       <c r="H18" s="197" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="271" t="s">
+      <c r="I18" s="269" t="s">
         <v>49</v>
       </c>
       <c r="J18" s="27">
@@ -8649,11 +8650,11 @@
       <c r="A19" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="272" t="s">
+      <c r="B19" s="270" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="273"/>
-      <c r="D19" s="272">
+      <c r="C19" s="271"/>
+      <c r="D19" s="270">
         <v>1</v>
       </c>
       <c r="E19" s="140">
@@ -8669,7 +8670,7 @@
       <c r="H19" s="152" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="258" t="s">
+      <c r="I19" s="256" t="s">
         <v>49</v>
       </c>
       <c r="J19" s="27">
@@ -8687,7 +8688,7 @@
         <v>58</v>
       </c>
       <c r="C20" s="139"/>
-      <c r="D20" s="272">
+      <c r="D20" s="270">
         <v>1</v>
       </c>
       <c r="E20" s="140">
@@ -8703,7 +8704,7 @@
       <c r="H20" s="152" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="258" t="s">
+      <c r="I20" s="256" t="s">
         <v>49</v>
       </c>
       <c r="J20" s="27">
@@ -8717,7 +8718,7 @@
       <c r="A21" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="272" t="s">
+      <c r="B21" s="270" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="162"/>
@@ -8737,7 +8738,7 @@
       <c r="H21" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="I21" s="258" t="s">
+      <c r="I21" s="256" t="s">
         <v>62</v>
       </c>
       <c r="J21" s="27">
@@ -8751,7 +8752,7 @@
       <c r="A22" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="264" t="s">
+      <c r="B22" s="262" t="s">
         <v>63</v>
       </c>
       <c r="C22" s="163" t="s">
@@ -8773,7 +8774,7 @@
       <c r="H22" s="152" t="s">
         <v>65</v>
       </c>
-      <c r="I22" s="258" t="s">
+      <c r="I22" s="256" t="s">
         <v>66</v>
       </c>
       <c r="J22" s="27">
@@ -8856,14 +8857,14 @@
       <c r="B25" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="269"/>
-      <c r="D25" s="268">
+      <c r="C25" s="267"/>
+      <c r="D25" s="266">
         <v>1</v>
       </c>
       <c r="E25" s="140">
         <v>1</v>
       </c>
-      <c r="F25" s="270">
+      <c r="F25" s="268">
         <v>16</v>
       </c>
       <c r="G25" s="141">
@@ -8907,7 +8908,7 @@
       <c r="H26" s="152" t="s">
         <v>76</v>
       </c>
-      <c r="I26" s="258" t="s">
+      <c r="I26" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J26" s="27">
@@ -8941,7 +8942,7 @@
       <c r="H27" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="I27" s="258" t="s">
+      <c r="I27" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J27" s="27">
@@ -8975,7 +8976,7 @@
       <c r="H28" s="198" t="s">
         <v>80</v>
       </c>
-      <c r="I28" s="258" t="s">
+      <c r="I28" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J28" s="94">
@@ -8989,7 +8990,7 @@
       <c r="A29" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="265" t="s">
+      <c r="B29" s="263" t="s">
         <v>81</v>
       </c>
       <c r="C29" s="164"/>
@@ -9009,7 +9010,7 @@
       <c r="H29" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="I29" s="258" t="s">
+      <c r="I29" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J29" s="27">
@@ -9026,7 +9027,7 @@
       <c r="B30" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="269"/>
+      <c r="C30" s="267"/>
       <c r="D30" s="13">
         <v>3</v>
       </c>
@@ -9043,7 +9044,7 @@
       <c r="H30" s="152" t="s">
         <v>83</v>
       </c>
-      <c r="I30" s="266" t="s">
+      <c r="I30" s="264" t="s">
         <v>33</v>
       </c>
       <c r="J30" s="27">
@@ -9057,7 +9058,7 @@
       <c r="A31" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="265" t="s">
+      <c r="B31" s="263" t="s">
         <v>84</v>
       </c>
       <c r="C31" s="139"/>
@@ -9077,7 +9078,7 @@
       <c r="H31" s="152" t="s">
         <v>85</v>
       </c>
-      <c r="I31" s="258" t="s">
+      <c r="I31" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J31" s="27">
@@ -9227,17 +9228,17 @@
       <c r="A36" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="268" t="s">
+      <c r="B36" s="266" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="269"/>
+      <c r="C36" s="267"/>
       <c r="D36" s="13">
         <v>1</v>
       </c>
       <c r="E36" s="140">
         <v>1</v>
       </c>
-      <c r="F36" s="270">
+      <c r="F36" s="268">
         <v>3.22</v>
       </c>
       <c r="G36" s="141">
@@ -9281,7 +9282,7 @@
       <c r="H37" s="152" t="s">
         <v>99</v>
       </c>
-      <c r="I37" s="266" t="s">
+      <c r="I37" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J37" s="27">
@@ -9315,7 +9316,7 @@
       <c r="H38" s="152" t="s">
         <v>101</v>
       </c>
-      <c r="I38" s="266" t="s">
+      <c r="I38" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J38" s="27">
@@ -9349,7 +9350,7 @@
       <c r="H39" s="152" t="s">
         <v>103</v>
       </c>
-      <c r="I39" s="266" t="s">
+      <c r="I39" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J39" s="27">
@@ -9366,8 +9367,8 @@
       <c r="B40" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="269"/>
-      <c r="D40" s="274">
+      <c r="C40" s="267"/>
+      <c r="D40" s="272">
         <v>2</v>
       </c>
       <c r="E40" s="140">
@@ -9383,7 +9384,7 @@
       <c r="H40" s="152" t="s">
         <v>105</v>
       </c>
-      <c r="I40" s="266" t="s">
+      <c r="I40" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J40" s="27">
@@ -9397,11 +9398,11 @@
       <c r="A41" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="267" t="s">
+      <c r="B41" s="265" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="269"/>
-      <c r="D41" s="274">
+      <c r="C41" s="267"/>
+      <c r="D41" s="272">
         <v>5</v>
       </c>
       <c r="E41" s="140">
@@ -9417,7 +9418,7 @@
       <c r="H41" s="152" t="s">
         <v>107</v>
       </c>
-      <c r="I41" s="266" t="s">
+      <c r="I41" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J41" s="27">
@@ -9434,8 +9435,8 @@
       <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="269"/>
-      <c r="D42" s="274">
+      <c r="C42" s="267"/>
+      <c r="D42" s="272">
         <v>2</v>
       </c>
       <c r="E42" s="140">
@@ -9451,7 +9452,7 @@
       <c r="H42" s="152" t="s">
         <v>109</v>
       </c>
-      <c r="I42" s="266" t="s">
+      <c r="I42" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J42" s="27">
@@ -9468,7 +9469,7 @@
       <c r="B43" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="269"/>
+      <c r="C43" s="267"/>
       <c r="D43" s="13">
         <v>5</v>
       </c>
@@ -9485,7 +9486,7 @@
       <c r="H43" s="152" t="s">
         <v>111</v>
       </c>
-      <c r="I43" s="266" t="s">
+      <c r="I43" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J43" s="27">
@@ -9502,8 +9503,8 @@
       <c r="B44" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="269"/>
-      <c r="D44" s="274">
+      <c r="C44" s="267"/>
+      <c r="D44" s="272">
         <v>2</v>
       </c>
       <c r="E44" s="140">
@@ -9519,7 +9520,7 @@
       <c r="H44" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="I44" s="266" t="s">
+      <c r="I44" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J44" s="27">
@@ -9536,7 +9537,7 @@
       <c r="B45" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="269"/>
+      <c r="C45" s="267"/>
       <c r="D45" s="13">
         <v>5</v>
       </c>
@@ -9553,7 +9554,7 @@
       <c r="H45" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="I45" s="266" t="s">
+      <c r="I45" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J45" s="27">
@@ -9567,10 +9568,10 @@
       <c r="A46" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="268" t="s">
+      <c r="B46" s="266" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="269"/>
+      <c r="C46" s="267"/>
       <c r="D46" s="13">
         <v>5</v>
       </c>
@@ -9587,7 +9588,7 @@
       <c r="H46" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="I46" s="266" t="s">
+      <c r="I46" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J46" s="27">
@@ -9604,8 +9605,8 @@
       <c r="B47" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C47" s="269"/>
-      <c r="D47" s="274">
+      <c r="C47" s="267"/>
+      <c r="D47" s="272">
         <v>2</v>
       </c>
       <c r="E47" s="140">
@@ -9621,7 +9622,7 @@
       <c r="H47" s="152" t="s">
         <v>119</v>
       </c>
-      <c r="I47" s="266" t="s">
+      <c r="I47" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J47" s="27">
@@ -9638,8 +9639,8 @@
       <c r="B48" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="C48" s="269"/>
-      <c r="D48" s="274">
+      <c r="C48" s="267"/>
+      <c r="D48" s="272">
         <v>5</v>
       </c>
       <c r="E48" s="140">
@@ -9655,7 +9656,7 @@
       <c r="H48" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="I48" s="266" t="s">
+      <c r="I48" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J48" s="27">
@@ -9669,11 +9670,11 @@
       <c r="A49" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="268" t="s">
+      <c r="B49" s="266" t="s">
         <v>122</v>
       </c>
-      <c r="C49" s="269"/>
-      <c r="D49" s="274">
+      <c r="C49" s="267"/>
+      <c r="D49" s="272">
         <v>5</v>
       </c>
       <c r="E49" s="140">
@@ -9689,7 +9690,7 @@
       <c r="H49" s="152" t="s">
         <v>123</v>
       </c>
-      <c r="I49" s="266" t="s">
+      <c r="I49" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J49" s="27">
@@ -9703,11 +9704,11 @@
       <c r="A50" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="268" t="s">
+      <c r="B50" s="266" t="s">
         <v>124</v>
       </c>
-      <c r="C50" s="269"/>
-      <c r="D50" s="274">
+      <c r="C50" s="267"/>
+      <c r="D50" s="272">
         <v>5</v>
       </c>
       <c r="E50" s="140">
@@ -9723,7 +9724,7 @@
       <c r="H50" s="152" t="s">
         <v>125</v>
       </c>
-      <c r="I50" s="266" t="s">
+      <c r="I50" s="264" t="s">
         <v>40</v>
       </c>
       <c r="J50" s="27">
@@ -9757,7 +9758,7 @@
       <c r="H51" s="152" t="s">
         <v>126</v>
       </c>
-      <c r="I51" s="327"/>
+      <c r="I51" s="311"/>
       <c r="J51" s="94"/>
       <c r="K51" s="10"/>
       <c r="L51" s="68"/>
@@ -9767,7 +9768,7 @@
       <c r="A52" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="267" t="s">
+      <c r="B52" s="265" t="s">
         <v>127</v>
       </c>
       <c r="C52" s="2"/>
@@ -9787,7 +9788,7 @@
       <c r="H52" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="I52" s="327"/>
+      <c r="I52" s="311"/>
       <c r="J52" s="94"/>
       <c r="K52" s="10"/>
       <c r="L52" s="68"/>
@@ -9797,7 +9798,7 @@
       <c r="A53" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B53" s="257" t="s">
+      <c r="B53" s="255" t="s">
         <v>128</v>
       </c>
       <c r="C53" s="139"/>
@@ -9831,7 +9832,7 @@
       <c r="A54" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B54" s="257" t="s">
+      <c r="B54" s="255" t="s">
         <v>131</v>
       </c>
       <c r="C54" s="156"/>
@@ -9865,17 +9866,17 @@
       <c r="A55" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="268" t="s">
+      <c r="B55" s="266" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="269"/>
-      <c r="D55" s="268">
+      <c r="C55" s="267"/>
+      <c r="D55" s="266">
         <v>1</v>
       </c>
       <c r="E55" s="140">
         <v>1</v>
       </c>
-      <c r="F55" s="270">
+      <c r="F55" s="268">
         <v>33.700000000000003</v>
       </c>
       <c r="G55" s="141">
@@ -9919,7 +9920,7 @@
       <c r="H56" s="152" t="s">
         <v>136</v>
       </c>
-      <c r="I56" s="258" t="s">
+      <c r="I56" s="256" t="s">
         <v>137</v>
       </c>
       <c r="J56" s="27">
@@ -9953,7 +9954,7 @@
       <c r="H57" s="152" t="s">
         <v>139</v>
       </c>
-      <c r="I57" s="275" t="s">
+      <c r="I57" s="273" t="s">
         <v>140</v>
       </c>
       <c r="J57" s="27">
@@ -9987,7 +9988,7 @@
       <c r="H58" s="152" t="s">
         <v>142</v>
       </c>
-      <c r="I58" s="258" t="s">
+      <c r="I58" s="256" t="s">
         <v>143</v>
       </c>
       <c r="J58" s="27">
@@ -10021,7 +10022,7 @@
       <c r="H59" s="152" t="s">
         <v>145</v>
       </c>
-      <c r="I59" s="258" t="s">
+      <c r="I59" s="256" t="s">
         <v>49</v>
       </c>
       <c r="J59" s="94"/>
@@ -10033,11 +10034,11 @@
       <c r="A60" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B60" s="268" t="s">
+      <c r="B60" s="266" t="s">
         <v>146</v>
       </c>
-      <c r="C60" s="269"/>
-      <c r="D60" s="268">
+      <c r="C60" s="267"/>
+      <c r="D60" s="266">
         <v>1</v>
       </c>
       <c r="E60" s="140">
@@ -10053,7 +10054,7 @@
       <c r="H60" s="152" t="s">
         <v>147</v>
       </c>
-      <c r="I60" s="266" t="s">
+      <c r="I60" s="264" t="s">
         <v>148</v>
       </c>
       <c r="J60" s="27">
@@ -10067,7 +10068,7 @@
       <c r="A61" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="257" t="s">
+      <c r="B61" s="255" t="s">
         <v>149</v>
       </c>
       <c r="C61" s="139"/>
@@ -10087,7 +10088,7 @@
       <c r="H61" s="152" t="s">
         <v>150</v>
       </c>
-      <c r="I61" s="266" t="s">
+      <c r="I61" s="264" t="s">
         <v>151</v>
       </c>
       <c r="J61" s="27">
@@ -10103,7 +10104,7 @@
       <c r="A62" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B62" s="257" t="s">
+      <c r="B62" s="255" t="s">
         <v>153</v>
       </c>
       <c r="C62" s="139"/>
@@ -10123,7 +10124,7 @@
       <c r="H62" s="152" t="s">
         <v>154</v>
       </c>
-      <c r="I62" s="266" t="s">
+      <c r="I62" s="264" t="s">
         <v>151</v>
       </c>
       <c r="J62" s="94"/>
@@ -10135,7 +10136,7 @@
       <c r="A63" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="257" t="s">
+      <c r="B63" s="255" t="s">
         <v>155</v>
       </c>
       <c r="C63" s="139"/>
@@ -10151,7 +10152,7 @@
       <c r="H63" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="I63" s="327"/>
+      <c r="I63" s="311"/>
       <c r="J63" s="94"/>
       <c r="K63" s="10"/>
       <c r="L63" s="68"/>
@@ -10163,7 +10164,7 @@
       <c r="A64" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B64" s="268" t="s">
+      <c r="B64" s="266" t="s">
         <v>158</v>
       </c>
       <c r="C64" s="160"/>
@@ -10183,7 +10184,7 @@
       <c r="H64" s="152" t="s">
         <v>159</v>
       </c>
-      <c r="I64" s="266" t="s">
+      <c r="I64" s="264" t="s">
         <v>151</v>
       </c>
       <c r="J64" s="27">
@@ -10216,7 +10217,7 @@
       <c r="H65" s="167" t="s">
         <v>162</v>
       </c>
-      <c r="I65" s="258" t="s">
+      <c r="I65" s="256" t="s">
         <v>163</v>
       </c>
       <c r="J65" s="27">
@@ -10249,7 +10250,7 @@
       <c r="H66" s="167" t="s">
         <v>165</v>
       </c>
-      <c r="I66" s="258" t="s">
+      <c r="I66" s="256" t="s">
         <v>163</v>
       </c>
       <c r="J66" s="27">
@@ -10334,7 +10335,7 @@
       <c r="A69" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B69" s="268" t="s">
+      <c r="B69" s="266" t="s">
         <v>172</v>
       </c>
       <c r="C69" s="151"/>
@@ -10980,7 +10981,7 @@
       <c r="A87" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B87" s="264" t="s">
+      <c r="B87" s="262" t="s">
         <v>207</v>
       </c>
       <c r="C87" s="139"/>
@@ -11070,7 +11071,7 @@
       <c r="H89" s="169" t="s">
         <v>212</v>
       </c>
-      <c r="I89" s="258" t="s">
+      <c r="I89" s="256" t="s">
         <v>171</v>
       </c>
       <c r="J89" s="27">
@@ -11121,7 +11122,7 @@
       <c r="A91" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="B91" s="264" t="s">
+      <c r="B91" s="262" t="s">
         <v>215</v>
       </c>
       <c r="C91" s="139"/>
@@ -11519,7 +11520,7 @@
       <c r="A102" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="B102" s="257" t="s">
+      <c r="B102" s="255" t="s">
         <v>237</v>
       </c>
       <c r="C102" s="156"/>
@@ -11551,79 +11552,79 @@
       <c r="L102" s="68"/>
       <c r="M102" s="129"/>
     </row>
-    <row r="103" spans="1:13" s="307" customFormat="1">
-      <c r="A103" s="299" t="s">
+    <row r="103" spans="1:13" s="304" customFormat="1">
+      <c r="A103" s="296" t="s">
         <v>160</v>
       </c>
-      <c r="B103" s="300" t="s">
+      <c r="B103" s="297" t="s">
         <v>238</v>
       </c>
-      <c r="C103" s="301"/>
-      <c r="D103" s="300">
+      <c r="C103" s="298"/>
+      <c r="D103" s="297">
         <v>44</v>
       </c>
-      <c r="E103" s="302">
+      <c r="E103" s="299">
         <v>5</v>
       </c>
-      <c r="F103" s="303">
+      <c r="F103" s="300">
         <v>3.21</v>
       </c>
-      <c r="G103" s="303">
+      <c r="G103" s="300">
         <f t="shared" ref="G103:G134" si="4">E103*F103</f>
         <v>16.05</v>
       </c>
-      <c r="H103" s="304" t="s">
+      <c r="H103" s="301" t="s">
         <v>239</v>
       </c>
-      <c r="I103" s="305" t="s">
+      <c r="I103" s="302" t="s">
         <v>171</v>
       </c>
-      <c r="J103" s="306">
+      <c r="J103" s="303">
         <v>10</v>
       </c>
-      <c r="K103" s="307">
+      <c r="K103" s="304">
         <v>933</v>
       </c>
-      <c r="L103" s="308"/>
-      <c r="M103" s="309" t="s">
+      <c r="L103" s="305"/>
+      <c r="M103" s="306" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="104" spans="1:13" s="307" customFormat="1">
-      <c r="A104" s="299" t="s">
+    <row r="104" spans="1:13" s="304" customFormat="1">
+      <c r="A104" s="296" t="s">
         <v>160</v>
       </c>
-      <c r="B104" s="300" t="s">
+      <c r="B104" s="297" t="s">
         <v>241</v>
       </c>
-      <c r="C104" s="301"/>
-      <c r="D104" s="300">
+      <c r="C104" s="298"/>
+      <c r="D104" s="297">
         <v>17</v>
       </c>
-      <c r="E104" s="302">
+      <c r="E104" s="299">
         <v>2</v>
       </c>
-      <c r="F104" s="303">
+      <c r="F104" s="300">
         <v>3.57</v>
       </c>
-      <c r="G104" s="303">
+      <c r="G104" s="300">
         <f t="shared" si="4"/>
         <v>7.14</v>
       </c>
-      <c r="H104" s="304" t="s">
+      <c r="H104" s="301" t="s">
         <v>242</v>
       </c>
-      <c r="I104" s="305" t="s">
+      <c r="I104" s="302" t="s">
         <v>171</v>
       </c>
-      <c r="J104" s="306">
+      <c r="J104" s="303">
         <v>10</v>
       </c>
-      <c r="K104" s="307">
+      <c r="K104" s="304">
         <v>933</v>
       </c>
-      <c r="L104" s="308"/>
-      <c r="M104" s="309" t="s">
+      <c r="L104" s="305"/>
+      <c r="M104" s="306" t="s">
         <v>243</v>
       </c>
     </row>
@@ -11687,7 +11688,7 @@
       <c r="H106" s="168" t="s">
         <v>248</v>
       </c>
-      <c r="I106" s="258" t="s">
+      <c r="I106" s="256" t="s">
         <v>249</v>
       </c>
       <c r="J106" s="27">
@@ -11721,7 +11722,7 @@
       <c r="H107" s="168" t="s">
         <v>251</v>
       </c>
-      <c r="I107" s="258" t="s">
+      <c r="I107" s="256" t="s">
         <v>249</v>
       </c>
       <c r="J107" s="27"/>
@@ -11787,7 +11788,7 @@
       <c r="H109" s="168" t="s">
         <v>255</v>
       </c>
-      <c r="I109" s="258" t="s">
+      <c r="I109" s="256" t="s">
         <v>249</v>
       </c>
       <c r="J109" s="27">
@@ -11821,7 +11822,7 @@
       <c r="H110" s="168" t="s">
         <v>257</v>
       </c>
-      <c r="I110" s="258" t="s">
+      <c r="I110" s="256" t="s">
         <v>249</v>
       </c>
       <c r="J110" s="27">
@@ -11857,7 +11858,7 @@
       <c r="H111" s="169" t="s">
         <v>261</v>
       </c>
-      <c r="I111" s="258" t="s">
+      <c r="I111" s="256" t="s">
         <v>262</v>
       </c>
       <c r="J111" s="27"/>
@@ -11889,7 +11890,7 @@
       <c r="H112" s="167" t="s">
         <v>264</v>
       </c>
-      <c r="I112" s="258" t="s">
+      <c r="I112" s="256" t="s">
         <v>265</v>
       </c>
       <c r="J112" s="27">
@@ -11955,7 +11956,7 @@
       <c r="H114" s="169" t="s">
         <v>270</v>
       </c>
-      <c r="I114" s="258" t="s">
+      <c r="I114" s="256" t="s">
         <v>171</v>
       </c>
       <c r="J114" s="27">
@@ -11989,7 +11990,7 @@
       <c r="H115" s="152" t="s">
         <v>273</v>
       </c>
-      <c r="I115" s="258" t="s">
+      <c r="I115" s="256" t="s">
         <v>274</v>
       </c>
       <c r="J115" s="27">
@@ -12071,7 +12072,7 @@
       <c r="A118" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B118" s="267" t="s">
+      <c r="B118" s="265" t="s">
         <v>281</v>
       </c>
       <c r="C118" s="180"/>
@@ -12091,7 +12092,7 @@
       <c r="H118" s="152" t="s">
         <v>282</v>
       </c>
-      <c r="I118" s="258" t="s">
+      <c r="I118" s="256" t="s">
         <v>283</v>
       </c>
       <c r="J118" s="27">
@@ -12105,7 +12106,7 @@
       <c r="A119" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B119" s="267" t="s">
+      <c r="B119" s="265" t="s">
         <v>284</v>
       </c>
       <c r="C119" s="180"/>
@@ -12125,7 +12126,7 @@
       <c r="H119" s="197" t="s">
         <v>285</v>
       </c>
-      <c r="I119" s="258"/>
+      <c r="I119" s="256"/>
       <c r="J119" s="27">
         <v>1</v>
       </c>
@@ -12159,7 +12160,7 @@
       <c r="H120" s="152" t="s">
         <v>288</v>
       </c>
-      <c r="I120" s="258" t="s">
+      <c r="I120" s="256" t="s">
         <v>289</v>
       </c>
       <c r="J120" s="27">
@@ -12173,7 +12174,7 @@
       <c r="A121" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="B121" s="267" t="s">
+      <c r="B121" s="265" t="s">
         <v>290</v>
       </c>
       <c r="C121" s="180"/>
@@ -12193,7 +12194,7 @@
       <c r="H121" s="152" t="s">
         <v>291</v>
       </c>
-      <c r="I121" s="258" t="s">
+      <c r="I121" s="256" t="s">
         <v>289</v>
       </c>
       <c r="J121" s="27">
@@ -12207,7 +12208,7 @@
       <c r="A122" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="265" t="s">
+      <c r="B122" s="263" t="s">
         <v>292</v>
       </c>
       <c r="C122" s="139"/>
@@ -12227,7 +12228,7 @@
       <c r="H122" s="167" t="s">
         <v>293</v>
       </c>
-      <c r="I122" s="258" t="s">
+      <c r="I122" s="256" t="s">
         <v>294</v>
       </c>
       <c r="J122" s="27">
@@ -12241,7 +12242,7 @@
       <c r="A123" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="B123" s="276" t="s">
+      <c r="B123" s="274" t="s">
         <v>296</v>
       </c>
       <c r="C123" s="182">
@@ -12263,7 +12264,7 @@
       <c r="H123" s="169" t="s">
         <v>297</v>
       </c>
-      <c r="I123" s="266" t="s">
+      <c r="I123" s="264" t="s">
         <v>298</v>
       </c>
       <c r="J123" s="27">
@@ -12277,7 +12278,7 @@
       <c r="A124" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="B124" s="257" t="s">
+      <c r="B124" s="255" t="s">
         <v>299</v>
       </c>
       <c r="C124" s="156">
@@ -12299,7 +12300,7 @@
       <c r="H124" s="169" t="s">
         <v>300</v>
       </c>
-      <c r="I124" s="266" t="s">
+      <c r="I124" s="264" t="s">
         <v>298</v>
       </c>
       <c r="J124" s="27">
@@ -12316,7 +12317,7 @@
       <c r="B125" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="C125" s="269" t="s">
+      <c r="C125" s="267" t="s">
         <v>302</v>
       </c>
       <c r="D125" s="13">
@@ -12335,7 +12336,7 @@
       <c r="H125" s="152" t="s">
         <v>303</v>
       </c>
-      <c r="I125" s="266" t="s">
+      <c r="I125" s="264" t="s">
         <v>298</v>
       </c>
       <c r="J125" s="27">
@@ -12369,7 +12370,7 @@
       <c r="H126" s="169" t="s">
         <v>305</v>
       </c>
-      <c r="I126" s="258" t="s">
+      <c r="I126" s="256" t="s">
         <v>163</v>
       </c>
       <c r="J126" s="27">
@@ -12405,7 +12406,7 @@
       <c r="H127" s="169" t="s">
         <v>307</v>
       </c>
-      <c r="I127" s="258" t="s">
+      <c r="I127" s="256" t="s">
         <v>308</v>
       </c>
       <c r="J127" s="27">
@@ -12441,7 +12442,7 @@
       <c r="H128" s="169" t="s">
         <v>310</v>
       </c>
-      <c r="I128" s="258" t="s">
+      <c r="I128" s="256" t="s">
         <v>308</v>
       </c>
       <c r="J128" s="27">
@@ -12477,7 +12478,7 @@
       <c r="H129" s="169" t="s">
         <v>312</v>
       </c>
-      <c r="I129" s="258" t="s">
+      <c r="I129" s="256" t="s">
         <v>308</v>
       </c>
       <c r="J129" s="27">
@@ -12513,7 +12514,7 @@
       <c r="H130" s="169" t="s">
         <v>314</v>
       </c>
-      <c r="I130" s="258" t="s">
+      <c r="I130" s="256" t="s">
         <v>308</v>
       </c>
       <c r="J130" s="27">
@@ -12549,7 +12550,7 @@
       <c r="H131" s="169" t="s">
         <v>316</v>
       </c>
-      <c r="I131" s="258" t="s">
+      <c r="I131" s="256" t="s">
         <v>308</v>
       </c>
       <c r="J131" s="27">
@@ -12585,7 +12586,7 @@
       <c r="H132" s="169" t="s">
         <v>318</v>
       </c>
-      <c r="I132" s="258" t="s">
+      <c r="I132" s="256" t="s">
         <v>308</v>
       </c>
       <c r="J132" s="27">
@@ -12619,7 +12620,7 @@
       <c r="H133" s="169" t="s">
         <v>320</v>
       </c>
-      <c r="I133" s="258" t="s">
+      <c r="I133" s="256" t="s">
         <v>321</v>
       </c>
       <c r="J133" s="27">
@@ -12655,7 +12656,7 @@
       <c r="H134" s="187" t="s">
         <v>324</v>
       </c>
-      <c r="I134" s="258" t="s">
+      <c r="I134" s="256" t="s">
         <v>325</v>
       </c>
       <c r="J134" s="27">
@@ -12691,7 +12692,7 @@
       <c r="H135" s="167" t="s">
         <v>327</v>
       </c>
-      <c r="I135" s="258" t="s">
+      <c r="I135" s="256" t="s">
         <v>328</v>
       </c>
       <c r="J135" s="27">
@@ -12701,11 +12702,11 @@
       <c r="L135" s="68"/>
       <c r="M135" s="130"/>
     </row>
-    <row r="136" spans="1:13" s="12" customFormat="1" ht="16.5">
+    <row r="136" spans="1:13" s="12" customFormat="1" ht="15.75">
       <c r="A136" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B136" s="257" t="s">
+      <c r="B136" s="255" t="s">
         <v>330</v>
       </c>
       <c r="C136" s="156"/>
@@ -12725,7 +12726,7 @@
       <c r="H136" s="167" t="s">
         <v>331</v>
       </c>
-      <c r="I136" s="258" t="s">
+      <c r="I136" s="256" t="s">
         <v>332</v>
       </c>
       <c r="J136" s="27">
@@ -12733,7 +12734,7 @@
       </c>
       <c r="K136" s="69"/>
       <c r="L136" s="70"/>
-      <c r="M136" s="296" t="s">
+      <c r="M136" s="294" t="s">
         <v>333</v>
       </c>
     </row>
@@ -12741,7 +12742,7 @@
       <c r="A137" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B137" s="257" t="s">
+      <c r="B137" s="255" t="s">
         <v>334</v>
       </c>
       <c r="C137" s="156"/>
@@ -12761,7 +12762,7 @@
       <c r="H137" s="167" t="s">
         <v>335</v>
       </c>
-      <c r="I137" s="258" t="s">
+      <c r="I137" s="256" t="s">
         <v>332</v>
       </c>
       <c r="J137" s="27">
@@ -12769,13 +12770,13 @@
       </c>
       <c r="K137" s="69"/>
       <c r="L137" s="70"/>
-      <c r="M137" s="295"/>
+      <c r="M137" s="293"/>
     </row>
     <row r="138" spans="1:13" s="12" customFormat="1" ht="15.75">
       <c r="A138" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="B138" s="257" t="s">
+      <c r="B138" s="255" t="s">
         <v>336</v>
       </c>
       <c r="C138" s="139"/>
@@ -12795,7 +12796,7 @@
       <c r="H138" s="167" t="s">
         <v>337</v>
       </c>
-      <c r="I138" s="258" t="s">
+      <c r="I138" s="256" t="s">
         <v>332</v>
       </c>
       <c r="J138" s="27">
@@ -12809,7 +12810,7 @@
       <c r="A139" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B139" s="257" t="s">
+      <c r="B139" s="255" t="s">
         <v>338</v>
       </c>
       <c r="C139" s="156"/>
@@ -12829,7 +12830,7 @@
       <c r="H139" s="167" t="s">
         <v>339</v>
       </c>
-      <c r="I139" s="258" t="s">
+      <c r="I139" s="256" t="s">
         <v>332</v>
       </c>
       <c r="J139" s="27">
@@ -12843,7 +12844,7 @@
       <c r="A140" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B140" s="257" t="s">
+      <c r="B140" s="255" t="s">
         <v>340</v>
       </c>
       <c r="C140" s="156"/>
@@ -12863,7 +12864,7 @@
       <c r="H140" s="167" t="s">
         <v>341</v>
       </c>
-      <c r="I140" s="258" t="s">
+      <c r="I140" s="256" t="s">
         <v>332</v>
       </c>
       <c r="J140" s="27">
@@ -12933,7 +12934,7 @@
       <c r="H142" s="167" t="s">
         <v>345</v>
       </c>
-      <c r="I142" s="258" t="s">
+      <c r="I142" s="256" t="s">
         <v>346</v>
       </c>
       <c r="J142" s="27">
@@ -12981,7 +12982,7 @@
       <c r="A144" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="B144" s="265" t="s">
+      <c r="B144" s="263" t="s">
         <v>352</v>
       </c>
       <c r="C144" s="164"/>
@@ -13001,7 +13002,7 @@
       <c r="H144" s="167" t="s">
         <v>353</v>
       </c>
-      <c r="I144" s="258" t="s">
+      <c r="I144" s="256" t="s">
         <v>354</v>
       </c>
       <c r="J144" s="27">
@@ -13015,7 +13016,7 @@
       <c r="A145" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="B145" s="265" t="s">
+      <c r="B145" s="263" t="s">
         <v>355</v>
       </c>
       <c r="C145" s="139"/>
@@ -13035,7 +13036,7 @@
       <c r="H145" s="167" t="s">
         <v>356</v>
       </c>
-      <c r="I145" s="258" t="s">
+      <c r="I145" s="256" t="s">
         <v>357</v>
       </c>
       <c r="J145" s="94"/>
@@ -13101,7 +13102,7 @@
       <c r="H147" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="I147" s="258" t="s">
+      <c r="I147" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J147" s="27">
@@ -13135,7 +13136,7 @@
       <c r="H148" s="167" t="s">
         <v>364</v>
       </c>
-      <c r="I148" s="258" t="s">
+      <c r="I148" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J148" s="27">
@@ -13169,7 +13170,7 @@
       <c r="H149" s="167" t="s">
         <v>366</v>
       </c>
-      <c r="I149" s="258" t="s">
+      <c r="I149" s="256" t="s">
         <v>33</v>
       </c>
       <c r="J149" s="27">
@@ -13237,7 +13238,7 @@
       <c r="H151" s="167" t="s">
         <v>370</v>
       </c>
-      <c r="I151" s="258" t="s">
+      <c r="I151" s="256" t="s">
         <v>371</v>
       </c>
       <c r="J151" s="27">
@@ -13304,13 +13305,13 @@
     </row>
     <row r="154" spans="1:13">
       <c r="G154" s="11"/>
-      <c r="K154" s="277"/>
+      <c r="K154" s="275"/>
     </row>
     <row r="155" spans="1:13">
-      <c r="K155" s="277"/>
+      <c r="K155" s="275"/>
     </row>
     <row r="156" spans="1:13">
-      <c r="K156" s="277"/>
+      <c r="K156" s="275"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14704,7 +14705,7 @@
       <c r="H51" s="112"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="297" t="s">
+      <c r="A52" s="295" t="s">
         <v>689</v>
       </c>
       <c r="B52" s="36" t="s">
@@ -14725,7 +14726,7 @@
       <c r="H52" s="112"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="297" t="s">
+      <c r="A53" s="295" t="s">
         <v>689</v>
       </c>
       <c r="B53" s="36" t="s">
@@ -15603,10 +15604,10 @@
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="328" t="s">
+      <c r="A93" s="312" t="s">
         <v>689</v>
       </c>
-      <c r="B93" s="298" t="s">
+      <c r="B93" t="s">
         <v>697</v>
       </c>
       <c r="D93">
@@ -15620,7 +15621,7 @@
       </c>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="297" t="s">
+      <c r="A94" s="295" t="s">
         <v>689</v>
       </c>
       <c r="B94" t="s">
@@ -15637,10 +15638,10 @@
       </c>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="297" t="s">
+      <c r="A95" s="295" t="s">
         <v>689</v>
       </c>
-      <c r="B95" s="298" t="s">
+      <c r="B95" t="s">
         <v>700</v>
       </c>
       <c r="I95" t="s">
@@ -15661,7 +15662,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.140625" customWidth="1"/>
@@ -15705,7 +15706,7 @@
       <c r="B3" t="s">
         <v>710</v>
       </c>
-      <c r="C3" s="325" t="s">
+      <c r="C3" s="309" t="s">
         <v>711</v>
       </c>
     </row>
@@ -15719,7 +15720,7 @@
       <c r="C4" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="D4" s="326" t="s">
+      <c r="D4" s="310" t="s">
         <v>715</v>
       </c>
     </row>
@@ -15786,6 +15787,22 @@
     <row r="12" spans="1:4">
       <c r="A12" t="s">
         <v>730</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1099</v>
       </c>
     </row>
   </sheetData>
@@ -16293,14 +16310,14 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617F1214-FEDF-4959-B6B1-8C60CA48A0FC}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="51.42578125" customWidth="1"/>
     <col min="2" max="2" width="20.42578125" customWidth="1"/>
     <col min="3" max="3" width="32.85546875" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" customWidth="1"/>
-    <col min="5" max="5" width="34.42578125" customWidth="1"/>
+    <col min="5" max="5" width="71.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -16411,11 +16428,38 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="315" t="s">
+      <c r="A14" s="308" t="s">
         <v>854</v>
       </c>
       <c r="E14" s="134" t="s">
         <v>855</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>856</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>858</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>859</v>
       </c>
     </row>
   </sheetData>
@@ -16439,7 +16483,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="205" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -16447,32 +16491,32 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="206" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="207" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="205" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="205" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="205" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="205" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -16480,17 +16524,17 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="206" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="207" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="205" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -16498,37 +16542,37 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="206" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="205" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="205" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="205" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="205" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="205" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="205" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -16536,22 +16580,22 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="206" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="205" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="205" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="205" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
     </row>
   </sheetData>
@@ -16577,33 +16621,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="204" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="B1" s="210" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="C1" s="210" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="D1" s="210" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="E1" s="210" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
       <c r="F1" s="210" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="G1" s="209" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="H1" s="208" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="204" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="B2" s="210">
         <v>1</v>
@@ -16621,7 +16665,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="209" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="H2" s="208">
         <v>2</v>
@@ -16629,30 +16673,30 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="204" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="B3" s="210" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="C3" s="210" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="D3" s="219" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="E3" s="219" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="F3" s="210" t="s">
         <v>156</v>
       </c>
       <c r="H3" s="208" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="204" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B4" s="210">
         <v>450</v>
@@ -16661,7 +16705,7 @@
         <v>450</v>
       </c>
       <c r="D4" s="210" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="E4" s="210">
         <v>285</v>
@@ -16673,18 +16717,18 @@
         <v>300</v>
       </c>
       <c r="H4" s="208" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="204" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B5" s="210" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="C5" s="210" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="D5" s="210">
         <v>150</v>
@@ -16699,12 +16743,12 @@
         <v>120</v>
       </c>
       <c r="H5" s="208" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="204" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="B6" s="210">
         <v>80</v>
@@ -16725,168 +16769,168 @@
         <v>60</v>
       </c>
       <c r="H6" s="208" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="204" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="B7" s="210" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="C7" s="210" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="D7" s="210" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="E7" s="210" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="F7" s="210" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="G7" s="209" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="H7" s="208" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="204" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="B8" s="210" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="C8" s="210" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="D8" s="210" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="E8" s="210" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="F8" s="210" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="G8" s="209" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="H8" s="208" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="204" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B9" s="210" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C9" s="210" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="D9" s="210" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="E9" s="210" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="F9" s="210" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="H9" s="208" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="204" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="B10" s="215" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C10" s="215" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="D10" s="215" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="E10" s="215" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="F10" s="218" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="G10" s="217" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="H10" s="208" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="204" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="B11" s="210" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="C11" s="210" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="D11" s="210" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="E11" s="210" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="F11" s="210" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="G11" s="209" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="H11" s="208" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.25" customHeight="1">
       <c r="A12" s="216" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B12" s="215" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="C12" s="215" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="D12" s="214" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="E12" s="215" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="F12" s="214" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="H12" s="208" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="204" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B13" s="210" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="C13" s="210" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="D13" s="210">
         <v>120</v>
@@ -16895,265 +16939,265 @@
         <v>156</v>
       </c>
       <c r="F13" s="210" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="G13" s="209" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="H13" s="208" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="204" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B14" s="210" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="C14" s="210" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D14" s="210" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="E14" s="210" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="F14" s="210" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="H14" s="208" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="213" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="C15" s="210" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H15" s="208" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="204" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="B16" s="210" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="C16" s="210" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="D16" s="210" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="E16" s="210" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="F16" s="210" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="H16" s="208" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="204" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B17" s="210" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C17" s="210" t="s">
+        <v>962</v>
+      </c>
+      <c r="D17" s="210" t="s">
+        <v>963</v>
+      </c>
+      <c r="E17" s="210" t="s">
         <v>958</v>
       </c>
-      <c r="D17" s="210" t="s">
-        <v>959</v>
-      </c>
-      <c r="E17" s="210" t="s">
-        <v>954</v>
-      </c>
       <c r="F17" s="210" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="H17" s="208" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="204" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="B18" s="210" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C18" s="210" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="D18" s="210" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="E18" s="210" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="F18" s="210" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="H18" s="208" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="204" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B19" s="210" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="C19" s="210" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="D19" s="210" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="E19" s="210" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="F19" s="210" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="G19" s="209" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="H19" s="209" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="213" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B20" s="208" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C20" s="208" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="G20" s="209" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="H20" s="208" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="204" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C21" s="210" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D21" s="210" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="E21" s="210" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="G21" s="212" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="H21" s="208" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="204" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B22" s="210" t="s">
+        <v>987</v>
+      </c>
+      <c r="C22" s="210" t="s">
+        <v>988</v>
+      </c>
+      <c r="D22" s="210" t="s">
         <v>983</v>
       </c>
-      <c r="C22" s="210" t="s">
-        <v>984</v>
-      </c>
-      <c r="D22" s="210" t="s">
-        <v>979</v>
-      </c>
       <c r="E22" s="210" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="F22" s="210" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="G22" s="209" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="H22" s="208" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="204" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="B23" s="210" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C23" s="210" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D23" s="210" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="E23" s="210" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="F23" s="210" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="G23" s="209" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="H23" s="208" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="204" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="B24" s="210" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C24" s="210" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D24" s="210" t="s">
         <v>156</v>
       </c>
       <c r="E24" s="210" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="H24" s="208" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="204" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="B25" s="210">
         <v>0.05</v>
@@ -17176,194 +17220,194 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="204" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B26" s="210" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="C26" s="210" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D26" s="210" t="s">
         <v>156</v>
       </c>
       <c r="E26" s="210" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="G26" s="209" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="H26" s="208" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="204" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B27" s="210" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="C27" s="210" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="D27" s="210" t="s">
         <v>156</v>
       </c>
       <c r="E27" s="210" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="H27" s="210" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="204" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="B28" s="210" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C28" s="210" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="D28" s="210" t="s">
         <v>156</v>
       </c>
       <c r="E28" s="210" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="G28" s="210" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="H28" s="208" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="204" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="B29" s="210" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="C29" s="210" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="D29" s="210" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E29" s="210" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="G29" s="209" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="H29" s="208" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="204" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="B30" s="210" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C30" s="210" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D30" s="210" t="s">
         <v>1009</v>
-      </c>
-      <c r="C30" s="210" t="s">
-        <v>1010</v>
-      </c>
-      <c r="D30" s="210" t="s">
-        <v>1005</v>
       </c>
       <c r="E30" s="210" t="s">
         <v>156</v>
       </c>
       <c r="G30" s="209" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="H30" s="208" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="204" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B31" s="210" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C31" s="210" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="D31" s="210" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E31" s="210" t="s">
         <v>156</v>
       </c>
       <c r="G31" s="209" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="H31" s="210" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="204" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B32" s="210" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="C32" s="210" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="D32" s="210" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E32" s="210" t="s">
         <v>156</v>
       </c>
       <c r="G32" s="209" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="H32" s="208" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="204" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="B33" s="210" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="C33" s="210" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="D33" s="210" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E33" s="210" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="G33" s="209" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="H33" s="208" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="204" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="B34" s="210" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="C34" s="210" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="D34" s="210">
         <v>1000</v>
@@ -17383,7 +17427,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="204" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="B35" s="210">
         <v>1.75</v>
@@ -17444,104 +17488,86 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1">
       <c r="A1" s="223" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B1" s="256"/>
-      <c r="C1" s="256"/>
-      <c r="D1" s="256"/>
-      <c r="E1" s="256"/>
-      <c r="F1" s="256"/>
-      <c r="G1" s="256"/>
-      <c r="H1" s="256"/>
-      <c r="I1" s="256"/>
-      <c r="J1" s="256"/>
-      <c r="K1" s="256"/>
-      <c r="L1" s="256"/>
+        <v>1033</v>
+      </c>
+      <c r="B1" s="220"/>
+      <c r="C1" s="220"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="224" t="s">
-        <v>1030</v>
-      </c>
-      <c r="B2" s="256"/>
-      <c r="C2" s="256"/>
-      <c r="D2" s="256"/>
-      <c r="E2" s="256"/>
-      <c r="F2" s="256"/>
-      <c r="G2" s="256"/>
-      <c r="H2" s="256"/>
-      <c r="I2" s="256"/>
-      <c r="J2" s="256"/>
-      <c r="K2" s="256"/>
-      <c r="L2" s="256"/>
+        <v>1034</v>
+      </c>
+      <c r="B2" s="220"/>
+      <c r="C2" s="220"/>
     </row>
     <row r="3" spans="1:12" s="222" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="246"/>
       <c r="B3" s="247"/>
       <c r="C3" s="247"/>
       <c r="D3" s="226" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="E3" s="226" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="F3" s="226" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="G3" s="226" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="H3" s="226" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="I3" s="226" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="J3" s="252" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="K3" s="226" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="L3" s="228" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="222" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
       <c r="A4" s="242" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="B4" s="243" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="C4" s="244" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="D4" s="244" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="E4" s="244" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="F4" s="244" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="G4" s="244" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="H4" s="244" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="I4" s="244" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="J4" s="244" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="K4" s="244" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="L4" s="245" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
@@ -17549,7 +17575,7 @@
         <v>675</v>
       </c>
       <c r="B5" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C5" s="239">
         <v>0</v>
@@ -17587,10 +17613,10 @@
         <v>676</v>
       </c>
       <c r="B6" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C6" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D6" s="239">
         <v>90</v>
@@ -17622,10 +17648,10 @@
     </row>
     <row r="7" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="237" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B7" s="238" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C7" s="239">
         <v>0</v>
@@ -17660,10 +17686,10 @@
     </row>
     <row r="8" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="248" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="B8" s="238" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C8" s="239">
         <v>0</v>
@@ -17698,11 +17724,11 @@
     </row>
     <row r="9" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="237" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="B9" s="238"/>
       <c r="C9" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D9" s="239">
         <v>158</v>
@@ -17734,13 +17760,13 @@
     </row>
     <row r="10" spans="1:12" s="222" customFormat="1" ht="17.25" customHeight="1">
       <c r="A10" s="248" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="B10" s="238" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C10" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D10" s="239">
         <v>165</v>
@@ -17772,13 +17798,13 @@
     </row>
     <row r="11" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="237" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="B11" s="238" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C11" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D11" s="239">
         <v>165</v>
@@ -17810,7 +17836,7 @@
     </row>
     <row r="12" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="237" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="B12" s="238"/>
       <c r="C12" s="239">
@@ -17846,10 +17872,10 @@
     </row>
     <row r="13" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A13" s="248" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="B13" s="238" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C13" s="239">
         <v>0</v>
@@ -17884,11 +17910,11 @@
     </row>
     <row r="14" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A14" s="248" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="B14" s="238"/>
       <c r="C14" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D14" s="239">
         <v>170</v>
@@ -17903,10 +17929,10 @@
         <v>100</v>
       </c>
       <c r="H14" s="239" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="I14" s="240" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="J14" s="239">
         <v>158</v>
@@ -17920,13 +17946,13 @@
     </row>
     <row r="15" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="237" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="B15" s="238" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="C15" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D15" s="239">
         <v>105</v>
@@ -17958,13 +17984,13 @@
     </row>
     <row r="16" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A16" s="237" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="B16" s="238" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="C16" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D16" s="239">
         <v>70</v>
@@ -17996,13 +18022,13 @@
     </row>
     <row r="17" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A17" s="248" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="B17" s="238" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C17" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D17" s="239">
         <v>143</v>
@@ -18034,13 +18060,13 @@
     </row>
     <row r="18" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="237" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B18" s="238" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="C18" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D18" s="239">
         <v>60</v>
@@ -18072,13 +18098,13 @@
     </row>
     <row r="19" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="237" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B19" s="238" t="s">
         <v>1066</v>
       </c>
-      <c r="B19" s="238" t="s">
-        <v>1062</v>
-      </c>
       <c r="C19" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D19" s="239">
         <v>60</v>
@@ -18110,10 +18136,10 @@
     </row>
     <row r="20" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="237" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="B20" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C20" s="239">
         <v>0</v>
@@ -18148,11 +18174,11 @@
     </row>
     <row r="21" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A21" s="237" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="B21" s="238"/>
       <c r="C21" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D21" s="239">
         <v>143</v>
@@ -18184,11 +18210,11 @@
     </row>
     <row r="22" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="248" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="B22" s="238"/>
       <c r="C22" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D22" s="239">
         <v>137</v>
@@ -18220,11 +18246,11 @@
     </row>
     <row r="23" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A23" s="248" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B23" s="238"/>
       <c r="C23" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D23" s="239">
         <v>126</v>
@@ -18256,11 +18282,11 @@
     </row>
     <row r="24" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="248" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B24" s="238"/>
       <c r="C24" s="239" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D24" s="239">
         <v>80</v>
@@ -18292,13 +18318,13 @@
     </row>
     <row r="25" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="237" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="B25" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C25" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D25" s="239">
         <v>113</v>
@@ -18330,13 +18356,13 @@
     </row>
     <row r="26" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A26" s="237" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="B26" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C26" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D26" s="239">
         <v>113</v>
@@ -18368,13 +18394,13 @@
     </row>
     <row r="27" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A27" s="237" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="B27" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C27" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D27" s="239">
         <v>145</v>
@@ -18406,13 +18432,13 @@
     </row>
     <row r="28" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A28" s="249" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="B28" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C28" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D28" s="239">
         <v>70</v>
@@ -18444,13 +18470,13 @@
     </row>
     <row r="29" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="237" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B29" s="238" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="C29" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D29" s="239">
         <v>60</v>
@@ -18486,7 +18512,7 @@
       </c>
       <c r="B30" s="238"/>
       <c r="C30" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D30" s="239">
         <v>140</v>
@@ -18521,10 +18547,10 @@
         <v>821</v>
       </c>
       <c r="B31" s="238" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C31" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D31" s="239">
         <v>105</v>
@@ -18556,13 +18582,13 @@
     </row>
     <row r="32" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="248" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="B32" s="238" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C32" s="239" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="D32" s="239">
         <v>105</v>
@@ -18594,10 +18620,10 @@
     </row>
     <row r="33" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A33" s="248" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="B33" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C33" s="239">
         <v>0</v>
@@ -18629,14 +18655,13 @@
       <c r="L33" s="239">
         <v>2540</v>
       </c>
-      <c r="M33" s="255"/>
     </row>
     <row r="34" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="248" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="B34" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C34" s="239">
         <v>0</v>
@@ -18654,10 +18679,10 @@
         <v>50</v>
       </c>
       <c r="H34" s="239" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="I34" s="240" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="J34" s="239">
         <v>80</v>
@@ -18668,17 +18693,16 @@
       <c r="L34" s="239">
         <v>1600</v>
       </c>
-      <c r="M34" s="255"/>
     </row>
     <row r="35" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="248" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="B35" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C35" s="239" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D35" s="239">
         <v>90</v>
@@ -18707,17 +18731,16 @@
       <c r="L35" s="239">
         <v>1900</v>
       </c>
-      <c r="M35" s="255"/>
     </row>
     <row r="36" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="248" t="s">
         <v>822</v>
       </c>
       <c r="B36" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C36" s="239" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D36" s="239">
         <v>80</v>
@@ -18746,17 +18769,16 @@
       <c r="L36" s="239">
         <v>1600</v>
       </c>
-      <c r="M36" s="255"/>
     </row>
     <row r="37" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="248" t="s">
         <v>820</v>
       </c>
       <c r="B37" s="238" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C37" s="239" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="D37" s="239">
         <v>85</v>
@@ -18785,175 +18807,115 @@
       <c r="L37" s="239">
         <v>3500</v>
       </c>
-      <c r="M37" s="255"/>
     </row>
     <row r="38" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="227"/>
-      <c r="B38" s="311"/>
-      <c r="C38" s="311"/>
-      <c r="D38" s="312"/>
-      <c r="E38" s="312"/>
-      <c r="F38" s="312"/>
-      <c r="G38" s="312"/>
-      <c r="H38" s="312"/>
-      <c r="I38" s="312"/>
-      <c r="J38" s="312"/>
+      <c r="B38" s="314"/>
+      <c r="C38" s="314"/>
+      <c r="D38" s="315"/>
+      <c r="E38" s="315"/>
+      <c r="F38" s="315"/>
+      <c r="G38" s="315"/>
+      <c r="H38" s="315"/>
+      <c r="I38" s="315"/>
+      <c r="J38" s="315"/>
       <c r="K38" s="229"/>
       <c r="L38" s="229"/>
       <c r="M38" s="230"/>
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1">
       <c r="A39" s="225" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B39" s="310"/>
-      <c r="C39" s="310"/>
-      <c r="D39" s="256"/>
-      <c r="E39" s="256"/>
-      <c r="F39" s="256"/>
-      <c r="G39" s="256"/>
-      <c r="H39" s="256"/>
-      <c r="I39" s="256"/>
-      <c r="J39" s="256"/>
+        <v>1088</v>
+      </c>
+      <c r="B39" s="307"/>
+      <c r="C39" s="307"/>
       <c r="K39" s="231"/>
       <c r="L39" s="231"/>
       <c r="M39" s="232"/>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1">
-      <c r="B40" s="310"/>
-      <c r="C40" s="310"/>
-      <c r="D40" s="256"/>
-      <c r="E40" s="256"/>
-      <c r="F40" s="256"/>
-      <c r="G40" s="256"/>
-      <c r="H40" s="256"/>
-      <c r="I40" s="256"/>
-      <c r="J40" s="256"/>
+      <c r="B40" s="307"/>
+      <c r="C40" s="307"/>
       <c r="K40" s="231"/>
       <c r="L40" s="231"/>
       <c r="M40" s="232"/>
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1">
       <c r="A41" s="225" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B41" s="313"/>
-      <c r="C41" s="313"/>
-      <c r="D41" s="314"/>
-      <c r="E41" s="314"/>
-      <c r="F41" s="314"/>
-      <c r="G41" s="314"/>
-      <c r="H41" s="314"/>
-      <c r="I41" s="314"/>
-      <c r="J41" s="314"/>
-      <c r="K41" s="314"/>
-      <c r="L41" s="256"/>
+        <v>1089</v>
+      </c>
+      <c r="B41" s="316"/>
+      <c r="C41" s="316"/>
+      <c r="D41" s="317"/>
+      <c r="E41" s="317"/>
+      <c r="F41" s="317"/>
+      <c r="G41" s="317"/>
+      <c r="H41" s="317"/>
+      <c r="I41" s="317"/>
+      <c r="J41" s="317"/>
+      <c r="K41" s="317"/>
       <c r="M41" s="232"/>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A42" s="310" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B42" s="256"/>
-      <c r="C42" s="256"/>
-      <c r="D42" s="256"/>
-      <c r="E42" s="256"/>
-      <c r="F42" s="256"/>
-      <c r="G42" s="256"/>
-      <c r="H42" s="256"/>
-      <c r="I42" s="256"/>
+      <c r="A42" s="307" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B42" s="220"/>
+      <c r="C42" s="220"/>
       <c r="J42" s="231"/>
-      <c r="K42" s="256"/>
-      <c r="L42" s="256"/>
       <c r="M42" s="232"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A43" s="310" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B43" s="256"/>
-      <c r="C43" s="256"/>
-      <c r="D43" s="256"/>
-      <c r="E43" s="256"/>
-      <c r="F43" s="256"/>
-      <c r="G43" s="256"/>
-      <c r="H43" s="256"/>
-      <c r="I43" s="256"/>
+      <c r="A43" s="307" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B43" s="220"/>
+      <c r="C43" s="220"/>
       <c r="J43" s="231"/>
-      <c r="K43" s="256"/>
-      <c r="L43" s="256"/>
       <c r="M43" s="232"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A44" s="310" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B44" s="256"/>
-      <c r="C44" s="256"/>
-      <c r="D44" s="256"/>
-      <c r="E44" s="256"/>
-      <c r="F44" s="256"/>
-      <c r="G44" s="256"/>
-      <c r="H44" s="256"/>
-      <c r="I44" s="256"/>
-      <c r="J44" s="256"/>
-      <c r="K44" s="256"/>
-      <c r="L44" s="256"/>
+      <c r="A44" s="307" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B44" s="220"/>
+      <c r="C44" s="220"/>
       <c r="M44" s="232"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A45" s="310" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B45" s="256"/>
-      <c r="C45" s="256"/>
-      <c r="D45" s="256"/>
-      <c r="E45" s="256"/>
-      <c r="F45" s="256"/>
-      <c r="G45" s="256"/>
-      <c r="H45" s="256"/>
-      <c r="I45" s="256"/>
-      <c r="J45" s="256"/>
-      <c r="K45" s="256"/>
-      <c r="L45" s="256"/>
+      <c r="A45" s="307" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B45" s="220"/>
+      <c r="C45" s="220"/>
       <c r="M45" s="232"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A46" s="310" t="s">
-        <v>1090</v>
-      </c>
-      <c r="B46" s="256"/>
-      <c r="C46" s="256"/>
-      <c r="D46" s="256"/>
-      <c r="E46" s="256"/>
-      <c r="F46" s="256"/>
-      <c r="G46" s="256"/>
-      <c r="H46" s="256"/>
+      <c r="A46" s="307" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B46" s="220"/>
+      <c r="C46" s="220"/>
       <c r="I46" s="231"/>
       <c r="J46" s="231"/>
-      <c r="K46" s="256"/>
-      <c r="L46" s="256"/>
       <c r="M46" s="232"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
       <c r="A47" s="233" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="B47" s="233"/>
       <c r="C47" s="233"/>
       <c r="D47" s="233"/>
       <c r="E47" s="234"/>
       <c r="F47" s="234"/>
-      <c r="G47" s="294"/>
+      <c r="G47" s="292"/>
       <c r="H47" s="233"/>
       <c r="I47" s="233"/>
       <c r="J47" s="233"/>
-      <c r="K47" s="256"/>
-      <c r="L47" s="256"/>
       <c r="M47" s="232"/>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D48" s="256"/>
       <c r="E48" s="236"/>
       <c r="F48" s="236"/>
       <c r="G48" s="236"/>
@@ -18966,9 +18928,8 @@
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1">
       <c r="A49" s="250" t="s">
-        <v>1092</v>
-      </c>
-      <c r="D49" s="256"/>
+        <v>1096</v>
+      </c>
       <c r="E49" s="236"/>
       <c r="F49" s="236"/>
       <c r="G49" s="236"/>
@@ -18981,9 +18942,8 @@
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1">
       <c r="A50" s="250" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D50" s="256"/>
+        <v>1097</v>
+      </c>
       <c r="E50" s="236"/>
       <c r="F50" s="236"/>
       <c r="G50" s="236"/>
@@ -18995,8 +18955,7 @@
       <c r="M50" s="232"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A51" s="329"/>
-      <c r="D51" s="256"/>
+      <c r="A51" s="313"/>
       <c r="E51" s="236"/>
       <c r="F51" s="236"/>
       <c r="G51" s="236"/>
@@ -19009,7 +18968,6 @@
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1">
       <c r="A52" s="251"/>
-      <c r="D52" s="256"/>
       <c r="E52" s="236"/>
       <c r="F52" s="236"/>
       <c r="G52" s="236"/>
@@ -19021,7 +18979,6 @@
       <c r="M52" s="232"/>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D53" s="256"/>
       <c r="E53" s="236"/>
       <c r="F53" s="236"/>
       <c r="G53" s="236"/>
@@ -19033,7 +18990,6 @@
       <c r="M53" s="232"/>
     </row>
     <row r="54" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D54" s="256"/>
       <c r="E54" s="236"/>
       <c r="F54" s="236"/>
       <c r="G54" s="236"/>
@@ -19045,7 +19001,6 @@
       <c r="M54" s="232"/>
     </row>
     <row r="55" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D55" s="256"/>
       <c r="E55" s="236"/>
       <c r="F55" s="236"/>
       <c r="G55" s="236"/>
@@ -19057,7 +19012,6 @@
       <c r="M55" s="232"/>
     </row>
     <row r="56" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D56" s="256"/>
       <c r="E56" s="236"/>
       <c r="F56" s="236"/>
       <c r="G56" s="236"/>
@@ -19069,7 +19023,6 @@
       <c r="M56" s="232"/>
     </row>
     <row r="57" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D57" s="256"/>
       <c r="E57" s="236"/>
       <c r="F57" s="236"/>
       <c r="G57" s="236"/>
@@ -19081,7 +19034,6 @@
       <c r="M57" s="232"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D58" s="256"/>
       <c r="E58" s="236"/>
       <c r="F58" s="236"/>
       <c r="G58" s="236"/>
@@ -19093,7 +19045,6 @@
       <c r="M58" s="232"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D59" s="256"/>
       <c r="E59" s="236"/>
       <c r="F59" s="236"/>
       <c r="G59" s="236"/>
@@ -19105,7 +19056,6 @@
       <c r="M59" s="232"/>
     </row>
     <row r="60" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D60" s="256"/>
       <c r="E60" s="236"/>
       <c r="F60" s="236"/>
       <c r="G60" s="236"/>
@@ -19117,7 +19067,6 @@
       <c r="M60" s="232"/>
     </row>
     <row r="61" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D61" s="256"/>
       <c r="E61" s="236"/>
       <c r="F61" s="236"/>
       <c r="G61" s="236"/>
@@ -19129,7 +19078,6 @@
       <c r="M61" s="232"/>
     </row>
     <row r="62" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D62" s="256"/>
       <c r="E62" s="236"/>
       <c r="F62" s="236"/>
       <c r="G62" s="236"/>
@@ -19141,7 +19089,6 @@
       <c r="M62" s="232"/>
     </row>
     <row r="63" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D63" s="256"/>
       <c r="E63" s="236"/>
       <c r="F63" s="236"/>
       <c r="G63" s="236"/>
@@ -19153,7 +19100,6 @@
       <c r="M63" s="232"/>
     </row>
     <row r="64" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D64" s="256"/>
       <c r="E64" s="236"/>
       <c r="F64" s="236"/>
       <c r="G64" s="236"/>
@@ -26246,13 +26192,13 @@
       <c r="B1" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="263" t="s">
+      <c r="C1" s="261" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="263" t="s">
+      <c r="D1" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="263" t="s">
+      <c r="E1" s="261" t="s">
         <v>379</v>
       </c>
       <c r="F1" s="81"/>
@@ -26267,7 +26213,7 @@
       <c r="C2" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D2" s="278">
+      <c r="D2" s="276">
         <v>420</v>
       </c>
       <c r="E2" s="1">
@@ -26276,10 +26222,10 @@
       <c r="F2" s="82" t="s">
         <v>383</v>
       </c>
-      <c r="G2" s="279"/>
-      <c r="H2" s="279"/>
-      <c r="I2" s="279"/>
-      <c r="J2" s="279"/>
+      <c r="G2" s="277"/>
+      <c r="H2" s="277"/>
+      <c r="I2" s="277"/>
+      <c r="J2" s="277"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="47" t="s">
@@ -26291,19 +26237,19 @@
       <c r="C3" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D3" s="278">
+      <c r="D3" s="276">
         <v>368</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="280" t="s">
+      <c r="F3" s="278" t="s">
         <v>386</v>
       </c>
-      <c r="G3" s="279"/>
-      <c r="H3" s="279"/>
-      <c r="I3" s="279"/>
-      <c r="J3" s="279"/>
+      <c r="G3" s="277"/>
+      <c r="H3" s="277"/>
+      <c r="I3" s="277"/>
+      <c r="J3" s="277"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="47" t="s">
@@ -26315,19 +26261,19 @@
       <c r="C4" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D4" s="278">
+      <c r="D4" s="276">
         <v>172</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="280" t="s">
+      <c r="F4" s="278" t="s">
         <v>389</v>
       </c>
-      <c r="G4" s="279"/>
-      <c r="H4" s="279"/>
-      <c r="I4" s="279"/>
-      <c r="J4" s="279"/>
+      <c r="G4" s="277"/>
+      <c r="H4" s="277"/>
+      <c r="I4" s="277"/>
+      <c r="J4" s="277"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="47" t="s">
@@ -26339,19 +26285,19 @@
       <c r="C5" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D5" s="278">
+      <c r="D5" s="276">
         <v>420</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="280" t="s">
+      <c r="F5" s="278" t="s">
         <v>393</v>
       </c>
-      <c r="G5" s="279"/>
-      <c r="H5" s="279"/>
-      <c r="I5" s="279"/>
-      <c r="J5" s="279"/>
+      <c r="G5" s="277"/>
+      <c r="H5" s="277"/>
+      <c r="I5" s="277"/>
+      <c r="J5" s="277"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="23"/>
@@ -26361,17 +26307,17 @@
       <c r="C6" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D6" s="278">
+      <c r="D6" s="276">
         <v>480</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="83"/>
-      <c r="G6" s="279"/>
-      <c r="H6" s="279"/>
-      <c r="I6" s="279"/>
-      <c r="J6" s="279"/>
+      <c r="G6" s="277"/>
+      <c r="H6" s="277"/>
+      <c r="I6" s="277"/>
+      <c r="J6" s="277"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="23"/>
@@ -26381,17 +26327,17 @@
       <c r="C7" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D7" s="278">
+      <c r="D7" s="276">
         <v>750</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="83"/>
-      <c r="G7" s="279"/>
-      <c r="H7" s="279"/>
-      <c r="I7" s="279"/>
-      <c r="J7" s="279"/>
+      <c r="G7" s="277"/>
+      <c r="H7" s="277"/>
+      <c r="I7" s="277"/>
+      <c r="J7" s="277"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="23"/>
@@ -26401,15 +26347,15 @@
       <c r="C8" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D8" s="278"/>
+      <c r="D8" s="276"/>
       <c r="E8" s="1">
         <v>34</v>
       </c>
       <c r="F8" s="83"/>
-      <c r="G8" s="279"/>
-      <c r="H8" s="279"/>
-      <c r="I8" s="279"/>
-      <c r="J8" s="279"/>
+      <c r="G8" s="277"/>
+      <c r="H8" s="277"/>
+      <c r="I8" s="277"/>
+      <c r="J8" s="277"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="23"/>
@@ -26419,51 +26365,51 @@
       <c r="C9" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D9" s="278"/>
+      <c r="D9" s="276"/>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="83"/>
-      <c r="G9" s="279"/>
-      <c r="H9" s="279"/>
-      <c r="I9" s="279"/>
-      <c r="J9" s="279"/>
+      <c r="G9" s="277"/>
+      <c r="H9" s="277"/>
+      <c r="I9" s="277"/>
+      <c r="J9" s="277"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="23"/>
       <c r="B10" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="C10" s="268" t="s">
+      <c r="C10" s="266" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="278"/>
+      <c r="D10" s="276"/>
       <c r="E10" s="1">
         <v>81</v>
       </c>
       <c r="F10" s="83"/>
-      <c r="G10" s="279"/>
-      <c r="H10" s="279"/>
-      <c r="I10" s="279"/>
-      <c r="J10" s="279"/>
+      <c r="G10" s="277"/>
+      <c r="H10" s="277"/>
+      <c r="I10" s="277"/>
+      <c r="J10" s="277"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="23"/>
       <c r="B11" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="C11" s="268" t="s">
+      <c r="C11" s="266" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="278"/>
+      <c r="D11" s="276"/>
       <c r="E11" s="1">
         <v>8</v>
       </c>
       <c r="F11" s="87"/>
-      <c r="G11" s="279"/>
-      <c r="H11" s="279"/>
-      <c r="I11" s="279"/>
-      <c r="J11" s="279"/>
+      <c r="G11" s="277"/>
+      <c r="H11" s="277"/>
+      <c r="I11" s="277"/>
+      <c r="J11" s="277"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="47" t="s">
@@ -26472,72 +26418,72 @@
       <c r="B12" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="C12" s="268" t="s">
+      <c r="C12" s="266" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="278"/>
+      <c r="D12" s="276"/>
       <c r="E12" s="1">
         <v>78</v>
       </c>
       <c r="F12" s="91"/>
-      <c r="G12" s="279"/>
-      <c r="H12" s="279"/>
-      <c r="I12" s="279"/>
-      <c r="J12" s="279"/>
+      <c r="G12" s="277"/>
+      <c r="H12" s="277"/>
+      <c r="I12" s="277"/>
+      <c r="J12" s="277"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="23"/>
       <c r="B13" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="268" t="s">
+      <c r="C13" s="266" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="278"/>
+      <c r="D13" s="276"/>
       <c r="E13" s="1">
         <v>81</v>
       </c>
       <c r="F13" s="88"/>
-      <c r="G13" s="279"/>
-      <c r="H13" s="279"/>
-      <c r="I13" s="279"/>
-      <c r="J13" s="279"/>
+      <c r="G13" s="277"/>
+      <c r="H13" s="277"/>
+      <c r="I13" s="277"/>
+      <c r="J13" s="277"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="23"/>
       <c r="B14" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="C14" s="268" t="s">
+      <c r="C14" s="266" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="278"/>
+      <c r="D14" s="276"/>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="87"/>
-      <c r="G14" s="279"/>
-      <c r="H14" s="279"/>
-      <c r="I14" s="279"/>
-      <c r="J14" s="279"/>
+      <c r="G14" s="277"/>
+      <c r="H14" s="277"/>
+      <c r="I14" s="277"/>
+      <c r="J14" s="277"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="23"/>
       <c r="B15" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="268" t="s">
+      <c r="C15" s="266" t="s">
         <v>160</v>
       </c>
-      <c r="D15" s="278"/>
+      <c r="D15" s="276"/>
       <c r="E15" s="1">
         <v>24</v>
       </c>
       <c r="F15" s="88"/>
-      <c r="G15" s="279"/>
-      <c r="H15" s="279"/>
-      <c r="I15" s="279"/>
-      <c r="J15" s="279"/>
+      <c r="G15" s="277"/>
+      <c r="H15" s="277"/>
+      <c r="I15" s="277"/>
+      <c r="J15" s="277"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="92" t="s">
@@ -26549,15 +26495,15 @@
       <c r="C16" s="86" t="s">
         <v>405</v>
       </c>
-      <c r="D16" s="278"/>
+      <c r="D16" s="276"/>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="84"/>
-      <c r="G16" s="279"/>
-      <c r="H16" s="279"/>
-      <c r="I16" s="279"/>
-      <c r="J16" s="279"/>
+      <c r="G16" s="277"/>
+      <c r="H16" s="277"/>
+      <c r="I16" s="277"/>
+      <c r="J16" s="277"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="23"/>
@@ -26567,12 +26513,12 @@
       <c r="C17" s="85" t="s">
         <v>407</v>
       </c>
-      <c r="D17" s="278"/>
+      <c r="D17" s="276"/>
       <c r="E17" s="1">
         <v>4</v>
       </c>
       <c r="F17" s="87"/>
-      <c r="G17" s="279"/>
+      <c r="G17" s="277"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="23"/>
@@ -26582,12 +26528,12 @@
       <c r="C18" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D18" s="278"/>
+      <c r="D18" s="276"/>
       <c r="E18" s="1">
         <v>4</v>
       </c>
       <c r="F18" s="87"/>
-      <c r="G18" s="279"/>
+      <c r="G18" s="277"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="57"/>
@@ -26597,18 +26543,18 @@
       <c r="C19" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D19" s="281"/>
+      <c r="D19" s="279"/>
       <c r="E19" s="40">
         <v>4</v>
       </c>
       <c r="F19" s="89"/>
-      <c r="G19" s="279"/>
+      <c r="G19" s="277"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="B20" s="279"/>
-      <c r="C20" s="279"/>
-      <c r="E20" s="279"/>
-      <c r="G20" s="279"/>
+      <c r="B20" s="277"/>
+      <c r="C20" s="277"/>
+      <c r="E20" s="277"/>
+      <c r="G20" s="277"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26658,10 +26604,10 @@
       <c r="B1" s="97" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="282" t="s">
+      <c r="C1" s="280" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="282" t="s">
+      <c r="D1" s="280" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="98"/>
@@ -26672,7 +26618,7 @@
       <c r="A2" s="99" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="268" t="s">
+      <c r="B2" s="266" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="26"/>
@@ -26696,7 +26642,7 @@
       <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="283" t="s">
+      <c r="E3" s="281" t="s">
         <v>386</v>
       </c>
       <c r="G3"/>
@@ -26706,14 +26652,14 @@
       <c r="A4" s="101" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="268" t="s">
+      <c r="B4" s="266" t="s">
         <v>172</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="13">
         <v>36</v>
       </c>
-      <c r="E4" s="283" t="s">
+      <c r="E4" s="281" t="s">
         <v>389</v>
       </c>
       <c r="G4"/>
@@ -26723,14 +26669,14 @@
       <c r="A5" s="101" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="268" t="s">
+      <c r="B5" s="266" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="13">
         <v>24</v>
       </c>
-      <c r="E5" s="283" t="s">
+      <c r="E5" s="281" t="s">
         <v>393</v>
       </c>
       <c r="G5"/>
@@ -26738,7 +26684,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="102"/>
-      <c r="B6" s="268" t="s">
+      <c r="B6" s="266" t="s">
         <v>338</v>
       </c>
       <c r="C6" s="26"/>
@@ -26751,7 +26697,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="102"/>
-      <c r="B7" s="268" t="s">
+      <c r="B7" s="266" t="s">
         <v>340</v>
       </c>
       <c r="C7" s="26"/>
@@ -26764,7 +26710,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="102"/>
-      <c r="B8" s="268" t="s">
+      <c r="B8" s="266" t="s">
         <v>411</v>
       </c>
       <c r="C8" s="26"/>
@@ -26833,7 +26779,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="102"/>
-      <c r="B13" s="268" t="s">
+      <c r="B13" s="266" t="s">
         <v>416</v>
       </c>
       <c r="C13" s="26"/>
@@ -26848,7 +26794,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="102"/>
-      <c r="B14" s="268" t="s">
+      <c r="B14" s="266" t="s">
         <v>418</v>
       </c>
       <c r="C14" s="26"/>
@@ -27004,7 +26950,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="102"/>
-      <c r="B26" s="268" t="s">
+      <c r="B26" s="266" t="s">
         <v>422</v>
       </c>
       <c r="C26" s="95" t="s">
@@ -27019,7 +26965,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="102"/>
-      <c r="B27" s="268" t="s">
+      <c r="B27" s="266" t="s">
         <v>424</v>
       </c>
       <c r="C27" s="95" t="s">
@@ -27034,7 +26980,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="102"/>
-      <c r="B28" s="268" t="s">
+      <c r="B28" s="266" t="s">
         <v>426</v>
       </c>
       <c r="C28" s="26"/>
@@ -27057,7 +27003,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="103"/>
-      <c r="F29" s="268"/>
+      <c r="F29" s="266"/>
       <c r="G29"/>
       <c r="H29"/>
     </row>
@@ -27066,14 +27012,14 @@
       <c r="B30" s="36" t="s">
         <v>428</v>
       </c>
-      <c r="C30" s="268" t="s">
+      <c r="C30" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D30" s="13">
         <v>4</v>
       </c>
       <c r="E30" s="103"/>
-      <c r="F30" s="268"/>
+      <c r="F30" s="266"/>
       <c r="G30"/>
       <c r="H30"/>
     </row>
@@ -27082,15 +27028,15 @@
       <c r="B31" t="s">
         <v>429</v>
       </c>
-      <c r="C31" s="268" t="s">
+      <c r="C31" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D31" s="13">
         <v>2</v>
       </c>
       <c r="E31" s="103"/>
-      <c r="F31" s="268"/>
-      <c r="G31" s="268"/>
+      <c r="F31" s="266"/>
+      <c r="G31" s="266"/>
       <c r="H31"/>
     </row>
     <row r="32" spans="1:8">
@@ -27098,14 +27044,14 @@
       <c r="B32" t="s">
         <v>430</v>
       </c>
-      <c r="C32" s="268" t="s">
+      <c r="C32" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D32" s="13">
         <v>1</v>
       </c>
       <c r="E32" s="103"/>
-      <c r="F32" s="268"/>
+      <c r="F32" s="266"/>
       <c r="G32"/>
       <c r="H32"/>
     </row>
@@ -27114,14 +27060,14 @@
       <c r="B33" s="36" t="s">
         <v>431</v>
       </c>
-      <c r="C33" s="268" t="s">
+      <c r="C33" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D33" s="13">
         <v>1</v>
       </c>
       <c r="E33" s="103"/>
-      <c r="F33" s="268"/>
+      <c r="F33" s="266"/>
       <c r="G33"/>
       <c r="H33"/>
     </row>
@@ -27130,14 +27076,14 @@
       <c r="B34" t="s">
         <v>432</v>
       </c>
-      <c r="C34" s="268" t="s">
+      <c r="C34" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D34" s="13">
         <v>1</v>
       </c>
       <c r="E34" s="103"/>
-      <c r="F34" s="268"/>
+      <c r="F34" s="266"/>
       <c r="G34"/>
       <c r="H34"/>
     </row>
@@ -27146,14 +27092,14 @@
       <c r="B35" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C35" s="268" t="s">
+      <c r="C35" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D35" s="13">
         <v>1</v>
       </c>
       <c r="E35" s="103"/>
-      <c r="F35" s="268"/>
+      <c r="F35" s="266"/>
       <c r="G35"/>
       <c r="H35"/>
     </row>
@@ -27162,14 +27108,14 @@
       <c r="B36" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C36" s="268" t="s">
+      <c r="C36" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D36" s="13">
         <v>1</v>
       </c>
       <c r="E36" s="103"/>
-      <c r="F36" s="268"/>
+      <c r="F36" s="266"/>
       <c r="G36"/>
       <c r="H36"/>
     </row>
@@ -27178,14 +27124,14 @@
       <c r="B37" s="36" t="s">
         <v>435</v>
       </c>
-      <c r="C37" s="268" t="s">
+      <c r="C37" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D37" s="13">
         <v>2</v>
       </c>
       <c r="E37" s="103"/>
-      <c r="F37" s="268"/>
+      <c r="F37" s="266"/>
       <c r="G37"/>
       <c r="H37"/>
     </row>
@@ -27194,14 +27140,14 @@
       <c r="B38" s="36" t="s">
         <v>436</v>
       </c>
-      <c r="C38" s="268" t="s">
+      <c r="C38" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D38" s="13">
         <v>2</v>
       </c>
       <c r="E38" s="103"/>
-      <c r="F38" s="268"/>
+      <c r="F38" s="266"/>
       <c r="G38" s="1"/>
       <c r="H38"/>
     </row>
@@ -27210,14 +27156,14 @@
       <c r="B39" s="36" t="s">
         <v>437</v>
       </c>
-      <c r="C39" s="268" t="s">
+      <c r="C39" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D39" s="13">
         <v>1</v>
       </c>
       <c r="E39" s="103"/>
-      <c r="F39" s="268"/>
+      <c r="F39" s="266"/>
       <c r="G39"/>
       <c r="H39"/>
     </row>
@@ -27226,14 +27172,14 @@
       <c r="B40" s="36" t="s">
         <v>438</v>
       </c>
-      <c r="C40" s="268" t="s">
+      <c r="C40" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D40" s="13">
         <v>1</v>
       </c>
       <c r="E40" s="103"/>
-      <c r="F40" s="268"/>
+      <c r="F40" s="266"/>
       <c r="G40"/>
       <c r="H40"/>
     </row>
@@ -27242,14 +27188,14 @@
       <c r="B41" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C41" s="268" t="s">
+      <c r="C41" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D41" s="13">
         <v>1</v>
       </c>
       <c r="E41" s="103"/>
-      <c r="F41" s="268"/>
+      <c r="F41" s="266"/>
       <c r="G41"/>
       <c r="H41"/>
     </row>
@@ -27258,14 +27204,14 @@
       <c r="B42" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C42" s="268" t="s">
+      <c r="C42" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D42" s="13">
         <v>1</v>
       </c>
       <c r="E42" s="103"/>
-      <c r="F42" s="268"/>
+      <c r="F42" s="266"/>
       <c r="G42"/>
       <c r="H42"/>
     </row>
@@ -27274,14 +27220,14 @@
       <c r="B43" s="36" t="s">
         <v>441</v>
       </c>
-      <c r="C43" s="268" t="s">
+      <c r="C43" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D43" s="13">
         <v>1</v>
       </c>
       <c r="E43" s="103"/>
-      <c r="F43" s="268"/>
+      <c r="F43" s="266"/>
       <c r="G43"/>
       <c r="H43"/>
     </row>
@@ -27290,19 +27236,19 @@
       <c r="B44" s="36" t="s">
         <v>442</v>
       </c>
-      <c r="C44" s="284" t="s">
+      <c r="C44" s="282" t="s">
         <v>405</v>
       </c>
       <c r="D44" s="106">
         <v>1</v>
       </c>
       <c r="E44" s="107"/>
-      <c r="F44" s="268"/>
+      <c r="F44" s="266"/>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="F45" s="268"/>
+      <c r="F45" s="266"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27353,10 +27299,10 @@
       <c r="B1" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="263" t="s">
+      <c r="C1" s="261" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="263" t="s">
+      <c r="D1" s="261" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -27365,7 +27311,7 @@
       <c r="A2" s="50" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="268" t="s">
+      <c r="B2" s="266" t="s">
         <v>443</v>
       </c>
       <c r="C2"/>
@@ -27380,14 +27326,14 @@
       <c r="A3" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="265" t="s">
+      <c r="B3" s="263" t="s">
         <v>352</v>
       </c>
-      <c r="C3" s="265"/>
+      <c r="C3" s="263"/>
       <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="285" t="s">
+      <c r="E3" s="283" t="s">
         <v>386</v>
       </c>
     </row>
@@ -27395,14 +27341,14 @@
       <c r="A4" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="265" t="s">
+      <c r="B4" s="263" t="s">
         <v>444</v>
       </c>
-      <c r="C4" s="265"/>
+      <c r="C4" s="263"/>
       <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="285" t="s">
+      <c r="E4" s="283" t="s">
         <v>389</v>
       </c>
     </row>
@@ -27417,7 +27363,7 @@
       <c r="D5" s="13">
         <v>1</v>
       </c>
-      <c r="E5" s="285" t="s">
+      <c r="E5" s="283" t="s">
         <v>393</v>
       </c>
     </row>
@@ -27560,7 +27506,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="23"/>
-      <c r="B18" s="286" t="s">
+      <c r="B18" s="284" t="s">
         <v>456</v>
       </c>
       <c r="C18" s="64" t="s">
@@ -27584,10 +27530,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23"/>
-      <c r="B20" s="287" t="s">
+      <c r="B20" s="285" t="s">
         <v>459</v>
       </c>
-      <c r="C20" s="287"/>
+      <c r="C20" s="285"/>
       <c r="D20" s="13">
         <v>1</v>
       </c>
@@ -27606,10 +27552,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="23"/>
-      <c r="B22" s="287" t="s">
+      <c r="B22" s="285" t="s">
         <v>461</v>
       </c>
-      <c r="C22" s="287"/>
+      <c r="C22" s="285"/>
       <c r="D22" s="13">
         <v>1</v>
       </c>
@@ -27663,7 +27609,7 @@
       <c r="A27" s="23"/>
       <c r="B27" s="60"/>
       <c r="C27" s="60"/>
-      <c r="D27" s="279"/>
+      <c r="D27" s="277"/>
       <c r="E27" s="52"/>
     </row>
     <row r="28" spans="1:5" ht="18.75">
@@ -27680,10 +27626,10 @@
       <c r="B29" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="C29" s="288" t="s">
+      <c r="C29" s="286" t="s">
         <v>378</v>
       </c>
-      <c r="D29" s="289" t="s">
+      <c r="D29" s="287" t="s">
         <v>379</v>
       </c>
       <c r="E29" s="52"/>
@@ -27759,7 +27705,7 @@
       <c r="B36" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="C36" s="287"/>
+      <c r="C36" s="285"/>
       <c r="D36" s="43">
         <v>1</v>
       </c>
@@ -27844,10 +27790,10 @@
       <c r="B1" s="97" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="282" t="s">
+      <c r="C1" s="280" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="282" t="s">
+      <c r="D1" s="280" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="98"/>
@@ -27856,11 +27802,10 @@
       <c r="A2" s="99" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="317" t="s">
+      <c r="B2" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="316"/>
-      <c r="D2" s="318">
+      <c r="D2" s="13">
         <v>12</v>
       </c>
       <c r="E2" s="100" t="s">
@@ -27871,14 +27816,14 @@
       <c r="A3" s="101" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="319" t="s">
+      <c r="B3" s="266" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="319"/>
-      <c r="D3" s="318">
+      <c r="C3" s="266"/>
+      <c r="D3" s="13">
         <v>12</v>
       </c>
-      <c r="E3" s="283" t="s">
+      <c r="E3" s="281" t="s">
         <v>386</v>
       </c>
     </row>
@@ -27886,14 +27831,14 @@
       <c r="A4" s="101" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="319" t="s">
+      <c r="B4" s="266" t="s">
         <v>330</v>
       </c>
-      <c r="C4" s="319"/>
-      <c r="D4" s="318">
+      <c r="C4" s="266"/>
+      <c r="D4" s="13">
         <v>3</v>
       </c>
-      <c r="E4" s="283" t="s">
+      <c r="E4" s="281" t="s">
         <v>389</v>
       </c>
     </row>
@@ -27901,83 +27846,82 @@
       <c r="A5" s="101" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="319" t="s">
+      <c r="B5" s="266" t="s">
         <v>336</v>
       </c>
-      <c r="C5" s="319"/>
-      <c r="D5" s="318">
+      <c r="C5" s="266"/>
+      <c r="D5" s="13">
         <v>6</v>
       </c>
-      <c r="E5" s="283" t="s">
+      <c r="E5" s="281" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="102"/>
-      <c r="B6" s="320" t="s">
+      <c r="B6" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="C6" s="319" t="s">
+      <c r="C6" s="266" t="s">
         <v>323</v>
       </c>
-      <c r="D6" s="321">
+      <c r="D6" s="272">
         <v>1</v>
       </c>
       <c r="E6" s="103"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="102"/>
-      <c r="B7" s="322" t="s">
+      <c r="B7" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="C7" s="319" t="s">
+      <c r="C7" s="266" t="s">
         <v>473</v>
       </c>
-      <c r="D7" s="321">
+      <c r="D7" s="272">
         <v>28</v>
       </c>
       <c r="E7" s="103"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="102"/>
-      <c r="B8" s="319" t="s">
+      <c r="B8" s="266" t="s">
         <v>474</v>
       </c>
-      <c r="C8" s="319"/>
-      <c r="D8" s="318">
+      <c r="C8" s="266"/>
+      <c r="D8" s="13">
         <v>1</v>
       </c>
       <c r="E8" s="103"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="102"/>
-      <c r="B9" s="323" t="s">
+      <c r="B9" s="36" t="s">
         <v>475</v>
       </c>
-      <c r="C9" s="316"/>
-      <c r="D9" s="318">
+      <c r="D9" s="13">
         <v>3</v>
       </c>
       <c r="E9" s="103"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="102"/>
-      <c r="B10" s="319" t="s">
+      <c r="B10" s="266" t="s">
         <v>254</v>
       </c>
-      <c r="C10" s="319"/>
-      <c r="D10" s="321">
+      <c r="C10" s="266"/>
+      <c r="D10" s="272">
         <v>6</v>
       </c>
       <c r="E10" s="103"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="102"/>
-      <c r="B11" s="319" t="s">
+      <c r="B11" s="266" t="s">
         <v>476</v>
       </c>
-      <c r="C11" s="319"/>
-      <c r="D11" s="321">
+      <c r="C11" s="266"/>
+      <c r="D11" s="272">
         <v>3</v>
       </c>
       <c r="E11" s="103"/>
@@ -27986,391 +27930,376 @@
       <c r="A12" s="101" t="s">
         <v>401</v>
       </c>
-      <c r="B12" s="324" t="s">
+      <c r="B12" s="262" t="s">
         <v>477</v>
       </c>
-      <c r="C12" s="319"/>
-      <c r="D12" s="318">
+      <c r="C12" s="266"/>
+      <c r="D12" s="13">
         <v>1</v>
       </c>
       <c r="E12" s="103"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="102"/>
-      <c r="B13" s="319" t="s">
+      <c r="B13" s="266" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="319"/>
-      <c r="D13" s="318">
+      <c r="C13" s="266"/>
+      <c r="D13" s="13">
         <v>42</v>
       </c>
       <c r="E13" s="103"/>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="102"/>
-      <c r="B14" s="316" t="s">
+      <c r="B14" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="C14" s="316"/>
-      <c r="D14" s="318">
+      <c r="D14" s="13">
         <v>3</v>
       </c>
       <c r="E14" s="103"/>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="102"/>
-      <c r="B15" s="316" t="s">
+      <c r="B15" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="C15" s="316"/>
-      <c r="D15" s="318">
+      <c r="D15" s="13">
         <v>27</v>
       </c>
       <c r="E15" s="103"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="102"/>
-      <c r="B16" s="316" t="s">
+      <c r="B16" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C16" s="316"/>
-      <c r="D16" s="318">
+      <c r="D16" s="13">
         <v>54</v>
       </c>
       <c r="E16" s="103"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="102"/>
-      <c r="B17" s="316" t="s">
+      <c r="B17" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C17" s="316"/>
-      <c r="D17" s="318">
+      <c r="D17" s="13">
         <v>8</v>
       </c>
       <c r="E17" s="103"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="102"/>
-      <c r="B18" s="316" t="s">
+      <c r="B18" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C18" s="316"/>
-      <c r="D18" s="318">
+      <c r="D18" s="13">
         <v>7</v>
       </c>
       <c r="E18" s="103"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="102"/>
-      <c r="B19" s="316" t="s">
+      <c r="B19" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="C19" s="316"/>
-      <c r="D19" s="318">
+      <c r="D19" s="13">
         <v>3</v>
       </c>
       <c r="E19" s="103"/>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="102"/>
-      <c r="B20" s="316" t="s">
+      <c r="B20" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C20" s="316"/>
-      <c r="D20" s="318">
+      <c r="D20" s="13">
         <v>3</v>
       </c>
       <c r="E20" s="103"/>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="102"/>
-      <c r="B21" s="316" t="s">
+      <c r="B21" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C21" s="316"/>
-      <c r="D21" s="318">
+      <c r="D21" s="13">
         <v>3</v>
       </c>
       <c r="E21" s="103"/>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="102"/>
-      <c r="B22" s="316" t="s">
+      <c r="B22" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C22" s="316"/>
-      <c r="D22" s="318">
+      <c r="D22" s="13">
         <v>3</v>
       </c>
       <c r="E22" s="103"/>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="102"/>
-      <c r="B23" s="316" t="s">
+      <c r="B23" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C23" s="316"/>
-      <c r="D23" s="318">
+      <c r="D23" s="13">
         <v>3</v>
       </c>
       <c r="E23" s="103"/>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="102"/>
-      <c r="B24" s="316" t="s">
+      <c r="B24" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C24" s="316"/>
-      <c r="D24" s="318">
+      <c r="D24" s="13">
         <v>24</v>
       </c>
       <c r="E24" s="103"/>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="102"/>
-      <c r="B25" s="319" t="s">
+      <c r="B25" s="266" t="s">
         <v>402</v>
       </c>
-      <c r="C25" s="319"/>
-      <c r="D25" s="318">
+      <c r="C25" s="266"/>
+      <c r="D25" s="13">
         <v>6</v>
       </c>
       <c r="E25" s="103"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="102"/>
-      <c r="B26" s="319" t="s">
+      <c r="B26" s="266" t="s">
         <v>229</v>
       </c>
-      <c r="C26" s="319"/>
-      <c r="D26" s="318">
+      <c r="C26" s="266"/>
+      <c r="D26" s="13">
         <v>21</v>
       </c>
       <c r="E26" s="103"/>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="102"/>
-      <c r="B27" s="316" t="s">
+      <c r="B27" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C27" s="316"/>
-      <c r="D27" s="318">
+      <c r="D27" s="13">
         <v>3</v>
       </c>
       <c r="E27" s="103"/>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="102"/>
-      <c r="B28" s="316" t="s">
+      <c r="B28" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="C28" s="316"/>
-      <c r="D28" s="318">
+      <c r="D28" s="13">
         <v>3</v>
       </c>
       <c r="E28" s="103"/>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="102"/>
-      <c r="B29" s="316" t="s">
+      <c r="B29" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="C29" s="316"/>
-      <c r="D29" s="318">
+      <c r="D29" s="13">
         <v>3</v>
       </c>
       <c r="E29" s="103"/>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="102"/>
-      <c r="B30" s="316" t="s">
+      <c r="B30" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C30" s="316"/>
-      <c r="D30" s="318">
+      <c r="D30" s="13">
         <v>3</v>
       </c>
       <c r="E30" s="103"/>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="102"/>
-      <c r="B31" s="316" t="s">
+      <c r="B31" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="C31" s="316" t="s">
+      <c r="C31" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D31" s="318">
+      <c r="D31" s="13">
         <v>1</v>
       </c>
       <c r="E31" s="103"/>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="102"/>
-      <c r="B32" s="316" t="s">
+      <c r="B32" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="C32" s="316" t="s">
+      <c r="C32" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D32" s="318">
+      <c r="D32" s="13">
         <v>1</v>
       </c>
       <c r="E32" s="103"/>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="102"/>
-      <c r="B33" s="316" t="s">
+      <c r="B33" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="C33" s="316" t="s">
+      <c r="C33" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D33" s="318">
+      <c r="D33" s="13">
         <v>1</v>
       </c>
       <c r="E33" s="103"/>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="102"/>
-      <c r="B34" s="316" t="s">
+      <c r="B34" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="C34" s="316" t="s">
+      <c r="C34" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D34" s="318">
+      <c r="D34" s="13">
         <v>2</v>
       </c>
       <c r="E34" s="103"/>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="102"/>
-      <c r="B35" s="316" t="s">
+      <c r="B35" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="C35" s="316" t="s">
+      <c r="C35" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D35" s="318">
+      <c r="D35" s="13">
         <v>1</v>
       </c>
       <c r="E35" s="103"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="102"/>
-      <c r="B36" s="316" t="s">
+      <c r="B36" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="C36" s="316" t="s">
+      <c r="C36" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D36" s="318">
+      <c r="D36" s="13">
         <v>1</v>
       </c>
       <c r="E36" s="103"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="102"/>
-      <c r="B37" s="319" t="s">
+      <c r="B37" s="266" t="s">
         <v>493</v>
       </c>
-      <c r="C37" s="316" t="s">
+      <c r="C37" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D37" s="318">
+      <c r="D37" s="13">
         <v>1</v>
       </c>
       <c r="E37" s="103"/>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="102"/>
-      <c r="B38" s="316" t="s">
+      <c r="B38" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="C38" s="316" t="s">
+      <c r="C38" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D38" s="318">
+      <c r="D38" s="13">
         <v>1</v>
       </c>
       <c r="E38" s="103"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="102"/>
-      <c r="B39" s="316" t="s">
+      <c r="B39" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C39" s="316" t="s">
+      <c r="C39" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D39" s="318">
+      <c r="D39" s="13">
         <v>1</v>
       </c>
       <c r="E39" s="103"/>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="102"/>
-      <c r="B40" s="316" t="s">
+      <c r="B40" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="C40" s="316" t="s">
+      <c r="C40" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D40" s="318">
+      <c r="D40" s="13">
         <v>1</v>
       </c>
       <c r="E40" s="103"/>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="102"/>
-      <c r="B41" s="316" t="s">
+      <c r="B41" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="C41" s="316" t="s">
+      <c r="C41" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D41" s="318">
+      <c r="D41" s="13">
         <v>1</v>
       </c>
       <c r="E41" s="103"/>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="102"/>
-      <c r="B42" s="316" t="s">
+      <c r="B42" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="C42" s="316" t="s">
+      <c r="C42" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D42" s="318">
+      <c r="D42" s="13">
         <v>3</v>
       </c>
       <c r="E42" s="103"/>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="102"/>
-      <c r="B43" s="316" t="s">
+      <c r="B43" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="C43" s="316" t="s">
+      <c r="C43" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D43" s="318">
+      <c r="D43" s="13">
         <v>1</v>
       </c>
       <c r="E43" s="103"/>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="102"/>
-      <c r="B44" s="316" t="s">
+      <c r="B44" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="C44" s="316" t="s">
+      <c r="C44" s="2" t="s">
         <v>487</v>
       </c>
-      <c r="D44" s="318">
+      <c r="D44" s="13">
         <v>1</v>
       </c>
       <c r="E44" s="103"/>
@@ -28380,7 +28309,7 @@
       <c r="B45" s="131" t="s">
         <v>501</v>
       </c>
-      <c r="C45" s="316" t="s">
+      <c r="C45" s="2" t="s">
         <v>487</v>
       </c>
       <c r="D45" s="106">
@@ -28438,10 +28367,10 @@
       <c r="B1" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="263" t="s">
+      <c r="C1" s="261" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="263" t="s">
+      <c r="D1" s="261" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -28453,7 +28382,7 @@
       <c r="B2" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="268"/>
+      <c r="C2" s="266"/>
       <c r="D2" s="13">
         <v>14</v>
       </c>
@@ -28468,11 +28397,11 @@
       <c r="B3" t="s">
         <v>503</v>
       </c>
-      <c r="C3" s="268"/>
+      <c r="C3" s="266"/>
       <c r="D3" s="13">
         <v>13</v>
       </c>
-      <c r="E3" s="285" t="s">
+      <c r="E3" s="283" t="s">
         <v>386</v>
       </c>
     </row>
@@ -28480,14 +28409,14 @@
       <c r="A4" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="268" t="s">
+      <c r="B4" s="266" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="268"/>
+      <c r="C4" s="266"/>
       <c r="D4" s="13">
         <v>2</v>
       </c>
-      <c r="E4" s="285" t="s">
+      <c r="E4" s="283" t="s">
         <v>389</v>
       </c>
     </row>
@@ -28498,20 +28427,20 @@
       <c r="B5" t="s">
         <v>504</v>
       </c>
-      <c r="C5" s="268"/>
+      <c r="C5" s="266"/>
       <c r="D5" s="13">
         <v>2</v>
       </c>
-      <c r="E5" s="285" t="s">
+      <c r="E5" s="283" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23"/>
-      <c r="B6" s="268" t="s">
+      <c r="B6" s="266" t="s">
         <v>505</v>
       </c>
-      <c r="C6" s="268"/>
+      <c r="C6" s="266"/>
       <c r="D6" s="13">
         <v>1</v>
       </c>
@@ -28519,10 +28448,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23"/>
-      <c r="B7" s="268" t="s">
+      <c r="B7" s="266" t="s">
         <v>506</v>
       </c>
-      <c r="C7" s="268"/>
+      <c r="C7" s="266"/>
       <c r="D7" s="13">
         <v>4</v>
       </c>
@@ -28533,7 +28462,7 @@
       <c r="B8" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C8" s="268"/>
+      <c r="C8" s="266"/>
       <c r="D8" s="13">
         <v>6</v>
       </c>
@@ -28544,7 +28473,7 @@
       <c r="B9" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C9" s="268"/>
+      <c r="C9" s="266"/>
       <c r="D9" s="13">
         <v>6</v>
       </c>
@@ -28555,7 +28484,7 @@
       <c r="B10" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="C10" s="269" t="s">
+      <c r="C10" s="267" t="s">
         <v>509</v>
       </c>
       <c r="D10" s="13">
@@ -28568,7 +28497,7 @@
       <c r="B11" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="C11" s="268"/>
+      <c r="C11" s="266"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
@@ -28576,10 +28505,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="23"/>
-      <c r="B12" s="268" t="s">
+      <c r="B12" s="266" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="268"/>
+      <c r="C12" s="266"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -28589,10 +28518,10 @@
       <c r="A13" s="47" t="s">
         <v>401</v>
       </c>
-      <c r="B13" s="268" t="s">
+      <c r="B13" s="266" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="268"/>
+      <c r="C13" s="266"/>
       <c r="D13" s="13">
         <v>1</v>
       </c>
@@ -28625,7 +28554,7 @@
       <c r="B16" t="s">
         <v>512</v>
       </c>
-      <c r="C16" s="268"/>
+      <c r="C16" s="266"/>
       <c r="D16" s="13">
         <v>4</v>
       </c>
@@ -28636,7 +28565,7 @@
       <c r="B17" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C17" s="268"/>
+      <c r="C17" s="266"/>
       <c r="D17" s="13">
         <v>19</v>
       </c>
@@ -28647,7 +28576,7 @@
       <c r="B18" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C18" s="268"/>
+      <c r="C18" s="266"/>
       <c r="D18" s="13">
         <v>6</v>
       </c>
@@ -28658,7 +28587,7 @@
       <c r="B19" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C19" s="268"/>
+      <c r="C19" s="266"/>
       <c r="D19" s="13">
         <v>13</v>
       </c>
@@ -28666,10 +28595,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23"/>
-      <c r="B20" s="268" t="s">
+      <c r="B20" s="266" t="s">
         <v>513</v>
       </c>
-      <c r="C20" s="268"/>
+      <c r="C20" s="266"/>
       <c r="D20" s="13">
         <v>4</v>
       </c>
@@ -28677,10 +28606,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="23"/>
-      <c r="B21" s="268" t="s">
+      <c r="B21" s="266" t="s">
         <v>514</v>
       </c>
-      <c r="C21" s="268"/>
+      <c r="C21" s="266"/>
       <c r="D21" s="13">
         <v>6</v>
       </c>
@@ -28691,7 +28620,7 @@
       <c r="B22" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="268"/>
+      <c r="C22" s="266"/>
       <c r="D22" s="13">
         <v>4</v>
       </c>
@@ -28702,7 +28631,7 @@
       <c r="B23" t="s">
         <v>515</v>
       </c>
-      <c r="C23" s="268"/>
+      <c r="C23" s="266"/>
       <c r="D23" s="13">
         <v>6</v>
       </c>
@@ -28713,7 +28642,7 @@
       <c r="B24" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="C24" s="268"/>
+      <c r="C24" s="266"/>
       <c r="D24" s="13">
         <v>4</v>
       </c>
@@ -28724,7 +28653,7 @@
       <c r="B25" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="268"/>
+      <c r="C25" s="266"/>
       <c r="D25" s="13">
         <v>4</v>
       </c>
@@ -28732,10 +28661,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="23"/>
-      <c r="B26" s="268" t="s">
+      <c r="B26" s="266" t="s">
         <v>516</v>
       </c>
-      <c r="C26" s="268"/>
+      <c r="C26" s="266"/>
       <c r="D26" s="13">
         <v>1</v>
       </c>
@@ -28743,10 +28672,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="23"/>
-      <c r="B27" s="268" t="s">
+      <c r="B27" s="266" t="s">
         <v>223</v>
       </c>
-      <c r="C27" s="268"/>
+      <c r="C27" s="266"/>
       <c r="D27" s="13">
         <v>16</v>
       </c>
@@ -28757,7 +28686,7 @@
       <c r="B28" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C28" s="268"/>
+      <c r="C28" s="266"/>
       <c r="D28" s="13">
         <v>52</v>
       </c>
@@ -28768,7 +28697,7 @@
       <c r="B29" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C29" s="268"/>
+      <c r="C29" s="266"/>
       <c r="D29" s="13">
         <v>77</v>
       </c>
@@ -28779,7 +28708,7 @@
       <c r="B30" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C30" s="268"/>
+      <c r="C30" s="266"/>
       <c r="D30" s="13">
         <v>16</v>
       </c>
@@ -28787,10 +28716,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="23"/>
-      <c r="B31" s="268" t="s">
+      <c r="B31" s="266" t="s">
         <v>517</v>
       </c>
-      <c r="C31" s="268"/>
+      <c r="C31" s="266"/>
       <c r="D31" s="13">
         <v>44</v>
       </c>
@@ -28798,10 +28727,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="23"/>
-      <c r="B32" s="268" t="s">
+      <c r="B32" s="266" t="s">
         <v>518</v>
       </c>
-      <c r="C32" s="268"/>
+      <c r="C32" s="266"/>
       <c r="D32" s="13">
         <v>17</v>
       </c>
@@ -28822,10 +28751,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="23"/>
-      <c r="B34" s="268" t="s">
+      <c r="B34" s="266" t="s">
         <v>521</v>
       </c>
-      <c r="C34" s="268" t="s">
+      <c r="C34" s="266" t="s">
         <v>522</v>
       </c>
       <c r="D34" s="13">
@@ -28835,7 +28764,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="23"/>
-      <c r="B35" s="268" t="s">
+      <c r="B35" s="266" t="s">
         <v>523</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -28874,10 +28803,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="23"/>
-      <c r="B38" s="286" t="s">
+      <c r="B38" s="284" t="s">
         <v>526</v>
       </c>
-      <c r="C38" s="286" t="s">
+      <c r="C38" s="284" t="s">
         <v>527</v>
       </c>
       <c r="D38" s="53">
@@ -28900,7 +28829,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="23"/>
-      <c r="B40" s="268" t="s">
+      <c r="B40" s="266" t="s">
         <v>529</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -29004,7 +28933,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="23"/>
-      <c r="B48" s="268" t="s">
+      <c r="B48" s="266" t="s">
         <v>537</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -29017,7 +28946,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="23"/>
-      <c r="B49" s="268" t="s">
+      <c r="B49" s="266" t="s">
         <v>538</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -29030,7 +28959,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="23"/>
-      <c r="B50" s="268" t="s">
+      <c r="B50" s="266" t="s">
         <v>539</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -29043,7 +28972,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="23"/>
-      <c r="B51" s="268" t="s">
+      <c r="B51" s="266" t="s">
         <v>540</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -29277,7 +29206,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23"/>
-      <c r="B69" s="268" t="s">
+      <c r="B69" s="266" t="s">
         <v>560</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -29306,7 +29235,7 @@
       <c r="B71" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="C71" s="268" t="s">
+      <c r="C71" s="266" t="s">
         <v>520</v>
       </c>
       <c r="D71" s="13">
@@ -29319,7 +29248,7 @@
       <c r="B72" t="s">
         <v>563</v>
       </c>
-      <c r="C72" s="268" t="s">
+      <c r="C72" s="266" t="s">
         <v>520</v>
       </c>
       <c r="D72" s="13">
@@ -29398,10 +29327,10 @@
       <c r="B1" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="288" t="s">
+      <c r="C1" s="286" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="288" t="s">
+      <c r="D1" s="286" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -29413,10 +29342,10 @@
       <c r="B2" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="C2" s="288" t="s">
+      <c r="C2" s="286" t="s">
         <v>567</v>
       </c>
-      <c r="D2" s="290" t="s">
+      <c r="D2" s="288" t="s">
         <v>568</v>
       </c>
       <c r="E2" s="51" t="s">
@@ -29427,16 +29356,16 @@
       <c r="A3" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="268" t="s">
+      <c r="B3" s="266" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="268" t="s">
+      <c r="C3" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D3" s="268">
-        <v>1</v>
-      </c>
-      <c r="E3" s="285" t="s">
+      <c r="D3" s="266">
+        <v>1</v>
+      </c>
+      <c r="E3" s="283" t="s">
         <v>386</v>
       </c>
     </row>
@@ -29447,13 +29376,13 @@
       <c r="B4" t="s">
         <v>503</v>
       </c>
-      <c r="C4" s="268" t="s">
+      <c r="C4" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D4" s="268">
+      <c r="D4" s="266">
         <v>4</v>
       </c>
-      <c r="E4" s="285" t="s">
+      <c r="E4" s="283" t="s">
         <v>389</v>
       </c>
     </row>
@@ -29461,16 +29390,16 @@
       <c r="A5" s="47" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="268" t="s">
+      <c r="B5" s="266" t="s">
         <v>330</v>
       </c>
-      <c r="C5" s="268" t="s">
+      <c r="C5" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D5" s="268">
+      <c r="D5" s="266">
         <v>3</v>
       </c>
-      <c r="E5" s="285" t="s">
+      <c r="E5" s="283" t="s">
         <v>393</v>
       </c>
     </row>
@@ -29479,20 +29408,20 @@
       <c r="B6" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="C6" s="268" t="s">
+      <c r="C6" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D6" s="268">
+      <c r="D6" s="266">
         <v>1</v>
       </c>
       <c r="E6" s="52"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23"/>
-      <c r="B7" s="268" t="s">
+      <c r="B7" s="266" t="s">
         <v>570</v>
       </c>
-      <c r="C7" s="268" t="s">
+      <c r="C7" s="266" t="s">
         <v>567</v>
       </c>
       <c r="D7" s="2">
@@ -29502,26 +29431,26 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="23"/>
-      <c r="B8" s="268" t="s">
+      <c r="B8" s="266" t="s">
         <v>571</v>
       </c>
-      <c r="C8" s="268" t="s">
+      <c r="C8" s="266" t="s">
         <v>572</v>
       </c>
-      <c r="D8" s="268">
+      <c r="D8" s="266">
         <v>1</v>
       </c>
       <c r="E8" s="52"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="23"/>
-      <c r="B9" s="272" t="s">
+      <c r="B9" s="270" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="268" t="s">
+      <c r="C9" s="266" t="s">
         <v>572</v>
       </c>
-      <c r="D9" s="268">
+      <c r="D9" s="266">
         <v>1</v>
       </c>
       <c r="E9" s="52"/>
@@ -29531,10 +29460,10 @@
       <c r="B10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="268" t="s">
+      <c r="C10" s="266" t="s">
         <v>572</v>
       </c>
-      <c r="D10" s="268">
+      <c r="D10" s="266">
         <v>1</v>
       </c>
       <c r="E10" s="52"/>
@@ -29544,10 +29473,10 @@
       <c r="B11" s="26" t="s">
         <v>573</v>
       </c>
-      <c r="C11" s="268" t="s">
+      <c r="C11" s="266" t="s">
         <v>572</v>
       </c>
-      <c r="D11" s="268">
+      <c r="D11" s="266">
         <v>1</v>
       </c>
       <c r="E11" s="52"/>
@@ -29559,23 +29488,23 @@
       <c r="B12" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="268" t="s">
+      <c r="C12" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D12" s="268">
+      <c r="D12" s="266">
         <v>10</v>
       </c>
       <c r="E12" s="52"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23"/>
-      <c r="B13" s="268" t="s">
+      <c r="B13" s="266" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="268" t="s">
+      <c r="C13" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D13" s="268">
+      <c r="D13" s="266">
         <v>1</v>
       </c>
       <c r="E13" s="52"/>
@@ -29585,10 +29514,10 @@
       <c r="B14" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C14" s="268" t="s">
+      <c r="C14" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D14" s="268">
+      <c r="D14" s="266">
         <v>2</v>
       </c>
       <c r="E14" s="52"/>
@@ -29598,10 +29527,10 @@
       <c r="B15" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="C15" s="268" t="s">
+      <c r="C15" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D15" s="268">
+      <c r="D15" s="266">
         <v>7</v>
       </c>
       <c r="E15" s="52"/>
@@ -29611,20 +29540,20 @@
       <c r="B16" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="268" t="s">
+      <c r="C16" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D16" s="268">
+      <c r="D16" s="266">
         <v>3</v>
       </c>
       <c r="E16" s="52"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="23"/>
-      <c r="B17" s="268" t="s">
+      <c r="B17" s="266" t="s">
         <v>576</v>
       </c>
-      <c r="C17" s="268" t="s">
+      <c r="C17" s="266" t="s">
         <v>567</v>
       </c>
       <c r="D17" s="2">
@@ -29634,13 +29563,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="23"/>
-      <c r="B18" s="268" t="s">
+      <c r="B18" s="266" t="s">
         <v>221</v>
       </c>
-      <c r="C18" s="268" t="s">
+      <c r="C18" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D18" s="268">
+      <c r="D18" s="266">
         <v>1</v>
       </c>
       <c r="E18" s="52"/>
@@ -29650,10 +29579,10 @@
       <c r="B19" t="s">
         <v>577</v>
       </c>
-      <c r="C19" s="268" t="s">
+      <c r="C19" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D19" s="268">
+      <c r="D19" s="266">
         <v>2</v>
       </c>
       <c r="E19" s="52"/>
@@ -29663,20 +29592,20 @@
       <c r="B20" t="s">
         <v>578</v>
       </c>
-      <c r="C20" s="268" t="s">
+      <c r="C20" s="266" t="s">
         <v>567</v>
       </c>
-      <c r="D20" s="268">
+      <c r="D20" s="266">
         <v>2</v>
       </c>
       <c r="E20" s="52"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="23"/>
-      <c r="B21" s="268" t="s">
+      <c r="B21" s="266" t="s">
         <v>579</v>
       </c>
-      <c r="C21" s="268" t="s">
+      <c r="C21" s="266" t="s">
         <v>572</v>
       </c>
       <c r="D21" s="2">
@@ -29692,7 +29621,7 @@
       <c r="B22" t="s">
         <v>581</v>
       </c>
-      <c r="C22" s="268" t="s">
+      <c r="C22" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D22" s="2">
@@ -29705,7 +29634,7 @@
       <c r="B23" t="s">
         <v>582</v>
       </c>
-      <c r="C23" s="268" t="s">
+      <c r="C23" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D23" s="2">
@@ -29718,7 +29647,7 @@
       <c r="B24" t="s">
         <v>583</v>
       </c>
-      <c r="C24" s="268" t="s">
+      <c r="C24" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D24" s="2">
@@ -29731,10 +29660,10 @@
       <c r="B25" t="s">
         <v>584</v>
       </c>
-      <c r="C25" s="268" t="s">
+      <c r="C25" s="266" t="s">
         <v>405</v>
       </c>
-      <c r="D25" s="268">
+      <c r="D25" s="266">
         <v>1</v>
       </c>
       <c r="E25" s="52"/>
@@ -29744,7 +29673,7 @@
       <c r="B26" t="s">
         <v>585</v>
       </c>
-      <c r="C26" s="268" t="s">
+      <c r="C26" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D26" s="1">
@@ -29757,7 +29686,7 @@
       <c r="B27" t="s">
         <v>586</v>
       </c>
-      <c r="C27" s="268" t="s">
+      <c r="C27" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D27" s="1">
@@ -29770,20 +29699,20 @@
       <c r="B28" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C28" s="268" t="s">
+      <c r="C28" s="266" t="s">
         <v>405</v>
       </c>
-      <c r="D28" s="268">
+      <c r="D28" s="266">
         <v>2</v>
       </c>
       <c r="E28" s="52"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="23"/>
-      <c r="B29" s="268" t="s">
+      <c r="B29" s="266" t="s">
         <v>588</v>
       </c>
-      <c r="C29" s="268" t="s">
+      <c r="C29" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D29" s="2">
@@ -29793,10 +29722,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="23"/>
-      <c r="B30" s="268" t="s">
+      <c r="B30" s="266" t="s">
         <v>589</v>
       </c>
-      <c r="C30" s="268" t="s">
+      <c r="C30" s="266" t="s">
         <v>551</v>
       </c>
       <c r="D30" s="2">
@@ -29809,10 +29738,10 @@
       <c r="B31" t="s">
         <v>590</v>
       </c>
-      <c r="C31" s="268" t="s">
+      <c r="C31" s="266" t="s">
         <v>405</v>
       </c>
-      <c r="D31" s="268">
+      <c r="D31" s="266">
         <v>1</v>
       </c>
       <c r="E31" s="52"/>
@@ -29822,10 +29751,10 @@
       <c r="B32" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C32" s="268" t="s">
+      <c r="C32" s="266" t="s">
         <v>592</v>
       </c>
-      <c r="D32" s="268">
+      <c r="D32" s="266">
         <v>2</v>
       </c>
       <c r="E32" s="52"/>
@@ -29835,10 +29764,10 @@
       <c r="B33" t="s">
         <v>593</v>
       </c>
-      <c r="C33" s="268" t="s">
+      <c r="C33" s="266" t="s">
         <v>594</v>
       </c>
-      <c r="D33" s="268">
+      <c r="D33" s="266">
         <v>2</v>
       </c>
       <c r="E33" s="52"/>
@@ -29848,10 +29777,10 @@
       <c r="B34" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C34" s="268" t="s">
+      <c r="C34" s="266" t="s">
         <v>596</v>
       </c>
-      <c r="D34" s="268">
+      <c r="D34" s="266">
         <v>2</v>
       </c>
       <c r="E34" s="52"/>
@@ -29861,36 +29790,36 @@
       <c r="B35" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C35" s="268" t="s">
+      <c r="C35" s="266" t="s">
         <v>592</v>
       </c>
-      <c r="D35" s="268">
+      <c r="D35" s="266">
         <v>2</v>
       </c>
       <c r="E35" s="52"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="23"/>
-      <c r="B36" s="268" t="s">
+      <c r="B36" s="266" t="s">
         <v>598</v>
       </c>
-      <c r="C36" s="268" t="s">
+      <c r="C36" s="266" t="s">
         <v>599</v>
       </c>
-      <c r="D36" s="268">
+      <c r="D36" s="266">
         <v>2</v>
       </c>
       <c r="E36" s="52"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="23"/>
-      <c r="B37" s="268" t="s">
+      <c r="B37" s="266" t="s">
         <v>600</v>
       </c>
-      <c r="C37" s="268" t="s">
+      <c r="C37" s="266" t="s">
         <v>596</v>
       </c>
-      <c r="D37" s="268">
+      <c r="D37" s="266">
         <v>2</v>
       </c>
       <c r="E37" s="52"/>
@@ -29900,20 +29829,20 @@
       <c r="B38" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C38" s="268" t="s">
+      <c r="C38" s="266" t="s">
         <v>405</v>
       </c>
-      <c r="D38" s="268">
+      <c r="D38" s="266">
         <v>1</v>
       </c>
       <c r="E38" s="52"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="23"/>
-      <c r="B39" s="268" t="s">
+      <c r="B39" s="266" t="s">
         <v>602</v>
       </c>
-      <c r="C39" s="268" t="s">
+      <c r="C39" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D39" s="2">
@@ -29923,10 +29852,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="23"/>
-      <c r="B40" s="268" t="s">
+      <c r="B40" s="266" t="s">
         <v>603</v>
       </c>
-      <c r="C40" s="268" t="s">
+      <c r="C40" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D40" s="2">
@@ -29936,10 +29865,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="23"/>
-      <c r="B41" s="268" t="s">
+      <c r="B41" s="266" t="s">
         <v>604</v>
       </c>
-      <c r="C41" s="268" t="s">
+      <c r="C41" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D41" s="2">
@@ -29949,10 +29878,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="23"/>
-      <c r="B42" s="268" t="s">
+      <c r="B42" s="266" t="s">
         <v>605</v>
       </c>
-      <c r="C42" s="268" t="s">
+      <c r="C42" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D42" s="2">
@@ -29962,23 +29891,23 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="23"/>
-      <c r="B43" s="268" t="s">
+      <c r="B43" s="266" t="s">
         <v>606</v>
       </c>
-      <c r="C43" s="268" t="s">
+      <c r="C43" s="266" t="s">
         <v>405</v>
       </c>
-      <c r="D43" s="268">
+      <c r="D43" s="266">
         <v>1</v>
       </c>
       <c r="E43" s="52"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1">
       <c r="A44" s="57"/>
-      <c r="B44" s="268" t="s">
+      <c r="B44" s="266" t="s">
         <v>607</v>
       </c>
-      <c r="C44" s="268" t="s">
+      <c r="C44" s="266" t="s">
         <v>405</v>
       </c>
       <c r="D44" s="2">
@@ -29987,7 +29916,7 @@
       <c r="E44" s="59"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="C45" s="279"/>
+      <c r="C45" s="277"/>
     </row>
     <row r="46" spans="1:5" ht="30">
       <c r="B46" s="128" t="s">
@@ -30039,10 +29968,10 @@
       <c r="B1" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="263" t="s">
+      <c r="C1" s="261" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="263" t="s">
+      <c r="D1" s="261" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -30054,8 +29983,8 @@
       <c r="B2" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="C2" s="268"/>
-      <c r="D2" s="268">
+      <c r="C2" s="266"/>
+      <c r="D2" s="266">
         <v>6</v>
       </c>
       <c r="E2" s="51" t="s">
@@ -30066,13 +29995,13 @@
       <c r="A3" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="267" t="s">
+      <c r="B3" s="265" t="s">
         <v>281</v>
       </c>
-      <c r="D3" s="268">
-        <v>1</v>
-      </c>
-      <c r="E3" s="285" t="s">
+      <c r="D3" s="266">
+        <v>1</v>
+      </c>
+      <c r="E3" s="283" t="s">
         <v>386</v>
       </c>
     </row>
@@ -30080,14 +30009,14 @@
       <c r="A4" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="268" t="s">
+      <c r="B4" s="266" t="s">
         <v>610</v>
       </c>
-      <c r="C4" s="268"/>
-      <c r="D4" s="268">
-        <v>1</v>
-      </c>
-      <c r="E4" s="285" t="s">
+      <c r="C4" s="266"/>
+      <c r="D4" s="266">
+        <v>1</v>
+      </c>
+      <c r="E4" s="283" t="s">
         <v>389</v>
       </c>
     </row>
@@ -30095,34 +30024,34 @@
       <c r="A5" s="47" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="267" t="s">
+      <c r="B5" s="265" t="s">
         <v>290</v>
       </c>
-      <c r="C5" s="268"/>
-      <c r="D5" s="268">
-        <v>1</v>
-      </c>
-      <c r="E5" s="285" t="s">
+      <c r="C5" s="266"/>
+      <c r="D5" s="266">
+        <v>1</v>
+      </c>
+      <c r="E5" s="283" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23"/>
-      <c r="B6" s="267" t="s">
+      <c r="B6" s="265" t="s">
         <v>611</v>
       </c>
-      <c r="D6" s="268">
+      <c r="D6" s="266">
         <v>1</v>
       </c>
       <c r="E6" s="52"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23"/>
-      <c r="B7" s="268" t="s">
+      <c r="B7" s="266" t="s">
         <v>612</v>
       </c>
-      <c r="C7" s="268"/>
-      <c r="D7" s="268">
+      <c r="C7" s="266"/>
+      <c r="D7" s="266">
         <v>1</v>
       </c>
       <c r="E7" s="52"/>
@@ -30132,8 +30061,8 @@
       <c r="B8" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="268"/>
-      <c r="D8" s="268">
+      <c r="C8" s="266"/>
+      <c r="D8" s="266">
         <v>4</v>
       </c>
       <c r="E8" s="52"/>
@@ -30143,7 +30072,7 @@
       <c r="B9" t="s">
         <v>180</v>
       </c>
-      <c r="D9" s="268">
+      <c r="D9" s="266">
         <v>12</v>
       </c>
       <c r="E9" s="52"/>
@@ -30153,7 +30082,7 @@
       <c r="B10" t="s">
         <v>613</v>
       </c>
-      <c r="D10" s="268">
+      <c r="D10" s="266">
         <v>4</v>
       </c>
       <c r="E10" s="52"/>
@@ -30163,7 +30092,7 @@
       <c r="B11" t="s">
         <v>452</v>
       </c>
-      <c r="D11" s="268">
+      <c r="D11" s="266">
         <v>4</v>
       </c>
       <c r="E11" s="52"/>
@@ -30175,7 +30104,7 @@
       <c r="B12" t="s">
         <v>400</v>
       </c>
-      <c r="D12" s="268">
+      <c r="D12" s="266">
         <v>2</v>
       </c>
       <c r="E12" s="52"/>
@@ -30185,7 +30114,7 @@
       <c r="B13" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D13" s="268">
+      <c r="D13" s="266">
         <v>2</v>
       </c>
       <c r="E13" s="52"/>
@@ -30195,7 +30124,7 @@
       <c r="B14" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D14" s="268">
+      <c r="D14" s="266">
         <v>6</v>
       </c>
       <c r="E14" s="52"/>
@@ -30205,17 +30134,17 @@
       <c r="B15" t="s">
         <v>614</v>
       </c>
-      <c r="D15" s="268">
+      <c r="D15" s="266">
         <v>1</v>
       </c>
       <c r="E15" s="52"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23"/>
-      <c r="B16" s="264" t="s">
+      <c r="B16" s="262" t="s">
         <v>615</v>
       </c>
-      <c r="D16" s="268">
+      <c r="D16" s="266">
         <v>1</v>
       </c>
       <c r="E16" s="52"/>
@@ -30225,7 +30154,7 @@
       <c r="B17" s="26" t="s">
         <v>616</v>
       </c>
-      <c r="D17" s="268">
+      <c r="D17" s="266">
         <v>1</v>
       </c>
       <c r="E17" s="52"/>
@@ -30236,7 +30165,7 @@
         <v>617</v>
       </c>
       <c r="C18" s="48"/>
-      <c r="D18" s="291">
+      <c r="D18" s="289">
         <v>1</v>
       </c>
       <c r="E18" s="59"/>
@@ -30287,10 +30216,10 @@
       <c r="B1" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="263" t="s">
+      <c r="C1" s="261" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="263" t="s">
+      <c r="D1" s="261" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -30325,7 +30254,7 @@
       <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="285" t="s">
+      <c r="E3" s="283" t="s">
         <v>386</v>
       </c>
     </row>
@@ -30342,7 +30271,7 @@
       <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="285" t="s">
+      <c r="E4" s="283" t="s">
         <v>389</v>
       </c>
     </row>
@@ -30353,25 +30282,25 @@
       <c r="B5" s="28" t="s">
         <v>622</v>
       </c>
-      <c r="C5" s="268" t="s">
+      <c r="C5" s="266" t="s">
         <v>623</v>
       </c>
-      <c r="D5" s="274">
+      <c r="D5" s="272">
         <v>2</v>
       </c>
-      <c r="E5" s="285" t="s">
+      <c r="E5" s="283" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23"/>
-      <c r="B6" s="292" t="s">
+      <c r="B6" s="290" t="s">
         <v>622</v>
       </c>
-      <c r="C6" s="268" t="s">
+      <c r="C6" s="266" t="s">
         <v>624</v>
       </c>
-      <c r="D6" s="274">
+      <c r="D6" s="272">
         <v>5</v>
       </c>
       <c r="E6" s="52"/>
@@ -30381,10 +30310,10 @@
       <c r="B7" s="18" t="s">
         <v>625</v>
       </c>
-      <c r="C7" s="268" t="s">
+      <c r="C7" s="266" t="s">
         <v>623</v>
       </c>
-      <c r="D7" s="274">
+      <c r="D7" s="272">
         <v>2</v>
       </c>
       <c r="E7" s="52"/>
@@ -30394,7 +30323,7 @@
       <c r="B8" s="18" t="s">
         <v>625</v>
       </c>
-      <c r="C8" s="268" t="s">
+      <c r="C8" s="266" t="s">
         <v>624</v>
       </c>
       <c r="D8" s="13">
@@ -30404,10 +30333,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="23"/>
-      <c r="B9" s="293" t="s">
+      <c r="B9" s="291" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="268" t="s">
+      <c r="C9" s="266" t="s">
         <v>626</v>
       </c>
       <c r="D9" s="13">
@@ -30420,10 +30349,10 @@
       <c r="B10" s="28" t="s">
         <v>627</v>
       </c>
-      <c r="C10" s="268" t="s">
+      <c r="C10" s="266" t="s">
         <v>623</v>
       </c>
-      <c r="D10" s="274">
+      <c r="D10" s="272">
         <v>2</v>
       </c>
       <c r="E10" s="52"/>
@@ -30433,7 +30362,7 @@
       <c r="B11" s="28" t="s">
         <v>627</v>
       </c>
-      <c r="C11" s="268" t="s">
+      <c r="C11" s="266" t="s">
         <v>624</v>
       </c>
       <c r="D11" s="13">
@@ -30445,10 +30374,10 @@
       <c r="A12" s="47" t="s">
         <v>401</v>
       </c>
-      <c r="B12" s="293" t="s">
+      <c r="B12" s="291" t="s">
         <v>628</v>
       </c>
-      <c r="C12" s="268" t="s">
+      <c r="C12" s="266" t="s">
         <v>629</v>
       </c>
       <c r="D12" s="13">
@@ -30461,10 +30390,10 @@
       <c r="B13" s="28" t="s">
         <v>630</v>
       </c>
-      <c r="C13" s="268" t="s">
+      <c r="C13" s="266" t="s">
         <v>631</v>
       </c>
-      <c r="D13" s="274">
+      <c r="D13" s="272">
         <v>2</v>
       </c>
       <c r="E13" s="52"/>
@@ -30474,10 +30403,10 @@
       <c r="B14" s="28" t="s">
         <v>622</v>
       </c>
-      <c r="C14" s="268" t="s">
+      <c r="C14" s="266" t="s">
         <v>631</v>
       </c>
-      <c r="D14" s="274">
+      <c r="D14" s="272">
         <v>2</v>
       </c>
       <c r="E14" s="52"/>
@@ -30487,10 +30416,10 @@
       <c r="B15" s="28" t="s">
         <v>630</v>
       </c>
-      <c r="C15" s="268" t="s">
+      <c r="C15" s="266" t="s">
         <v>623</v>
       </c>
-      <c r="D15" s="274">
+      <c r="D15" s="272">
         <v>2</v>
       </c>
       <c r="E15" s="52"/>
@@ -30500,36 +30429,36 @@
       <c r="B16" s="28" t="s">
         <v>630</v>
       </c>
-      <c r="C16" s="268" t="s">
+      <c r="C16" s="266" t="s">
         <v>624</v>
       </c>
-      <c r="D16" s="274">
+      <c r="D16" s="272">
         <v>5</v>
       </c>
       <c r="E16" s="52"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="23"/>
-      <c r="B17" s="293" t="s">
+      <c r="B17" s="291" t="s">
         <v>632</v>
       </c>
-      <c r="C17" s="268" t="s">
+      <c r="C17" s="266" t="s">
         <v>633</v>
       </c>
-      <c r="D17" s="274">
+      <c r="D17" s="272">
         <v>5</v>
       </c>
       <c r="E17" s="52"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="23"/>
-      <c r="B18" s="293" t="s">
+      <c r="B18" s="291" t="s">
         <v>632</v>
       </c>
-      <c r="C18" s="268" t="s">
+      <c r="C18" s="266" t="s">
         <v>624</v>
       </c>
-      <c r="D18" s="274">
+      <c r="D18" s="272">
         <v>5</v>
       </c>
       <c r="E18" s="52"/>
@@ -30549,7 +30478,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23"/>
-      <c r="B20" s="292" t="s">
+      <c r="B20" s="290" t="s">
         <v>622</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -30601,10 +30530,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="23"/>
-      <c r="B24" s="286" t="s">
+      <c r="B24" s="284" t="s">
         <v>639</v>
       </c>
-      <c r="C24" s="286" t="s">
+      <c r="C24" s="284" t="s">
         <v>457</v>
       </c>
       <c r="D24" s="53"/>
@@ -30612,20 +30541,20 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="23"/>
-      <c r="B25" s="268" t="s">
+      <c r="B25" s="266" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="268" t="s">
+      <c r="C25" s="266" t="s">
         <v>640</v>
       </c>
-      <c r="D25" s="268">
+      <c r="D25" s="266">
         <v>1</v>
       </c>
       <c r="E25" s="52"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="23"/>
-      <c r="B26" s="268" t="s">
+      <c r="B26" s="266" t="s">
         <v>641</v>
       </c>
       <c r="D26" s="13">
@@ -30689,10 +30618,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="23"/>
-      <c r="B32" s="267" t="s">
+      <c r="B32" s="265" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="268">
+      <c r="D32" s="266">
         <v>1</v>
       </c>
       <c r="E32" s="52"/>
@@ -30787,10 +30716,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="23"/>
-      <c r="B41" s="293" t="s">
+      <c r="B41" s="291" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="268" t="s">
+      <c r="C41" s="266" t="s">
         <v>642</v>
       </c>
       <c r="D41" s="13">
@@ -30800,10 +30729,10 @@
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="23"/>
-      <c r="B42" s="293" t="s">
+      <c r="B42" s="291" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="268" t="s">
+      <c r="C42" s="266" t="s">
         <v>642</v>
       </c>
       <c r="D42" s="13">
@@ -30816,7 +30745,7 @@
       <c r="B43" s="23" t="s">
         <v>643</v>
       </c>
-      <c r="C43" s="268" t="s">
+      <c r="C43" s="266" t="s">
         <v>642</v>
       </c>
       <c r="D43" s="13">
@@ -30826,10 +30755,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="23"/>
-      <c r="B44" s="293" t="s">
+      <c r="B44" s="291" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="268" t="s">
+      <c r="C44" s="266" t="s">
         <v>644</v>
       </c>
       <c r="D44" s="13">
@@ -30842,23 +30771,23 @@
       <c r="B45" s="15" t="s">
         <v>645</v>
       </c>
-      <c r="C45" s="268" t="s">
+      <c r="C45" s="266" t="s">
         <v>646</v>
       </c>
-      <c r="D45" s="268">
+      <c r="D45" s="266">
         <v>1</v>
       </c>
       <c r="E45" s="52"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="23"/>
-      <c r="B46" s="293" t="s">
+      <c r="B46" s="291" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="268" t="s">
+      <c r="C46" s="266" t="s">
         <v>647</v>
       </c>
-      <c r="D46" s="268">
+      <c r="D46" s="266">
         <v>1</v>
       </c>
       <c r="E46" s="52"/>
@@ -30868,7 +30797,7 @@
       <c r="B47" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="268" t="s">
+      <c r="C47" s="266" t="s">
         <v>648</v>
       </c>
       <c r="D47" s="13">
@@ -30881,7 +30810,7 @@
       <c r="B48" t="s">
         <v>649</v>
       </c>
-      <c r="C48" s="268" t="s">
+      <c r="C48" s="266" t="s">
         <v>650</v>
       </c>
       <c r="D48" s="13">
@@ -30894,7 +30823,7 @@
       <c r="B49" t="s">
         <v>651</v>
       </c>
-      <c r="C49" s="268" t="s">
+      <c r="C49" s="266" t="s">
         <v>652</v>
       </c>
       <c r="D49" s="13">
@@ -30904,10 +30833,10 @@
     </row>
     <row r="50" spans="1:5" ht="16.5" customHeight="1">
       <c r="A50" s="23"/>
-      <c r="B50" s="268" t="s">
+      <c r="B50" s="266" t="s">
         <v>653</v>
       </c>
-      <c r="C50" s="268" t="s">
+      <c r="C50" s="266" t="s">
         <v>654</v>
       </c>
       <c r="D50" s="13">
@@ -30920,7 +30849,7 @@
       <c r="B51" s="45" t="s">
         <v>655</v>
       </c>
-      <c r="C51" s="291" t="s">
+      <c r="C51" s="289" t="s">
         <v>650</v>
       </c>
       <c r="D51" s="58">

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3293" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D10C75D7-64A4-4750-9268-7262A9680685}"/>
+  <xr:revisionPtr revIDLastSave="3305" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA3337A2-AE80-44D5-AF59-5165BA120F7C}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -3209,12 +3209,6 @@
     <t>Drying Time</t>
   </si>
   <si>
-    <t>HDT at 0.45 Mpa</t>
-  </si>
-  <si>
-    <t>Annealed HDT at 0.45 Mpa2</t>
-  </si>
-  <si>
     <t>Bending Modulus MPa</t>
   </si>
   <si>
@@ -3422,6 +3416,12 @@
   <si>
     <t>adapt the PSU 350 buddy to the LRS-350</t>
   </si>
+  <si>
+    <t>HDT</t>
+  </si>
+  <si>
+    <t>HDT Annealed</t>
+  </si>
 </sst>
 </file>
 
@@ -3437,7 +3437,7 @@
     <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="68">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3843,14 +3843,6 @@
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
@@ -4228,7 +4220,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="318">
+  <cellXfs count="315">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
@@ -4705,7 +4697,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="12" applyFont="1"/>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="12" applyFont="1"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="12" applyFont="1"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="12" applyFont="1"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4752,16 +4744,7 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="8" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="9" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="24" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -4779,13 +4762,13 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="12" applyFont="1"/>
-    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="61" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="12" applyFont="1"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -4876,7 +4859,7 @@
     <xf numFmtId="49" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4915,7 +4898,7 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -7680,8 +7663,8 @@
     <tableColumn id="8" xr3:uid="{DF87AE05-A3BC-421E-9BB7-23A2ABF4C361}" name="Chamber Temp" dataDxfId="5" dataCellStyle="Normal 12"/>
     <tableColumn id="9" xr3:uid="{845BBCDF-F13A-47FB-8E5D-2AECC511780B}" name="Drying Temp" dataDxfId="4" dataCellStyle="Normal 12"/>
     <tableColumn id="10" xr3:uid="{D362A04F-6A04-476D-AC24-1BCA0C4F59DB}" name="Drying Time" dataDxfId="3" dataCellStyle="Normal 12"/>
-    <tableColumn id="11" xr3:uid="{6994BD7F-8192-40FA-9548-36A5EE628106}" name="HDT at 0.45 Mpa" dataDxfId="2" dataCellStyle="Normal 12"/>
-    <tableColumn id="12" xr3:uid="{0856005B-5B46-415C-BB48-BE1984071133}" name="Annealed HDT at 0.45 Mpa2" dataDxfId="1" dataCellStyle="Normal 12"/>
+    <tableColumn id="11" xr3:uid="{6994BD7F-8192-40FA-9548-36A5EE628106}" name="HDT" dataDxfId="2" dataCellStyle="Normal 12"/>
+    <tableColumn id="12" xr3:uid="{0856005B-5B46-415C-BB48-BE1984071133}" name="HDT Annealed" dataDxfId="1" dataCellStyle="Normal 12"/>
     <tableColumn id="13" xr3:uid="{AC83266E-6805-4F79-BED7-5D3490D455AA}" name="Bending Modulus MPa" dataDxfId="0" dataCellStyle="Normal 12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -8035,31 +8018,31 @@
       <c r="A1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="257" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="258" t="s">
+      <c r="B1" s="254" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="255" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="257" t="s">
+      <c r="D1" s="254" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="257" t="s">
+      <c r="E1" s="254" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="257" t="s">
+      <c r="F1" s="254" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="257" t="s">
+      <c r="G1" s="254" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="259" t="s">
+      <c r="H1" s="256" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="260" t="s">
+      <c r="I1" s="257" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="261" t="s">
+      <c r="J1" s="258" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="67" t="s">
@@ -8177,7 +8160,7 @@
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="262" t="s">
+      <c r="B5" s="259" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="139"/>
@@ -8211,7 +8194,7 @@
       <c r="A6" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="255" t="s">
+      <c r="B6" s="252" t="s">
         <v>24</v>
       </c>
       <c r="C6" s="156"/>
@@ -8245,7 +8228,7 @@
       <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="255" t="s">
+      <c r="B7" s="252" t="s">
         <v>26</v>
       </c>
       <c r="C7" s="156"/>
@@ -8279,7 +8262,7 @@
       <c r="A8" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="263" t="s">
+      <c r="B8" s="260" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="139"/>
@@ -8313,7 +8296,7 @@
       <c r="A9" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="262" t="s">
+      <c r="B9" s="259" t="s">
         <v>31</v>
       </c>
       <c r="C9" s="139"/>
@@ -8333,7 +8316,7 @@
       <c r="H9" s="152" t="s">
         <v>32</v>
       </c>
-      <c r="I9" s="256" t="s">
+      <c r="I9" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J9" s="27">
@@ -8366,7 +8349,7 @@
       <c r="H10" s="152" t="s">
         <v>35</v>
       </c>
-      <c r="I10" s="256" t="s">
+      <c r="I10" s="253" t="s">
         <v>36</v>
       </c>
       <c r="J10" s="27">
@@ -8400,7 +8383,7 @@
       <c r="H11" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="I11" s="264" t="s">
+      <c r="I11" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J11" s="27">
@@ -8434,7 +8417,7 @@
       <c r="H12" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="I12" s="264" t="s">
+      <c r="I12" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J12" s="27">
@@ -8468,7 +8451,7 @@
       <c r="H13" s="152" t="s">
         <v>43</v>
       </c>
-      <c r="I13" s="264" t="s">
+      <c r="I13" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J13" s="27">
@@ -8482,11 +8465,11 @@
       <c r="A14" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="265" t="s">
+      <c r="B14" s="262" t="s">
         <v>44</v>
       </c>
       <c r="C14" s="160"/>
-      <c r="D14" s="266">
+      <c r="D14" s="263">
         <v>1</v>
       </c>
       <c r="E14" s="140">
@@ -8502,7 +8485,7 @@
       <c r="H14" s="152" t="s">
         <v>45</v>
       </c>
-      <c r="I14" s="264" t="s">
+      <c r="I14" s="261" t="s">
         <v>46</v>
       </c>
       <c r="J14" s="27">
@@ -8516,17 +8499,17 @@
       <c r="A15" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="266" t="s">
+      <c r="B15" s="263" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="267"/>
+      <c r="C15" s="264"/>
       <c r="D15" s="13">
         <v>2</v>
       </c>
       <c r="E15" s="140">
         <v>1</v>
       </c>
-      <c r="F15" s="266">
+      <c r="F15" s="263">
         <v>2.3199999999999998</v>
       </c>
       <c r="G15" s="141">
@@ -8536,7 +8519,7 @@
       <c r="H15" s="152" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="264" t="s">
+      <c r="I15" s="261" t="s">
         <v>49</v>
       </c>
       <c r="J15" s="27">
@@ -8550,17 +8533,17 @@
       <c r="A16" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="266" t="s">
+      <c r="B16" s="263" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="267"/>
+      <c r="C16" s="264"/>
       <c r="D16" s="13">
         <v>1</v>
       </c>
       <c r="E16" s="140">
         <v>1</v>
       </c>
-      <c r="F16" s="268">
+      <c r="F16" s="265">
         <v>4.82</v>
       </c>
       <c r="G16" s="141">
@@ -8570,7 +8553,7 @@
       <c r="H16" s="152" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="269" t="s">
+      <c r="I16" s="266" t="s">
         <v>49</v>
       </c>
       <c r="J16" s="27">
@@ -8604,7 +8587,7 @@
       <c r="H17" s="202" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="269" t="s">
+      <c r="I17" s="266" t="s">
         <v>49</v>
       </c>
       <c r="J17" s="94">
@@ -8621,14 +8604,14 @@
       <c r="B18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C18" s="267"/>
+      <c r="C18" s="264"/>
       <c r="D18" s="13">
         <v>1</v>
       </c>
       <c r="E18" s="140">
         <v>1</v>
       </c>
-      <c r="F18" s="268"/>
+      <c r="F18" s="265"/>
       <c r="G18" s="141">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -8636,7 +8619,7 @@
       <c r="H18" s="197" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="269" t="s">
+      <c r="I18" s="266" t="s">
         <v>49</v>
       </c>
       <c r="J18" s="27">
@@ -8650,11 +8633,11 @@
       <c r="A19" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="270" t="s">
+      <c r="B19" s="267" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="271"/>
-      <c r="D19" s="270">
+      <c r="C19" s="268"/>
+      <c r="D19" s="267">
         <v>1</v>
       </c>
       <c r="E19" s="140">
@@ -8670,7 +8653,7 @@
       <c r="H19" s="152" t="s">
         <v>57</v>
       </c>
-      <c r="I19" s="256" t="s">
+      <c r="I19" s="253" t="s">
         <v>49</v>
       </c>
       <c r="J19" s="27">
@@ -8688,7 +8671,7 @@
         <v>58</v>
       </c>
       <c r="C20" s="139"/>
-      <c r="D20" s="270">
+      <c r="D20" s="267">
         <v>1</v>
       </c>
       <c r="E20" s="140">
@@ -8704,7 +8687,7 @@
       <c r="H20" s="152" t="s">
         <v>59</v>
       </c>
-      <c r="I20" s="256" t="s">
+      <c r="I20" s="253" t="s">
         <v>49</v>
       </c>
       <c r="J20" s="27">
@@ -8718,7 +8701,7 @@
       <c r="A21" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="270" t="s">
+      <c r="B21" s="267" t="s">
         <v>60</v>
       </c>
       <c r="C21" s="162"/>
@@ -8738,7 +8721,7 @@
       <c r="H21" s="152" t="s">
         <v>61</v>
       </c>
-      <c r="I21" s="256" t="s">
+      <c r="I21" s="253" t="s">
         <v>62</v>
       </c>
       <c r="J21" s="27">
@@ -8752,7 +8735,7 @@
       <c r="A22" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="262" t="s">
+      <c r="B22" s="259" t="s">
         <v>63</v>
       </c>
       <c r="C22" s="163" t="s">
@@ -8774,7 +8757,7 @@
       <c r="H22" s="152" t="s">
         <v>65</v>
       </c>
-      <c r="I22" s="256" t="s">
+      <c r="I22" s="253" t="s">
         <v>66</v>
       </c>
       <c r="J22" s="27">
@@ -8857,14 +8840,14 @@
       <c r="B25" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="267"/>
-      <c r="D25" s="266">
+      <c r="C25" s="264"/>
+      <c r="D25" s="263">
         <v>1</v>
       </c>
       <c r="E25" s="140">
         <v>1</v>
       </c>
-      <c r="F25" s="268">
+      <c r="F25" s="265">
         <v>16</v>
       </c>
       <c r="G25" s="141">
@@ -8908,7 +8891,7 @@
       <c r="H26" s="152" t="s">
         <v>76</v>
       </c>
-      <c r="I26" s="256" t="s">
+      <c r="I26" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J26" s="27">
@@ -8942,7 +8925,7 @@
       <c r="H27" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="I27" s="256" t="s">
+      <c r="I27" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J27" s="27">
@@ -8976,7 +8959,7 @@
       <c r="H28" s="198" t="s">
         <v>80</v>
       </c>
-      <c r="I28" s="256" t="s">
+      <c r="I28" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J28" s="94">
@@ -8990,7 +8973,7 @@
       <c r="A29" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="263" t="s">
+      <c r="B29" s="260" t="s">
         <v>81</v>
       </c>
       <c r="C29" s="164"/>
@@ -9010,7 +8993,7 @@
       <c r="H29" s="152" t="s">
         <v>78</v>
       </c>
-      <c r="I29" s="256" t="s">
+      <c r="I29" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J29" s="27">
@@ -9027,7 +9010,7 @@
       <c r="B30" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="267"/>
+      <c r="C30" s="264"/>
       <c r="D30" s="13">
         <v>3</v>
       </c>
@@ -9044,7 +9027,7 @@
       <c r="H30" s="152" t="s">
         <v>83</v>
       </c>
-      <c r="I30" s="264" t="s">
+      <c r="I30" s="261" t="s">
         <v>33</v>
       </c>
       <c r="J30" s="27">
@@ -9058,7 +9041,7 @@
       <c r="A31" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="263" t="s">
+      <c r="B31" s="260" t="s">
         <v>84</v>
       </c>
       <c r="C31" s="139"/>
@@ -9078,7 +9061,7 @@
       <c r="H31" s="152" t="s">
         <v>85</v>
       </c>
-      <c r="I31" s="256" t="s">
+      <c r="I31" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J31" s="27">
@@ -9228,17 +9211,17 @@
       <c r="A36" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="266" t="s">
+      <c r="B36" s="263" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="267"/>
+      <c r="C36" s="264"/>
       <c r="D36" s="13">
         <v>1</v>
       </c>
       <c r="E36" s="140">
         <v>1</v>
       </c>
-      <c r="F36" s="268">
+      <c r="F36" s="265">
         <v>3.22</v>
       </c>
       <c r="G36" s="141">
@@ -9282,7 +9265,7 @@
       <c r="H37" s="152" t="s">
         <v>99</v>
       </c>
-      <c r="I37" s="264" t="s">
+      <c r="I37" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J37" s="27">
@@ -9316,7 +9299,7 @@
       <c r="H38" s="152" t="s">
         <v>101</v>
       </c>
-      <c r="I38" s="264" t="s">
+      <c r="I38" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J38" s="27">
@@ -9350,7 +9333,7 @@
       <c r="H39" s="152" t="s">
         <v>103</v>
       </c>
-      <c r="I39" s="264" t="s">
+      <c r="I39" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J39" s="27">
@@ -9367,8 +9350,8 @@
       <c r="B40" s="26" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="267"/>
-      <c r="D40" s="272">
+      <c r="C40" s="264"/>
+      <c r="D40" s="269">
         <v>2</v>
       </c>
       <c r="E40" s="140">
@@ -9384,7 +9367,7 @@
       <c r="H40" s="152" t="s">
         <v>105</v>
       </c>
-      <c r="I40" s="264" t="s">
+      <c r="I40" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J40" s="27">
@@ -9398,11 +9381,11 @@
       <c r="A41" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="265" t="s">
+      <c r="B41" s="262" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="267"/>
-      <c r="D41" s="272">
+      <c r="C41" s="264"/>
+      <c r="D41" s="269">
         <v>5</v>
       </c>
       <c r="E41" s="140">
@@ -9418,7 +9401,7 @@
       <c r="H41" s="152" t="s">
         <v>107</v>
       </c>
-      <c r="I41" s="264" t="s">
+      <c r="I41" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J41" s="27">
@@ -9435,8 +9418,8 @@
       <c r="B42" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="C42" s="267"/>
-      <c r="D42" s="272">
+      <c r="C42" s="264"/>
+      <c r="D42" s="269">
         <v>2</v>
       </c>
       <c r="E42" s="140">
@@ -9452,7 +9435,7 @@
       <c r="H42" s="152" t="s">
         <v>109</v>
       </c>
-      <c r="I42" s="264" t="s">
+      <c r="I42" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J42" s="27">
@@ -9469,7 +9452,7 @@
       <c r="B43" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C43" s="267"/>
+      <c r="C43" s="264"/>
       <c r="D43" s="13">
         <v>5</v>
       </c>
@@ -9486,7 +9469,7 @@
       <c r="H43" s="152" t="s">
         <v>111</v>
       </c>
-      <c r="I43" s="264" t="s">
+      <c r="I43" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J43" s="27">
@@ -9503,8 +9486,8 @@
       <c r="B44" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C44" s="267"/>
-      <c r="D44" s="272">
+      <c r="C44" s="264"/>
+      <c r="D44" s="269">
         <v>2</v>
       </c>
       <c r="E44" s="140">
@@ -9520,7 +9503,7 @@
       <c r="H44" s="152" t="s">
         <v>113</v>
       </c>
-      <c r="I44" s="264" t="s">
+      <c r="I44" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J44" s="27">
@@ -9537,7 +9520,7 @@
       <c r="B45" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C45" s="267"/>
+      <c r="C45" s="264"/>
       <c r="D45" s="13">
         <v>5</v>
       </c>
@@ -9554,7 +9537,7 @@
       <c r="H45" s="152" t="s">
         <v>115</v>
       </c>
-      <c r="I45" s="264" t="s">
+      <c r="I45" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J45" s="27">
@@ -9568,10 +9551,10 @@
       <c r="A46" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B46" s="266" t="s">
+      <c r="B46" s="263" t="s">
         <v>116</v>
       </c>
-      <c r="C46" s="267"/>
+      <c r="C46" s="264"/>
       <c r="D46" s="13">
         <v>5</v>
       </c>
@@ -9588,7 +9571,7 @@
       <c r="H46" s="152" t="s">
         <v>117</v>
       </c>
-      <c r="I46" s="264" t="s">
+      <c r="I46" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J46" s="27">
@@ -9605,8 +9588,8 @@
       <c r="B47" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="C47" s="267"/>
-      <c r="D47" s="272">
+      <c r="C47" s="264"/>
+      <c r="D47" s="269">
         <v>2</v>
       </c>
       <c r="E47" s="140">
@@ -9622,7 +9605,7 @@
       <c r="H47" s="152" t="s">
         <v>119</v>
       </c>
-      <c r="I47" s="264" t="s">
+      <c r="I47" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J47" s="27">
@@ -9639,8 +9622,8 @@
       <c r="B48" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="C48" s="267"/>
-      <c r="D48" s="272">
+      <c r="C48" s="264"/>
+      <c r="D48" s="269">
         <v>5</v>
       </c>
       <c r="E48" s="140">
@@ -9656,7 +9639,7 @@
       <c r="H48" s="152" t="s">
         <v>121</v>
       </c>
-      <c r="I48" s="264" t="s">
+      <c r="I48" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J48" s="27">
@@ -9670,11 +9653,11 @@
       <c r="A49" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="266" t="s">
+      <c r="B49" s="263" t="s">
         <v>122</v>
       </c>
-      <c r="C49" s="267"/>
-      <c r="D49" s="272">
+      <c r="C49" s="264"/>
+      <c r="D49" s="269">
         <v>5</v>
       </c>
       <c r="E49" s="140">
@@ -9690,7 +9673,7 @@
       <c r="H49" s="152" t="s">
         <v>123</v>
       </c>
-      <c r="I49" s="264" t="s">
+      <c r="I49" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J49" s="27">
@@ -9704,11 +9687,11 @@
       <c r="A50" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B50" s="266" t="s">
+      <c r="B50" s="263" t="s">
         <v>124</v>
       </c>
-      <c r="C50" s="267"/>
-      <c r="D50" s="272">
+      <c r="C50" s="264"/>
+      <c r="D50" s="269">
         <v>5</v>
       </c>
       <c r="E50" s="140">
@@ -9724,7 +9707,7 @@
       <c r="H50" s="152" t="s">
         <v>125</v>
       </c>
-      <c r="I50" s="264" t="s">
+      <c r="I50" s="261" t="s">
         <v>40</v>
       </c>
       <c r="J50" s="27">
@@ -9758,7 +9741,7 @@
       <c r="H51" s="152" t="s">
         <v>126</v>
       </c>
-      <c r="I51" s="311"/>
+      <c r="I51" s="308"/>
       <c r="J51" s="94"/>
       <c r="K51" s="10"/>
       <c r="L51" s="68"/>
@@ -9768,7 +9751,7 @@
       <c r="A52" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="265" t="s">
+      <c r="B52" s="262" t="s">
         <v>127</v>
       </c>
       <c r="C52" s="2"/>
@@ -9788,7 +9771,7 @@
       <c r="H52" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="I52" s="311"/>
+      <c r="I52" s="308"/>
       <c r="J52" s="94"/>
       <c r="K52" s="10"/>
       <c r="L52" s="68"/>
@@ -9798,7 +9781,7 @@
       <c r="A53" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B53" s="255" t="s">
+      <c r="B53" s="252" t="s">
         <v>128</v>
       </c>
       <c r="C53" s="139"/>
@@ -9832,7 +9815,7 @@
       <c r="A54" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B54" s="255" t="s">
+      <c r="B54" s="252" t="s">
         <v>131</v>
       </c>
       <c r="C54" s="156"/>
@@ -9866,17 +9849,17 @@
       <c r="A55" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B55" s="266" t="s">
+      <c r="B55" s="263" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="267"/>
-      <c r="D55" s="266">
+      <c r="C55" s="264"/>
+      <c r="D55" s="263">
         <v>1</v>
       </c>
       <c r="E55" s="140">
         <v>1</v>
       </c>
-      <c r="F55" s="268">
+      <c r="F55" s="265">
         <v>33.700000000000003</v>
       </c>
       <c r="G55" s="141">
@@ -9920,7 +9903,7 @@
       <c r="H56" s="152" t="s">
         <v>136</v>
       </c>
-      <c r="I56" s="256" t="s">
+      <c r="I56" s="253" t="s">
         <v>137</v>
       </c>
       <c r="J56" s="27">
@@ -9954,7 +9937,7 @@
       <c r="H57" s="152" t="s">
         <v>139</v>
       </c>
-      <c r="I57" s="273" t="s">
+      <c r="I57" s="270" t="s">
         <v>140</v>
       </c>
       <c r="J57" s="27">
@@ -9988,7 +9971,7 @@
       <c r="H58" s="152" t="s">
         <v>142</v>
       </c>
-      <c r="I58" s="256" t="s">
+      <c r="I58" s="253" t="s">
         <v>143</v>
       </c>
       <c r="J58" s="27">
@@ -10022,7 +10005,7 @@
       <c r="H59" s="152" t="s">
         <v>145</v>
       </c>
-      <c r="I59" s="256" t="s">
+      <c r="I59" s="253" t="s">
         <v>49</v>
       </c>
       <c r="J59" s="94"/>
@@ -10034,11 +10017,11 @@
       <c r="A60" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B60" s="266" t="s">
+      <c r="B60" s="263" t="s">
         <v>146</v>
       </c>
-      <c r="C60" s="267"/>
-      <c r="D60" s="266">
+      <c r="C60" s="264"/>
+      <c r="D60" s="263">
         <v>1</v>
       </c>
       <c r="E60" s="140">
@@ -10054,7 +10037,7 @@
       <c r="H60" s="152" t="s">
         <v>147</v>
       </c>
-      <c r="I60" s="264" t="s">
+      <c r="I60" s="261" t="s">
         <v>148</v>
       </c>
       <c r="J60" s="27">
@@ -10068,7 +10051,7 @@
       <c r="A61" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B61" s="255" t="s">
+      <c r="B61" s="252" t="s">
         <v>149</v>
       </c>
       <c r="C61" s="139"/>
@@ -10088,7 +10071,7 @@
       <c r="H61" s="152" t="s">
         <v>150</v>
       </c>
-      <c r="I61" s="264" t="s">
+      <c r="I61" s="261" t="s">
         <v>151</v>
       </c>
       <c r="J61" s="27">
@@ -10104,7 +10087,7 @@
       <c r="A62" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B62" s="255" t="s">
+      <c r="B62" s="252" t="s">
         <v>153</v>
       </c>
       <c r="C62" s="139"/>
@@ -10124,7 +10107,7 @@
       <c r="H62" s="152" t="s">
         <v>154</v>
       </c>
-      <c r="I62" s="264" t="s">
+      <c r="I62" s="261" t="s">
         <v>151</v>
       </c>
       <c r="J62" s="94"/>
@@ -10136,7 +10119,7 @@
       <c r="A63" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B63" s="255" t="s">
+      <c r="B63" s="252" t="s">
         <v>155</v>
       </c>
       <c r="C63" s="139"/>
@@ -10152,7 +10135,7 @@
       <c r="H63" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="I63" s="311"/>
+      <c r="I63" s="308"/>
       <c r="J63" s="94"/>
       <c r="K63" s="10"/>
       <c r="L63" s="68"/>
@@ -10164,7 +10147,7 @@
       <c r="A64" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="B64" s="266" t="s">
+      <c r="B64" s="263" t="s">
         <v>158</v>
       </c>
       <c r="C64" s="160"/>
@@ -10184,7 +10167,7 @@
       <c r="H64" s="152" t="s">
         <v>159</v>
       </c>
-      <c r="I64" s="264" t="s">
+      <c r="I64" s="261" t="s">
         <v>151</v>
       </c>
       <c r="J64" s="27">
@@ -10217,7 +10200,7 @@
       <c r="H65" s="167" t="s">
         <v>162</v>
       </c>
-      <c r="I65" s="256" t="s">
+      <c r="I65" s="253" t="s">
         <v>163</v>
       </c>
       <c r="J65" s="27">
@@ -10250,7 +10233,7 @@
       <c r="H66" s="167" t="s">
         <v>165</v>
       </c>
-      <c r="I66" s="256" t="s">
+      <c r="I66" s="253" t="s">
         <v>163</v>
       </c>
       <c r="J66" s="27">
@@ -10335,7 +10318,7 @@
       <c r="A69" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B69" s="266" t="s">
+      <c r="B69" s="263" t="s">
         <v>172</v>
       </c>
       <c r="C69" s="151"/>
@@ -10981,7 +10964,7 @@
       <c r="A87" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="B87" s="262" t="s">
+      <c r="B87" s="259" t="s">
         <v>207</v>
       </c>
       <c r="C87" s="139"/>
@@ -11071,7 +11054,7 @@
       <c r="H89" s="169" t="s">
         <v>212</v>
       </c>
-      <c r="I89" s="256" t="s">
+      <c r="I89" s="253" t="s">
         <v>171</v>
       </c>
       <c r="J89" s="27">
@@ -11122,7 +11105,7 @@
       <c r="A91" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="B91" s="262" t="s">
+      <c r="B91" s="259" t="s">
         <v>215</v>
       </c>
       <c r="C91" s="139"/>
@@ -11520,7 +11503,7 @@
       <c r="A102" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="B102" s="255" t="s">
+      <c r="B102" s="252" t="s">
         <v>237</v>
       </c>
       <c r="C102" s="156"/>
@@ -11552,79 +11535,79 @@
       <c r="L102" s="68"/>
       <c r="M102" s="129"/>
     </row>
-    <row r="103" spans="1:13" s="304" customFormat="1">
-      <c r="A103" s="296" t="s">
+    <row r="103" spans="1:13" s="301" customFormat="1">
+      <c r="A103" s="293" t="s">
         <v>160</v>
       </c>
-      <c r="B103" s="297" t="s">
+      <c r="B103" s="294" t="s">
         <v>238</v>
       </c>
-      <c r="C103" s="298"/>
-      <c r="D103" s="297">
+      <c r="C103" s="295"/>
+      <c r="D103" s="294">
         <v>44</v>
       </c>
-      <c r="E103" s="299">
+      <c r="E103" s="296">
         <v>5</v>
       </c>
-      <c r="F103" s="300">
+      <c r="F103" s="297">
         <v>3.21</v>
       </c>
-      <c r="G103" s="300">
+      <c r="G103" s="297">
         <f t="shared" ref="G103:G134" si="4">E103*F103</f>
         <v>16.05</v>
       </c>
-      <c r="H103" s="301" t="s">
+      <c r="H103" s="298" t="s">
         <v>239</v>
       </c>
-      <c r="I103" s="302" t="s">
+      <c r="I103" s="299" t="s">
         <v>171</v>
       </c>
-      <c r="J103" s="303">
+      <c r="J103" s="300">
         <v>10</v>
       </c>
-      <c r="K103" s="304">
+      <c r="K103" s="301">
         <v>933</v>
       </c>
-      <c r="L103" s="305"/>
-      <c r="M103" s="306" t="s">
+      <c r="L103" s="302"/>
+      <c r="M103" s="303" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="104" spans="1:13" s="304" customFormat="1">
-      <c r="A104" s="296" t="s">
+    <row r="104" spans="1:13" s="301" customFormat="1">
+      <c r="A104" s="293" t="s">
         <v>160</v>
       </c>
-      <c r="B104" s="297" t="s">
+      <c r="B104" s="294" t="s">
         <v>241</v>
       </c>
-      <c r="C104" s="298"/>
-      <c r="D104" s="297">
+      <c r="C104" s="295"/>
+      <c r="D104" s="294">
         <v>17</v>
       </c>
-      <c r="E104" s="299">
+      <c r="E104" s="296">
         <v>2</v>
       </c>
-      <c r="F104" s="300">
+      <c r="F104" s="297">
         <v>3.57</v>
       </c>
-      <c r="G104" s="300">
+      <c r="G104" s="297">
         <f t="shared" si="4"/>
         <v>7.14</v>
       </c>
-      <c r="H104" s="301" t="s">
+      <c r="H104" s="298" t="s">
         <v>242</v>
       </c>
-      <c r="I104" s="302" t="s">
+      <c r="I104" s="299" t="s">
         <v>171</v>
       </c>
-      <c r="J104" s="303">
+      <c r="J104" s="300">
         <v>10</v>
       </c>
-      <c r="K104" s="304">
+      <c r="K104" s="301">
         <v>933</v>
       </c>
-      <c r="L104" s="305"/>
-      <c r="M104" s="306" t="s">
+      <c r="L104" s="302"/>
+      <c r="M104" s="303" t="s">
         <v>243</v>
       </c>
     </row>
@@ -11688,7 +11671,7 @@
       <c r="H106" s="168" t="s">
         <v>248</v>
       </c>
-      <c r="I106" s="256" t="s">
+      <c r="I106" s="253" t="s">
         <v>249</v>
       </c>
       <c r="J106" s="27">
@@ -11722,7 +11705,7 @@
       <c r="H107" s="168" t="s">
         <v>251</v>
       </c>
-      <c r="I107" s="256" t="s">
+      <c r="I107" s="253" t="s">
         <v>249</v>
       </c>
       <c r="J107" s="27"/>
@@ -11788,7 +11771,7 @@
       <c r="H109" s="168" t="s">
         <v>255</v>
       </c>
-      <c r="I109" s="256" t="s">
+      <c r="I109" s="253" t="s">
         <v>249</v>
       </c>
       <c r="J109" s="27">
@@ -11822,7 +11805,7 @@
       <c r="H110" s="168" t="s">
         <v>257</v>
       </c>
-      <c r="I110" s="256" t="s">
+      <c r="I110" s="253" t="s">
         <v>249</v>
       </c>
       <c r="J110" s="27">
@@ -11858,7 +11841,7 @@
       <c r="H111" s="169" t="s">
         <v>261</v>
       </c>
-      <c r="I111" s="256" t="s">
+      <c r="I111" s="253" t="s">
         <v>262</v>
       </c>
       <c r="J111" s="27"/>
@@ -11890,7 +11873,7 @@
       <c r="H112" s="167" t="s">
         <v>264</v>
       </c>
-      <c r="I112" s="256" t="s">
+      <c r="I112" s="253" t="s">
         <v>265</v>
       </c>
       <c r="J112" s="27">
@@ -11956,7 +11939,7 @@
       <c r="H114" s="169" t="s">
         <v>270</v>
       </c>
-      <c r="I114" s="256" t="s">
+      <c r="I114" s="253" t="s">
         <v>171</v>
       </c>
       <c r="J114" s="27">
@@ -11990,7 +11973,7 @@
       <c r="H115" s="152" t="s">
         <v>273</v>
       </c>
-      <c r="I115" s="256" t="s">
+      <c r="I115" s="253" t="s">
         <v>274</v>
       </c>
       <c r="J115" s="27">
@@ -12072,7 +12055,7 @@
       <c r="A118" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B118" s="265" t="s">
+      <c r="B118" s="262" t="s">
         <v>281</v>
       </c>
       <c r="C118" s="180"/>
@@ -12092,7 +12075,7 @@
       <c r="H118" s="152" t="s">
         <v>282</v>
       </c>
-      <c r="I118" s="256" t="s">
+      <c r="I118" s="253" t="s">
         <v>283</v>
       </c>
       <c r="J118" s="27">
@@ -12106,7 +12089,7 @@
       <c r="A119" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="B119" s="265" t="s">
+      <c r="B119" s="262" t="s">
         <v>284</v>
       </c>
       <c r="C119" s="180"/>
@@ -12126,7 +12109,7 @@
       <c r="H119" s="197" t="s">
         <v>285</v>
       </c>
-      <c r="I119" s="256"/>
+      <c r="I119" s="253"/>
       <c r="J119" s="27">
         <v>1</v>
       </c>
@@ -12160,7 +12143,7 @@
       <c r="H120" s="152" t="s">
         <v>288</v>
       </c>
-      <c r="I120" s="256" t="s">
+      <c r="I120" s="253" t="s">
         <v>289</v>
       </c>
       <c r="J120" s="27">
@@ -12174,7 +12157,7 @@
       <c r="A121" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="B121" s="265" t="s">
+      <c r="B121" s="262" t="s">
         <v>290</v>
       </c>
       <c r="C121" s="180"/>
@@ -12194,7 +12177,7 @@
       <c r="H121" s="152" t="s">
         <v>291</v>
       </c>
-      <c r="I121" s="256" t="s">
+      <c r="I121" s="253" t="s">
         <v>289</v>
       </c>
       <c r="J121" s="27">
@@ -12208,7 +12191,7 @@
       <c r="A122" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="B122" s="263" t="s">
+      <c r="B122" s="260" t="s">
         <v>292</v>
       </c>
       <c r="C122" s="139"/>
@@ -12228,7 +12211,7 @@
       <c r="H122" s="167" t="s">
         <v>293</v>
       </c>
-      <c r="I122" s="256" t="s">
+      <c r="I122" s="253" t="s">
         <v>294</v>
       </c>
       <c r="J122" s="27">
@@ -12242,7 +12225,7 @@
       <c r="A123" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="B123" s="274" t="s">
+      <c r="B123" s="271" t="s">
         <v>296</v>
       </c>
       <c r="C123" s="182">
@@ -12264,7 +12247,7 @@
       <c r="H123" s="169" t="s">
         <v>297</v>
       </c>
-      <c r="I123" s="264" t="s">
+      <c r="I123" s="261" t="s">
         <v>298</v>
       </c>
       <c r="J123" s="27">
@@ -12278,7 +12261,7 @@
       <c r="A124" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="B124" s="255" t="s">
+      <c r="B124" s="252" t="s">
         <v>299</v>
       </c>
       <c r="C124" s="156">
@@ -12300,7 +12283,7 @@
       <c r="H124" s="169" t="s">
         <v>300</v>
       </c>
-      <c r="I124" s="264" t="s">
+      <c r="I124" s="261" t="s">
         <v>298</v>
       </c>
       <c r="J124" s="27">
@@ -12317,7 +12300,7 @@
       <c r="B125" s="26" t="s">
         <v>301</v>
       </c>
-      <c r="C125" s="267" t="s">
+      <c r="C125" s="264" t="s">
         <v>302</v>
       </c>
       <c r="D125" s="13">
@@ -12336,7 +12319,7 @@
       <c r="H125" s="152" t="s">
         <v>303</v>
       </c>
-      <c r="I125" s="264" t="s">
+      <c r="I125" s="261" t="s">
         <v>298</v>
       </c>
       <c r="J125" s="27">
@@ -12370,7 +12353,7 @@
       <c r="H126" s="169" t="s">
         <v>305</v>
       </c>
-      <c r="I126" s="256" t="s">
+      <c r="I126" s="253" t="s">
         <v>163</v>
       </c>
       <c r="J126" s="27">
@@ -12406,7 +12389,7 @@
       <c r="H127" s="169" t="s">
         <v>307</v>
       </c>
-      <c r="I127" s="256" t="s">
+      <c r="I127" s="253" t="s">
         <v>308</v>
       </c>
       <c r="J127" s="27">
@@ -12442,7 +12425,7 @@
       <c r="H128" s="169" t="s">
         <v>310</v>
       </c>
-      <c r="I128" s="256" t="s">
+      <c r="I128" s="253" t="s">
         <v>308</v>
       </c>
       <c r="J128" s="27">
@@ -12478,7 +12461,7 @@
       <c r="H129" s="169" t="s">
         <v>312</v>
       </c>
-      <c r="I129" s="256" t="s">
+      <c r="I129" s="253" t="s">
         <v>308</v>
       </c>
       <c r="J129" s="27">
@@ -12514,7 +12497,7 @@
       <c r="H130" s="169" t="s">
         <v>314</v>
       </c>
-      <c r="I130" s="256" t="s">
+      <c r="I130" s="253" t="s">
         <v>308</v>
       </c>
       <c r="J130" s="27">
@@ -12550,7 +12533,7 @@
       <c r="H131" s="169" t="s">
         <v>316</v>
       </c>
-      <c r="I131" s="256" t="s">
+      <c r="I131" s="253" t="s">
         <v>308</v>
       </c>
       <c r="J131" s="27">
@@ -12586,7 +12569,7 @@
       <c r="H132" s="169" t="s">
         <v>318</v>
       </c>
-      <c r="I132" s="256" t="s">
+      <c r="I132" s="253" t="s">
         <v>308</v>
       </c>
       <c r="J132" s="27">
@@ -12620,7 +12603,7 @@
       <c r="H133" s="169" t="s">
         <v>320</v>
       </c>
-      <c r="I133" s="256" t="s">
+      <c r="I133" s="253" t="s">
         <v>321</v>
       </c>
       <c r="J133" s="27">
@@ -12656,7 +12639,7 @@
       <c r="H134" s="187" t="s">
         <v>324</v>
       </c>
-      <c r="I134" s="256" t="s">
+      <c r="I134" s="253" t="s">
         <v>325</v>
       </c>
       <c r="J134" s="27">
@@ -12692,7 +12675,7 @@
       <c r="H135" s="167" t="s">
         <v>327</v>
       </c>
-      <c r="I135" s="256" t="s">
+      <c r="I135" s="253" t="s">
         <v>328</v>
       </c>
       <c r="J135" s="27">
@@ -12706,7 +12689,7 @@
       <c r="A136" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B136" s="255" t="s">
+      <c r="B136" s="252" t="s">
         <v>330</v>
       </c>
       <c r="C136" s="156"/>
@@ -12726,7 +12709,7 @@
       <c r="H136" s="167" t="s">
         <v>331</v>
       </c>
-      <c r="I136" s="256" t="s">
+      <c r="I136" s="253" t="s">
         <v>332</v>
       </c>
       <c r="J136" s="27">
@@ -12734,7 +12717,7 @@
       </c>
       <c r="K136" s="69"/>
       <c r="L136" s="70"/>
-      <c r="M136" s="294" t="s">
+      <c r="M136" s="291" t="s">
         <v>333</v>
       </c>
     </row>
@@ -12742,7 +12725,7 @@
       <c r="A137" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B137" s="255" t="s">
+      <c r="B137" s="252" t="s">
         <v>334</v>
       </c>
       <c r="C137" s="156"/>
@@ -12762,7 +12745,7 @@
       <c r="H137" s="167" t="s">
         <v>335</v>
       </c>
-      <c r="I137" s="256" t="s">
+      <c r="I137" s="253" t="s">
         <v>332</v>
       </c>
       <c r="J137" s="27">
@@ -12770,13 +12753,13 @@
       </c>
       <c r="K137" s="69"/>
       <c r="L137" s="70"/>
-      <c r="M137" s="293"/>
+      <c r="M137" s="290"/>
     </row>
     <row r="138" spans="1:13" s="12" customFormat="1" ht="15.75">
       <c r="A138" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="B138" s="255" t="s">
+      <c r="B138" s="252" t="s">
         <v>336</v>
       </c>
       <c r="C138" s="139"/>
@@ -12796,7 +12779,7 @@
       <c r="H138" s="167" t="s">
         <v>337</v>
       </c>
-      <c r="I138" s="256" t="s">
+      <c r="I138" s="253" t="s">
         <v>332</v>
       </c>
       <c r="J138" s="27">
@@ -12810,7 +12793,7 @@
       <c r="A139" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B139" s="255" t="s">
+      <c r="B139" s="252" t="s">
         <v>338</v>
       </c>
       <c r="C139" s="156"/>
@@ -12830,7 +12813,7 @@
       <c r="H139" s="167" t="s">
         <v>339</v>
       </c>
-      <c r="I139" s="256" t="s">
+      <c r="I139" s="253" t="s">
         <v>332</v>
       </c>
       <c r="J139" s="27">
@@ -12844,7 +12827,7 @@
       <c r="A140" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="B140" s="255" t="s">
+      <c r="B140" s="252" t="s">
         <v>340</v>
       </c>
       <c r="C140" s="156"/>
@@ -12864,7 +12847,7 @@
       <c r="H140" s="167" t="s">
         <v>341</v>
       </c>
-      <c r="I140" s="256" t="s">
+      <c r="I140" s="253" t="s">
         <v>332</v>
       </c>
       <c r="J140" s="27">
@@ -12934,7 +12917,7 @@
       <c r="H142" s="167" t="s">
         <v>345</v>
       </c>
-      <c r="I142" s="256" t="s">
+      <c r="I142" s="253" t="s">
         <v>346</v>
       </c>
       <c r="J142" s="27">
@@ -12982,7 +12965,7 @@
       <c r="A144" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="B144" s="263" t="s">
+      <c r="B144" s="260" t="s">
         <v>352</v>
       </c>
       <c r="C144" s="164"/>
@@ -13002,7 +12985,7 @@
       <c r="H144" s="167" t="s">
         <v>353</v>
       </c>
-      <c r="I144" s="256" t="s">
+      <c r="I144" s="253" t="s">
         <v>354</v>
       </c>
       <c r="J144" s="27">
@@ -13016,7 +12999,7 @@
       <c r="A145" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="B145" s="263" t="s">
+      <c r="B145" s="260" t="s">
         <v>355</v>
       </c>
       <c r="C145" s="139"/>
@@ -13036,7 +13019,7 @@
       <c r="H145" s="167" t="s">
         <v>356</v>
       </c>
-      <c r="I145" s="256" t="s">
+      <c r="I145" s="253" t="s">
         <v>357</v>
       </c>
       <c r="J145" s="94"/>
@@ -13102,7 +13085,7 @@
       <c r="H147" s="167" t="s">
         <v>362</v>
       </c>
-      <c r="I147" s="256" t="s">
+      <c r="I147" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J147" s="27">
@@ -13136,7 +13119,7 @@
       <c r="H148" s="167" t="s">
         <v>364</v>
       </c>
-      <c r="I148" s="256" t="s">
+      <c r="I148" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J148" s="27">
@@ -13170,7 +13153,7 @@
       <c r="H149" s="167" t="s">
         <v>366</v>
       </c>
-      <c r="I149" s="256" t="s">
+      <c r="I149" s="253" t="s">
         <v>33</v>
       </c>
       <c r="J149" s="27">
@@ -13238,7 +13221,7 @@
       <c r="H151" s="167" t="s">
         <v>370</v>
       </c>
-      <c r="I151" s="256" t="s">
+      <c r="I151" s="253" t="s">
         <v>371</v>
       </c>
       <c r="J151" s="27">
@@ -13305,13 +13288,13 @@
     </row>
     <row r="154" spans="1:13">
       <c r="G154" s="11"/>
-      <c r="K154" s="275"/>
+      <c r="K154" s="272"/>
     </row>
     <row r="155" spans="1:13">
-      <c r="K155" s="275"/>
+      <c r="K155" s="272"/>
     </row>
     <row r="156" spans="1:13">
-      <c r="K156" s="275"/>
+      <c r="K156" s="272"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -14705,7 +14688,7 @@
       <c r="H51" s="112"/>
     </row>
     <row r="52" spans="1:8">
-      <c r="A52" s="295" t="s">
+      <c r="A52" s="292" t="s">
         <v>689</v>
       </c>
       <c r="B52" s="36" t="s">
@@ -14726,7 +14709,7 @@
       <c r="H52" s="112"/>
     </row>
     <row r="53" spans="1:8">
-      <c r="A53" s="295" t="s">
+      <c r="A53" s="292" t="s">
         <v>689</v>
       </c>
       <c r="B53" s="36" t="s">
@@ -15604,7 +15587,7 @@
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="312" t="s">
+      <c r="A93" s="309" t="s">
         <v>689</v>
       </c>
       <c r="B93" t="s">
@@ -15621,7 +15604,7 @@
       </c>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="295" t="s">
+      <c r="A94" s="292" t="s">
         <v>689</v>
       </c>
       <c r="B94" t="s">
@@ -15638,7 +15621,7 @@
       </c>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="295" t="s">
+      <c r="A95" s="292" t="s">
         <v>689</v>
       </c>
       <c r="B95" t="s">
@@ -15706,7 +15689,7 @@
       <c r="B3" t="s">
         <v>710</v>
       </c>
-      <c r="C3" s="309" t="s">
+      <c r="C3" s="306" t="s">
         <v>711</v>
       </c>
     </row>
@@ -15720,7 +15703,7 @@
       <c r="C4" s="6" t="s">
         <v>714</v>
       </c>
-      <c r="D4" s="310" t="s">
+      <c r="D4" s="307" t="s">
         <v>715</v>
       </c>
     </row>
@@ -15791,18 +15774,18 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B14" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="B15" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
     </row>
   </sheetData>
@@ -15955,7 +15938,7 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="254" t="s">
+      <c r="A12" s="251" t="s">
         <v>765</v>
       </c>
       <c r="B12" s="38" t="s">
@@ -16040,7 +16023,7 @@
       <c r="C21" t="s">
         <v>782</v>
       </c>
-      <c r="D21" s="253" t="s">
+      <c r="D21" s="250" t="s">
         <v>783</v>
       </c>
     </row>
@@ -16428,7 +16411,7 @@
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="308" t="s">
+      <c r="A14" s="305" t="s">
         <v>854</v>
       </c>
       <c r="E14" s="134" t="s">
@@ -17476,7 +17459,7 @@
     <col min="4" max="4" width="8.42578125" style="220" customWidth="1"/>
     <col min="5" max="5" width="7.140625" style="220" customWidth="1"/>
     <col min="6" max="6" width="7.140625" style="220" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.140625" style="220" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="220" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" style="220" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.85546875" style="220" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" style="220" customWidth="1"/>
@@ -17501,9 +17484,9 @@
       <c r="C2" s="220"/>
     </row>
     <row r="3" spans="1:12" s="222" customFormat="1" ht="15" customHeight="1">
-      <c r="A3" s="246"/>
-      <c r="B3" s="247"/>
-      <c r="C3" s="247"/>
+      <c r="A3" s="243"/>
+      <c r="B3" s="244"/>
+      <c r="C3" s="244"/>
       <c r="D3" s="226" t="s">
         <v>1035</v>
       </c>
@@ -17522,7 +17505,7 @@
       <c r="I3" s="226" t="s">
         <v>1036</v>
       </c>
-      <c r="J3" s="252" t="s">
+      <c r="J3" s="249" t="s">
         <v>1037</v>
       </c>
       <c r="K3" s="226" t="s">
@@ -17536,38 +17519,38 @@
       <c r="A4" s="242" t="s">
         <v>1040</v>
       </c>
-      <c r="B4" s="243" t="s">
+      <c r="B4" s="242" t="s">
         <v>1041</v>
       </c>
-      <c r="C4" s="244" t="s">
+      <c r="C4" s="242" t="s">
         <v>1042</v>
       </c>
-      <c r="D4" s="244" t="s">
+      <c r="D4" s="242" t="s">
         <v>1043</v>
       </c>
-      <c r="E4" s="244" t="s">
+      <c r="E4" s="242" t="s">
         <v>1044</v>
       </c>
-      <c r="F4" s="244" t="s">
+      <c r="F4" s="242" t="s">
         <v>1045</v>
       </c>
-      <c r="G4" s="244" t="s">
+      <c r="G4" s="242" t="s">
         <v>1046</v>
       </c>
-      <c r="H4" s="244" t="s">
+      <c r="H4" s="242" t="s">
         <v>1047</v>
       </c>
-      <c r="I4" s="244" t="s">
+      <c r="I4" s="242" t="s">
         <v>1048</v>
       </c>
-      <c r="J4" s="244" t="s">
+      <c r="J4" s="242" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K4" s="242" t="s">
+        <v>1100</v>
+      </c>
+      <c r="L4" s="242" t="s">
         <v>1049</v>
-      </c>
-      <c r="K4" s="244" t="s">
-        <v>1050</v>
-      </c>
-      <c r="L4" s="245" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
@@ -17575,7 +17558,7 @@
         <v>675</v>
       </c>
       <c r="B5" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C5" s="239">
         <v>0</v>
@@ -17613,10 +17596,10 @@
         <v>676</v>
       </c>
       <c r="B6" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C6" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D6" s="239">
         <v>90</v>
@@ -17648,10 +17631,10 @@
     </row>
     <row r="7" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="237" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="B7" s="238" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C7" s="239">
         <v>0</v>
@@ -17685,11 +17668,11 @@
       </c>
     </row>
     <row r="8" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A8" s="248" t="s">
-        <v>1056</v>
+      <c r="A8" s="245" t="s">
+        <v>1054</v>
       </c>
       <c r="B8" s="238" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="C8" s="239">
         <v>0</v>
@@ -17724,11 +17707,11 @@
     </row>
     <row r="9" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="237" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B9" s="238"/>
       <c r="C9" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D9" s="239">
         <v>158</v>
@@ -17759,14 +17742,14 @@
       </c>
     </row>
     <row r="10" spans="1:12" s="222" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A10" s="248" t="s">
-        <v>1058</v>
+      <c r="A10" s="245" t="s">
+        <v>1056</v>
       </c>
       <c r="B10" s="238" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C10" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D10" s="239">
         <v>165</v>
@@ -17798,13 +17781,13 @@
     </row>
     <row r="11" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="237" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B11" s="238" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C11" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D11" s="239">
         <v>165</v>
@@ -17836,7 +17819,7 @@
     </row>
     <row r="12" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="237" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B12" s="238"/>
       <c r="C12" s="239">
@@ -17871,11 +17854,11 @@
       </c>
     </row>
     <row r="13" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A13" s="248" t="s">
-        <v>1062</v>
+      <c r="A13" s="245" t="s">
+        <v>1060</v>
       </c>
       <c r="B13" s="238" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="C13" s="239">
         <v>0</v>
@@ -17909,12 +17892,12 @@
       </c>
     </row>
     <row r="14" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A14" s="248" t="s">
-        <v>1064</v>
+      <c r="A14" s="245" t="s">
+        <v>1062</v>
       </c>
       <c r="B14" s="238"/>
       <c r="C14" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D14" s="239">
         <v>170</v>
@@ -17946,13 +17929,13 @@
     </row>
     <row r="15" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="237" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B15" s="238" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C15" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D15" s="239">
         <v>105</v>
@@ -17984,13 +17967,13 @@
     </row>
     <row r="16" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A16" s="237" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B16" s="238" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C16" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D16" s="239">
         <v>70</v>
@@ -18021,14 +18004,14 @@
       </c>
     </row>
     <row r="17" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A17" s="248" t="s">
-        <v>1068</v>
+      <c r="A17" s="245" t="s">
+        <v>1066</v>
       </c>
       <c r="B17" s="238" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="C17" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D17" s="239">
         <v>143</v>
@@ -18060,13 +18043,13 @@
     </row>
     <row r="18" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="237" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B18" s="238" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C18" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D18" s="239">
         <v>60</v>
@@ -18098,13 +18081,13 @@
     </row>
     <row r="19" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="237" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B19" s="238" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C19" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D19" s="239">
         <v>60</v>
@@ -18136,10 +18119,10 @@
     </row>
     <row r="20" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="237" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B20" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C20" s="239">
         <v>0</v>
@@ -18174,11 +18157,11 @@
     </row>
     <row r="21" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A21" s="237" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B21" s="238"/>
       <c r="C21" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D21" s="239">
         <v>143</v>
@@ -18209,12 +18192,12 @@
       </c>
     </row>
     <row r="22" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A22" s="248" t="s">
-        <v>1073</v>
+      <c r="A22" s="245" t="s">
+        <v>1071</v>
       </c>
       <c r="B22" s="238"/>
       <c r="C22" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D22" s="239">
         <v>137</v>
@@ -18245,12 +18228,12 @@
       </c>
     </row>
     <row r="23" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A23" s="248" t="s">
-        <v>1074</v>
+      <c r="A23" s="245" t="s">
+        <v>1072</v>
       </c>
       <c r="B23" s="238"/>
       <c r="C23" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D23" s="239">
         <v>126</v>
@@ -18281,12 +18264,12 @@
       </c>
     </row>
     <row r="24" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A24" s="248" t="s">
-        <v>1075</v>
+      <c r="A24" s="245" t="s">
+        <v>1073</v>
       </c>
       <c r="B24" s="238"/>
       <c r="C24" s="239" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D24" s="239">
         <v>80</v>
@@ -18318,13 +18301,13 @@
     </row>
     <row r="25" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="237" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B25" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C25" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D25" s="239">
         <v>113</v>
@@ -18356,13 +18339,13 @@
     </row>
     <row r="26" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A26" s="237" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B26" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C26" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D26" s="239">
         <v>113</v>
@@ -18394,13 +18377,13 @@
     </row>
     <row r="27" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A27" s="237" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B27" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C27" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D27" s="239">
         <v>145</v>
@@ -18431,14 +18414,14 @@
       </c>
     </row>
     <row r="28" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A28" s="249" t="s">
-        <v>1080</v>
+      <c r="A28" s="246" t="s">
+        <v>1078</v>
       </c>
       <c r="B28" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C28" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D28" s="239">
         <v>70</v>
@@ -18470,13 +18453,13 @@
     </row>
     <row r="29" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="237" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B29" s="238" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C29" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D29" s="239">
         <v>60</v>
@@ -18512,7 +18495,7 @@
       </c>
       <c r="B30" s="238"/>
       <c r="C30" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D30" s="239">
         <v>140</v>
@@ -18543,14 +18526,14 @@
       </c>
     </row>
     <row r="31" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A31" s="248" t="s">
+      <c r="A31" s="245" t="s">
         <v>821</v>
       </c>
       <c r="B31" s="238" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C31" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D31" s="239">
         <v>105</v>
@@ -18581,14 +18564,14 @@
       </c>
     </row>
     <row r="32" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A32" s="248" t="s">
-        <v>1083</v>
+      <c r="A32" s="245" t="s">
+        <v>1081</v>
       </c>
       <c r="B32" s="238" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="C32" s="239" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="D32" s="239">
         <v>105</v>
@@ -18619,11 +18602,11 @@
       </c>
     </row>
     <row r="33" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A33" s="248" t="s">
-        <v>1084</v>
+      <c r="A33" s="245" t="s">
+        <v>1082</v>
       </c>
       <c r="B33" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C33" s="239">
         <v>0</v>
@@ -18657,11 +18640,11 @@
       </c>
     </row>
     <row r="34" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A34" s="248" t="s">
-        <v>1085</v>
+      <c r="A34" s="245" t="s">
+        <v>1083</v>
       </c>
       <c r="B34" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C34" s="239">
         <v>0</v>
@@ -18695,14 +18678,14 @@
       </c>
     </row>
     <row r="35" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A35" s="248" t="s">
-        <v>1086</v>
+      <c r="A35" s="245" t="s">
+        <v>1084</v>
       </c>
       <c r="B35" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C35" s="239" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D35" s="239">
         <v>90</v>
@@ -18733,14 +18716,14 @@
       </c>
     </row>
     <row r="36" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A36" s="248" t="s">
+      <c r="A36" s="245" t="s">
         <v>822</v>
       </c>
       <c r="B36" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C36" s="239" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="D36" s="239">
         <v>80</v>
@@ -18771,14 +18754,14 @@
       </c>
     </row>
     <row r="37" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A37" s="248" t="s">
+      <c r="A37" s="245" t="s">
         <v>820</v>
       </c>
       <c r="B37" s="238" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C37" s="239" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="D37" s="239">
         <v>85</v>
@@ -18810,55 +18793,55 @@
     </row>
     <row r="38" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="227"/>
-      <c r="B38" s="314"/>
-      <c r="C38" s="314"/>
-      <c r="D38" s="315"/>
-      <c r="E38" s="315"/>
-      <c r="F38" s="315"/>
-      <c r="G38" s="315"/>
-      <c r="H38" s="315"/>
-      <c r="I38" s="315"/>
-      <c r="J38" s="315"/>
+      <c r="B38" s="311"/>
+      <c r="C38" s="311"/>
+      <c r="D38" s="312"/>
+      <c r="E38" s="312"/>
+      <c r="F38" s="312"/>
+      <c r="G38" s="312"/>
+      <c r="H38" s="312"/>
+      <c r="I38" s="312"/>
+      <c r="J38" s="312"/>
       <c r="K38" s="229"/>
       <c r="L38" s="229"/>
       <c r="M38" s="230"/>
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1">
       <c r="A39" s="225" t="s">
-        <v>1088</v>
-      </c>
-      <c r="B39" s="307"/>
-      <c r="C39" s="307"/>
+        <v>1086</v>
+      </c>
+      <c r="B39" s="304"/>
+      <c r="C39" s="304"/>
       <c r="K39" s="231"/>
       <c r="L39" s="231"/>
       <c r="M39" s="232"/>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1">
-      <c r="B40" s="307"/>
-      <c r="C40" s="307"/>
+      <c r="B40" s="304"/>
+      <c r="C40" s="304"/>
       <c r="K40" s="231"/>
       <c r="L40" s="231"/>
       <c r="M40" s="232"/>
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1">
       <c r="A41" s="225" t="s">
-        <v>1089</v>
-      </c>
-      <c r="B41" s="316"/>
-      <c r="C41" s="316"/>
-      <c r="D41" s="317"/>
-      <c r="E41" s="317"/>
-      <c r="F41" s="317"/>
-      <c r="G41" s="317"/>
-      <c r="H41" s="317"/>
-      <c r="I41" s="317"/>
-      <c r="J41" s="317"/>
-      <c r="K41" s="317"/>
+        <v>1087</v>
+      </c>
+      <c r="B41" s="313"/>
+      <c r="C41" s="313"/>
+      <c r="D41" s="314"/>
+      <c r="E41" s="314"/>
+      <c r="F41" s="314"/>
+      <c r="G41" s="314"/>
+      <c r="H41" s="314"/>
+      <c r="I41" s="314"/>
+      <c r="J41" s="314"/>
+      <c r="K41" s="314"/>
       <c r="M41" s="232"/>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A42" s="307" t="s">
-        <v>1090</v>
+      <c r="A42" s="304" t="s">
+        <v>1088</v>
       </c>
       <c r="B42" s="220"/>
       <c r="C42" s="220"/>
@@ -18866,8 +18849,8 @@
       <c r="M42" s="232"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A43" s="307" t="s">
-        <v>1091</v>
+      <c r="A43" s="304" t="s">
+        <v>1089</v>
       </c>
       <c r="B43" s="220"/>
       <c r="C43" s="220"/>
@@ -18875,24 +18858,24 @@
       <c r="M43" s="232"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A44" s="307" t="s">
-        <v>1092</v>
+      <c r="A44" s="304" t="s">
+        <v>1090</v>
       </c>
       <c r="B44" s="220"/>
       <c r="C44" s="220"/>
       <c r="M44" s="232"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A45" s="307" t="s">
-        <v>1093</v>
+      <c r="A45" s="304" t="s">
+        <v>1091</v>
       </c>
       <c r="B45" s="220"/>
       <c r="C45" s="220"/>
       <c r="M45" s="232"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A46" s="307" t="s">
-        <v>1094</v>
+      <c r="A46" s="304" t="s">
+        <v>1092</v>
       </c>
       <c r="B46" s="220"/>
       <c r="C46" s="220"/>
@@ -18902,14 +18885,14 @@
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
       <c r="A47" s="233" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B47" s="233"/>
       <c r="C47" s="233"/>
       <c r="D47" s="233"/>
       <c r="E47" s="234"/>
       <c r="F47" s="234"/>
-      <c r="G47" s="292"/>
+      <c r="G47" s="289"/>
       <c r="H47" s="233"/>
       <c r="I47" s="233"/>
       <c r="J47" s="233"/>
@@ -18927,8 +18910,8 @@
       <c r="M48" s="232"/>
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A49" s="250" t="s">
-        <v>1096</v>
+      <c r="A49" s="247" t="s">
+        <v>1094</v>
       </c>
       <c r="E49" s="236"/>
       <c r="F49" s="236"/>
@@ -18941,8 +18924,8 @@
       <c r="M49" s="232"/>
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A50" s="250" t="s">
-        <v>1097</v>
+      <c r="A50" s="247" t="s">
+        <v>1095</v>
       </c>
       <c r="E50" s="236"/>
       <c r="F50" s="236"/>
@@ -18955,7 +18938,7 @@
       <c r="M50" s="232"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A51" s="313"/>
+      <c r="A51" s="310"/>
       <c r="E51" s="236"/>
       <c r="F51" s="236"/>
       <c r="G51" s="236"/>
@@ -18967,7 +18950,7 @@
       <c r="M51" s="232"/>
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A52" s="251"/>
+      <c r="A52" s="248"/>
       <c r="E52" s="236"/>
       <c r="F52" s="236"/>
       <c r="G52" s="236"/>
@@ -26192,13 +26175,13 @@
       <c r="B1" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="261" t="s">
+      <c r="C1" s="258" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="261" t="s">
+      <c r="D1" s="258" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="261" t="s">
+      <c r="E1" s="258" t="s">
         <v>379</v>
       </c>
       <c r="F1" s="81"/>
@@ -26213,7 +26196,7 @@
       <c r="C2" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="D2" s="276">
+      <c r="D2" s="273">
         <v>420</v>
       </c>
       <c r="E2" s="1">
@@ -26222,10 +26205,10 @@
       <c r="F2" s="82" t="s">
         <v>383</v>
       </c>
-      <c r="G2" s="277"/>
-      <c r="H2" s="277"/>
-      <c r="I2" s="277"/>
-      <c r="J2" s="277"/>
+      <c r="G2" s="274"/>
+      <c r="H2" s="274"/>
+      <c r="I2" s="274"/>
+      <c r="J2" s="274"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="47" t="s">
@@ -26237,19 +26220,19 @@
       <c r="C3" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="D3" s="276">
+      <c r="D3" s="273">
         <v>368</v>
       </c>
       <c r="E3" s="1">
         <v>1</v>
       </c>
-      <c r="F3" s="278" t="s">
+      <c r="F3" s="275" t="s">
         <v>386</v>
       </c>
-      <c r="G3" s="277"/>
-      <c r="H3" s="277"/>
-      <c r="I3" s="277"/>
-      <c r="J3" s="277"/>
+      <c r="G3" s="274"/>
+      <c r="H3" s="274"/>
+      <c r="I3" s="274"/>
+      <c r="J3" s="274"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="47" t="s">
@@ -26261,19 +26244,19 @@
       <c r="C4" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="D4" s="276">
+      <c r="D4" s="273">
         <v>172</v>
       </c>
       <c r="E4" s="1">
         <v>1</v>
       </c>
-      <c r="F4" s="278" t="s">
+      <c r="F4" s="275" t="s">
         <v>389</v>
       </c>
-      <c r="G4" s="277"/>
-      <c r="H4" s="277"/>
-      <c r="I4" s="277"/>
-      <c r="J4" s="277"/>
+      <c r="G4" s="274"/>
+      <c r="H4" s="274"/>
+      <c r="I4" s="274"/>
+      <c r="J4" s="274"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="47" t="s">
@@ -26285,19 +26268,19 @@
       <c r="C5" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="D5" s="276">
+      <c r="D5" s="273">
         <v>420</v>
       </c>
       <c r="E5" s="1">
         <v>4</v>
       </c>
-      <c r="F5" s="278" t="s">
+      <c r="F5" s="275" t="s">
         <v>393</v>
       </c>
-      <c r="G5" s="277"/>
-      <c r="H5" s="277"/>
-      <c r="I5" s="277"/>
-      <c r="J5" s="277"/>
+      <c r="G5" s="274"/>
+      <c r="H5" s="274"/>
+      <c r="I5" s="274"/>
+      <c r="J5" s="274"/>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="23"/>
@@ -26307,17 +26290,17 @@
       <c r="C6" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D6" s="276">
+      <c r="D6" s="273">
         <v>480</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="F6" s="83"/>
-      <c r="G6" s="277"/>
-      <c r="H6" s="277"/>
-      <c r="I6" s="277"/>
-      <c r="J6" s="277"/>
+      <c r="G6" s="274"/>
+      <c r="H6" s="274"/>
+      <c r="I6" s="274"/>
+      <c r="J6" s="274"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="23"/>
@@ -26327,17 +26310,17 @@
       <c r="C7" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="D7" s="276">
+      <c r="D7" s="273">
         <v>750</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="F7" s="83"/>
-      <c r="G7" s="277"/>
-      <c r="H7" s="277"/>
-      <c r="I7" s="277"/>
-      <c r="J7" s="277"/>
+      <c r="G7" s="274"/>
+      <c r="H7" s="274"/>
+      <c r="I7" s="274"/>
+      <c r="J7" s="274"/>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="23"/>
@@ -26347,15 +26330,15 @@
       <c r="C8" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D8" s="276"/>
+      <c r="D8" s="273"/>
       <c r="E8" s="1">
         <v>34</v>
       </c>
       <c r="F8" s="83"/>
-      <c r="G8" s="277"/>
-      <c r="H8" s="277"/>
-      <c r="I8" s="277"/>
-      <c r="J8" s="277"/>
+      <c r="G8" s="274"/>
+      <c r="H8" s="274"/>
+      <c r="I8" s="274"/>
+      <c r="J8" s="274"/>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="23"/>
@@ -26365,51 +26348,51 @@
       <c r="C9" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="D9" s="276"/>
+      <c r="D9" s="273"/>
       <c r="E9" s="1">
         <v>2</v>
       </c>
       <c r="F9" s="83"/>
-      <c r="G9" s="277"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="277"/>
+      <c r="G9" s="274"/>
+      <c r="H9" s="274"/>
+      <c r="I9" s="274"/>
+      <c r="J9" s="274"/>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="23"/>
       <c r="B10" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="C10" s="266" t="s">
+      <c r="C10" s="263" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="276"/>
+      <c r="D10" s="273"/>
       <c r="E10" s="1">
         <v>81</v>
       </c>
       <c r="F10" s="83"/>
-      <c r="G10" s="277"/>
-      <c r="H10" s="277"/>
-      <c r="I10" s="277"/>
-      <c r="J10" s="277"/>
+      <c r="G10" s="274"/>
+      <c r="H10" s="274"/>
+      <c r="I10" s="274"/>
+      <c r="J10" s="274"/>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="23"/>
       <c r="B11" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="263" t="s">
         <v>160</v>
       </c>
-      <c r="D11" s="276"/>
+      <c r="D11" s="273"/>
       <c r="E11" s="1">
         <v>8</v>
       </c>
       <c r="F11" s="87"/>
-      <c r="G11" s="277"/>
-      <c r="H11" s="277"/>
-      <c r="I11" s="277"/>
-      <c r="J11" s="277"/>
+      <c r="G11" s="274"/>
+      <c r="H11" s="274"/>
+      <c r="I11" s="274"/>
+      <c r="J11" s="274"/>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="47" t="s">
@@ -26418,72 +26401,72 @@
       <c r="B12" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="C12" s="266" t="s">
+      <c r="C12" s="263" t="s">
         <v>160</v>
       </c>
-      <c r="D12" s="276"/>
+      <c r="D12" s="273"/>
       <c r="E12" s="1">
         <v>78</v>
       </c>
       <c r="F12" s="91"/>
-      <c r="G12" s="277"/>
-      <c r="H12" s="277"/>
-      <c r="I12" s="277"/>
-      <c r="J12" s="277"/>
+      <c r="G12" s="274"/>
+      <c r="H12" s="274"/>
+      <c r="I12" s="274"/>
+      <c r="J12" s="274"/>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="23"/>
       <c r="B13" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="263" t="s">
         <v>160</v>
       </c>
-      <c r="D13" s="276"/>
+      <c r="D13" s="273"/>
       <c r="E13" s="1">
         <v>81</v>
       </c>
       <c r="F13" s="88"/>
-      <c r="G13" s="277"/>
-      <c r="H13" s="277"/>
-      <c r="I13" s="277"/>
-      <c r="J13" s="277"/>
+      <c r="G13" s="274"/>
+      <c r="H13" s="274"/>
+      <c r="I13" s="274"/>
+      <c r="J13" s="274"/>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="23"/>
       <c r="B14" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="C14" s="266" t="s">
+      <c r="C14" s="263" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="276"/>
+      <c r="D14" s="273"/>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="F14" s="87"/>
-      <c r="G14" s="277"/>
-      <c r="H14" s="277"/>
-      <c r="I14" s="277"/>
-      <c r="J14" s="277"/>
+      <c r="G14" s="274"/>
+      <c r="H14" s="274"/>
+      <c r="I14" s="274"/>
+      <c r="J14" s="274"/>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="23"/>
       <c r="B15" s="18" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="266" t="s">
+      <c r="C15" s="263" t="s">
         <v>160</v>
       </c>
-      <c r="D15" s="276"/>
+      <c r="D15" s="273"/>
       <c r="E15" s="1">
         <v>24</v>
       </c>
       <c r="F15" s="88"/>
-      <c r="G15" s="277"/>
-      <c r="H15" s="277"/>
-      <c r="I15" s="277"/>
-      <c r="J15" s="277"/>
+      <c r="G15" s="274"/>
+      <c r="H15" s="274"/>
+      <c r="I15" s="274"/>
+      <c r="J15" s="274"/>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="92" t="s">
@@ -26495,15 +26478,15 @@
       <c r="C16" s="86" t="s">
         <v>405</v>
       </c>
-      <c r="D16" s="276"/>
+      <c r="D16" s="273"/>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="84"/>
-      <c r="G16" s="277"/>
-      <c r="H16" s="277"/>
-      <c r="I16" s="277"/>
-      <c r="J16" s="277"/>
+      <c r="G16" s="274"/>
+      <c r="H16" s="274"/>
+      <c r="I16" s="274"/>
+      <c r="J16" s="274"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="23"/>
@@ -26513,12 +26496,12 @@
       <c r="C17" s="85" t="s">
         <v>407</v>
       </c>
-      <c r="D17" s="276"/>
+      <c r="D17" s="273"/>
       <c r="E17" s="1">
         <v>4</v>
       </c>
       <c r="F17" s="87"/>
-      <c r="G17" s="277"/>
+      <c r="G17" s="274"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="23"/>
@@ -26528,12 +26511,12 @@
       <c r="C18" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D18" s="276"/>
+      <c r="D18" s="273"/>
       <c r="E18" s="1">
         <v>4</v>
       </c>
       <c r="F18" s="87"/>
-      <c r="G18" s="277"/>
+      <c r="G18" s="274"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="57"/>
@@ -26543,18 +26526,18 @@
       <c r="C19" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="D19" s="279"/>
+      <c r="D19" s="276"/>
       <c r="E19" s="40">
         <v>4</v>
       </c>
       <c r="F19" s="89"/>
-      <c r="G19" s="277"/>
+      <c r="G19" s="274"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="B20" s="277"/>
-      <c r="C20" s="277"/>
-      <c r="E20" s="277"/>
-      <c r="G20" s="277"/>
+      <c r="B20" s="274"/>
+      <c r="C20" s="274"/>
+      <c r="E20" s="274"/>
+      <c r="G20" s="274"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -26604,10 +26587,10 @@
       <c r="B1" s="97" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="280" t="s">
+      <c r="C1" s="277" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="280" t="s">
+      <c r="D1" s="277" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="98"/>
@@ -26618,7 +26601,7 @@
       <c r="A2" s="99" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="266" t="s">
+      <c r="B2" s="263" t="s">
         <v>14</v>
       </c>
       <c r="C2" s="26"/>
@@ -26642,7 +26625,7 @@
       <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="281" t="s">
+      <c r="E3" s="278" t="s">
         <v>386</v>
       </c>
       <c r="G3"/>
@@ -26652,14 +26635,14 @@
       <c r="A4" s="101" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="266" t="s">
+      <c r="B4" s="263" t="s">
         <v>172</v>
       </c>
       <c r="C4" s="26"/>
       <c r="D4" s="13">
         <v>36</v>
       </c>
-      <c r="E4" s="281" t="s">
+      <c r="E4" s="278" t="s">
         <v>389</v>
       </c>
       <c r="G4"/>
@@ -26669,14 +26652,14 @@
       <c r="A5" s="101" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="266" t="s">
+      <c r="B5" s="263" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="26"/>
       <c r="D5" s="13">
         <v>24</v>
       </c>
-      <c r="E5" s="281" t="s">
+      <c r="E5" s="278" t="s">
         <v>393</v>
       </c>
       <c r="G5"/>
@@ -26684,7 +26667,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="102"/>
-      <c r="B6" s="266" t="s">
+      <c r="B6" s="263" t="s">
         <v>338</v>
       </c>
       <c r="C6" s="26"/>
@@ -26697,7 +26680,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="102"/>
-      <c r="B7" s="266" t="s">
+      <c r="B7" s="263" t="s">
         <v>340</v>
       </c>
       <c r="C7" s="26"/>
@@ -26710,7 +26693,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="102"/>
-      <c r="B8" s="266" t="s">
+      <c r="B8" s="263" t="s">
         <v>411</v>
       </c>
       <c r="C8" s="26"/>
@@ -26779,7 +26762,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="102"/>
-      <c r="B13" s="266" t="s">
+      <c r="B13" s="263" t="s">
         <v>416</v>
       </c>
       <c r="C13" s="26"/>
@@ -26794,7 +26777,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="102"/>
-      <c r="B14" s="266" t="s">
+      <c r="B14" s="263" t="s">
         <v>418</v>
       </c>
       <c r="C14" s="26"/>
@@ -26950,7 +26933,7 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="102"/>
-      <c r="B26" s="266" t="s">
+      <c r="B26" s="263" t="s">
         <v>422</v>
       </c>
       <c r="C26" s="95" t="s">
@@ -26965,7 +26948,7 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="102"/>
-      <c r="B27" s="266" t="s">
+      <c r="B27" s="263" t="s">
         <v>424</v>
       </c>
       <c r="C27" s="95" t="s">
@@ -26980,7 +26963,7 @@
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="102"/>
-      <c r="B28" s="266" t="s">
+      <c r="B28" s="263" t="s">
         <v>426</v>
       </c>
       <c r="C28" s="26"/>
@@ -27003,7 +26986,7 @@
         <v>1</v>
       </c>
       <c r="E29" s="103"/>
-      <c r="F29" s="266"/>
+      <c r="F29" s="263"/>
       <c r="G29"/>
       <c r="H29"/>
     </row>
@@ -27012,14 +26995,14 @@
       <c r="B30" s="36" t="s">
         <v>428</v>
       </c>
-      <c r="C30" s="266" t="s">
+      <c r="C30" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D30" s="13">
         <v>4</v>
       </c>
       <c r="E30" s="103"/>
-      <c r="F30" s="266"/>
+      <c r="F30" s="263"/>
       <c r="G30"/>
       <c r="H30"/>
     </row>
@@ -27028,15 +27011,15 @@
       <c r="B31" t="s">
         <v>429</v>
       </c>
-      <c r="C31" s="266" t="s">
+      <c r="C31" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D31" s="13">
         <v>2</v>
       </c>
       <c r="E31" s="103"/>
-      <c r="F31" s="266"/>
-      <c r="G31" s="266"/>
+      <c r="F31" s="263"/>
+      <c r="G31" s="263"/>
       <c r="H31"/>
     </row>
     <row r="32" spans="1:8">
@@ -27044,14 +27027,14 @@
       <c r="B32" t="s">
         <v>430</v>
       </c>
-      <c r="C32" s="266" t="s">
+      <c r="C32" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D32" s="13">
         <v>1</v>
       </c>
       <c r="E32" s="103"/>
-      <c r="F32" s="266"/>
+      <c r="F32" s="263"/>
       <c r="G32"/>
       <c r="H32"/>
     </row>
@@ -27060,14 +27043,14 @@
       <c r="B33" s="36" t="s">
         <v>431</v>
       </c>
-      <c r="C33" s="266" t="s">
+      <c r="C33" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D33" s="13">
         <v>1</v>
       </c>
       <c r="E33" s="103"/>
-      <c r="F33" s="266"/>
+      <c r="F33" s="263"/>
       <c r="G33"/>
       <c r="H33"/>
     </row>
@@ -27076,14 +27059,14 @@
       <c r="B34" t="s">
         <v>432</v>
       </c>
-      <c r="C34" s="266" t="s">
+      <c r="C34" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D34" s="13">
         <v>1</v>
       </c>
       <c r="E34" s="103"/>
-      <c r="F34" s="266"/>
+      <c r="F34" s="263"/>
       <c r="G34"/>
       <c r="H34"/>
     </row>
@@ -27092,14 +27075,14 @@
       <c r="B35" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="C35" s="266" t="s">
+      <c r="C35" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D35" s="13">
         <v>1</v>
       </c>
       <c r="E35" s="103"/>
-      <c r="F35" s="266"/>
+      <c r="F35" s="263"/>
       <c r="G35"/>
       <c r="H35"/>
     </row>
@@ -27108,14 +27091,14 @@
       <c r="B36" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="C36" s="266" t="s">
+      <c r="C36" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D36" s="13">
         <v>1</v>
       </c>
       <c r="E36" s="103"/>
-      <c r="F36" s="266"/>
+      <c r="F36" s="263"/>
       <c r="G36"/>
       <c r="H36"/>
     </row>
@@ -27124,14 +27107,14 @@
       <c r="B37" s="36" t="s">
         <v>435</v>
       </c>
-      <c r="C37" s="266" t="s">
+      <c r="C37" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D37" s="13">
         <v>2</v>
       </c>
       <c r="E37" s="103"/>
-      <c r="F37" s="266"/>
+      <c r="F37" s="263"/>
       <c r="G37"/>
       <c r="H37"/>
     </row>
@@ -27140,14 +27123,14 @@
       <c r="B38" s="36" t="s">
         <v>436</v>
       </c>
-      <c r="C38" s="266" t="s">
+      <c r="C38" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D38" s="13">
         <v>2</v>
       </c>
       <c r="E38" s="103"/>
-      <c r="F38" s="266"/>
+      <c r="F38" s="263"/>
       <c r="G38" s="1"/>
       <c r="H38"/>
     </row>
@@ -27156,14 +27139,14 @@
       <c r="B39" s="36" t="s">
         <v>437</v>
       </c>
-      <c r="C39" s="266" t="s">
+      <c r="C39" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D39" s="13">
         <v>1</v>
       </c>
       <c r="E39" s="103"/>
-      <c r="F39" s="266"/>
+      <c r="F39" s="263"/>
       <c r="G39"/>
       <c r="H39"/>
     </row>
@@ -27172,14 +27155,14 @@
       <c r="B40" s="36" t="s">
         <v>438</v>
       </c>
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D40" s="13">
         <v>1</v>
       </c>
       <c r="E40" s="103"/>
-      <c r="F40" s="266"/>
+      <c r="F40" s="263"/>
       <c r="G40"/>
       <c r="H40"/>
     </row>
@@ -27188,14 +27171,14 @@
       <c r="B41" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C41" s="266" t="s">
+      <c r="C41" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D41" s="13">
         <v>1</v>
       </c>
       <c r="E41" s="103"/>
-      <c r="F41" s="266"/>
+      <c r="F41" s="263"/>
       <c r="G41"/>
       <c r="H41"/>
     </row>
@@ -27204,14 +27187,14 @@
       <c r="B42" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="C42" s="266" t="s">
+      <c r="C42" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D42" s="13">
         <v>1</v>
       </c>
       <c r="E42" s="103"/>
-      <c r="F42" s="266"/>
+      <c r="F42" s="263"/>
       <c r="G42"/>
       <c r="H42"/>
     </row>
@@ -27220,14 +27203,14 @@
       <c r="B43" s="36" t="s">
         <v>441</v>
       </c>
-      <c r="C43" s="266" t="s">
+      <c r="C43" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D43" s="13">
         <v>1</v>
       </c>
       <c r="E43" s="103"/>
-      <c r="F43" s="266"/>
+      <c r="F43" s="263"/>
       <c r="G43"/>
       <c r="H43"/>
     </row>
@@ -27236,19 +27219,19 @@
       <c r="B44" s="36" t="s">
         <v>442</v>
       </c>
-      <c r="C44" s="282" t="s">
+      <c r="C44" s="279" t="s">
         <v>405</v>
       </c>
       <c r="D44" s="106">
         <v>1</v>
       </c>
       <c r="E44" s="107"/>
-      <c r="F44" s="266"/>
+      <c r="F44" s="263"/>
       <c r="G44"/>
       <c r="H44"/>
     </row>
     <row r="45" spans="1:8">
-      <c r="F45" s="266"/>
+      <c r="F45" s="263"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -27299,10 +27282,10 @@
       <c r="B1" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="261" t="s">
+      <c r="C1" s="258" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="261" t="s">
+      <c r="D1" s="258" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -27311,7 +27294,7 @@
       <c r="A2" s="50" t="s">
         <v>380</v>
       </c>
-      <c r="B2" s="266" t="s">
+      <c r="B2" s="263" t="s">
         <v>443</v>
       </c>
       <c r="C2"/>
@@ -27326,14 +27309,14 @@
       <c r="A3" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="263" t="s">
+      <c r="B3" s="260" t="s">
         <v>352</v>
       </c>
-      <c r="C3" s="263"/>
+      <c r="C3" s="260"/>
       <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="283" t="s">
+      <c r="E3" s="280" t="s">
         <v>386</v>
       </c>
     </row>
@@ -27341,14 +27324,14 @@
       <c r="A4" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="263" t="s">
+      <c r="B4" s="260" t="s">
         <v>444</v>
       </c>
-      <c r="C4" s="263"/>
+      <c r="C4" s="260"/>
       <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="283" t="s">
+      <c r="E4" s="280" t="s">
         <v>389</v>
       </c>
     </row>
@@ -27363,7 +27346,7 @@
       <c r="D5" s="13">
         <v>1</v>
       </c>
-      <c r="E5" s="283" t="s">
+      <c r="E5" s="280" t="s">
         <v>393</v>
       </c>
     </row>
@@ -27506,7 +27489,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="23"/>
-      <c r="B18" s="284" t="s">
+      <c r="B18" s="281" t="s">
         <v>456</v>
       </c>
       <c r="C18" s="64" t="s">
@@ -27530,10 +27513,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23"/>
-      <c r="B20" s="285" t="s">
+      <c r="B20" s="282" t="s">
         <v>459</v>
       </c>
-      <c r="C20" s="285"/>
+      <c r="C20" s="282"/>
       <c r="D20" s="13">
         <v>1</v>
       </c>
@@ -27552,10 +27535,10 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="23"/>
-      <c r="B22" s="285" t="s">
+      <c r="B22" s="282" t="s">
         <v>461</v>
       </c>
-      <c r="C22" s="285"/>
+      <c r="C22" s="282"/>
       <c r="D22" s="13">
         <v>1</v>
       </c>
@@ -27609,7 +27592,7 @@
       <c r="A27" s="23"/>
       <c r="B27" s="60"/>
       <c r="C27" s="60"/>
-      <c r="D27" s="277"/>
+      <c r="D27" s="274"/>
       <c r="E27" s="52"/>
     </row>
     <row r="28" spans="1:5" ht="18.75">
@@ -27626,10 +27609,10 @@
       <c r="B29" s="21" t="s">
         <v>377</v>
       </c>
-      <c r="C29" s="286" t="s">
+      <c r="C29" s="283" t="s">
         <v>378</v>
       </c>
-      <c r="D29" s="287" t="s">
+      <c r="D29" s="284" t="s">
         <v>379</v>
       </c>
       <c r="E29" s="52"/>
@@ -27705,7 +27688,7 @@
       <c r="B36" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="C36" s="285"/>
+      <c r="C36" s="282"/>
       <c r="D36" s="43">
         <v>1</v>
       </c>
@@ -27790,10 +27773,10 @@
       <c r="B1" s="97" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="280" t="s">
+      <c r="C1" s="277" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="280" t="s">
+      <c r="D1" s="277" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="98"/>
@@ -27816,14 +27799,14 @@
       <c r="A3" s="101" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="266" t="s">
+      <c r="B3" s="263" t="s">
         <v>471</v>
       </c>
-      <c r="C3" s="266"/>
+      <c r="C3" s="263"/>
       <c r="D3" s="13">
         <v>12</v>
       </c>
-      <c r="E3" s="281" t="s">
+      <c r="E3" s="278" t="s">
         <v>386</v>
       </c>
     </row>
@@ -27831,14 +27814,14 @@
       <c r="A4" s="101" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="266" t="s">
+      <c r="B4" s="263" t="s">
         <v>330</v>
       </c>
-      <c r="C4" s="266"/>
+      <c r="C4" s="263"/>
       <c r="D4" s="13">
         <v>3</v>
       </c>
-      <c r="E4" s="281" t="s">
+      <c r="E4" s="278" t="s">
         <v>389</v>
       </c>
     </row>
@@ -27846,14 +27829,14 @@
       <c r="A5" s="101" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="266" t="s">
+      <c r="B5" s="263" t="s">
         <v>336</v>
       </c>
-      <c r="C5" s="266"/>
+      <c r="C5" s="263"/>
       <c r="D5" s="13">
         <v>6</v>
       </c>
-      <c r="E5" s="281" t="s">
+      <c r="E5" s="278" t="s">
         <v>393</v>
       </c>
     </row>
@@ -27862,10 +27845,10 @@
       <c r="B6" s="41" t="s">
         <v>322</v>
       </c>
-      <c r="C6" s="266" t="s">
+      <c r="C6" s="263" t="s">
         <v>323</v>
       </c>
-      <c r="D6" s="272">
+      <c r="D6" s="269">
         <v>1</v>
       </c>
       <c r="E6" s="103"/>
@@ -27875,20 +27858,20 @@
       <c r="B7" s="11" t="s">
         <v>472</v>
       </c>
-      <c r="C7" s="266" t="s">
+      <c r="C7" s="263" t="s">
         <v>473</v>
       </c>
-      <c r="D7" s="272">
+      <c r="D7" s="269">
         <v>28</v>
       </c>
       <c r="E7" s="103"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="102"/>
-      <c r="B8" s="266" t="s">
+      <c r="B8" s="263" t="s">
         <v>474</v>
       </c>
-      <c r="C8" s="266"/>
+      <c r="C8" s="263"/>
       <c r="D8" s="13">
         <v>1</v>
       </c>
@@ -27906,22 +27889,22 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="102"/>
-      <c r="B10" s="266" t="s">
+      <c r="B10" s="263" t="s">
         <v>254</v>
       </c>
-      <c r="C10" s="266"/>
-      <c r="D10" s="272">
+      <c r="C10" s="263"/>
+      <c r="D10" s="269">
         <v>6</v>
       </c>
       <c r="E10" s="103"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="102"/>
-      <c r="B11" s="266" t="s">
+      <c r="B11" s="263" t="s">
         <v>476</v>
       </c>
-      <c r="C11" s="266"/>
-      <c r="D11" s="272">
+      <c r="C11" s="263"/>
+      <c r="D11" s="269">
         <v>3</v>
       </c>
       <c r="E11" s="103"/>
@@ -27930,10 +27913,10 @@
       <c r="A12" s="101" t="s">
         <v>401</v>
       </c>
-      <c r="B12" s="262" t="s">
+      <c r="B12" s="259" t="s">
         <v>477</v>
       </c>
-      <c r="C12" s="266"/>
+      <c r="C12" s="263"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -27941,10 +27924,10 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="102"/>
-      <c r="B13" s="266" t="s">
+      <c r="B13" s="263" t="s">
         <v>415</v>
       </c>
-      <c r="C13" s="266"/>
+      <c r="C13" s="263"/>
       <c r="D13" s="13">
         <v>42</v>
       </c>
@@ -28062,10 +28045,10 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="102"/>
-      <c r="B25" s="266" t="s">
+      <c r="B25" s="263" t="s">
         <v>402</v>
       </c>
-      <c r="C25" s="266"/>
+      <c r="C25" s="263"/>
       <c r="D25" s="13">
         <v>6</v>
       </c>
@@ -28073,10 +28056,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="102"/>
-      <c r="B26" s="266" t="s">
+      <c r="B26" s="263" t="s">
         <v>229</v>
       </c>
-      <c r="C26" s="266"/>
+      <c r="C26" s="263"/>
       <c r="D26" s="13">
         <v>21</v>
       </c>
@@ -28202,7 +28185,7 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="102"/>
-      <c r="B37" s="266" t="s">
+      <c r="B37" s="263" t="s">
         <v>493</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -28367,10 +28350,10 @@
       <c r="B1" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="261" t="s">
+      <c r="C1" s="258" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="261" t="s">
+      <c r="D1" s="258" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -28382,7 +28365,7 @@
       <c r="B2" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="C2" s="266"/>
+      <c r="C2" s="263"/>
       <c r="D2" s="13">
         <v>14</v>
       </c>
@@ -28397,11 +28380,11 @@
       <c r="B3" t="s">
         <v>503</v>
       </c>
-      <c r="C3" s="266"/>
+      <c r="C3" s="263"/>
       <c r="D3" s="13">
         <v>13</v>
       </c>
-      <c r="E3" s="283" t="s">
+      <c r="E3" s="280" t="s">
         <v>386</v>
       </c>
     </row>
@@ -28409,14 +28392,14 @@
       <c r="A4" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="266" t="s">
+      <c r="B4" s="263" t="s">
         <v>174</v>
       </c>
-      <c r="C4" s="266"/>
+      <c r="C4" s="263"/>
       <c r="D4" s="13">
         <v>2</v>
       </c>
-      <c r="E4" s="283" t="s">
+      <c r="E4" s="280" t="s">
         <v>389</v>
       </c>
     </row>
@@ -28427,20 +28410,20 @@
       <c r="B5" t="s">
         <v>504</v>
       </c>
-      <c r="C5" s="266"/>
+      <c r="C5" s="263"/>
       <c r="D5" s="13">
         <v>2</v>
       </c>
-      <c r="E5" s="283" t="s">
+      <c r="E5" s="280" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23"/>
-      <c r="B6" s="266" t="s">
+      <c r="B6" s="263" t="s">
         <v>505</v>
       </c>
-      <c r="C6" s="266"/>
+      <c r="C6" s="263"/>
       <c r="D6" s="13">
         <v>1</v>
       </c>
@@ -28448,10 +28431,10 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23"/>
-      <c r="B7" s="266" t="s">
+      <c r="B7" s="263" t="s">
         <v>506</v>
       </c>
-      <c r="C7" s="266"/>
+      <c r="C7" s="263"/>
       <c r="D7" s="13">
         <v>4</v>
       </c>
@@ -28462,7 +28445,7 @@
       <c r="B8" s="1" t="s">
         <v>507</v>
       </c>
-      <c r="C8" s="266"/>
+      <c r="C8" s="263"/>
       <c r="D8" s="13">
         <v>6</v>
       </c>
@@ -28473,7 +28456,7 @@
       <c r="B9" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C9" s="266"/>
+      <c r="C9" s="263"/>
       <c r="D9" s="13">
         <v>6</v>
       </c>
@@ -28484,7 +28467,7 @@
       <c r="B10" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="C10" s="267" t="s">
+      <c r="C10" s="264" t="s">
         <v>509</v>
       </c>
       <c r="D10" s="13">
@@ -28497,7 +28480,7 @@
       <c r="B11" s="11" t="s">
         <v>510</v>
       </c>
-      <c r="C11" s="266"/>
+      <c r="C11" s="263"/>
       <c r="D11" s="13">
         <v>1</v>
       </c>
@@ -28505,10 +28488,10 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="23"/>
-      <c r="B12" s="266" t="s">
+      <c r="B12" s="263" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="266"/>
+      <c r="C12" s="263"/>
       <c r="D12" s="13">
         <v>1</v>
       </c>
@@ -28518,10 +28501,10 @@
       <c r="A13" s="47" t="s">
         <v>401</v>
       </c>
-      <c r="B13" s="266" t="s">
+      <c r="B13" s="263" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="266"/>
+      <c r="C13" s="263"/>
       <c r="D13" s="13">
         <v>1</v>
       </c>
@@ -28554,7 +28537,7 @@
       <c r="B16" t="s">
         <v>512</v>
       </c>
-      <c r="C16" s="266"/>
+      <c r="C16" s="263"/>
       <c r="D16" s="13">
         <v>4</v>
       </c>
@@ -28565,7 +28548,7 @@
       <c r="B17" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="C17" s="266"/>
+      <c r="C17" s="263"/>
       <c r="D17" s="13">
         <v>19</v>
       </c>
@@ -28576,7 +28559,7 @@
       <c r="B18" s="61" t="s">
         <v>193</v>
       </c>
-      <c r="C18" s="266"/>
+      <c r="C18" s="263"/>
       <c r="D18" s="13">
         <v>6</v>
       </c>
@@ -28587,7 +28570,7 @@
       <c r="B19" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="C19" s="266"/>
+      <c r="C19" s="263"/>
       <c r="D19" s="13">
         <v>13</v>
       </c>
@@ -28595,10 +28578,10 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23"/>
-      <c r="B20" s="266" t="s">
+      <c r="B20" s="263" t="s">
         <v>513</v>
       </c>
-      <c r="C20" s="266"/>
+      <c r="C20" s="263"/>
       <c r="D20" s="13">
         <v>4</v>
       </c>
@@ -28606,10 +28589,10 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="23"/>
-      <c r="B21" s="266" t="s">
+      <c r="B21" s="263" t="s">
         <v>514</v>
       </c>
-      <c r="C21" s="266"/>
+      <c r="C21" s="263"/>
       <c r="D21" s="13">
         <v>6</v>
       </c>
@@ -28620,7 +28603,7 @@
       <c r="B22" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="266"/>
+      <c r="C22" s="263"/>
       <c r="D22" s="13">
         <v>4</v>
       </c>
@@ -28631,7 +28614,7 @@
       <c r="B23" t="s">
         <v>515</v>
       </c>
-      <c r="C23" s="266"/>
+      <c r="C23" s="263"/>
       <c r="D23" s="13">
         <v>6</v>
       </c>
@@ -28642,7 +28625,7 @@
       <c r="B24" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="C24" s="266"/>
+      <c r="C24" s="263"/>
       <c r="D24" s="13">
         <v>4</v>
       </c>
@@ -28653,7 +28636,7 @@
       <c r="B25" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="266"/>
+      <c r="C25" s="263"/>
       <c r="D25" s="13">
         <v>4</v>
       </c>
@@ -28661,10 +28644,10 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="23"/>
-      <c r="B26" s="266" t="s">
+      <c r="B26" s="263" t="s">
         <v>516</v>
       </c>
-      <c r="C26" s="266"/>
+      <c r="C26" s="263"/>
       <c r="D26" s="13">
         <v>1</v>
       </c>
@@ -28672,10 +28655,10 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="23"/>
-      <c r="B27" s="266" t="s">
+      <c r="B27" s="263" t="s">
         <v>223</v>
       </c>
-      <c r="C27" s="266"/>
+      <c r="C27" s="263"/>
       <c r="D27" s="13">
         <v>16</v>
       </c>
@@ -28686,7 +28669,7 @@
       <c r="B28" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C28" s="266"/>
+      <c r="C28" s="263"/>
       <c r="D28" s="13">
         <v>52</v>
       </c>
@@ -28697,7 +28680,7 @@
       <c r="B29" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C29" s="266"/>
+      <c r="C29" s="263"/>
       <c r="D29" s="13">
         <v>77</v>
       </c>
@@ -28708,7 +28691,7 @@
       <c r="B30" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C30" s="266"/>
+      <c r="C30" s="263"/>
       <c r="D30" s="13">
         <v>16</v>
       </c>
@@ -28716,10 +28699,10 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="23"/>
-      <c r="B31" s="266" t="s">
+      <c r="B31" s="263" t="s">
         <v>517</v>
       </c>
-      <c r="C31" s="266"/>
+      <c r="C31" s="263"/>
       <c r="D31" s="13">
         <v>44</v>
       </c>
@@ -28727,10 +28710,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="23"/>
-      <c r="B32" s="266" t="s">
+      <c r="B32" s="263" t="s">
         <v>518</v>
       </c>
-      <c r="C32" s="266"/>
+      <c r="C32" s="263"/>
       <c r="D32" s="13">
         <v>17</v>
       </c>
@@ -28751,10 +28734,10 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="23"/>
-      <c r="B34" s="266" t="s">
+      <c r="B34" s="263" t="s">
         <v>521</v>
       </c>
-      <c r="C34" s="266" t="s">
+      <c r="C34" s="263" t="s">
         <v>522</v>
       </c>
       <c r="D34" s="13">
@@ -28764,7 +28747,7 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="23"/>
-      <c r="B35" s="266" t="s">
+      <c r="B35" s="263" t="s">
         <v>523</v>
       </c>
       <c r="C35" s="2" t="s">
@@ -28803,10 +28786,10 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="23"/>
-      <c r="B38" s="284" t="s">
+      <c r="B38" s="281" t="s">
         <v>526</v>
       </c>
-      <c r="C38" s="284" t="s">
+      <c r="C38" s="281" t="s">
         <v>527</v>
       </c>
       <c r="D38" s="53">
@@ -28829,7 +28812,7 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="23"/>
-      <c r="B40" s="266" t="s">
+      <c r="B40" s="263" t="s">
         <v>529</v>
       </c>
       <c r="C40" s="2" t="s">
@@ -28933,7 +28916,7 @@
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="23"/>
-      <c r="B48" s="266" t="s">
+      <c r="B48" s="263" t="s">
         <v>537</v>
       </c>
       <c r="C48" s="2" t="s">
@@ -28946,7 +28929,7 @@
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="23"/>
-      <c r="B49" s="266" t="s">
+      <c r="B49" s="263" t="s">
         <v>538</v>
       </c>
       <c r="C49" s="2" t="s">
@@ -28959,7 +28942,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="23"/>
-      <c r="B50" s="266" t="s">
+      <c r="B50" s="263" t="s">
         <v>539</v>
       </c>
       <c r="C50" s="2" t="s">
@@ -28972,7 +28955,7 @@
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="23"/>
-      <c r="B51" s="266" t="s">
+      <c r="B51" s="263" t="s">
         <v>540</v>
       </c>
       <c r="C51" s="2" t="s">
@@ -29206,7 +29189,7 @@
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="23"/>
-      <c r="B69" s="266" t="s">
+      <c r="B69" s="263" t="s">
         <v>560</v>
       </c>
       <c r="C69" s="2" t="s">
@@ -29235,7 +29218,7 @@
       <c r="B71" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="C71" s="266" t="s">
+      <c r="C71" s="263" t="s">
         <v>520</v>
       </c>
       <c r="D71" s="13">
@@ -29248,7 +29231,7 @@
       <c r="B72" t="s">
         <v>563</v>
       </c>
-      <c r="C72" s="266" t="s">
+      <c r="C72" s="263" t="s">
         <v>520</v>
       </c>
       <c r="D72" s="13">
@@ -29327,10 +29310,10 @@
       <c r="B1" s="8" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="286" t="s">
+      <c r="C1" s="283" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="286" t="s">
+      <c r="D1" s="283" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -29342,10 +29325,10 @@
       <c r="B2" s="11" t="s">
         <v>566</v>
       </c>
-      <c r="C2" s="286" t="s">
+      <c r="C2" s="283" t="s">
         <v>567</v>
       </c>
-      <c r="D2" s="288" t="s">
+      <c r="D2" s="285" t="s">
         <v>568</v>
       </c>
       <c r="E2" s="51" t="s">
@@ -29356,16 +29339,16 @@
       <c r="A3" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="266" t="s">
+      <c r="B3" s="263" t="s">
         <v>166</v>
       </c>
-      <c r="C3" s="266" t="s">
+      <c r="C3" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D3" s="266">
-        <v>1</v>
-      </c>
-      <c r="E3" s="283" t="s">
+      <c r="D3" s="263">
+        <v>1</v>
+      </c>
+      <c r="E3" s="280" t="s">
         <v>386</v>
       </c>
     </row>
@@ -29376,13 +29359,13 @@
       <c r="B4" t="s">
         <v>503</v>
       </c>
-      <c r="C4" s="266" t="s">
+      <c r="C4" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D4" s="266">
+      <c r="D4" s="263">
         <v>4</v>
       </c>
-      <c r="E4" s="283" t="s">
+      <c r="E4" s="280" t="s">
         <v>389</v>
       </c>
     </row>
@@ -29390,16 +29373,16 @@
       <c r="A5" s="47" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="266" t="s">
+      <c r="B5" s="263" t="s">
         <v>330</v>
       </c>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D5" s="266">
+      <c r="D5" s="263">
         <v>3</v>
       </c>
-      <c r="E5" s="283" t="s">
+      <c r="E5" s="280" t="s">
         <v>393</v>
       </c>
     </row>
@@ -29408,20 +29391,20 @@
       <c r="B6" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="C6" s="266" t="s">
+      <c r="C6" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D6" s="266">
+      <c r="D6" s="263">
         <v>1</v>
       </c>
       <c r="E6" s="52"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23"/>
-      <c r="B7" s="266" t="s">
+      <c r="B7" s="263" t="s">
         <v>570</v>
       </c>
-      <c r="C7" s="266" t="s">
+      <c r="C7" s="263" t="s">
         <v>567</v>
       </c>
       <c r="D7" s="2">
@@ -29431,26 +29414,26 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="23"/>
-      <c r="B8" s="266" t="s">
+      <c r="B8" s="263" t="s">
         <v>571</v>
       </c>
-      <c r="C8" s="266" t="s">
+      <c r="C8" s="263" t="s">
         <v>572</v>
       </c>
-      <c r="D8" s="266">
+      <c r="D8" s="263">
         <v>1</v>
       </c>
       <c r="E8" s="52"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="23"/>
-      <c r="B9" s="270" t="s">
+      <c r="B9" s="267" t="s">
         <v>60</v>
       </c>
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="263" t="s">
         <v>572</v>
       </c>
-      <c r="D9" s="266">
+      <c r="D9" s="263">
         <v>1</v>
       </c>
       <c r="E9" s="52"/>
@@ -29460,10 +29443,10 @@
       <c r="B10" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="266" t="s">
+      <c r="C10" s="263" t="s">
         <v>572</v>
       </c>
-      <c r="D10" s="266">
+      <c r="D10" s="263">
         <v>1</v>
       </c>
       <c r="E10" s="52"/>
@@ -29473,10 +29456,10 @@
       <c r="B11" s="26" t="s">
         <v>573</v>
       </c>
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="263" t="s">
         <v>572</v>
       </c>
-      <c r="D11" s="266">
+      <c r="D11" s="263">
         <v>1</v>
       </c>
       <c r="E11" s="52"/>
@@ -29488,23 +29471,23 @@
       <c r="B12" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="C12" s="266" t="s">
+      <c r="C12" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D12" s="266">
+      <c r="D12" s="263">
         <v>10</v>
       </c>
       <c r="E12" s="52"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="23"/>
-      <c r="B13" s="266" t="s">
+      <c r="B13" s="263" t="s">
         <v>191</v>
       </c>
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D13" s="266">
+      <c r="D13" s="263">
         <v>1</v>
       </c>
       <c r="E13" s="52"/>
@@ -29514,10 +29497,10 @@
       <c r="B14" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="C14" s="266" t="s">
+      <c r="C14" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D14" s="266">
+      <c r="D14" s="263">
         <v>2</v>
       </c>
       <c r="E14" s="52"/>
@@ -29527,10 +29510,10 @@
       <c r="B15" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="C15" s="266" t="s">
+      <c r="C15" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D15" s="266">
+      <c r="D15" s="263">
         <v>7</v>
       </c>
       <c r="E15" s="52"/>
@@ -29540,20 +29523,20 @@
       <c r="B16" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C16" s="266" t="s">
+      <c r="C16" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D16" s="266">
+      <c r="D16" s="263">
         <v>3</v>
       </c>
       <c r="E16" s="52"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="23"/>
-      <c r="B17" s="266" t="s">
+      <c r="B17" s="263" t="s">
         <v>576</v>
       </c>
-      <c r="C17" s="266" t="s">
+      <c r="C17" s="263" t="s">
         <v>567</v>
       </c>
       <c r="D17" s="2">
@@ -29563,13 +29546,13 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="23"/>
-      <c r="B18" s="266" t="s">
+      <c r="B18" s="263" t="s">
         <v>221</v>
       </c>
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D18" s="266">
+      <c r="D18" s="263">
         <v>1</v>
       </c>
       <c r="E18" s="52"/>
@@ -29579,10 +29562,10 @@
       <c r="B19" t="s">
         <v>577</v>
       </c>
-      <c r="C19" s="266" t="s">
+      <c r="C19" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D19" s="266">
+      <c r="D19" s="263">
         <v>2</v>
       </c>
       <c r="E19" s="52"/>
@@ -29592,20 +29575,20 @@
       <c r="B20" t="s">
         <v>578</v>
       </c>
-      <c r="C20" s="266" t="s">
+      <c r="C20" s="263" t="s">
         <v>567</v>
       </c>
-      <c r="D20" s="266">
+      <c r="D20" s="263">
         <v>2</v>
       </c>
       <c r="E20" s="52"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="23"/>
-      <c r="B21" s="266" t="s">
+      <c r="B21" s="263" t="s">
         <v>579</v>
       </c>
-      <c r="C21" s="266" t="s">
+      <c r="C21" s="263" t="s">
         <v>572</v>
       </c>
       <c r="D21" s="2">
@@ -29621,7 +29604,7 @@
       <c r="B22" t="s">
         <v>581</v>
       </c>
-      <c r="C22" s="266" t="s">
+      <c r="C22" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D22" s="2">
@@ -29634,7 +29617,7 @@
       <c r="B23" t="s">
         <v>582</v>
       </c>
-      <c r="C23" s="266" t="s">
+      <c r="C23" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D23" s="2">
@@ -29647,7 +29630,7 @@
       <c r="B24" t="s">
         <v>583</v>
       </c>
-      <c r="C24" s="266" t="s">
+      <c r="C24" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D24" s="2">
@@ -29660,10 +29643,10 @@
       <c r="B25" t="s">
         <v>584</v>
       </c>
-      <c r="C25" s="266" t="s">
+      <c r="C25" s="263" t="s">
         <v>405</v>
       </c>
-      <c r="D25" s="266">
+      <c r="D25" s="263">
         <v>1</v>
       </c>
       <c r="E25" s="52"/>
@@ -29673,7 +29656,7 @@
       <c r="B26" t="s">
         <v>585</v>
       </c>
-      <c r="C26" s="266" t="s">
+      <c r="C26" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D26" s="1">
@@ -29686,7 +29669,7 @@
       <c r="B27" t="s">
         <v>586</v>
       </c>
-      <c r="C27" s="266" t="s">
+      <c r="C27" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D27" s="1">
@@ -29699,20 +29682,20 @@
       <c r="B28" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="C28" s="266" t="s">
+      <c r="C28" s="263" t="s">
         <v>405</v>
       </c>
-      <c r="D28" s="266">
+      <c r="D28" s="263">
         <v>2</v>
       </c>
       <c r="E28" s="52"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="23"/>
-      <c r="B29" s="266" t="s">
+      <c r="B29" s="263" t="s">
         <v>588</v>
       </c>
-      <c r="C29" s="266" t="s">
+      <c r="C29" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D29" s="2">
@@ -29722,10 +29705,10 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="23"/>
-      <c r="B30" s="266" t="s">
+      <c r="B30" s="263" t="s">
         <v>589</v>
       </c>
-      <c r="C30" s="266" t="s">
+      <c r="C30" s="263" t="s">
         <v>551</v>
       </c>
       <c r="D30" s="2">
@@ -29738,10 +29721,10 @@
       <c r="B31" t="s">
         <v>590</v>
       </c>
-      <c r="C31" s="266" t="s">
+      <c r="C31" s="263" t="s">
         <v>405</v>
       </c>
-      <c r="D31" s="266">
+      <c r="D31" s="263">
         <v>1</v>
       </c>
       <c r="E31" s="52"/>
@@ -29751,10 +29734,10 @@
       <c r="B32" s="1" t="s">
         <v>591</v>
       </c>
-      <c r="C32" s="266" t="s">
+      <c r="C32" s="263" t="s">
         <v>592</v>
       </c>
-      <c r="D32" s="266">
+      <c r="D32" s="263">
         <v>2</v>
       </c>
       <c r="E32" s="52"/>
@@ -29764,10 +29747,10 @@
       <c r="B33" t="s">
         <v>593</v>
       </c>
-      <c r="C33" s="266" t="s">
+      <c r="C33" s="263" t="s">
         <v>594</v>
       </c>
-      <c r="D33" s="266">
+      <c r="D33" s="263">
         <v>2</v>
       </c>
       <c r="E33" s="52"/>
@@ -29777,10 +29760,10 @@
       <c r="B34" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="C34" s="266" t="s">
+      <c r="C34" s="263" t="s">
         <v>596</v>
       </c>
-      <c r="D34" s="266">
+      <c r="D34" s="263">
         <v>2</v>
       </c>
       <c r="E34" s="52"/>
@@ -29790,36 +29773,36 @@
       <c r="B35" s="1" t="s">
         <v>597</v>
       </c>
-      <c r="C35" s="266" t="s">
+      <c r="C35" s="263" t="s">
         <v>592</v>
       </c>
-      <c r="D35" s="266">
+      <c r="D35" s="263">
         <v>2</v>
       </c>
       <c r="E35" s="52"/>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="23"/>
-      <c r="B36" s="266" t="s">
+      <c r="B36" s="263" t="s">
         <v>598</v>
       </c>
-      <c r="C36" s="266" t="s">
+      <c r="C36" s="263" t="s">
         <v>599</v>
       </c>
-      <c r="D36" s="266">
+      <c r="D36" s="263">
         <v>2</v>
       </c>
       <c r="E36" s="52"/>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="23"/>
-      <c r="B37" s="266" t="s">
+      <c r="B37" s="263" t="s">
         <v>600</v>
       </c>
-      <c r="C37" s="266" t="s">
+      <c r="C37" s="263" t="s">
         <v>596</v>
       </c>
-      <c r="D37" s="266">
+      <c r="D37" s="263">
         <v>2</v>
       </c>
       <c r="E37" s="52"/>
@@ -29829,20 +29812,20 @@
       <c r="B38" s="1" t="s">
         <v>601</v>
       </c>
-      <c r="C38" s="266" t="s">
+      <c r="C38" s="263" t="s">
         <v>405</v>
       </c>
-      <c r="D38" s="266">
+      <c r="D38" s="263">
         <v>1</v>
       </c>
       <c r="E38" s="52"/>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="23"/>
-      <c r="B39" s="266" t="s">
+      <c r="B39" s="263" t="s">
         <v>602</v>
       </c>
-      <c r="C39" s="266" t="s">
+      <c r="C39" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D39" s="2">
@@ -29852,10 +29835,10 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="23"/>
-      <c r="B40" s="266" t="s">
+      <c r="B40" s="263" t="s">
         <v>603</v>
       </c>
-      <c r="C40" s="266" t="s">
+      <c r="C40" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D40" s="2">
@@ -29865,10 +29848,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="23"/>
-      <c r="B41" s="266" t="s">
+      <c r="B41" s="263" t="s">
         <v>604</v>
       </c>
-      <c r="C41" s="266" t="s">
+      <c r="C41" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D41" s="2">
@@ -29878,10 +29861,10 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="23"/>
-      <c r="B42" s="266" t="s">
+      <c r="B42" s="263" t="s">
         <v>605</v>
       </c>
-      <c r="C42" s="266" t="s">
+      <c r="C42" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D42" s="2">
@@ -29891,23 +29874,23 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="23"/>
-      <c r="B43" s="266" t="s">
+      <c r="B43" s="263" t="s">
         <v>606</v>
       </c>
-      <c r="C43" s="266" t="s">
+      <c r="C43" s="263" t="s">
         <v>405</v>
       </c>
-      <c r="D43" s="266">
+      <c r="D43" s="263">
         <v>1</v>
       </c>
       <c r="E43" s="52"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" thickBot="1">
       <c r="A44" s="57"/>
-      <c r="B44" s="266" t="s">
+      <c r="B44" s="263" t="s">
         <v>607</v>
       </c>
-      <c r="C44" s="266" t="s">
+      <c r="C44" s="263" t="s">
         <v>405</v>
       </c>
       <c r="D44" s="2">
@@ -29916,7 +29899,7 @@
       <c r="E44" s="59"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="C45" s="277"/>
+      <c r="C45" s="274"/>
     </row>
     <row r="46" spans="1:5" ht="30">
       <c r="B46" s="128" t="s">
@@ -29968,10 +29951,10 @@
       <c r="B1" s="62" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="261" t="s">
+      <c r="C1" s="258" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="261" t="s">
+      <c r="D1" s="258" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -29983,8 +29966,8 @@
       <c r="B2" s="11" t="s">
         <v>609</v>
       </c>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266">
+      <c r="C2" s="263"/>
+      <c r="D2" s="263">
         <v>6</v>
       </c>
       <c r="E2" s="51" t="s">
@@ -29995,13 +29978,13 @@
       <c r="A3" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="B3" s="265" t="s">
+      <c r="B3" s="262" t="s">
         <v>281</v>
       </c>
-      <c r="D3" s="266">
-        <v>1</v>
-      </c>
-      <c r="E3" s="283" t="s">
+      <c r="D3" s="263">
+        <v>1</v>
+      </c>
+      <c r="E3" s="280" t="s">
         <v>386</v>
       </c>
     </row>
@@ -30009,14 +29992,14 @@
       <c r="A4" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="B4" s="266" t="s">
+      <c r="B4" s="263" t="s">
         <v>610</v>
       </c>
-      <c r="C4" s="266"/>
-      <c r="D4" s="266">
-        <v>1</v>
-      </c>
-      <c r="E4" s="283" t="s">
+      <c r="C4" s="263"/>
+      <c r="D4" s="263">
+        <v>1</v>
+      </c>
+      <c r="E4" s="280" t="s">
         <v>389</v>
       </c>
     </row>
@@ -30024,34 +30007,34 @@
       <c r="A5" s="47" t="s">
         <v>390</v>
       </c>
-      <c r="B5" s="265" t="s">
+      <c r="B5" s="262" t="s">
         <v>290</v>
       </c>
-      <c r="C5" s="266"/>
-      <c r="D5" s="266">
-        <v>1</v>
-      </c>
-      <c r="E5" s="283" t="s">
+      <c r="C5" s="263"/>
+      <c r="D5" s="263">
+        <v>1</v>
+      </c>
+      <c r="E5" s="280" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23"/>
-      <c r="B6" s="265" t="s">
+      <c r="B6" s="262" t="s">
         <v>611</v>
       </c>
-      <c r="D6" s="266">
+      <c r="D6" s="263">
         <v>1</v>
       </c>
       <c r="E6" s="52"/>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="23"/>
-      <c r="B7" s="266" t="s">
+      <c r="B7" s="263" t="s">
         <v>612</v>
       </c>
-      <c r="C7" s="266"/>
-      <c r="D7" s="266">
+      <c r="C7" s="263"/>
+      <c r="D7" s="263">
         <v>1</v>
       </c>
       <c r="E7" s="52"/>
@@ -30061,8 +30044,8 @@
       <c r="B8" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="266"/>
-      <c r="D8" s="266">
+      <c r="C8" s="263"/>
+      <c r="D8" s="263">
         <v>4</v>
       </c>
       <c r="E8" s="52"/>
@@ -30072,7 +30055,7 @@
       <c r="B9" t="s">
         <v>180</v>
       </c>
-      <c r="D9" s="266">
+      <c r="D9" s="263">
         <v>12</v>
       </c>
       <c r="E9" s="52"/>
@@ -30082,7 +30065,7 @@
       <c r="B10" t="s">
         <v>613</v>
       </c>
-      <c r="D10" s="266">
+      <c r="D10" s="263">
         <v>4</v>
       </c>
       <c r="E10" s="52"/>
@@ -30092,7 +30075,7 @@
       <c r="B11" t="s">
         <v>452</v>
       </c>
-      <c r="D11" s="266">
+      <c r="D11" s="263">
         <v>4</v>
       </c>
       <c r="E11" s="52"/>
@@ -30104,7 +30087,7 @@
       <c r="B12" t="s">
         <v>400</v>
       </c>
-      <c r="D12" s="266">
+      <c r="D12" s="263">
         <v>2</v>
       </c>
       <c r="E12" s="52"/>
@@ -30114,7 +30097,7 @@
       <c r="B13" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="D13" s="266">
+      <c r="D13" s="263">
         <v>2</v>
       </c>
       <c r="E13" s="52"/>
@@ -30124,7 +30107,7 @@
       <c r="B14" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D14" s="266">
+      <c r="D14" s="263">
         <v>6</v>
       </c>
       <c r="E14" s="52"/>
@@ -30134,17 +30117,17 @@
       <c r="B15" t="s">
         <v>614</v>
       </c>
-      <c r="D15" s="266">
+      <c r="D15" s="263">
         <v>1</v>
       </c>
       <c r="E15" s="52"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="23"/>
-      <c r="B16" s="262" t="s">
+      <c r="B16" s="259" t="s">
         <v>615</v>
       </c>
-      <c r="D16" s="266">
+      <c r="D16" s="263">
         <v>1</v>
       </c>
       <c r="E16" s="52"/>
@@ -30154,7 +30137,7 @@
       <c r="B17" s="26" t="s">
         <v>616</v>
       </c>
-      <c r="D17" s="266">
+      <c r="D17" s="263">
         <v>1</v>
       </c>
       <c r="E17" s="52"/>
@@ -30165,7 +30148,7 @@
         <v>617</v>
       </c>
       <c r="C18" s="48"/>
-      <c r="D18" s="289">
+      <c r="D18" s="286">
         <v>1</v>
       </c>
       <c r="E18" s="59"/>
@@ -30216,10 +30199,10 @@
       <c r="B1" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="C1" s="261" t="s">
+      <c r="C1" s="258" t="s">
         <v>378</v>
       </c>
-      <c r="D1" s="261" t="s">
+      <c r="D1" s="258" t="s">
         <v>379</v>
       </c>
       <c r="E1" s="46"/>
@@ -30254,7 +30237,7 @@
       <c r="D3" s="13">
         <v>1</v>
       </c>
-      <c r="E3" s="283" t="s">
+      <c r="E3" s="280" t="s">
         <v>386</v>
       </c>
     </row>
@@ -30271,7 +30254,7 @@
       <c r="D4" s="13">
         <v>1</v>
       </c>
-      <c r="E4" s="283" t="s">
+      <c r="E4" s="280" t="s">
         <v>389</v>
       </c>
     </row>
@@ -30282,25 +30265,25 @@
       <c r="B5" s="28" t="s">
         <v>622</v>
       </c>
-      <c r="C5" s="266" t="s">
+      <c r="C5" s="263" t="s">
         <v>623</v>
       </c>
-      <c r="D5" s="272">
+      <c r="D5" s="269">
         <v>2</v>
       </c>
-      <c r="E5" s="283" t="s">
+      <c r="E5" s="280" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="23"/>
-      <c r="B6" s="290" t="s">
+      <c r="B6" s="287" t="s">
         <v>622</v>
       </c>
-      <c r="C6" s="266" t="s">
+      <c r="C6" s="263" t="s">
         <v>624</v>
       </c>
-      <c r="D6" s="272">
+      <c r="D6" s="269">
         <v>5</v>
       </c>
       <c r="E6" s="52"/>
@@ -30310,10 +30293,10 @@
       <c r="B7" s="18" t="s">
         <v>625</v>
       </c>
-      <c r="C7" s="266" t="s">
+      <c r="C7" s="263" t="s">
         <v>623</v>
       </c>
-      <c r="D7" s="272">
+      <c r="D7" s="269">
         <v>2</v>
       </c>
       <c r="E7" s="52"/>
@@ -30323,7 +30306,7 @@
       <c r="B8" s="18" t="s">
         <v>625</v>
       </c>
-      <c r="C8" s="266" t="s">
+      <c r="C8" s="263" t="s">
         <v>624</v>
       </c>
       <c r="D8" s="13">
@@ -30333,10 +30316,10 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="23"/>
-      <c r="B9" s="291" t="s">
+      <c r="B9" s="288" t="s">
         <v>149</v>
       </c>
-      <c r="C9" s="266" t="s">
+      <c r="C9" s="263" t="s">
         <v>626</v>
       </c>
       <c r="D9" s="13">
@@ -30349,10 +30332,10 @@
       <c r="B10" s="28" t="s">
         <v>627</v>
       </c>
-      <c r="C10" s="266" t="s">
+      <c r="C10" s="263" t="s">
         <v>623</v>
       </c>
-      <c r="D10" s="272">
+      <c r="D10" s="269">
         <v>2</v>
       </c>
       <c r="E10" s="52"/>
@@ -30362,7 +30345,7 @@
       <c r="B11" s="28" t="s">
         <v>627</v>
       </c>
-      <c r="C11" s="266" t="s">
+      <c r="C11" s="263" t="s">
         <v>624</v>
       </c>
       <c r="D11" s="13">
@@ -30374,10 +30357,10 @@
       <c r="A12" s="47" t="s">
         <v>401</v>
       </c>
-      <c r="B12" s="291" t="s">
+      <c r="B12" s="288" t="s">
         <v>628</v>
       </c>
-      <c r="C12" s="266" t="s">
+      <c r="C12" s="263" t="s">
         <v>629</v>
       </c>
       <c r="D12" s="13">
@@ -30390,10 +30373,10 @@
       <c r="B13" s="28" t="s">
         <v>630</v>
       </c>
-      <c r="C13" s="266" t="s">
+      <c r="C13" s="263" t="s">
         <v>631</v>
       </c>
-      <c r="D13" s="272">
+      <c r="D13" s="269">
         <v>2</v>
       </c>
       <c r="E13" s="52"/>
@@ -30403,10 +30386,10 @@
       <c r="B14" s="28" t="s">
         <v>622</v>
       </c>
-      <c r="C14" s="266" t="s">
+      <c r="C14" s="263" t="s">
         <v>631</v>
       </c>
-      <c r="D14" s="272">
+      <c r="D14" s="269">
         <v>2</v>
       </c>
       <c r="E14" s="52"/>
@@ -30416,10 +30399,10 @@
       <c r="B15" s="28" t="s">
         <v>630</v>
       </c>
-      <c r="C15" s="266" t="s">
+      <c r="C15" s="263" t="s">
         <v>623</v>
       </c>
-      <c r="D15" s="272">
+      <c r="D15" s="269">
         <v>2</v>
       </c>
       <c r="E15" s="52"/>
@@ -30429,36 +30412,36 @@
       <c r="B16" s="28" t="s">
         <v>630</v>
       </c>
-      <c r="C16" s="266" t="s">
+      <c r="C16" s="263" t="s">
         <v>624</v>
       </c>
-      <c r="D16" s="272">
+      <c r="D16" s="269">
         <v>5</v>
       </c>
       <c r="E16" s="52"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="23"/>
-      <c r="B17" s="291" t="s">
+      <c r="B17" s="288" t="s">
         <v>632</v>
       </c>
-      <c r="C17" s="266" t="s">
+      <c r="C17" s="263" t="s">
         <v>633</v>
       </c>
-      <c r="D17" s="272">
+      <c r="D17" s="269">
         <v>5</v>
       </c>
       <c r="E17" s="52"/>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="23"/>
-      <c r="B18" s="291" t="s">
+      <c r="B18" s="288" t="s">
         <v>632</v>
       </c>
-      <c r="C18" s="266" t="s">
+      <c r="C18" s="263" t="s">
         <v>624</v>
       </c>
-      <c r="D18" s="272">
+      <c r="D18" s="269">
         <v>5</v>
       </c>
       <c r="E18" s="52"/>
@@ -30478,7 +30461,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="23"/>
-      <c r="B20" s="290" t="s">
+      <c r="B20" s="287" t="s">
         <v>622</v>
       </c>
       <c r="C20" s="2" t="s">
@@ -30530,10 +30513,10 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="23"/>
-      <c r="B24" s="284" t="s">
+      <c r="B24" s="281" t="s">
         <v>639</v>
       </c>
-      <c r="C24" s="284" t="s">
+      <c r="C24" s="281" t="s">
         <v>457</v>
       </c>
       <c r="D24" s="53"/>
@@ -30541,20 +30524,20 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="23"/>
-      <c r="B25" s="266" t="s">
+      <c r="B25" s="263" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="266" t="s">
+      <c r="C25" s="263" t="s">
         <v>640</v>
       </c>
-      <c r="D25" s="266">
+      <c r="D25" s="263">
         <v>1</v>
       </c>
       <c r="E25" s="52"/>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="23"/>
-      <c r="B26" s="266" t="s">
+      <c r="B26" s="263" t="s">
         <v>641</v>
       </c>
       <c r="D26" s="13">
@@ -30618,10 +30601,10 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="23"/>
-      <c r="B32" s="265" t="s">
+      <c r="B32" s="262" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="266">
+      <c r="D32" s="263">
         <v>1</v>
       </c>
       <c r="E32" s="52"/>
@@ -30716,10 +30699,10 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="23"/>
-      <c r="B41" s="291" t="s">
+      <c r="B41" s="288" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="266" t="s">
+      <c r="C41" s="263" t="s">
         <v>642</v>
       </c>
       <c r="D41" s="13">
@@ -30729,10 +30712,10 @@
     </row>
     <row r="42" spans="1:5" ht="15" customHeight="1">
       <c r="A42" s="23"/>
-      <c r="B42" s="291" t="s">
+      <c r="B42" s="288" t="s">
         <v>50</v>
       </c>
-      <c r="C42" s="266" t="s">
+      <c r="C42" s="263" t="s">
         <v>642</v>
       </c>
       <c r="D42" s="13">
@@ -30745,7 +30728,7 @@
       <c r="B43" s="23" t="s">
         <v>643</v>
       </c>
-      <c r="C43" s="266" t="s">
+      <c r="C43" s="263" t="s">
         <v>642</v>
       </c>
       <c r="D43" s="13">
@@ -30755,10 +30738,10 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="23"/>
-      <c r="B44" s="291" t="s">
+      <c r="B44" s="288" t="s">
         <v>95</v>
       </c>
-      <c r="C44" s="266" t="s">
+      <c r="C44" s="263" t="s">
         <v>644</v>
       </c>
       <c r="D44" s="13">
@@ -30771,23 +30754,23 @@
       <c r="B45" s="15" t="s">
         <v>645</v>
       </c>
-      <c r="C45" s="266" t="s">
+      <c r="C45" s="263" t="s">
         <v>646</v>
       </c>
-      <c r="D45" s="266">
+      <c r="D45" s="263">
         <v>1</v>
       </c>
       <c r="E45" s="52"/>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="23"/>
-      <c r="B46" s="291" t="s">
+      <c r="B46" s="288" t="s">
         <v>133</v>
       </c>
-      <c r="C46" s="266" t="s">
+      <c r="C46" s="263" t="s">
         <v>647</v>
       </c>
-      <c r="D46" s="266">
+      <c r="D46" s="263">
         <v>1</v>
       </c>
       <c r="E46" s="52"/>
@@ -30797,7 +30780,7 @@
       <c r="B47" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C47" s="266" t="s">
+      <c r="C47" s="263" t="s">
         <v>648</v>
       </c>
       <c r="D47" s="13">
@@ -30810,7 +30793,7 @@
       <c r="B48" t="s">
         <v>649</v>
       </c>
-      <c r="C48" s="266" t="s">
+      <c r="C48" s="263" t="s">
         <v>650</v>
       </c>
       <c r="D48" s="13">
@@ -30823,7 +30806,7 @@
       <c r="B49" t="s">
         <v>651</v>
       </c>
-      <c r="C49" s="266" t="s">
+      <c r="C49" s="263" t="s">
         <v>652</v>
       </c>
       <c r="D49" s="13">
@@ -30833,10 +30816,10 @@
     </row>
     <row r="50" spans="1:5" ht="16.5" customHeight="1">
       <c r="A50" s="23"/>
-      <c r="B50" s="266" t="s">
+      <c r="B50" s="263" t="s">
         <v>653</v>
       </c>
-      <c r="C50" s="266" t="s">
+      <c r="C50" s="263" t="s">
         <v>654</v>
       </c>
       <c r="D50" s="13">
@@ -30849,7 +30832,7 @@
       <c r="B51" s="45" t="s">
         <v>655</v>
       </c>
-      <c r="C51" s="289" t="s">
+      <c r="C51" s="286" t="s">
         <v>650</v>
       </c>
       <c r="D51" s="58">

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3305" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA3337A2-AE80-44D5-AF59-5165BA120F7C}"/>
+  <xr:revisionPtr revIDLastSave="3311" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD8757C7-3111-4326-BB3A-D94B330F0C90}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2002" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="1100">
   <si>
     <t>Type</t>
   </si>
@@ -3406,9 +3406,6 @@
       </rPr>
       <t> to reach the high HDT values listed. Without annealing, these parts will soften significantly at much lower temperatures.</t>
     </r>
-  </si>
-  <si>
-    <t>make scrafitial layers in the gearbox</t>
   </si>
   <si>
     <t>R</t>
@@ -7651,7 +7648,7 @@
     <filterColumn colId="11" hiddenButton="1"/>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:L37">
-    <sortCondition descending="1" ref="J5:J37"/>
+    <sortCondition ref="A5:A37"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{197BC419-568C-45F9-A938-BCB10710A201}" name="Filament Name" dataDxfId="11" dataCellStyle="Normal 12"/>
@@ -15645,7 +15642,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="83.140625" customWidth="1"/>
@@ -15774,18 +15771,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B14" t="s">
         <v>1096</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1097</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>1098</v>
-      </c>
-      <c r="B15" t="s">
-        <v>1097</v>
       </c>
     </row>
   </sheetData>
@@ -17544,562 +17533,562 @@
         <v>1048</v>
       </c>
       <c r="J4" s="242" t="s">
+        <v>1098</v>
+      </c>
+      <c r="K4" s="242" t="s">
         <v>1099</v>
-      </c>
-      <c r="K4" s="242" t="s">
-        <v>1100</v>
       </c>
       <c r="L4" s="242" t="s">
         <v>1049</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A5" s="237" t="s">
-        <v>675</v>
+      <c r="A5" s="245" t="s">
+        <v>821</v>
       </c>
       <c r="B5" s="238" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C5" s="239">
-        <v>0</v>
+        <v>1080</v>
+      </c>
+      <c r="C5" s="239" t="s">
+        <v>1051</v>
       </c>
       <c r="D5" s="239">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E5" s="239">
-        <v>320</v>
+        <v>225</v>
       </c>
       <c r="F5" s="239">
         <v>110</v>
       </c>
       <c r="G5" s="239">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="H5" s="239">
+        <v>75</v>
+      </c>
+      <c r="I5" s="240">
+        <v>4</v>
+      </c>
+      <c r="J5" s="239">
+        <v>95</v>
+      </c>
+      <c r="K5" s="239">
         <v>100</v>
       </c>
-      <c r="I5" s="240">
-        <v>10</v>
-      </c>
-      <c r="J5" s="239">
-        <v>264</v>
-      </c>
-      <c r="K5" s="239">
-        <v>280</v>
-      </c>
       <c r="L5" s="239">
-        <v>7160</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A6" s="237" t="s">
-        <v>676</v>
+      <c r="A6" s="245" t="s">
+        <v>1081</v>
       </c>
       <c r="B6" s="238" t="s">
-        <v>1050</v>
+        <v>1080</v>
       </c>
       <c r="C6" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D6" s="239">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="E6" s="239">
-        <v>300</v>
+        <v>245</v>
       </c>
       <c r="F6" s="239">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="G6" s="239">
         <v>60</v>
       </c>
       <c r="H6" s="239">
+        <v>80</v>
+      </c>
+      <c r="I6" s="240">
+        <v>3</v>
+      </c>
+      <c r="J6" s="239">
+        <v>95</v>
+      </c>
+      <c r="K6" s="239">
         <v>100</v>
       </c>
-      <c r="I6" s="240">
-        <v>8</v>
-      </c>
-      <c r="J6" s="239">
-        <v>227</v>
-      </c>
-      <c r="K6" s="239">
+      <c r="L6" s="239">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A7" s="245" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B7" s="238" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C7" s="239" t="s">
+        <v>1074</v>
+      </c>
+      <c r="D7" s="239">
+        <v>90</v>
+      </c>
+      <c r="E7" s="239">
         <v>250</v>
       </c>
-      <c r="L6" s="239">
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A7" s="237" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B7" s="238" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C7" s="239">
-        <v>0</v>
-      </c>
-      <c r="D7" s="239">
-        <v>186</v>
-      </c>
-      <c r="E7" s="239">
-        <v>375</v>
-      </c>
       <c r="F7" s="239">
-        <v>135</v>
+        <v>80</v>
       </c>
       <c r="G7" s="239">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="H7" s="239">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I7" s="240">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" s="239">
-        <v>208</v>
+        <v>70</v>
       </c>
       <c r="K7" s="239">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="L7" s="239">
-        <v>3000</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="245" t="s">
-        <v>1054</v>
+        <v>1083</v>
       </c>
       <c r="B8" s="238" t="s">
-        <v>1053</v>
+        <v>1050</v>
       </c>
       <c r="C8" s="239">
         <v>0</v>
       </c>
       <c r="D8" s="239">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="E8" s="239">
-        <v>400</v>
+        <v>225</v>
       </c>
       <c r="F8" s="239">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="G8" s="239">
-        <v>100</v>
-      </c>
-      <c r="H8" s="239">
-        <v>120</v>
-      </c>
-      <c r="I8" s="240">
-        <v>4</v>
+        <v>50</v>
+      </c>
+      <c r="H8" s="239" t="s">
+        <v>913</v>
+      </c>
+      <c r="I8" s="240" t="s">
+        <v>913</v>
       </c>
       <c r="J8" s="239">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="K8" s="239">
-        <v>210</v>
+        <v>80</v>
       </c>
       <c r="L8" s="239">
-        <v>2215</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="237" t="s">
-        <v>1055</v>
-      </c>
-      <c r="B9" s="238"/>
+        <v>1063</v>
+      </c>
+      <c r="B9" s="238" t="s">
+        <v>1064</v>
+      </c>
       <c r="C9" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D9" s="239">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="E9" s="239">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="F9" s="239">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G9" s="239">
+        <v>70</v>
+      </c>
+      <c r="H9" s="239">
         <v>90</v>
       </c>
-      <c r="H9" s="239">
-        <v>80</v>
-      </c>
       <c r="I9" s="240">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J9" s="239">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="K9" s="239">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="L9" s="239">
-        <v>9800</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="222" customFormat="1" ht="17.25" customHeight="1">
-      <c r="A10" s="245" t="s">
-        <v>1056</v>
+      <c r="A10" s="237" t="s">
+        <v>1079</v>
       </c>
       <c r="B10" s="238" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="C10" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D10" s="239">
-        <v>165</v>
-      </c>
-      <c r="E10" s="239">
-        <v>370</v>
+        <v>60</v>
+      </c>
+      <c r="E10" s="241">
+        <v>260</v>
       </c>
       <c r="F10" s="239">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="G10" s="239">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="H10" s="239">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I10" s="240">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J10" s="239">
-        <v>182</v>
+        <v>110</v>
       </c>
       <c r="K10" s="239">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="L10" s="239">
-        <v>2900</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="237" t="s">
-        <v>1058</v>
+        <v>1067</v>
       </c>
       <c r="B11" s="238" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
       <c r="C11" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D11" s="239">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="E11" s="239">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="F11" s="239">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="G11" s="239">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="H11" s="239">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I11" s="240">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J11" s="239">
+        <v>135</v>
+      </c>
+      <c r="K11" s="239">
         <v>180</v>
       </c>
-      <c r="K11" s="239">
-        <v>300</v>
-      </c>
       <c r="L11" s="239">
-        <v>9850</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="237" t="s">
-        <v>1059</v>
-      </c>
-      <c r="B12" s="238"/>
-      <c r="C12" s="239">
-        <v>0</v>
+        <v>1068</v>
+      </c>
+      <c r="B12" s="238" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C12" s="239" t="s">
+        <v>1051</v>
       </c>
       <c r="D12" s="239">
-        <v>180</v>
+        <v>60</v>
       </c>
       <c r="E12" s="239">
-        <v>360</v>
+        <v>260</v>
       </c>
       <c r="F12" s="239">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="G12" s="239">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="H12" s="239">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="I12" s="240">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="239">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="K12" s="239">
         <v>180</v>
       </c>
       <c r="L12" s="239">
-        <v>2200</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A13" s="245" t="s">
-        <v>1060</v>
+      <c r="A13" s="237" t="s">
+        <v>1065</v>
       </c>
       <c r="B13" s="238" t="s">
-        <v>1061</v>
-      </c>
-      <c r="C13" s="239">
-        <v>0</v>
+        <v>1064</v>
+      </c>
+      <c r="C13" s="239" t="s">
+        <v>1051</v>
       </c>
       <c r="D13" s="239">
-        <v>187</v>
+        <v>70</v>
       </c>
       <c r="E13" s="239">
-        <v>365</v>
+        <v>260</v>
       </c>
       <c r="F13" s="239">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="G13" s="239">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="H13" s="239">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I13" s="240">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J13" s="239">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="K13" s="239">
         <v>180</v>
       </c>
       <c r="L13" s="239">
-        <v>2050</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A14" s="245" t="s">
-        <v>1062</v>
-      </c>
-      <c r="B14" s="238"/>
-      <c r="C14" s="239" t="s">
-        <v>1051</v>
+      <c r="A14" s="237" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B14" s="238" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C14" s="239">
+        <v>0</v>
       </c>
       <c r="D14" s="239">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="E14" s="239">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="F14" s="239">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="G14" s="239">
-        <v>100</v>
-      </c>
-      <c r="H14" s="239" t="s">
-        <v>913</v>
-      </c>
-      <c r="I14" s="240" t="s">
-        <v>913</v>
+        <v>60</v>
+      </c>
+      <c r="H14" s="239">
+        <v>120</v>
+      </c>
+      <c r="I14" s="240">
+        <v>4</v>
       </c>
       <c r="J14" s="239">
-        <v>158</v>
+        <v>135</v>
       </c>
       <c r="K14" s="239">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="L14" s="239">
-        <v>2100</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A15" s="237" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B15" s="238" t="s">
-        <v>1064</v>
-      </c>
+      <c r="A15" s="245" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B15" s="238"/>
       <c r="C15" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D15" s="239">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="E15" s="239">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="F15" s="239">
         <v>110</v>
       </c>
       <c r="G15" s="239">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H15" s="239">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="I15" s="240">
         <v>4</v>
       </c>
       <c r="J15" s="239">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="K15" s="239">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="L15" s="239">
-        <v>2050</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A16" s="237" t="s">
-        <v>1065</v>
-      </c>
-      <c r="B16" s="238" t="s">
-        <v>1064</v>
-      </c>
+      <c r="A16" s="245" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B16" s="238"/>
       <c r="C16" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D16" s="239">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="E16" s="239">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F16" s="239">
+        <v>110</v>
+      </c>
+      <c r="G16" s="239">
         <v>90</v>
       </c>
-      <c r="G16" s="239">
-        <v>60</v>
-      </c>
       <c r="H16" s="239">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="I16" s="240">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J16" s="239">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="K16" s="239">
-        <v>180</v>
+        <v>128</v>
       </c>
       <c r="L16" s="239">
-        <v>4800</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A17" s="245" t="s">
-        <v>1066</v>
+      <c r="A17" s="237" t="s">
+        <v>1077</v>
       </c>
       <c r="B17" s="238" t="s">
-        <v>1057</v>
+        <v>1050</v>
       </c>
       <c r="C17" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D17" s="239">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E17" s="239">
-        <v>390</v>
+        <v>260</v>
       </c>
       <c r="F17" s="239">
-        <v>135</v>
-      </c>
-      <c r="G17" s="239">
-        <v>100</v>
+        <v>90</v>
+      </c>
+      <c r="G17" s="241">
+        <v>60</v>
       </c>
       <c r="H17" s="239">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I17" s="240">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J17" s="239">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="K17" s="239">
-        <v>280</v>
+        <v>114</v>
       </c>
       <c r="L17" s="239">
-        <v>3700</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="237" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="B18" s="238" t="s">
-        <v>1064</v>
+        <v>1050</v>
       </c>
       <c r="C18" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D18" s="239">
+        <v>113</v>
+      </c>
+      <c r="E18" s="239">
+        <v>285</v>
+      </c>
+      <c r="F18" s="239">
+        <v>110</v>
+      </c>
+      <c r="G18" s="239">
         <v>60</v>
-      </c>
-      <c r="E18" s="239">
-        <v>260</v>
-      </c>
-      <c r="F18" s="239">
-        <v>80</v>
-      </c>
-      <c r="G18" s="239">
-        <v>55</v>
       </c>
       <c r="H18" s="239">
         <v>80</v>
       </c>
       <c r="I18" s="240">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J18" s="239">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K18" s="239">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="L18" s="239">
-        <v>3000</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="237" t="s">
-        <v>1068</v>
-      </c>
-      <c r="B19" s="238" t="s">
-        <v>1064</v>
-      </c>
+        <v>1055</v>
+      </c>
+      <c r="B19" s="238"/>
       <c r="C19" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D19" s="239">
-        <v>60</v>
+        <v>158</v>
       </c>
       <c r="E19" s="239">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="F19" s="239">
+        <v>100</v>
+      </c>
+      <c r="G19" s="239">
         <v>90</v>
-      </c>
-      <c r="G19" s="239">
-        <v>50</v>
       </c>
       <c r="H19" s="239">
         <v>80</v>
@@ -18108,69 +18097,67 @@
         <v>6</v>
       </c>
       <c r="J19" s="239">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="K19" s="239">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="L19" s="239">
-        <v>2900</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="237" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B20" s="238" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C20" s="239">
-        <v>0</v>
+        <v>1070</v>
+      </c>
+      <c r="B20" s="238"/>
+      <c r="C20" s="239" t="s">
+        <v>1051</v>
       </c>
       <c r="D20" s="239">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E20" s="239">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F20" s="239">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G20" s="239">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H20" s="239">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="I20" s="240">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J20" s="239">
         <v>135</v>
       </c>
       <c r="K20" s="239">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="L20" s="239">
-        <v>2200</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A21" s="237" t="s">
-        <v>1070</v>
+        <v>674</v>
       </c>
       <c r="B21" s="238"/>
       <c r="C21" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D21" s="239">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E21" s="239">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="F21" s="239">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G21" s="239">
         <v>100</v>
@@ -18182,164 +18169,170 @@
         <v>5</v>
       </c>
       <c r="J21" s="239">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K21" s="239">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="L21" s="239">
-        <v>6000</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A22" s="245" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B22" s="238"/>
+      <c r="A22" s="237" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B22" s="238" t="s">
+        <v>1050</v>
+      </c>
       <c r="C22" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D22" s="239">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="E22" s="239">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="F22" s="239">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="G22" s="239">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="H22" s="239">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="I22" s="240">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J22" s="239">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="K22" s="239">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="L22" s="239">
-        <v>2370</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A23" s="245" t="s">
-        <v>1072</v>
-      </c>
-      <c r="B23" s="238"/>
+        <v>1066</v>
+      </c>
+      <c r="B23" s="238" t="s">
+        <v>1057</v>
+      </c>
       <c r="C23" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D23" s="239">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="E23" s="239">
-        <v>265</v>
+        <v>390</v>
       </c>
       <c r="F23" s="239">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="G23" s="239">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="H23" s="239">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I23" s="240">
         <v>4</v>
       </c>
       <c r="J23" s="239">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="K23" s="239">
-        <v>128</v>
+        <v>280</v>
       </c>
       <c r="L23" s="239">
-        <v>2370</v>
+        <v>3700</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="245" t="s">
-        <v>1073</v>
-      </c>
-      <c r="B24" s="238"/>
+        <v>1056</v>
+      </c>
+      <c r="B24" s="238" t="s">
+        <v>1057</v>
+      </c>
       <c r="C24" s="239" t="s">
-        <v>1074</v>
+        <v>1051</v>
       </c>
       <c r="D24" s="239">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="E24" s="239">
-        <v>235</v>
+        <v>370</v>
       </c>
       <c r="F24" s="239">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="G24" s="239">
-        <v>35</v>
+        <v>150</v>
       </c>
       <c r="H24" s="239">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="I24" s="240">
         <v>4</v>
       </c>
       <c r="J24" s="239">
-        <v>120</v>
+        <v>182</v>
       </c>
       <c r="K24" s="239">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="L24" s="239">
-        <v>100</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="25" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="237" t="s">
-        <v>1075</v>
+        <v>1058</v>
       </c>
       <c r="B25" s="238" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
       <c r="C25" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D25" s="239">
-        <v>113</v>
+        <v>165</v>
       </c>
       <c r="E25" s="239">
-        <v>285</v>
+        <v>380</v>
       </c>
       <c r="F25" s="239">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="G25" s="239">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="H25" s="239">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I25" s="240">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J25" s="239">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="K25" s="239">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="L25" s="239">
-        <v>4200</v>
+        <v>9850</v>
       </c>
     </row>
     <row r="26" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A26" s="237" t="s">
-        <v>1076</v>
+      <c r="A26" s="246" t="s">
+        <v>1078</v>
       </c>
       <c r="B26" s="238" t="s">
         <v>1050</v>
@@ -18348,124 +18341,124 @@
         <v>1051</v>
       </c>
       <c r="D26" s="239">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="E26" s="239">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F26" s="239">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G26" s="239">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="H26" s="239">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="I26" s="240">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J26" s="239">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K26" s="239">
-        <v>116</v>
+        <v>225</v>
       </c>
       <c r="L26" s="239">
-        <v>2040</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="27" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A27" s="237" t="s">
-        <v>1077</v>
+      <c r="A27" s="245" t="s">
+        <v>822</v>
       </c>
       <c r="B27" s="238" t="s">
         <v>1050</v>
       </c>
       <c r="C27" s="239" t="s">
-        <v>1051</v>
+        <v>1074</v>
       </c>
       <c r="D27" s="239">
-        <v>145</v>
+        <v>80</v>
       </c>
       <c r="E27" s="239">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="F27" s="239">
-        <v>90</v>
-      </c>
-      <c r="G27" s="241">
-        <v>60</v>
+        <v>70</v>
+      </c>
+      <c r="G27" s="239">
+        <v>35</v>
       </c>
       <c r="H27" s="239">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I27" s="240">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J27" s="239">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="K27" s="239">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="L27" s="239">
-        <v>2300</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="28" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A28" s="246" t="s">
-        <v>1078</v>
+      <c r="A28" s="245" t="s">
+        <v>820</v>
       </c>
       <c r="B28" s="238" t="s">
         <v>1050</v>
       </c>
       <c r="C28" s="239" t="s">
-        <v>1051</v>
+        <v>1085</v>
       </c>
       <c r="D28" s="239">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="E28" s="239">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="F28" s="239">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="G28" s="239">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="H28" s="239">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I28" s="240">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J28" s="239">
-        <v>112</v>
+        <v>60</v>
       </c>
       <c r="K28" s="239">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="L28" s="239">
-        <v>6500</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="29" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A29" s="237" t="s">
-        <v>1079</v>
+        <v>676</v>
       </c>
       <c r="B29" s="238" t="s">
-        <v>1064</v>
+        <v>1050</v>
       </c>
       <c r="C29" s="239" t="s">
         <v>1051</v>
       </c>
       <c r="D29" s="239">
-        <v>60</v>
-      </c>
-      <c r="E29" s="241">
-        <v>260</v>
+        <v>90</v>
+      </c>
+      <c r="E29" s="239">
+        <v>300</v>
       </c>
       <c r="F29" s="239">
         <v>90</v>
@@ -18474,192 +18467,192 @@
         <v>60</v>
       </c>
       <c r="H29" s="239">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I29" s="240">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J29" s="239">
+        <v>227</v>
+      </c>
+      <c r="K29" s="239">
+        <v>250</v>
+      </c>
+      <c r="L29" s="239">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A30" s="245" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B30" s="238" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C30" s="239">
+        <v>0</v>
+      </c>
+      <c r="D30" s="239">
+        <v>283</v>
+      </c>
+      <c r="E30" s="239">
+        <v>340</v>
+      </c>
+      <c r="F30" s="239">
+        <v>120</v>
+      </c>
+      <c r="G30" s="239">
+        <v>70</v>
+      </c>
+      <c r="H30" s="239">
         <v>110</v>
       </c>
-      <c r="K29" s="239">
-        <v>180</v>
-      </c>
-      <c r="L29" s="239">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A30" s="237" t="s">
-        <v>674</v>
-      </c>
-      <c r="B30" s="238"/>
-      <c r="C30" s="239" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D30" s="239">
-        <v>140</v>
-      </c>
-      <c r="E30" s="239">
-        <v>260</v>
-      </c>
-      <c r="F30" s="239">
+      <c r="I30" s="240">
+        <v>4</v>
+      </c>
+      <c r="J30" s="239">
+        <v>90</v>
+      </c>
+      <c r="K30" s="239">
+        <v>250</v>
+      </c>
+      <c r="L30" s="239">
+        <v>2540</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
+      <c r="A31" s="237" t="s">
+        <v>675</v>
+      </c>
+      <c r="B31" s="238" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C31" s="239">
+        <v>0</v>
+      </c>
+      <c r="D31" s="239">
         <v>100</v>
       </c>
-      <c r="G30" s="239">
-        <v>100</v>
-      </c>
-      <c r="H30" s="239">
-        <v>80</v>
-      </c>
-      <c r="I30" s="240">
-        <v>5</v>
-      </c>
-      <c r="J30" s="239">
-        <v>110</v>
-      </c>
-      <c r="K30" s="239">
-        <v>110</v>
-      </c>
-      <c r="L30" s="239">
-        <v>6200</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A31" s="245" t="s">
-        <v>821</v>
-      </c>
-      <c r="B31" s="238" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C31" s="239" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D31" s="239">
-        <v>105</v>
-      </c>
       <c r="E31" s="239">
-        <v>225</v>
+        <v>320</v>
       </c>
       <c r="F31" s="239">
         <v>110</v>
       </c>
       <c r="G31" s="239">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="H31" s="239">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="I31" s="240">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J31" s="239">
-        <v>95</v>
+        <v>264</v>
       </c>
       <c r="K31" s="239">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="L31" s="239">
-        <v>2300</v>
+        <v>7160</v>
       </c>
     </row>
     <row r="32" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="245" t="s">
-        <v>1081</v>
+        <v>1054</v>
       </c>
       <c r="B32" s="238" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C32" s="239" t="s">
-        <v>1051</v>
+        <v>1053</v>
+      </c>
+      <c r="C32" s="239">
+        <v>0</v>
       </c>
       <c r="D32" s="239">
-        <v>105</v>
+        <v>230</v>
       </c>
       <c r="E32" s="239">
-        <v>245</v>
+        <v>400</v>
       </c>
       <c r="F32" s="239">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="G32" s="239">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H32" s="239">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="I32" s="240">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="239">
-        <v>95</v>
+        <v>190</v>
       </c>
       <c r="K32" s="239">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="L32" s="239">
-        <v>2000</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A33" s="245" t="s">
-        <v>1082</v>
+        <v>1060</v>
       </c>
       <c r="B33" s="238" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="C33" s="239">
         <v>0</v>
       </c>
       <c r="D33" s="239">
-        <v>283</v>
+        <v>187</v>
       </c>
       <c r="E33" s="239">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="F33" s="239">
+        <v>130</v>
+      </c>
+      <c r="G33" s="239">
+        <v>130</v>
+      </c>
+      <c r="H33" s="239">
         <v>120</v>
-      </c>
-      <c r="G33" s="239">
-        <v>70</v>
-      </c>
-      <c r="H33" s="239">
-        <v>110</v>
       </c>
       <c r="I33" s="240">
         <v>4</v>
       </c>
       <c r="J33" s="239">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="K33" s="239">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="L33" s="239">
-        <v>2540</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="245" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B34" s="238" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C34" s="239">
-        <v>0</v>
+        <v>1062</v>
+      </c>
+      <c r="B34" s="238"/>
+      <c r="C34" s="239" t="s">
+        <v>1051</v>
       </c>
       <c r="D34" s="239">
+        <v>170</v>
+      </c>
+      <c r="E34" s="239">
+        <v>265</v>
+      </c>
+      <c r="F34" s="239">
+        <v>105</v>
+      </c>
+      <c r="G34" s="239">
         <v>100</v>
-      </c>
-      <c r="E34" s="239">
-        <v>225</v>
-      </c>
-      <c r="F34" s="239">
-        <v>100</v>
-      </c>
-      <c r="G34" s="239">
-        <v>50</v>
       </c>
       <c r="H34" s="239" t="s">
         <v>913</v>
@@ -18668,127 +18661,123 @@
         <v>913</v>
       </c>
       <c r="J34" s="239">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="K34" s="239">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="L34" s="239">
-        <v>1600</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="245" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B35" s="238" t="s">
-        <v>1050</v>
-      </c>
+        <v>1073</v>
+      </c>
+      <c r="B35" s="238"/>
       <c r="C35" s="239" t="s">
         <v>1074</v>
       </c>
       <c r="D35" s="239">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E35" s="239">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="F35" s="239">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G35" s="239">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H35" s="239">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I35" s="240">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J35" s="239">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="K35" s="239">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="L35" s="239">
-        <v>1900</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A36" s="245" t="s">
-        <v>822</v>
+      <c r="A36" s="237" t="s">
+        <v>1052</v>
       </c>
       <c r="B36" s="238" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C36" s="239" t="s">
-        <v>1074</v>
+        <v>1053</v>
+      </c>
+      <c r="C36" s="239">
+        <v>0</v>
       </c>
       <c r="D36" s="239">
-        <v>80</v>
+        <v>186</v>
       </c>
       <c r="E36" s="239">
-        <v>245</v>
+        <v>375</v>
       </c>
       <c r="F36" s="239">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="G36" s="239">
-        <v>35</v>
+        <v>110</v>
       </c>
       <c r="H36" s="239">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="I36" s="240">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J36" s="239">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="K36" s="239">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="L36" s="239">
-        <v>1600</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A37" s="245" t="s">
-        <v>820</v>
-      </c>
-      <c r="B37" s="238" t="s">
-        <v>1050</v>
-      </c>
-      <c r="C37" s="239" t="s">
-        <v>1085</v>
+      <c r="A37" s="237" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B37" s="238"/>
+      <c r="C37" s="239">
+        <v>0</v>
       </c>
       <c r="D37" s="239">
-        <v>85</v>
+        <v>180</v>
       </c>
       <c r="E37" s="239">
-        <v>210</v>
+        <v>360</v>
       </c>
       <c r="F37" s="239">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="G37" s="239">
-        <v>25</v>
+        <v>170</v>
       </c>
       <c r="H37" s="239">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="I37" s="240">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J37" s="239">
-        <v>60</v>
+        <v>177</v>
       </c>
       <c r="K37" s="239">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="L37" s="239">
-        <v>3500</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3311" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD8757C7-3111-4326-BB3A-D94B330F0C90}"/>
+  <xr:revisionPtr revIDLastSave="3319" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15BAE4B1-9525-44BD-BBF2-8273753356D0}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" firstSheet="9" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -23,15 +23,15 @@
     <sheet name="V2 Liquid Cooling BOM" sheetId="41" r:id="rId8"/>
     <sheet name="V2 Electronics BOM" sheetId="42" r:id="rId9"/>
     <sheet name="V2 Printed Parts" sheetId="45" r:id="rId10"/>
-    <sheet name="To Do" sheetId="34" r:id="rId11"/>
-    <sheet name="Macro &amp; system names " sheetId="44" r:id="rId12"/>
-    <sheet name="MISC" sheetId="30" r:id="rId13"/>
-    <sheet name="V2 new features" sheetId="46" r:id="rId14"/>
-    <sheet name="Comparison " sheetId="47" r:id="rId15"/>
-    <sheet name="Filament Material Guide" sheetId="48" r:id="rId16"/>
+    <sheet name="Macro &amp; system names " sheetId="44" r:id="rId11"/>
+    <sheet name="Filament Material Guide" sheetId="48" r:id="rId12"/>
+    <sheet name="V2 new features" sheetId="46" r:id="rId13"/>
+    <sheet name="Comparison " sheetId="47" r:id="rId14"/>
+    <sheet name="MISC" sheetId="30" r:id="rId15"/>
+    <sheet name="To Do" sheetId="34" r:id="rId16"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'Filament Material Guide'!$B$4:$L$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Filament Material Guide'!$B$4:$L$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PARTS LIST'!$A$1:$L$153</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'V2 Printed Parts'!$A$1:$H$92</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'PARTS LIST'!$1:$1</definedName>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="1100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1093">
   <si>
     <t>Type</t>
   </si>
@@ -2220,21 +2220,6 @@
   </si>
   <si>
     <t>M/R</t>
-  </si>
-  <si>
-    <t>Work out gland sealing for cpap tube, water pipes , cable loom</t>
-  </si>
-  <si>
-    <t>WIP, 2 options in folder</t>
-  </si>
-  <si>
-    <t>toolhead cable entrance</t>
-  </si>
-  <si>
-    <t>WIP/ needs testing / new idea in folder</t>
-  </si>
-  <si>
-    <t>need brain storming session</t>
   </si>
   <si>
     <t>workout a way to get esp32 programmed easierly</t>
@@ -3406,12 +3391,6 @@
       </rPr>
       <t> to reach the high HDT values listed. Without annealing, these parts will soften significantly at much lower temperatures.</t>
     </r>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>adapt the PSU 350 buddy to the LRS-350</t>
   </si>
   <si>
     <t>HDT</t>
@@ -6655,23 +6634,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>323850</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>2000250</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BCB3B98-4EEB-1065-FD61-D80A860759F4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20BCE7E6-B909-3563-C8D7-20BE8E8C050F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6687,8 +6666,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12906375" y="7239000"/>
-          <a:ext cx="438150" cy="228600"/>
+          <a:off x="8020050" y="438150"/>
+          <a:ext cx="1676400" cy="1371600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7440,23 +7419,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>323850</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>2000250</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{20BCE7E6-B909-3563-C8D7-20BE8E8C050F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7BCB3B98-4EEB-1065-FD61-D80A860759F4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -7472,8 +7451,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8020050" y="438150"/>
-          <a:ext cx="1676400" cy="1371600"/>
+          <a:off x="12906375" y="7239000"/>
+          <a:ext cx="438150" cy="228600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7510,7 +7489,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M152" totalsRowShown="0" dataDxfId="101" headerRowBorderDxfId="102" tableBorderDxfId="100" headerRowCellStyle="Normal 2">
-  <autoFilter ref="A1:M152" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <autoFilter ref="A1:M152" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Plumbing"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L152">
     <sortCondition ref="A1:A152"/>
   </sortState>
@@ -8052,7 +8037,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" hidden="1">
       <c r="A2" s="15" t="s">
         <v>13</v>
       </c>
@@ -8086,7 +8071,7 @@
       <c r="L2" s="68"/>
       <c r="M2" s="129"/>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" hidden="1">
       <c r="A3" s="15" t="s">
         <v>13</v>
       </c>
@@ -8120,7 +8105,7 @@
       <c r="L3" s="68"/>
       <c r="M3" s="129"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" hidden="1">
       <c r="A4" s="15" t="s">
         <v>13</v>
       </c>
@@ -8153,7 +8138,7 @@
       <c r="L4" s="70"/>
       <c r="M4" s="129"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" hidden="1">
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
@@ -8187,7 +8172,7 @@
       <c r="L5" s="68"/>
       <c r="M5" s="129"/>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" hidden="1">
       <c r="A6" s="15" t="s">
         <v>13</v>
       </c>
@@ -8221,7 +8206,7 @@
       <c r="L6" s="68"/>
       <c r="M6" s="129"/>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" hidden="1">
       <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
@@ -8255,7 +8240,7 @@
       <c r="L7" s="68"/>
       <c r="M7" s="129"/>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" hidden="1">
       <c r="A8" s="15" t="s">
         <v>13</v>
       </c>
@@ -8289,7 +8274,7 @@
       <c r="L8" s="68"/>
       <c r="M8" s="129"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" hidden="1">
       <c r="A9" s="15" t="s">
         <v>13</v>
       </c>
@@ -8323,7 +8308,7 @@
       <c r="L9" s="68"/>
       <c r="M9" s="129"/>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" hidden="1">
       <c r="A10" s="15" t="s">
         <v>13</v>
       </c>
@@ -8356,7 +8341,7 @@
       <c r="L10" s="70"/>
       <c r="M10" s="129"/>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" hidden="1">
       <c r="A11" s="31" t="s">
         <v>37</v>
       </c>
@@ -8390,7 +8375,7 @@
       <c r="L11" s="68"/>
       <c r="M11" s="129"/>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" hidden="1">
       <c r="A12" s="31" t="s">
         <v>37</v>
       </c>
@@ -8424,7 +8409,7 @@
       <c r="L12" s="68"/>
       <c r="M12" s="129"/>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" hidden="1">
       <c r="A13" s="31" t="s">
         <v>37</v>
       </c>
@@ -8458,7 +8443,7 @@
       <c r="L13" s="68"/>
       <c r="M13" s="129"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" hidden="1">
       <c r="A14" s="31" t="s">
         <v>37</v>
       </c>
@@ -8492,7 +8477,7 @@
       <c r="L14" s="68"/>
       <c r="M14" s="129"/>
     </row>
-    <row r="15" spans="1:13">
+    <row r="15" spans="1:13" hidden="1">
       <c r="A15" s="31" t="s">
         <v>37</v>
       </c>
@@ -8526,7 +8511,7 @@
       <c r="L15" s="68"/>
       <c r="M15" s="129"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" hidden="1">
       <c r="A16" s="31" t="s">
         <v>37</v>
       </c>
@@ -8560,7 +8545,7 @@
       <c r="L16" s="68"/>
       <c r="M16" s="129"/>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" hidden="1">
       <c r="A17" s="31" t="s">
         <v>37</v>
       </c>
@@ -8594,7 +8579,7 @@
       <c r="L17" s="68"/>
       <c r="M17" s="129"/>
     </row>
-    <row r="18" spans="1:13">
+    <row r="18" spans="1:13" hidden="1">
       <c r="A18" s="31" t="s">
         <v>37</v>
       </c>
@@ -8626,7 +8611,7 @@
       <c r="L18" s="68"/>
       <c r="M18" s="129"/>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" hidden="1">
       <c r="A19" s="31" t="s">
         <v>37</v>
       </c>
@@ -8660,7 +8645,7 @@
       <c r="L19" s="68"/>
       <c r="M19" s="129"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" hidden="1">
       <c r="A20" s="31" t="s">
         <v>37</v>
       </c>
@@ -8694,7 +8679,7 @@
       <c r="L20" s="68"/>
       <c r="M20" s="129"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" hidden="1">
       <c r="A21" s="31" t="s">
         <v>37</v>
       </c>
@@ -8728,7 +8713,7 @@
       <c r="L21" s="68"/>
       <c r="M21" s="129"/>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" hidden="1">
       <c r="A22" s="31" t="s">
         <v>37</v>
       </c>
@@ -8764,7 +8749,7 @@
       <c r="L22" s="68"/>
       <c r="M22" s="129"/>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" hidden="1">
       <c r="A23" s="31" t="s">
         <v>37</v>
       </c>
@@ -8797,7 +8782,7 @@
       <c r="L23" s="68"/>
       <c r="M23" s="129"/>
     </row>
-    <row r="24" spans="1:13">
+    <row r="24" spans="1:13" hidden="1">
       <c r="A24" s="31" t="s">
         <v>37</v>
       </c>
@@ -8830,7 +8815,7 @@
       <c r="L24" s="68"/>
       <c r="M24" s="129"/>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" hidden="1">
       <c r="A25" s="31" t="s">
         <v>37</v>
       </c>
@@ -8864,7 +8849,7 @@
       <c r="L25" s="68"/>
       <c r="M25" s="129"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" hidden="1">
       <c r="A26" s="31" t="s">
         <v>37</v>
       </c>
@@ -8898,7 +8883,7 @@
       <c r="L26" s="68"/>
       <c r="M26" s="129"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75" customHeight="1">
+    <row r="27" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A27" s="16" t="s">
         <v>37</v>
       </c>
@@ -8932,7 +8917,7 @@
       <c r="L27" s="68"/>
       <c r="M27" s="129"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75" customHeight="1">
+    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A28" s="16" t="s">
         <v>37</v>
       </c>
@@ -8966,7 +8951,7 @@
       <c r="L28" s="68"/>
       <c r="M28" s="129"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" customHeight="1">
+    <row r="29" spans="1:13" ht="16.5" hidden="1" customHeight="1">
       <c r="A29" s="31" t="s">
         <v>37</v>
       </c>
@@ -9000,7 +8985,7 @@
       <c r="L29" s="68"/>
       <c r="M29" s="129"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" customHeight="1">
+    <row r="30" spans="1:13" ht="16.5" hidden="1" customHeight="1">
       <c r="A30" s="31" t="s">
         <v>37</v>
       </c>
@@ -9034,7 +9019,7 @@
       <c r="L30" s="68"/>
       <c r="M30" s="129"/>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" hidden="1">
       <c r="A31" s="31" t="s">
         <v>37</v>
       </c>
@@ -9068,7 +9053,7 @@
       <c r="L31" s="68"/>
       <c r="M31" s="129"/>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" hidden="1">
       <c r="A32" s="31" t="s">
         <v>37</v>
       </c>
@@ -9102,7 +9087,7 @@
       <c r="L32" s="68"/>
       <c r="M32" s="129"/>
     </row>
-    <row r="33" spans="1:13">
+    <row r="33" spans="1:13" hidden="1">
       <c r="A33" s="31" t="s">
         <v>37</v>
       </c>
@@ -9136,7 +9121,7 @@
       <c r="L33" s="68"/>
       <c r="M33" s="129"/>
     </row>
-    <row r="34" spans="1:13">
+    <row r="34" spans="1:13" hidden="1">
       <c r="A34" s="31" t="s">
         <v>37</v>
       </c>
@@ -9170,7 +9155,7 @@
       <c r="L34" s="68"/>
       <c r="M34" s="129"/>
     </row>
-    <row r="35" spans="1:13">
+    <row r="35" spans="1:13" hidden="1">
       <c r="A35" s="31" t="s">
         <v>37</v>
       </c>
@@ -9204,7 +9189,7 @@
       <c r="L35" s="68"/>
       <c r="M35" s="129"/>
     </row>
-    <row r="36" spans="1:13">
+    <row r="36" spans="1:13" hidden="1">
       <c r="A36" s="31" t="s">
         <v>37</v>
       </c>
@@ -9238,7 +9223,7 @@
       <c r="L36" s="68"/>
       <c r="M36" s="129"/>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" hidden="1">
       <c r="A37" s="31" t="s">
         <v>37</v>
       </c>
@@ -9272,7 +9257,7 @@
       <c r="L37" s="68"/>
       <c r="M37" s="129"/>
     </row>
-    <row r="38" spans="1:13">
+    <row r="38" spans="1:13" hidden="1">
       <c r="A38" s="31" t="s">
         <v>37</v>
       </c>
@@ -9306,7 +9291,7 @@
       <c r="L38" s="68"/>
       <c r="M38" s="129"/>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:13" hidden="1">
       <c r="A39" s="31" t="s">
         <v>37</v>
       </c>
@@ -9340,7 +9325,7 @@
       <c r="L39" s="68"/>
       <c r="M39" s="129"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:13" hidden="1">
       <c r="A40" s="31" t="s">
         <v>37</v>
       </c>
@@ -9374,7 +9359,7 @@
       <c r="L40" s="68"/>
       <c r="M40" s="129"/>
     </row>
-    <row r="41" spans="1:13">
+    <row r="41" spans="1:13" hidden="1">
       <c r="A41" s="31" t="s">
         <v>37</v>
       </c>
@@ -9408,7 +9393,7 @@
       <c r="L41" s="68"/>
       <c r="M41" s="129"/>
     </row>
-    <row r="42" spans="1:13">
+    <row r="42" spans="1:13" hidden="1">
       <c r="A42" s="31" t="s">
         <v>37</v>
       </c>
@@ -9442,7 +9427,7 @@
       <c r="L42" s="68"/>
       <c r="M42" s="129"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:13" hidden="1">
       <c r="A43" s="31" t="s">
         <v>37</v>
       </c>
@@ -9476,7 +9461,7 @@
       <c r="L43" s="68"/>
       <c r="M43" s="129"/>
     </row>
-    <row r="44" spans="1:13">
+    <row r="44" spans="1:13" hidden="1">
       <c r="A44" s="31" t="s">
         <v>37</v>
       </c>
@@ -9510,7 +9495,7 @@
       <c r="L44" s="68"/>
       <c r="M44" s="129"/>
     </row>
-    <row r="45" spans="1:13">
+    <row r="45" spans="1:13" hidden="1">
       <c r="A45" s="31" t="s">
         <v>37</v>
       </c>
@@ -9544,7 +9529,7 @@
       <c r="L45" s="68"/>
       <c r="M45" s="129"/>
     </row>
-    <row r="46" spans="1:13" ht="15.75" customHeight="1">
+    <row r="46" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A46" s="31" t="s">
         <v>37</v>
       </c>
@@ -9578,7 +9563,7 @@
       <c r="L46" s="68"/>
       <c r="M46" s="129"/>
     </row>
-    <row r="47" spans="1:13" ht="15.75" customHeight="1">
+    <row r="47" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A47" s="31" t="s">
         <v>37</v>
       </c>
@@ -9612,7 +9597,7 @@
       <c r="L47" s="68"/>
       <c r="M47" s="129"/>
     </row>
-    <row r="48" spans="1:13" ht="15.75" customHeight="1">
+    <row r="48" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A48" s="31" t="s">
         <v>37</v>
       </c>
@@ -9646,7 +9631,7 @@
       <c r="L48" s="68"/>
       <c r="M48" s="129"/>
     </row>
-    <row r="49" spans="1:13" ht="15.75" customHeight="1">
+    <row r="49" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A49" s="31" t="s">
         <v>37</v>
       </c>
@@ -9680,7 +9665,7 @@
       <c r="L49" s="68"/>
       <c r="M49" s="129"/>
     </row>
-    <row r="50" spans="1:13">
+    <row r="50" spans="1:13" hidden="1">
       <c r="A50" s="31" t="s">
         <v>37</v>
       </c>
@@ -9714,7 +9699,7 @@
       <c r="L50" s="68"/>
       <c r="M50" s="129"/>
     </row>
-    <row r="51" spans="1:13">
+    <row r="51" spans="1:13" hidden="1">
       <c r="A51" s="31" t="s">
         <v>37</v>
       </c>
@@ -9744,7 +9729,7 @@
       <c r="L51" s="68"/>
       <c r="M51" s="129"/>
     </row>
-    <row r="52" spans="1:13">
+    <row r="52" spans="1:13" hidden="1">
       <c r="A52" s="31" t="s">
         <v>37</v>
       </c>
@@ -9774,7 +9759,7 @@
       <c r="L52" s="68"/>
       <c r="M52" s="129"/>
     </row>
-    <row r="53" spans="1:13">
+    <row r="53" spans="1:13" hidden="1">
       <c r="A53" s="31" t="s">
         <v>37</v>
       </c>
@@ -9808,7 +9793,7 @@
       <c r="L53" s="68"/>
       <c r="M53" s="129"/>
     </row>
-    <row r="54" spans="1:13">
+    <row r="54" spans="1:13" hidden="1">
       <c r="A54" s="31" t="s">
         <v>37</v>
       </c>
@@ -9842,7 +9827,7 @@
       <c r="L54" s="68"/>
       <c r="M54" s="129"/>
     </row>
-    <row r="55" spans="1:13">
+    <row r="55" spans="1:13" hidden="1">
       <c r="A55" s="31" t="s">
         <v>37</v>
       </c>
@@ -9876,7 +9861,7 @@
       <c r="L55" s="68"/>
       <c r="M55" s="129"/>
     </row>
-    <row r="56" spans="1:13">
+    <row r="56" spans="1:13" hidden="1">
       <c r="A56" s="31" t="s">
         <v>37</v>
       </c>
@@ -9910,7 +9895,7 @@
       <c r="L56" s="68"/>
       <c r="M56" s="129"/>
     </row>
-    <row r="57" spans="1:13">
+    <row r="57" spans="1:13" hidden="1">
       <c r="A57" s="16" t="s">
         <v>37</v>
       </c>
@@ -9944,7 +9929,7 @@
       <c r="L57" s="37"/>
       <c r="M57" s="129"/>
     </row>
-    <row r="58" spans="1:13">
+    <row r="58" spans="1:13" hidden="1">
       <c r="A58" s="31" t="s">
         <v>37</v>
       </c>
@@ -9978,7 +9963,7 @@
       <c r="L58" s="68"/>
       <c r="M58" s="129"/>
     </row>
-    <row r="59" spans="1:13">
+    <row r="59" spans="1:13" hidden="1">
       <c r="A59" s="31" t="s">
         <v>37</v>
       </c>
@@ -10010,7 +9995,7 @@
       <c r="L59" s="68"/>
       <c r="M59" s="129"/>
     </row>
-    <row r="60" spans="1:13">
+    <row r="60" spans="1:13" hidden="1">
       <c r="A60" s="31" t="s">
         <v>37</v>
       </c>
@@ -10044,7 +10029,7 @@
       <c r="L60" s="68"/>
       <c r="M60" s="129"/>
     </row>
-    <row r="61" spans="1:13" ht="17.25" customHeight="1">
+    <row r="61" spans="1:13" ht="17.25" hidden="1" customHeight="1">
       <c r="A61" s="31" t="s">
         <v>37</v>
       </c>
@@ -10080,7 +10065,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="17.25" customHeight="1">
+    <row r="62" spans="1:13" ht="17.25" hidden="1" customHeight="1">
       <c r="A62" s="31" t="s">
         <v>37</v>
       </c>
@@ -10112,7 +10097,7 @@
       <c r="L62" s="68"/>
       <c r="M62" s="129"/>
     </row>
-    <row r="63" spans="1:13" ht="15.75">
+    <row r="63" spans="1:13" ht="15.75" hidden="1">
       <c r="A63" s="31" t="s">
         <v>37</v>
       </c>
@@ -10140,7 +10125,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
+    <row r="64" spans="1:13" hidden="1">
       <c r="A64" s="31" t="s">
         <v>37</v>
       </c>
@@ -10174,7 +10159,7 @@
       <c r="L64" s="68"/>
       <c r="M64" s="129"/>
     </row>
-    <row r="65" spans="1:13">
+    <row r="65" spans="1:13" hidden="1">
       <c r="A65" s="31" t="s">
         <v>160</v>
       </c>
@@ -10207,7 +10192,7 @@
       <c r="L65" s="68"/>
       <c r="M65" s="129"/>
     </row>
-    <row r="66" spans="1:13">
+    <row r="66" spans="1:13" hidden="1">
       <c r="A66" s="31" t="s">
         <v>160</v>
       </c>
@@ -10240,7 +10225,7 @@
       <c r="L66" s="70"/>
       <c r="M66" s="129"/>
     </row>
-    <row r="67" spans="1:13">
+    <row r="67" spans="1:13" hidden="1">
       <c r="A67" s="15" t="s">
         <v>160</v>
       </c>
@@ -10273,7 +10258,7 @@
       <c r="L67" s="68"/>
       <c r="M67" s="129"/>
     </row>
-    <row r="68" spans="1:13">
+    <row r="68" spans="1:13" hidden="1">
       <c r="A68" s="15" t="s">
         <v>160</v>
       </c>
@@ -10311,7 +10296,7 @@
       </c>
       <c r="M68" s="129"/>
     </row>
-    <row r="69" spans="1:13">
+    <row r="69" spans="1:13" hidden="1">
       <c r="A69" s="15" t="s">
         <v>160</v>
       </c>
@@ -10349,7 +10334,7 @@
       </c>
       <c r="M69" s="129"/>
     </row>
-    <row r="70" spans="1:13">
+    <row r="70" spans="1:13" hidden="1">
       <c r="A70" s="15" t="s">
         <v>160</v>
       </c>
@@ -10385,7 +10370,7 @@
       <c r="L70" s="68"/>
       <c r="M70" s="129"/>
     </row>
-    <row r="71" spans="1:13">
+    <row r="71" spans="1:13" hidden="1">
       <c r="A71" s="31" t="s">
         <v>160</v>
       </c>
@@ -10420,7 +10405,7 @@
       <c r="L71" s="68"/>
       <c r="M71" s="129"/>
     </row>
-    <row r="72" spans="1:13">
+    <row r="72" spans="1:13" hidden="1">
       <c r="A72" s="31" t="s">
         <v>160</v>
       </c>
@@ -10456,7 +10441,7 @@
       <c r="L72" s="70"/>
       <c r="M72" s="129"/>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" hidden="1">
       <c r="A73" s="31" t="s">
         <v>160</v>
       </c>
@@ -10492,7 +10477,7 @@
       <c r="L73" s="68"/>
       <c r="M73" s="129"/>
     </row>
-    <row r="74" spans="1:13">
+    <row r="74" spans="1:13" hidden="1">
       <c r="A74" s="31" t="s">
         <v>160</v>
       </c>
@@ -10527,7 +10512,7 @@
       <c r="L74" s="68"/>
       <c r="M74" s="129"/>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" hidden="1">
       <c r="A75" s="31" t="s">
         <v>160</v>
       </c>
@@ -10563,7 +10548,7 @@
       <c r="L75" s="68"/>
       <c r="M75" s="129"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" hidden="1">
       <c r="A76" s="31" t="s">
         <v>160</v>
       </c>
@@ -10599,7 +10584,7 @@
       </c>
       <c r="M76" s="129"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" hidden="1">
       <c r="A77" s="15" t="s">
         <v>160</v>
       </c>
@@ -10635,7 +10620,7 @@
       <c r="L77" s="68"/>
       <c r="M77" s="129"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" hidden="1">
       <c r="A78" s="31" t="s">
         <v>160</v>
       </c>
@@ -10671,7 +10656,7 @@
       <c r="L78" s="68"/>
       <c r="M78" s="129"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" hidden="1">
       <c r="A79" s="15" t="s">
         <v>160</v>
       </c>
@@ -10707,7 +10692,7 @@
       <c r="L79" s="70"/>
       <c r="M79" s="129"/>
     </row>
-    <row r="80" spans="1:13">
+    <row r="80" spans="1:13" hidden="1">
       <c r="A80" s="15" t="s">
         <v>160</v>
       </c>
@@ -10741,7 +10726,7 @@
       <c r="L80" s="68"/>
       <c r="M80" s="129"/>
     </row>
-    <row r="81" spans="1:13">
+    <row r="81" spans="1:13" hidden="1">
       <c r="A81" s="15" t="s">
         <v>160</v>
       </c>
@@ -10777,7 +10762,7 @@
       <c r="L81" s="68"/>
       <c r="M81" s="129"/>
     </row>
-    <row r="82" spans="1:13">
+    <row r="82" spans="1:13" hidden="1">
       <c r="A82" s="15" t="s">
         <v>160</v>
       </c>
@@ -10811,7 +10796,7 @@
       <c r="L82" s="68"/>
       <c r="M82" s="129"/>
     </row>
-    <row r="83" spans="1:13" ht="15.75" customHeight="1">
+    <row r="83" spans="1:13" ht="15.75" hidden="1" customHeight="1">
       <c r="A83" s="15" t="s">
         <v>160</v>
       </c>
@@ -10849,7 +10834,7 @@
       </c>
       <c r="M83" s="129"/>
     </row>
-    <row r="84" spans="1:13">
+    <row r="84" spans="1:13" hidden="1">
       <c r="A84" s="31" t="s">
         <v>160</v>
       </c>
@@ -10884,7 +10869,7 @@
       <c r="L84" s="70"/>
       <c r="M84" s="129"/>
     </row>
-    <row r="85" spans="1:13">
+    <row r="85" spans="1:13" hidden="1">
       <c r="A85" s="31" t="s">
         <v>160</v>
       </c>
@@ -10922,7 +10907,7 @@
       </c>
       <c r="M85" s="129"/>
     </row>
-    <row r="86" spans="1:13">
+    <row r="86" spans="1:13" hidden="1">
       <c r="A86" s="31" t="s">
         <v>160</v>
       </c>
@@ -10957,7 +10942,7 @@
       <c r="L86" s="70"/>
       <c r="M86" s="129"/>
     </row>
-    <row r="87" spans="1:13">
+    <row r="87" spans="1:13" hidden="1">
       <c r="A87" s="15" t="s">
         <v>160</v>
       </c>
@@ -10991,7 +10976,7 @@
       <c r="L87" s="68"/>
       <c r="M87" s="129"/>
     </row>
-    <row r="88" spans="1:13">
+    <row r="88" spans="1:13" hidden="1">
       <c r="A88" s="31" t="s">
         <v>160</v>
       </c>
@@ -11027,7 +11012,7 @@
       <c r="L88" s="68"/>
       <c r="M88" s="129"/>
     </row>
-    <row r="89" spans="1:13">
+    <row r="89" spans="1:13" hidden="1">
       <c r="A89" s="15" t="s">
         <v>160</v>
       </c>
@@ -11061,7 +11046,7 @@
       <c r="L89" s="68"/>
       <c r="M89" s="129"/>
     </row>
-    <row r="90" spans="1:13">
+    <row r="90" spans="1:13" hidden="1">
       <c r="A90" s="31" t="s">
         <v>160</v>
       </c>
@@ -11098,7 +11083,7 @@
       </c>
       <c r="M90" s="129"/>
     </row>
-    <row r="91" spans="1:13">
+    <row r="91" spans="1:13" hidden="1">
       <c r="A91" s="31" t="s">
         <v>160</v>
       </c>
@@ -11134,7 +11119,7 @@
       <c r="L91" s="70"/>
       <c r="M91" s="129"/>
     </row>
-    <row r="92" spans="1:13">
+    <row r="92" spans="1:13" hidden="1">
       <c r="A92" s="31" t="s">
         <v>160</v>
       </c>
@@ -11170,7 +11155,7 @@
       <c r="L92" s="70"/>
       <c r="M92" s="129"/>
     </row>
-    <row r="93" spans="1:13">
+    <row r="93" spans="1:13" hidden="1">
       <c r="A93" s="31" t="s">
         <v>160</v>
       </c>
@@ -11208,7 +11193,7 @@
       </c>
       <c r="M93" s="129"/>
     </row>
-    <row r="94" spans="1:13">
+    <row r="94" spans="1:13" hidden="1">
       <c r="A94" s="31" t="s">
         <v>160</v>
       </c>
@@ -11241,7 +11226,7 @@
       <c r="L94" s="68"/>
       <c r="M94" s="129"/>
     </row>
-    <row r="95" spans="1:13">
+    <row r="95" spans="1:13" hidden="1">
       <c r="A95" s="31" t="s">
         <v>160</v>
       </c>
@@ -11277,7 +11262,7 @@
       <c r="L95" s="70"/>
       <c r="M95" s="129"/>
     </row>
-    <row r="96" spans="1:13">
+    <row r="96" spans="1:13" hidden="1">
       <c r="A96" s="31" t="s">
         <v>160</v>
       </c>
@@ -11314,7 +11299,7 @@
       </c>
       <c r="M96" s="129"/>
     </row>
-    <row r="97" spans="1:13">
+    <row r="97" spans="1:13" hidden="1">
       <c r="A97" s="31" t="s">
         <v>160</v>
       </c>
@@ -11350,7 +11335,7 @@
       <c r="L97" s="68"/>
       <c r="M97" s="129"/>
     </row>
-    <row r="98" spans="1:13">
+    <row r="98" spans="1:13" hidden="1">
       <c r="A98" s="31" t="s">
         <v>160</v>
       </c>
@@ -11386,7 +11371,7 @@
       </c>
       <c r="M98" s="129"/>
     </row>
-    <row r="99" spans="1:13">
+    <row r="99" spans="1:13" hidden="1">
       <c r="A99" s="31" t="s">
         <v>160</v>
       </c>
@@ -11422,7 +11407,7 @@
       </c>
       <c r="M99" s="129"/>
     </row>
-    <row r="100" spans="1:13">
+    <row r="100" spans="1:13" hidden="1">
       <c r="A100" s="31" t="s">
         <v>160</v>
       </c>
@@ -11460,7 +11445,7 @@
       </c>
       <c r="M100" s="129"/>
     </row>
-    <row r="101" spans="1:13">
+    <row r="101" spans="1:13" hidden="1">
       <c r="A101" s="31" t="s">
         <v>160</v>
       </c>
@@ -11496,7 +11481,7 @@
       </c>
       <c r="M101" s="129"/>
     </row>
-    <row r="102" spans="1:13">
+    <row r="102" spans="1:13" hidden="1">
       <c r="A102" s="31" t="s">
         <v>160</v>
       </c>
@@ -11532,7 +11517,7 @@
       <c r="L102" s="68"/>
       <c r="M102" s="129"/>
     </row>
-    <row r="103" spans="1:13" s="301" customFormat="1">
+    <row r="103" spans="1:13" s="301" customFormat="1" hidden="1">
       <c r="A103" s="293" t="s">
         <v>160</v>
       </c>
@@ -11570,7 +11555,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="104" spans="1:13" s="301" customFormat="1">
+    <row r="104" spans="1:13" s="301" customFormat="1" hidden="1">
       <c r="A104" s="293" t="s">
         <v>160</v>
       </c>
@@ -11608,7 +11593,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="105" spans="1:13">
+    <row r="105" spans="1:13" hidden="1">
       <c r="A105" s="15" t="s">
         <v>160</v>
       </c>
@@ -11644,7 +11629,7 @@
       </c>
       <c r="M105" s="129"/>
     </row>
-    <row r="106" spans="1:13">
+    <row r="106" spans="1:13" hidden="1">
       <c r="A106" s="15" t="s">
         <v>246</v>
       </c>
@@ -11678,7 +11663,7 @@
       <c r="L106" s="68"/>
       <c r="M106" s="129"/>
     </row>
-    <row r="107" spans="1:13">
+    <row r="107" spans="1:13" hidden="1">
       <c r="A107" s="15" t="s">
         <v>246</v>
       </c>
@@ -11710,7 +11695,7 @@
       <c r="L107" s="68"/>
       <c r="M107" s="129"/>
     </row>
-    <row r="108" spans="1:13">
+    <row r="108" spans="1:13" hidden="1">
       <c r="A108" s="135" t="s">
         <v>246</v>
       </c>
@@ -11744,7 +11729,7 @@
       <c r="L108" s="137"/>
       <c r="M108" s="138"/>
     </row>
-    <row r="109" spans="1:13">
+    <row r="109" spans="1:13" hidden="1">
       <c r="A109" s="15" t="s">
         <v>246</v>
       </c>
@@ -11778,7 +11763,7 @@
       <c r="L109" s="68"/>
       <c r="M109" s="129"/>
     </row>
-    <row r="110" spans="1:13">
+    <row r="110" spans="1:13" hidden="1">
       <c r="A110" s="15" t="s">
         <v>246</v>
       </c>
@@ -11812,7 +11797,7 @@
       <c r="L110" s="68"/>
       <c r="M110" s="129"/>
     </row>
-    <row r="111" spans="1:13">
+    <row r="111" spans="1:13" hidden="1">
       <c r="A111" s="15" t="s">
         <v>258</v>
       </c>
@@ -11846,7 +11831,7 @@
       <c r="L111" s="68"/>
       <c r="M111" s="129"/>
     </row>
-    <row r="112" spans="1:13" ht="15.75" thickBot="1">
+    <row r="112" spans="1:13" hidden="1">
       <c r="A112" s="15" t="s">
         <v>258</v>
       </c>
@@ -11880,7 +11865,7 @@
       <c r="L112" s="68"/>
       <c r="M112" s="129"/>
     </row>
-    <row r="113" spans="1:13" ht="15.75" thickBot="1">
+    <row r="113" spans="1:13" hidden="1">
       <c r="A113" s="15" t="s">
         <v>258</v>
       </c>
@@ -11913,7 +11898,7 @@
       <c r="L113" s="68"/>
       <c r="M113" s="129"/>
     </row>
-    <row r="114" spans="1:13" ht="15.75" thickBot="1">
+    <row r="114" spans="1:13" hidden="1">
       <c r="A114" s="15" t="s">
         <v>258</v>
       </c>
@@ -11946,7 +11931,7 @@
       <c r="L114" s="68"/>
       <c r="M114" s="129"/>
     </row>
-    <row r="115" spans="1:13" ht="15.75" thickBot="1">
+    <row r="115" spans="1:13">
       <c r="A115" s="31" t="s">
         <v>271</v>
       </c>
@@ -11980,7 +11965,7 @@
       <c r="L115" s="68"/>
       <c r="M115" s="129"/>
     </row>
-    <row r="116" spans="1:13" ht="15.75" thickBot="1">
+    <row r="116" spans="1:13">
       <c r="A116" s="31" t="s">
         <v>271</v>
       </c>
@@ -12014,7 +11999,7 @@
       <c r="L116" s="68"/>
       <c r="M116" s="129"/>
     </row>
-    <row r="117" spans="1:13" ht="15.75" thickBot="1">
+    <row r="117" spans="1:13">
       <c r="A117" s="31" t="s">
         <v>271</v>
       </c>
@@ -12048,7 +12033,7 @@
       <c r="L117" s="68"/>
       <c r="M117" s="129"/>
     </row>
-    <row r="118" spans="1:13" ht="15.75" thickBot="1">
+    <row r="118" spans="1:13">
       <c r="A118" s="15" t="s">
         <v>271</v>
       </c>
@@ -12082,7 +12067,7 @@
       <c r="L118" s="68"/>
       <c r="M118" s="129"/>
     </row>
-    <row r="119" spans="1:13" ht="15.75" thickBot="1">
+    <row r="119" spans="1:13">
       <c r="A119" s="15" t="s">
         <v>271</v>
       </c>
@@ -12116,7 +12101,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="15.75" thickBot="1">
+    <row r="120" spans="1:13">
       <c r="A120" s="31" t="s">
         <v>271</v>
       </c>
@@ -12150,7 +12135,7 @@
       <c r="L120" s="68"/>
       <c r="M120" s="129"/>
     </row>
-    <row r="121" spans="1:13" ht="15.75" thickBot="1">
+    <row r="121" spans="1:13">
       <c r="A121" s="31" t="s">
         <v>271</v>
       </c>
@@ -12218,7 +12203,7 @@
       <c r="L122" s="68"/>
       <c r="M122" s="129"/>
     </row>
-    <row r="123" spans="1:13" ht="15.75" thickBot="1">
+    <row r="123" spans="1:13" ht="15.75" hidden="1" thickBot="1">
       <c r="A123" s="31" t="s">
         <v>295</v>
       </c>
@@ -12254,7 +12239,7 @@
       <c r="L123" s="68"/>
       <c r="M123" s="129"/>
     </row>
-    <row r="124" spans="1:13" ht="15.75" thickBot="1">
+    <row r="124" spans="1:13" ht="15.75" hidden="1" thickBot="1">
       <c r="A124" s="31" t="s">
         <v>295</v>
       </c>
@@ -12290,7 +12275,7 @@
       <c r="L124" s="68"/>
       <c r="M124" s="129"/>
     </row>
-    <row r="125" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="125" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A125" s="15" t="s">
         <v>295</v>
       </c>
@@ -12326,7 +12311,7 @@
       <c r="L125" s="68"/>
       <c r="M125" s="130"/>
     </row>
-    <row r="126" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="126" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A126" s="31" t="s">
         <v>295</v>
       </c>
@@ -12360,7 +12345,7 @@
       <c r="L126" s="68"/>
       <c r="M126" s="130"/>
     </row>
-    <row r="127" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="127" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A127" s="15" t="s">
         <v>295</v>
       </c>
@@ -12396,7 +12381,7 @@
       <c r="L127" s="68"/>
       <c r="M127" s="130"/>
     </row>
-    <row r="128" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="128" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A128" s="15" t="s">
         <v>295</v>
       </c>
@@ -12432,7 +12417,7 @@
       <c r="L128" s="68"/>
       <c r="M128" s="130"/>
     </row>
-    <row r="129" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="129" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A129" s="15" t="s">
         <v>295</v>
       </c>
@@ -12468,7 +12453,7 @@
       <c r="L129" s="68"/>
       <c r="M129" s="130"/>
     </row>
-    <row r="130" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="130" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A130" s="15" t="s">
         <v>295</v>
       </c>
@@ -12504,7 +12489,7 @@
       <c r="L130" s="68"/>
       <c r="M130" s="130"/>
     </row>
-    <row r="131" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="131" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A131" s="15" t="s">
         <v>295</v>
       </c>
@@ -12540,7 +12525,7 @@
       <c r="L131" s="68"/>
       <c r="M131" s="130"/>
     </row>
-    <row r="132" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="132" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A132" s="15" t="s">
         <v>295</v>
       </c>
@@ -12576,7 +12561,7 @@
       <c r="L132" s="68"/>
       <c r="M132" s="130"/>
     </row>
-    <row r="133" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="133" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A133" s="31" t="s">
         <v>295</v>
       </c>
@@ -12610,7 +12595,7 @@
       <c r="L133" s="68"/>
       <c r="M133" s="130"/>
     </row>
-    <row r="134" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="134" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A134" s="15" t="s">
         <v>295</v>
       </c>
@@ -12646,7 +12631,7 @@
       <c r="L134" s="68"/>
       <c r="M134" s="130"/>
     </row>
-    <row r="135" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="135" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A135" s="15" t="s">
         <v>295</v>
       </c>
@@ -12682,7 +12667,7 @@
       <c r="L135" s="68"/>
       <c r="M135" s="130"/>
     </row>
-    <row r="136" spans="1:13" s="12" customFormat="1" ht="15.75">
+    <row r="136" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A136" s="15" t="s">
         <v>329</v>
       </c>
@@ -12718,7 +12703,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="137" spans="1:13" s="12" customFormat="1" ht="15.75">
+    <row r="137" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A137" s="15" t="s">
         <v>329</v>
       </c>
@@ -12752,7 +12737,7 @@
       <c r="L137" s="70"/>
       <c r="M137" s="290"/>
     </row>
-    <row r="138" spans="1:13" s="12" customFormat="1" ht="15.75">
+    <row r="138" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A138" s="31" t="s">
         <v>329</v>
       </c>
@@ -12786,7 +12771,7 @@
       <c r="L138" s="70"/>
       <c r="M138" s="130"/>
     </row>
-    <row r="139" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="139" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A139" s="15" t="s">
         <v>329</v>
       </c>
@@ -12820,7 +12805,7 @@
       <c r="L139" s="70"/>
       <c r="M139" s="130"/>
     </row>
-    <row r="140" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="140" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A140" s="15" t="s">
         <v>329</v>
       </c>
@@ -12854,7 +12839,7 @@
       <c r="L140" s="70"/>
       <c r="M140" s="130"/>
     </row>
-    <row r="141" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="141" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A141" s="15" t="s">
         <v>329</v>
       </c>
@@ -12888,7 +12873,7 @@
       <c r="L141" s="70"/>
       <c r="M141" s="130"/>
     </row>
-    <row r="142" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="142" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A142" s="15" t="s">
         <v>329</v>
       </c>
@@ -12924,7 +12909,7 @@
       <c r="L142" s="70"/>
       <c r="M142" s="130"/>
     </row>
-    <row r="143" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="143" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A143" s="15" t="s">
         <v>347</v>
       </c>
@@ -12958,7 +12943,7 @@
       <c r="L143" s="68"/>
       <c r="M143" s="130"/>
     </row>
-    <row r="144" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="144" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A144" s="15" t="s">
         <v>351</v>
       </c>
@@ -12992,7 +12977,7 @@
       <c r="L144" s="68"/>
       <c r="M144" s="130"/>
     </row>
-    <row r="145" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="145" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A145" s="15" t="s">
         <v>351</v>
       </c>
@@ -13024,7 +13009,7 @@
       <c r="L145" s="68"/>
       <c r="M145" s="130"/>
     </row>
-    <row r="146" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="146" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A146" s="15" t="s">
         <v>351</v>
       </c>
@@ -13058,7 +13043,7 @@
       <c r="L146" s="68"/>
       <c r="M146" s="130"/>
     </row>
-    <row r="147" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="147" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A147" s="15" t="s">
         <v>351</v>
       </c>
@@ -13092,7 +13077,7 @@
       <c r="L147" s="68"/>
       <c r="M147" s="130"/>
     </row>
-    <row r="148" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="148" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A148" s="15" t="s">
         <v>351</v>
       </c>
@@ -13126,7 +13111,7 @@
       <c r="L148" s="68"/>
       <c r="M148" s="130"/>
     </row>
-    <row r="149" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="149" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A149" s="15" t="s">
         <v>351</v>
       </c>
@@ -13160,7 +13145,7 @@
       <c r="L149" s="68"/>
       <c r="M149" s="130"/>
     </row>
-    <row r="150" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="150" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A150" s="15" t="s">
         <v>351</v>
       </c>
@@ -13194,7 +13179,7 @@
       <c r="L150" s="68"/>
       <c r="M150" s="130"/>
     </row>
-    <row r="151" spans="1:13" s="12" customFormat="1" ht="16.5" thickBot="1">
+    <row r="151" spans="1:13" s="12" customFormat="1" ht="16.5" hidden="1" thickBot="1">
       <c r="A151" s="15" t="s">
         <v>351</v>
       </c>
@@ -13228,7 +13213,7 @@
       <c r="L151" s="68"/>
       <c r="M151" s="130"/>
     </row>
-    <row r="152" spans="1:13" ht="15.75" thickBot="1">
+    <row r="152" spans="1:13" ht="15.75" hidden="1" thickBot="1">
       <c r="A152" s="189" t="s">
         <v>351</v>
       </c>
@@ -13273,7 +13258,7 @@
       <c r="F153" s="34"/>
       <c r="G153" s="35">
         <f>SUBTOTAL(109,Table1321[*Cost Price $USD])</f>
-        <v>2381.4700000000007</v>
+        <v>157.46</v>
       </c>
       <c r="H153" s="196" t="s">
         <v>376</v>
@@ -15638,154 +15623,6 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EDA9B0-1F64-43EA-B8A8-B58E6C73D378}">
-  <sheetPr>
-    <tabColor rgb="FFFF0000"/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="83.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="46.140625" customWidth="1"/>
-    <col min="4" max="4" width="70.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15.75">
-      <c r="A1" s="5" t="s">
-        <v>701</v>
-      </c>
-      <c r="B1" t="s">
-        <v>702</v>
-      </c>
-      <c r="C1" t="s">
-        <v>703</v>
-      </c>
-      <c r="D1" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="20.25" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="B2" t="s">
-        <v>706</v>
-      </c>
-      <c r="C2" s="124" t="s">
-        <v>707</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" customHeight="1">
-      <c r="A3" t="s">
-        <v>709</v>
-      </c>
-      <c r="B3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C3" s="306" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="6" t="s">
-        <v>712</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>713</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="D4" s="307" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>716</v>
-      </c>
-      <c r="C5" s="125" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="B6" t="s">
-        <v>719</v>
-      </c>
-      <c r="C6" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>720</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>713</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>722</v>
-      </c>
-      <c r="C8" s="123" t="s">
-        <v>723</v>
-      </c>
-      <c r="D8" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>725</v>
-      </c>
-      <c r="B9" t="s">
-        <v>726</v>
-      </c>
-      <c r="C9" s="123" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>728</v>
-      </c>
-      <c r="B10" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>1097</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" xr:uid="{36F730E6-D2FB-4DE8-A8CA-115837D74B28}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F4FD623-0653-4148-A217-057459B36D84}">
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
@@ -15801,140 +15638,140 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B1" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="C1" t="s">
         <v>378</v>
       </c>
       <c r="D1" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="C4" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C5" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12" customHeight="1">
       <c r="A6" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="C6" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="C7" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="B8" s="203" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="C8" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C9" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="C10" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="C11" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="251" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C12" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -15942,7 +15779,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="B14" s="93" t="s">
         <v>661</v>
@@ -15956,151 +15793,151 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="C15" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="38" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="B17" s="38" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="C17" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="38" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="C18" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" s="38" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="C19" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="38" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="C20" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="38" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="C21" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="D21" s="250" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="C22" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="D22" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="38" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="C23" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="38" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C24" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="38" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="C25" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C26" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="D26" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="C27" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="B28" s="38" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="C28" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="38" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="C29" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="B30" s="38" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="C30" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -16111,10 +15948,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C33" t="s">
         <v>378</v>
@@ -16122,68 +15959,68 @@
     </row>
     <row r="34" spans="1:4">
       <c r="B34" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="C34" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="B35" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="C35" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="C36" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="B37" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="C37" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="B39" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="C39" t="s">
+        <v>805</v>
+      </c>
+      <c r="D39" t="s">
         <v>810</v>
-      </c>
-      <c r="D39" t="s">
-        <v>815</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="D40" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="B41" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="B42" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="B44" s="60" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="C44" t="s">
         <v>378</v>
@@ -16191,82 +16028,82 @@
     </row>
     <row r="45" spans="1:4">
       <c r="B45" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="C45" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="B46" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="C46" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="B47" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="C47" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="B48" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="C48" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="B49" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="C49" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="B50" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="C50" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="B51" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="C51" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="B52" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="C52" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="C53" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
     <row r="54" spans="2:3">
       <c r="B54" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="C54" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
     </row>
   </sheetData>
@@ -16280,1160 +16117,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617F1214-FEDF-4959-B6B1-8C60CA48A0FC}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="51.42578125" customWidth="1"/>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="3" max="3" width="32.85546875" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" customWidth="1"/>
-    <col min="5" max="5" width="71.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
-        <v>833</v>
-      </c>
-      <c r="B2" t="s">
-        <v>834</v>
-      </c>
-      <c r="C2" t="s">
-        <v>835</v>
-      </c>
-      <c r="D2" t="s">
-        <v>836</v>
-      </c>
-      <c r="E2" s="109" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
-        <v>838</v>
-      </c>
-      <c r="C3" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A6" t="s">
-        <v>842</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="14.25" customHeight="1">
-      <c r="A10" s="4" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>849</v>
-      </c>
-      <c r="C12" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>851</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13" t="s">
-        <v>852</v>
-      </c>
-      <c r="E13" s="134" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="305" t="s">
-        <v>854</v>
-      </c>
-      <c r="E14" s="134" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>856</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>858</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>859</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="E13" r:id="rId1" xr:uid="{3BD14087-096D-4B95-8D2A-BB6B2E6ECB04}"/>
-    <hyperlink ref="E14" r:id="rId2" xr:uid="{9746E316-C540-456C-8DB2-33AE97228441}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35C039F-5462-40EB-AF1D-F8681FB2D0C5}">
-  <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="92" style="204" bestFit="1" customWidth="1"/>
-    <col min="2" max="16384" width="9.140625" style="204"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="205" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="205"/>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="206" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="207" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="205" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="205" t="s">
-        <v>864</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="205" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="205" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="205"/>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="206" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="207" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="205" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="205"/>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="206" t="s">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="205" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="205" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="205" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="205" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="205" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="205" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="205"/>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="206" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="205" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="205" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="205" t="s">
-        <v>880</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B154CA9-6DBE-440D-B5D1-A4C053DC51C7}">
-  <dimension ref="A1:H37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="29.140625" style="204" customWidth="1"/>
-    <col min="2" max="2" width="35.7109375" style="210" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.85546875" style="210" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" style="210" customWidth="1"/>
-    <col min="5" max="5" width="35.28515625" style="210" customWidth="1"/>
-    <col min="6" max="6" width="32" style="210" customWidth="1"/>
-    <col min="7" max="7" width="30.85546875" style="209" customWidth="1"/>
-    <col min="8" max="8" width="56.85546875" style="208" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="204"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="204" t="s">
-        <v>881</v>
-      </c>
-      <c r="B1" s="210" t="s">
-        <v>882</v>
-      </c>
-      <c r="C1" s="210" t="s">
-        <v>883</v>
-      </c>
-      <c r="D1" s="210" t="s">
-        <v>884</v>
-      </c>
-      <c r="E1" s="210" t="s">
-        <v>885</v>
-      </c>
-      <c r="F1" s="210" t="s">
-        <v>886</v>
-      </c>
-      <c r="G1" s="209" t="s">
-        <v>887</v>
-      </c>
-      <c r="H1" s="208" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="204" t="s">
-        <v>889</v>
-      </c>
-      <c r="B2" s="210">
-        <v>1</v>
-      </c>
-      <c r="C2" s="210">
-        <v>1</v>
-      </c>
-      <c r="D2" s="210">
-        <v>1</v>
-      </c>
-      <c r="E2" s="210">
-        <v>1</v>
-      </c>
-      <c r="F2" s="210">
-        <v>1</v>
-      </c>
-      <c r="G2" s="209" t="s">
-        <v>890</v>
-      </c>
-      <c r="H2" s="208">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="204" t="s">
-        <v>891</v>
-      </c>
-      <c r="B3" s="210" t="s">
-        <v>892</v>
-      </c>
-      <c r="C3" s="210" t="s">
-        <v>893</v>
-      </c>
-      <c r="D3" s="219" t="s">
-        <v>892</v>
-      </c>
-      <c r="E3" s="219" t="s">
-        <v>892</v>
-      </c>
-      <c r="F3" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="208" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="204" t="s">
-        <v>894</v>
-      </c>
-      <c r="B4" s="210">
-        <v>450</v>
-      </c>
-      <c r="C4" s="210">
-        <v>450</v>
-      </c>
-      <c r="D4" s="210" t="s">
-        <v>895</v>
-      </c>
-      <c r="E4" s="210">
-        <v>285</v>
-      </c>
-      <c r="F4" s="210">
-        <v>285</v>
-      </c>
-      <c r="G4" s="209">
-        <v>300</v>
-      </c>
-      <c r="H4" s="208" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="204" t="s">
-        <v>897</v>
-      </c>
-      <c r="B5" s="210" t="s">
-        <v>898</v>
-      </c>
-      <c r="C5" s="210" t="s">
-        <v>899</v>
-      </c>
-      <c r="D5" s="210">
-        <v>150</v>
-      </c>
-      <c r="E5" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" s="210">
-        <v>157</v>
-      </c>
-      <c r="G5" s="209">
-        <v>120</v>
-      </c>
-      <c r="H5" s="208" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="204" t="s">
-        <v>901</v>
-      </c>
-      <c r="B6" s="210">
-        <v>80</v>
-      </c>
-      <c r="C6" s="210">
-        <v>100</v>
-      </c>
-      <c r="D6" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="E6" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="G6" s="209">
-        <v>60</v>
-      </c>
-      <c r="H6" s="208" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="204" t="s">
-        <v>903</v>
-      </c>
-      <c r="B7" s="210" t="s">
-        <v>904</v>
-      </c>
-      <c r="C7" s="210" t="s">
-        <v>905</v>
-      </c>
-      <c r="D7" s="210" t="s">
-        <v>906</v>
-      </c>
-      <c r="E7" s="210" t="s">
-        <v>907</v>
-      </c>
-      <c r="F7" s="210" t="s">
-        <v>908</v>
-      </c>
-      <c r="G7" s="209" t="s">
-        <v>909</v>
-      </c>
-      <c r="H7" s="208" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="204" t="s">
-        <v>911</v>
-      </c>
-      <c r="B8" s="210" t="s">
-        <v>912</v>
-      </c>
-      <c r="C8" s="210" t="s">
-        <v>912</v>
-      </c>
-      <c r="D8" s="210" t="s">
-        <v>913</v>
-      </c>
-      <c r="E8" s="210" t="s">
-        <v>912</v>
-      </c>
-      <c r="F8" s="210" t="s">
-        <v>912</v>
-      </c>
-      <c r="G8" s="209" t="s">
-        <v>914</v>
-      </c>
-      <c r="H8" s="208" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="204" t="s">
-        <v>916</v>
-      </c>
-      <c r="B9" s="210" t="s">
-        <v>917</v>
-      </c>
-      <c r="C9" s="210" t="s">
-        <v>917</v>
-      </c>
-      <c r="D9" s="210" t="s">
-        <v>918</v>
-      </c>
-      <c r="E9" s="210" t="s">
-        <v>919</v>
-      </c>
-      <c r="F9" s="210" t="s">
-        <v>920</v>
-      </c>
-      <c r="H9" s="208" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="204" t="s">
-        <v>922</v>
-      </c>
-      <c r="B10" s="215" t="s">
-        <v>923</v>
-      </c>
-      <c r="C10" s="215" t="s">
-        <v>924</v>
-      </c>
-      <c r="D10" s="215" t="s">
-        <v>925</v>
-      </c>
-      <c r="E10" s="215" t="s">
-        <v>926</v>
-      </c>
-      <c r="F10" s="218" t="s">
-        <v>927</v>
-      </c>
-      <c r="G10" s="217" t="s">
-        <v>928</v>
-      </c>
-      <c r="H10" s="208" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="204" t="s">
-        <v>930</v>
-      </c>
-      <c r="B11" s="210" t="s">
-        <v>931</v>
-      </c>
-      <c r="C11" s="210" t="s">
-        <v>931</v>
-      </c>
-      <c r="D11" s="210" t="s">
-        <v>932</v>
-      </c>
-      <c r="E11" s="210" t="s">
-        <v>933</v>
-      </c>
-      <c r="F11" s="210" t="s">
-        <v>934</v>
-      </c>
-      <c r="G11" s="209" t="s">
-        <v>914</v>
-      </c>
-      <c r="H11" s="208" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A12" s="216" t="s">
-        <v>935</v>
-      </c>
-      <c r="B12" s="215" t="s">
-        <v>936</v>
-      </c>
-      <c r="C12" s="215" t="s">
-        <v>937</v>
-      </c>
-      <c r="D12" s="214" t="s">
-        <v>938</v>
-      </c>
-      <c r="E12" s="215" t="s">
-        <v>939</v>
-      </c>
-      <c r="F12" s="214" t="s">
-        <v>940</v>
-      </c>
-      <c r="H12" s="208" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="204" t="s">
-        <v>942</v>
-      </c>
-      <c r="B13" s="210" t="s">
-        <v>943</v>
-      </c>
-      <c r="C13" s="210" t="s">
-        <v>943</v>
-      </c>
-      <c r="D13" s="210">
-        <v>120</v>
-      </c>
-      <c r="E13" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="F13" s="210" t="s">
-        <v>944</v>
-      </c>
-      <c r="G13" s="209" t="s">
-        <v>945</v>
-      </c>
-      <c r="H13" s="208" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="204" t="s">
-        <v>946</v>
-      </c>
-      <c r="B14" s="210" t="s">
-        <v>947</v>
-      </c>
-      <c r="C14" s="210" t="s">
-        <v>947</v>
-      </c>
-      <c r="D14" s="210" t="s">
-        <v>948</v>
-      </c>
-      <c r="E14" s="210" t="s">
-        <v>949</v>
-      </c>
-      <c r="F14" s="210" t="s">
-        <v>950</v>
-      </c>
-      <c r="G14" s="209" t="s">
-        <v>951</v>
-      </c>
-      <c r="H14" s="208" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="213" t="s">
-        <v>953</v>
-      </c>
-      <c r="B15" s="210" t="s">
-        <v>912</v>
-      </c>
-      <c r="C15" s="210" t="s">
-        <v>912</v>
-      </c>
-      <c r="H15" s="208" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="204" t="s">
-        <v>954</v>
-      </c>
-      <c r="B16" s="210" t="s">
-        <v>955</v>
-      </c>
-      <c r="C16" s="210" t="s">
-        <v>956</v>
-      </c>
-      <c r="D16" s="210" t="s">
-        <v>957</v>
-      </c>
-      <c r="E16" s="210" t="s">
-        <v>958</v>
-      </c>
-      <c r="F16" s="210" t="s">
-        <v>958</v>
-      </c>
-      <c r="H16" s="208" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="204" t="s">
-        <v>960</v>
-      </c>
-      <c r="B17" s="210" t="s">
-        <v>961</v>
-      </c>
-      <c r="C17" s="210" t="s">
-        <v>962</v>
-      </c>
-      <c r="D17" s="210" t="s">
-        <v>963</v>
-      </c>
-      <c r="E17" s="210" t="s">
-        <v>958</v>
-      </c>
-      <c r="F17" s="210" t="s">
-        <v>958</v>
-      </c>
-      <c r="H17" s="208" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="204" t="s">
-        <v>964</v>
-      </c>
-      <c r="B18" s="210" t="s">
-        <v>965</v>
-      </c>
-      <c r="C18" s="210" t="s">
-        <v>966</v>
-      </c>
-      <c r="D18" s="210" t="s">
-        <v>967</v>
-      </c>
-      <c r="E18" s="210" t="s">
-        <v>968</v>
-      </c>
-      <c r="F18" s="210" t="s">
-        <v>969</v>
-      </c>
-      <c r="H18" s="208" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="204" t="s">
-        <v>971</v>
-      </c>
-      <c r="B19" s="210" t="s">
-        <v>972</v>
-      </c>
-      <c r="C19" s="210" t="s">
-        <v>972</v>
-      </c>
-      <c r="D19" s="210" t="s">
-        <v>973</v>
-      </c>
-      <c r="E19" s="210" t="s">
-        <v>974</v>
-      </c>
-      <c r="F19" s="210" t="s">
-        <v>975</v>
-      </c>
-      <c r="G19" s="209" t="s">
-        <v>973</v>
-      </c>
-      <c r="H19" s="209" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="213" t="s">
-        <v>976</v>
-      </c>
-      <c r="B20" s="208" t="s">
-        <v>977</v>
-      </c>
-      <c r="C20" s="208" t="s">
-        <v>978</v>
-      </c>
-      <c r="G20" s="209" t="s">
-        <v>979</v>
-      </c>
-      <c r="H20" s="208" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" s="204" t="s">
-        <v>981</v>
-      </c>
-      <c r="B21" s="210" t="s">
-        <v>982</v>
-      </c>
-      <c r="C21" s="210" t="s">
-        <v>982</v>
-      </c>
-      <c r="D21" s="210" t="s">
-        <v>983</v>
-      </c>
-      <c r="E21" s="210" t="s">
-        <v>983</v>
-      </c>
-      <c r="G21" s="212" t="s">
-        <v>984</v>
-      </c>
-      <c r="H21" s="208" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="204" t="s">
-        <v>986</v>
-      </c>
-      <c r="B22" s="210" t="s">
-        <v>987</v>
-      </c>
-      <c r="C22" s="210" t="s">
-        <v>988</v>
-      </c>
-      <c r="D22" s="210" t="s">
-        <v>983</v>
-      </c>
-      <c r="E22" s="210" t="s">
-        <v>983</v>
-      </c>
-      <c r="F22" s="210" t="s">
-        <v>983</v>
-      </c>
-      <c r="G22" s="209" t="s">
-        <v>989</v>
-      </c>
-      <c r="H22" s="208" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="204" t="s">
-        <v>991</v>
-      </c>
-      <c r="B23" s="210" t="s">
-        <v>982</v>
-      </c>
-      <c r="C23" s="210" t="s">
-        <v>982</v>
-      </c>
-      <c r="D23" s="210" t="s">
-        <v>983</v>
-      </c>
-      <c r="E23" s="210" t="s">
-        <v>983</v>
-      </c>
-      <c r="F23" s="210" t="s">
-        <v>983</v>
-      </c>
-      <c r="G23" s="209" t="s">
-        <v>992</v>
-      </c>
-      <c r="H23" s="208" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="204" t="s">
-        <v>993</v>
-      </c>
-      <c r="B24" s="210" t="s">
-        <v>982</v>
-      </c>
-      <c r="C24" s="210" t="s">
-        <v>982</v>
-      </c>
-      <c r="D24" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="E24" s="210" t="s">
-        <v>912</v>
-      </c>
-      <c r="H24" s="208" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="204" t="s">
-        <v>994</v>
-      </c>
-      <c r="B25" s="210">
-        <v>0.05</v>
-      </c>
-      <c r="C25" s="210">
-        <v>0.05</v>
-      </c>
-      <c r="D25" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="E25" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="G25" s="209">
-        <v>0.05</v>
-      </c>
-      <c r="H25" s="208">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" s="204" t="s">
-        <v>995</v>
-      </c>
-      <c r="B26" s="210" t="s">
-        <v>982</v>
-      </c>
-      <c r="C26" s="210" t="s">
-        <v>996</v>
-      </c>
-      <c r="D26" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="E26" s="210" t="s">
-        <v>997</v>
-      </c>
-      <c r="G26" s="209" t="s">
-        <v>998</v>
-      </c>
-      <c r="H26" s="208" t="s">
-        <v>912</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" s="204" t="s">
-        <v>999</v>
-      </c>
-      <c r="B27" s="210" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C27" s="210" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D27" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="E27" s="210" t="s">
-        <v>1001</v>
-      </c>
-      <c r="H27" s="210" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28" s="204" t="s">
-        <v>1002</v>
-      </c>
-      <c r="B28" s="210" t="s">
-        <v>1003</v>
-      </c>
-      <c r="C28" s="210" t="s">
-        <v>1003</v>
-      </c>
-      <c r="D28" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="E28" s="210" t="s">
-        <v>1004</v>
-      </c>
-      <c r="G28" s="210" t="s">
-        <v>1005</v>
-      </c>
-      <c r="H28" s="208" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29" s="204" t="s">
-        <v>1006</v>
-      </c>
-      <c r="B29" s="210" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C29" s="210" t="s">
-        <v>1008</v>
-      </c>
-      <c r="D29" s="210" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E29" s="210" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G29" s="209" t="s">
-        <v>1010</v>
-      </c>
-      <c r="H29" s="208" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30" s="204" t="s">
-        <v>1012</v>
-      </c>
-      <c r="B30" s="210" t="s">
-        <v>1013</v>
-      </c>
-      <c r="C30" s="210" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D30" s="210" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E30" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="G30" s="209" t="s">
-        <v>992</v>
-      </c>
-      <c r="H30" s="208" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31" s="204" t="s">
-        <v>1016</v>
-      </c>
-      <c r="B31" s="210" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C31" s="210" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D31" s="210" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E31" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="G31" s="209" t="s">
-        <v>1018</v>
-      </c>
-      <c r="H31" s="210" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
-      <c r="A32" s="204" t="s">
-        <v>1019</v>
-      </c>
-      <c r="B32" s="210" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C32" s="210" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D32" s="210" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E32" s="210" t="s">
-        <v>156</v>
-      </c>
-      <c r="G32" s="209" t="s">
-        <v>1021</v>
-      </c>
-      <c r="H32" s="208" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
-      <c r="A33" s="204" t="s">
-        <v>1023</v>
-      </c>
-      <c r="B33" s="210" t="s">
-        <v>1024</v>
-      </c>
-      <c r="C33" s="210" t="s">
-        <v>1025</v>
-      </c>
-      <c r="D33" s="210" t="s">
-        <v>1009</v>
-      </c>
-      <c r="E33" s="210" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G33" s="209" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H33" s="208" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
-      <c r="A34" s="204" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B34" s="210" t="s">
-        <v>1030</v>
-      </c>
-      <c r="C34" s="210" t="s">
-        <v>1031</v>
-      </c>
-      <c r="D34" s="210">
-        <v>1000</v>
-      </c>
-      <c r="E34" s="210">
-        <v>1200</v>
-      </c>
-      <c r="F34" s="210">
-        <v>1700</v>
-      </c>
-      <c r="G34" s="211">
-        <v>10305</v>
-      </c>
-      <c r="H34" s="208">
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" s="204" t="s">
-        <v>1032</v>
-      </c>
-      <c r="B35" s="210">
-        <v>1.75</v>
-      </c>
-      <c r="C35" s="210">
-        <v>1.75</v>
-      </c>
-      <c r="D35" s="210">
-        <v>1.75</v>
-      </c>
-      <c r="E35" s="210">
-        <v>1.75</v>
-      </c>
-      <c r="F35" s="210">
-        <v>1.75</v>
-      </c>
-      <c r="G35" s="209">
-        <v>2.85</v>
-      </c>
-      <c r="H35" s="208">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
-      <c r="B37" s="221"/>
-      <c r="C37" s="221"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8E22203-A011-45DE-AFDE-3A21369FA217}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -17460,14 +16144,14 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1">
       <c r="A1" s="223" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="B1" s="220"/>
       <c r="C1" s="220"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="224" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="B2" s="220"/>
       <c r="C2" s="220"/>
@@ -17477,80 +16161,80 @@
       <c r="B3" s="244"/>
       <c r="C3" s="244"/>
       <c r="D3" s="226" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="E3" s="226" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="F3" s="226" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G3" s="226" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="H3" s="226" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="I3" s="226" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="J3" s="249" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="K3" s="226" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="L3" s="228" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="222" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
       <c r="A4" s="242" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B4" s="242" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C4" s="242" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D4" s="242" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E4" s="242" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F4" s="242" t="s">
         <v>1040</v>
       </c>
-      <c r="B4" s="242" t="s">
+      <c r="G4" s="242" t="s">
         <v>1041</v>
       </c>
-      <c r="C4" s="242" t="s">
+      <c r="H4" s="242" t="s">
         <v>1042</v>
       </c>
-      <c r="D4" s="242" t="s">
+      <c r="I4" s="242" t="s">
         <v>1043</v>
       </c>
-      <c r="E4" s="242" t="s">
+      <c r="J4" s="242" t="s">
+        <v>1091</v>
+      </c>
+      <c r="K4" s="242" t="s">
+        <v>1092</v>
+      </c>
+      <c r="L4" s="242" t="s">
         <v>1044</v>
-      </c>
-      <c r="F4" s="242" t="s">
-        <v>1045</v>
-      </c>
-      <c r="G4" s="242" t="s">
-        <v>1046</v>
-      </c>
-      <c r="H4" s="242" t="s">
-        <v>1047</v>
-      </c>
-      <c r="I4" s="242" t="s">
-        <v>1048</v>
-      </c>
-      <c r="J4" s="242" t="s">
-        <v>1098</v>
-      </c>
-      <c r="K4" s="242" t="s">
-        <v>1099</v>
-      </c>
-      <c r="L4" s="242" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A5" s="245" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="B5" s="238" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="C5" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D5" s="239">
         <v>105</v>
@@ -17582,13 +16266,13 @@
     </row>
     <row r="6" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A6" s="245" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="B6" s="238" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="C6" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D6" s="239">
         <v>105</v>
@@ -17620,13 +16304,13 @@
     </row>
     <row r="7" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="245" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="B7" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C7" s="239" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="D7" s="239">
         <v>90</v>
@@ -17658,10 +16342,10 @@
     </row>
     <row r="8" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="245" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="B8" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C8" s="239">
         <v>0</v>
@@ -17679,10 +16363,10 @@
         <v>50</v>
       </c>
       <c r="H8" s="239" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="I8" s="240" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="J8" s="239">
         <v>80</v>
@@ -17696,13 +16380,13 @@
     </row>
     <row r="9" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="237" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="B9" s="238" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="C9" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D9" s="239">
         <v>105</v>
@@ -17734,13 +16418,13 @@
     </row>
     <row r="10" spans="1:12" s="222" customFormat="1" ht="17.25" customHeight="1">
       <c r="A10" s="237" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="B10" s="238" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="C10" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D10" s="239">
         <v>60</v>
@@ -17772,13 +16456,13 @@
     </row>
     <row r="11" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="237" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="B11" s="238" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="C11" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D11" s="239">
         <v>60</v>
@@ -17810,13 +16494,13 @@
     </row>
     <row r="12" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="237" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="B12" s="238" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="C12" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D12" s="239">
         <v>60</v>
@@ -17848,13 +16532,13 @@
     </row>
     <row r="13" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A13" s="237" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="B13" s="238" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="C13" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D13" s="239">
         <v>70</v>
@@ -17886,10 +16570,10 @@
     </row>
     <row r="14" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A14" s="237" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="B14" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C14" s="239">
         <v>0</v>
@@ -17924,11 +16608,11 @@
     </row>
     <row r="15" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="245" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
       <c r="B15" s="238"/>
       <c r="C15" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D15" s="239">
         <v>137</v>
@@ -17960,11 +16644,11 @@
     </row>
     <row r="16" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A16" s="245" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="B16" s="238"/>
       <c r="C16" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D16" s="239">
         <v>126</v>
@@ -17996,13 +16680,13 @@
     </row>
     <row r="17" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A17" s="237" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="B17" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C17" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D17" s="239">
         <v>145</v>
@@ -18034,13 +16718,13 @@
     </row>
     <row r="18" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="237" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="B18" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C18" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D18" s="239">
         <v>113</v>
@@ -18072,11 +16756,11 @@
     </row>
     <row r="19" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="237" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="B19" s="238"/>
       <c r="C19" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D19" s="239">
         <v>158</v>
@@ -18108,11 +16792,11 @@
     </row>
     <row r="20" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="237" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="B20" s="238"/>
       <c r="C20" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D20" s="239">
         <v>143</v>
@@ -18148,7 +16832,7 @@
       </c>
       <c r="B21" s="238"/>
       <c r="C21" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D21" s="239">
         <v>140</v>
@@ -18180,13 +16864,13 @@
     </row>
     <row r="22" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="237" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
       <c r="B22" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C22" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D22" s="239">
         <v>113</v>
@@ -18218,13 +16902,13 @@
     </row>
     <row r="23" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A23" s="245" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="B23" s="238" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="C23" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D23" s="239">
         <v>143</v>
@@ -18256,13 +16940,13 @@
     </row>
     <row r="24" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="245" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="B24" s="238" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="C24" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D24" s="239">
         <v>165</v>
@@ -18294,13 +16978,13 @@
     </row>
     <row r="25" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="237" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="B25" s="238" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="C25" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D25" s="239">
         <v>165</v>
@@ -18332,13 +17016,13 @@
     </row>
     <row r="26" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A26" s="246" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="B26" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C26" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D26" s="239">
         <v>70</v>
@@ -18370,13 +17054,13 @@
     </row>
     <row r="27" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A27" s="245" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="B27" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C27" s="239" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="D27" s="239">
         <v>80</v>
@@ -18408,13 +17092,13 @@
     </row>
     <row r="28" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A28" s="245" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="B28" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C28" s="239" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="D28" s="239">
         <v>85</v>
@@ -18449,10 +17133,10 @@
         <v>676</v>
       </c>
       <c r="B29" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C29" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D29" s="239">
         <v>90</v>
@@ -18484,10 +17168,10 @@
     </row>
     <row r="30" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A30" s="245" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="B30" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C30" s="239">
         <v>0</v>
@@ -18525,7 +17209,7 @@
         <v>675</v>
       </c>
       <c r="B31" s="238" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="C31" s="239">
         <v>0</v>
@@ -18560,10 +17244,10 @@
     </row>
     <row r="32" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="245" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="B32" s="238" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C32" s="239">
         <v>0</v>
@@ -18598,10 +17282,10 @@
     </row>
     <row r="33" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A33" s="245" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="B33" s="238" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="C33" s="239">
         <v>0</v>
@@ -18636,11 +17320,11 @@
     </row>
     <row r="34" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="245" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="B34" s="238"/>
       <c r="C34" s="239" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="D34" s="239">
         <v>170</v>
@@ -18655,10 +17339,10 @@
         <v>100</v>
       </c>
       <c r="H34" s="239" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="I34" s="240" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="J34" s="239">
         <v>158</v>
@@ -18672,11 +17356,11 @@
     </row>
     <row r="35" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="245" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="B35" s="238"/>
       <c r="C35" s="239" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="D35" s="239">
         <v>80</v>
@@ -18708,10 +17392,10 @@
     </row>
     <row r="36" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="237" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="B36" s="238" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="C36" s="239">
         <v>0</v>
@@ -18746,7 +17430,7 @@
     </row>
     <row r="37" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="237" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="B37" s="238"/>
       <c r="C37" s="239">
@@ -18797,7 +17481,7 @@
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1">
       <c r="A39" s="225" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="B39" s="304"/>
       <c r="C39" s="304"/>
@@ -18814,7 +17498,7 @@
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1">
       <c r="A41" s="225" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="B41" s="313"/>
       <c r="C41" s="313"/>
@@ -18830,7 +17514,7 @@
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
       <c r="A42" s="304" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="B42" s="220"/>
       <c r="C42" s="220"/>
@@ -18839,7 +17523,7 @@
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
       <c r="A43" s="304" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="B43" s="220"/>
       <c r="C43" s="220"/>
@@ -18848,7 +17532,7 @@
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
       <c r="A44" s="304" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="B44" s="220"/>
       <c r="C44" s="220"/>
@@ -18856,7 +17540,7 @@
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
       <c r="A45" s="304" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
       <c r="B45" s="220"/>
       <c r="C45" s="220"/>
@@ -18864,7 +17548,7 @@
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
       <c r="A46" s="304" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="B46" s="220"/>
       <c r="C46" s="220"/>
@@ -18874,7 +17558,7 @@
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
       <c r="A47" s="233" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="B47" s="233"/>
       <c r="C47" s="233"/>
@@ -18900,7 +17584,7 @@
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1">
       <c r="A49" s="247" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="E49" s="236"/>
       <c r="F49" s="236"/>
@@ -18914,7 +17598,7 @@
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1">
       <c r="A50" s="247" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="E50" s="236"/>
       <c r="F50" s="236"/>
@@ -26137,6 +24821,1277 @@
   <tableParts count="1">
     <tablePart r:id="rId3"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35C039F-5462-40EB-AF1D-F8681FB2D0C5}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="92" style="204" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="204"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="205" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="205"/>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="206" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="207" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="205" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="205" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="205" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="205" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="205"/>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="206" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="207" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="205" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="205"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="206" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="205" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="205" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="205" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="205" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="205" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="205" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="205"/>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="206" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="205" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="205" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="205" t="s">
+        <v>875</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B154CA9-6DBE-440D-B5D1-A4C053DC51C7}">
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="29.140625" style="204" customWidth="1"/>
+    <col min="2" max="2" width="35.7109375" style="210" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.85546875" style="210" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" style="210" customWidth="1"/>
+    <col min="5" max="5" width="35.28515625" style="210" customWidth="1"/>
+    <col min="6" max="6" width="32" style="210" customWidth="1"/>
+    <col min="7" max="7" width="30.85546875" style="209" customWidth="1"/>
+    <col min="8" max="8" width="56.85546875" style="208" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="204"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="204" t="s">
+        <v>876</v>
+      </c>
+      <c r="B1" s="210" t="s">
+        <v>877</v>
+      </c>
+      <c r="C1" s="210" t="s">
+        <v>878</v>
+      </c>
+      <c r="D1" s="210" t="s">
+        <v>879</v>
+      </c>
+      <c r="E1" s="210" t="s">
+        <v>880</v>
+      </c>
+      <c r="F1" s="210" t="s">
+        <v>881</v>
+      </c>
+      <c r="G1" s="209" t="s">
+        <v>882</v>
+      </c>
+      <c r="H1" s="208" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="204" t="s">
+        <v>884</v>
+      </c>
+      <c r="B2" s="210">
+        <v>1</v>
+      </c>
+      <c r="C2" s="210">
+        <v>1</v>
+      </c>
+      <c r="D2" s="210">
+        <v>1</v>
+      </c>
+      <c r="E2" s="210">
+        <v>1</v>
+      </c>
+      <c r="F2" s="210">
+        <v>1</v>
+      </c>
+      <c r="G2" s="209" t="s">
+        <v>885</v>
+      </c>
+      <c r="H2" s="208">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="204" t="s">
+        <v>886</v>
+      </c>
+      <c r="B3" s="210" t="s">
+        <v>887</v>
+      </c>
+      <c r="C3" s="210" t="s">
+        <v>888</v>
+      </c>
+      <c r="D3" s="219" t="s">
+        <v>887</v>
+      </c>
+      <c r="E3" s="219" t="s">
+        <v>887</v>
+      </c>
+      <c r="F3" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="H3" s="208" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="204" t="s">
+        <v>889</v>
+      </c>
+      <c r="B4" s="210">
+        <v>450</v>
+      </c>
+      <c r="C4" s="210">
+        <v>450</v>
+      </c>
+      <c r="D4" s="210" t="s">
+        <v>890</v>
+      </c>
+      <c r="E4" s="210">
+        <v>285</v>
+      </c>
+      <c r="F4" s="210">
+        <v>285</v>
+      </c>
+      <c r="G4" s="209">
+        <v>300</v>
+      </c>
+      <c r="H4" s="208" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="204" t="s">
+        <v>892</v>
+      </c>
+      <c r="B5" s="210" t="s">
+        <v>893</v>
+      </c>
+      <c r="C5" s="210" t="s">
+        <v>894</v>
+      </c>
+      <c r="D5" s="210">
+        <v>150</v>
+      </c>
+      <c r="E5" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="210">
+        <v>157</v>
+      </c>
+      <c r="G5" s="209">
+        <v>120</v>
+      </c>
+      <c r="H5" s="208" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="204" t="s">
+        <v>896</v>
+      </c>
+      <c r="B6" s="210">
+        <v>80</v>
+      </c>
+      <c r="C6" s="210">
+        <v>100</v>
+      </c>
+      <c r="D6" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="E6" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="G6" s="209">
+        <v>60</v>
+      </c>
+      <c r="H6" s="208" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="204" t="s">
+        <v>898</v>
+      </c>
+      <c r="B7" s="210" t="s">
+        <v>899</v>
+      </c>
+      <c r="C7" s="210" t="s">
+        <v>900</v>
+      </c>
+      <c r="D7" s="210" t="s">
+        <v>901</v>
+      </c>
+      <c r="E7" s="210" t="s">
+        <v>902</v>
+      </c>
+      <c r="F7" s="210" t="s">
+        <v>903</v>
+      </c>
+      <c r="G7" s="209" t="s">
+        <v>904</v>
+      </c>
+      <c r="H7" s="208" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="204" t="s">
+        <v>906</v>
+      </c>
+      <c r="B8" s="210" t="s">
+        <v>907</v>
+      </c>
+      <c r="C8" s="210" t="s">
+        <v>907</v>
+      </c>
+      <c r="D8" s="210" t="s">
+        <v>908</v>
+      </c>
+      <c r="E8" s="210" t="s">
+        <v>907</v>
+      </c>
+      <c r="F8" s="210" t="s">
+        <v>907</v>
+      </c>
+      <c r="G8" s="209" t="s">
+        <v>909</v>
+      </c>
+      <c r="H8" s="208" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="204" t="s">
+        <v>911</v>
+      </c>
+      <c r="B9" s="210" t="s">
+        <v>912</v>
+      </c>
+      <c r="C9" s="210" t="s">
+        <v>912</v>
+      </c>
+      <c r="D9" s="210" t="s">
+        <v>913</v>
+      </c>
+      <c r="E9" s="210" t="s">
+        <v>914</v>
+      </c>
+      <c r="F9" s="210" t="s">
+        <v>915</v>
+      </c>
+      <c r="H9" s="208" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="204" t="s">
+        <v>917</v>
+      </c>
+      <c r="B10" s="215" t="s">
+        <v>918</v>
+      </c>
+      <c r="C10" s="215" t="s">
+        <v>919</v>
+      </c>
+      <c r="D10" s="215" t="s">
+        <v>920</v>
+      </c>
+      <c r="E10" s="215" t="s">
+        <v>921</v>
+      </c>
+      <c r="F10" s="218" t="s">
+        <v>922</v>
+      </c>
+      <c r="G10" s="217" t="s">
+        <v>923</v>
+      </c>
+      <c r="H10" s="208" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="204" t="s">
+        <v>925</v>
+      </c>
+      <c r="B11" s="210" t="s">
+        <v>926</v>
+      </c>
+      <c r="C11" s="210" t="s">
+        <v>926</v>
+      </c>
+      <c r="D11" s="210" t="s">
+        <v>927</v>
+      </c>
+      <c r="E11" s="210" t="s">
+        <v>928</v>
+      </c>
+      <c r="F11" s="210" t="s">
+        <v>929</v>
+      </c>
+      <c r="G11" s="209" t="s">
+        <v>909</v>
+      </c>
+      <c r="H11" s="208" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="17.25" customHeight="1">
+      <c r="A12" s="216" t="s">
+        <v>930</v>
+      </c>
+      <c r="B12" s="215" t="s">
+        <v>931</v>
+      </c>
+      <c r="C12" s="215" t="s">
+        <v>932</v>
+      </c>
+      <c r="D12" s="214" t="s">
+        <v>933</v>
+      </c>
+      <c r="E12" s="215" t="s">
+        <v>934</v>
+      </c>
+      <c r="F12" s="214" t="s">
+        <v>935</v>
+      </c>
+      <c r="H12" s="208" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="204" t="s">
+        <v>937</v>
+      </c>
+      <c r="B13" s="210" t="s">
+        <v>938</v>
+      </c>
+      <c r="C13" s="210" t="s">
+        <v>938</v>
+      </c>
+      <c r="D13" s="210">
+        <v>120</v>
+      </c>
+      <c r="E13" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="210" t="s">
+        <v>939</v>
+      </c>
+      <c r="G13" s="209" t="s">
+        <v>940</v>
+      </c>
+      <c r="H13" s="208" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="204" t="s">
+        <v>941</v>
+      </c>
+      <c r="B14" s="210" t="s">
+        <v>942</v>
+      </c>
+      <c r="C14" s="210" t="s">
+        <v>942</v>
+      </c>
+      <c r="D14" s="210" t="s">
+        <v>943</v>
+      </c>
+      <c r="E14" s="210" t="s">
+        <v>944</v>
+      </c>
+      <c r="F14" s="210" t="s">
+        <v>945</v>
+      </c>
+      <c r="G14" s="209" t="s">
+        <v>946</v>
+      </c>
+      <c r="H14" s="208" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="213" t="s">
+        <v>948</v>
+      </c>
+      <c r="B15" s="210" t="s">
+        <v>907</v>
+      </c>
+      <c r="C15" s="210" t="s">
+        <v>907</v>
+      </c>
+      <c r="H15" s="208" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="204" t="s">
+        <v>949</v>
+      </c>
+      <c r="B16" s="210" t="s">
+        <v>950</v>
+      </c>
+      <c r="C16" s="210" t="s">
+        <v>951</v>
+      </c>
+      <c r="D16" s="210" t="s">
+        <v>952</v>
+      </c>
+      <c r="E16" s="210" t="s">
+        <v>953</v>
+      </c>
+      <c r="F16" s="210" t="s">
+        <v>953</v>
+      </c>
+      <c r="H16" s="208" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="204" t="s">
+        <v>955</v>
+      </c>
+      <c r="B17" s="210" t="s">
+        <v>956</v>
+      </c>
+      <c r="C17" s="210" t="s">
+        <v>957</v>
+      </c>
+      <c r="D17" s="210" t="s">
+        <v>958</v>
+      </c>
+      <c r="E17" s="210" t="s">
+        <v>953</v>
+      </c>
+      <c r="F17" s="210" t="s">
+        <v>953</v>
+      </c>
+      <c r="H17" s="208" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="204" t="s">
+        <v>959</v>
+      </c>
+      <c r="B18" s="210" t="s">
+        <v>960</v>
+      </c>
+      <c r="C18" s="210" t="s">
+        <v>961</v>
+      </c>
+      <c r="D18" s="210" t="s">
+        <v>962</v>
+      </c>
+      <c r="E18" s="210" t="s">
+        <v>963</v>
+      </c>
+      <c r="F18" s="210" t="s">
+        <v>964</v>
+      </c>
+      <c r="H18" s="208" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="204" t="s">
+        <v>966</v>
+      </c>
+      <c r="B19" s="210" t="s">
+        <v>967</v>
+      </c>
+      <c r="C19" s="210" t="s">
+        <v>967</v>
+      </c>
+      <c r="D19" s="210" t="s">
+        <v>968</v>
+      </c>
+      <c r="E19" s="210" t="s">
+        <v>969</v>
+      </c>
+      <c r="F19" s="210" t="s">
+        <v>970</v>
+      </c>
+      <c r="G19" s="209" t="s">
+        <v>968</v>
+      </c>
+      <c r="H19" s="209" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="213" t="s">
+        <v>971</v>
+      </c>
+      <c r="B20" s="208" t="s">
+        <v>972</v>
+      </c>
+      <c r="C20" s="208" t="s">
+        <v>973</v>
+      </c>
+      <c r="G20" s="209" t="s">
+        <v>974</v>
+      </c>
+      <c r="H20" s="208" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" s="204" t="s">
+        <v>976</v>
+      </c>
+      <c r="B21" s="210" t="s">
+        <v>977</v>
+      </c>
+      <c r="C21" s="210" t="s">
+        <v>977</v>
+      </c>
+      <c r="D21" s="210" t="s">
+        <v>978</v>
+      </c>
+      <c r="E21" s="210" t="s">
+        <v>978</v>
+      </c>
+      <c r="G21" s="212" t="s">
+        <v>979</v>
+      </c>
+      <c r="H21" s="208" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" s="204" t="s">
+        <v>981</v>
+      </c>
+      <c r="B22" s="210" t="s">
+        <v>982</v>
+      </c>
+      <c r="C22" s="210" t="s">
+        <v>983</v>
+      </c>
+      <c r="D22" s="210" t="s">
+        <v>978</v>
+      </c>
+      <c r="E22" s="210" t="s">
+        <v>978</v>
+      </c>
+      <c r="F22" s="210" t="s">
+        <v>978</v>
+      </c>
+      <c r="G22" s="209" t="s">
+        <v>984</v>
+      </c>
+      <c r="H22" s="208" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="204" t="s">
+        <v>986</v>
+      </c>
+      <c r="B23" s="210" t="s">
+        <v>977</v>
+      </c>
+      <c r="C23" s="210" t="s">
+        <v>977</v>
+      </c>
+      <c r="D23" s="210" t="s">
+        <v>978</v>
+      </c>
+      <c r="E23" s="210" t="s">
+        <v>978</v>
+      </c>
+      <c r="F23" s="210" t="s">
+        <v>978</v>
+      </c>
+      <c r="G23" s="209" t="s">
+        <v>987</v>
+      </c>
+      <c r="H23" s="208" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="204" t="s">
+        <v>988</v>
+      </c>
+      <c r="B24" s="210" t="s">
+        <v>977</v>
+      </c>
+      <c r="C24" s="210" t="s">
+        <v>977</v>
+      </c>
+      <c r="D24" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="E24" s="210" t="s">
+        <v>907</v>
+      </c>
+      <c r="H24" s="208" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" s="204" t="s">
+        <v>989</v>
+      </c>
+      <c r="B25" s="210">
+        <v>0.05</v>
+      </c>
+      <c r="C25" s="210">
+        <v>0.05</v>
+      </c>
+      <c r="D25" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="E25" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="G25" s="209">
+        <v>0.05</v>
+      </c>
+      <c r="H25" s="208">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" s="204" t="s">
+        <v>990</v>
+      </c>
+      <c r="B26" s="210" t="s">
+        <v>977</v>
+      </c>
+      <c r="C26" s="210" t="s">
+        <v>991</v>
+      </c>
+      <c r="D26" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="E26" s="210" t="s">
+        <v>992</v>
+      </c>
+      <c r="G26" s="209" t="s">
+        <v>993</v>
+      </c>
+      <c r="H26" s="208" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" s="204" t="s">
+        <v>994</v>
+      </c>
+      <c r="B27" s="210" t="s">
+        <v>995</v>
+      </c>
+      <c r="C27" s="210" t="s">
+        <v>995</v>
+      </c>
+      <c r="D27" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="E27" s="210" t="s">
+        <v>996</v>
+      </c>
+      <c r="H27" s="210" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" s="204" t="s">
+        <v>997</v>
+      </c>
+      <c r="B28" s="210" t="s">
+        <v>998</v>
+      </c>
+      <c r="C28" s="210" t="s">
+        <v>998</v>
+      </c>
+      <c r="D28" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="E28" s="210" t="s">
+        <v>999</v>
+      </c>
+      <c r="G28" s="210" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H28" s="208" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" s="204" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B29" s="210" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C29" s="210" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D29" s="210" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E29" s="210" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G29" s="209" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H29" s="208" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" s="204" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B30" s="210" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C30" s="210" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D30" s="210" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E30" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="G30" s="209" t="s">
+        <v>987</v>
+      </c>
+      <c r="H30" s="208" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="204" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B31" s="210" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C31" s="210" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D31" s="210" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E31" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="G31" s="209" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H31" s="210" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="204" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B32" s="210" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C32" s="210" t="s">
+        <v>1015</v>
+      </c>
+      <c r="D32" s="210" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E32" s="210" t="s">
+        <v>156</v>
+      </c>
+      <c r="G32" s="209" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H32" s="208" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="204" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B33" s="210" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C33" s="210" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D33" s="210" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E33" s="210" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G33" s="209" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H33" s="208" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="204" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B34" s="210" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C34" s="210" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D34" s="210">
+        <v>1000</v>
+      </c>
+      <c r="E34" s="210">
+        <v>1200</v>
+      </c>
+      <c r="F34" s="210">
+        <v>1700</v>
+      </c>
+      <c r="G34" s="211">
+        <v>10305</v>
+      </c>
+      <c r="H34" s="208">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="204" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B35" s="210">
+        <v>1.75</v>
+      </c>
+      <c r="C35" s="210">
+        <v>1.75</v>
+      </c>
+      <c r="D35" s="210">
+        <v>1.75</v>
+      </c>
+      <c r="E35" s="210">
+        <v>1.75</v>
+      </c>
+      <c r="F35" s="210">
+        <v>1.75</v>
+      </c>
+      <c r="G35" s="209">
+        <v>2.85</v>
+      </c>
+      <c r="H35" s="208">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="B37" s="221"/>
+      <c r="C37" s="221"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617F1214-FEDF-4959-B6B1-8C60CA48A0FC}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="51.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="32.85546875" customWidth="1"/>
+    <col min="4" max="4" width="19.42578125" customWidth="1"/>
+    <col min="5" max="5" width="71.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B2" t="s">
+        <v>829</v>
+      </c>
+      <c r="C2" t="s">
+        <v>830</v>
+      </c>
+      <c r="D2" t="s">
+        <v>831</v>
+      </c>
+      <c r="E2" s="109" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>833</v>
+      </c>
+      <c r="C3" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16.5" customHeight="1">
+      <c r="A6" t="s">
+        <v>837</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="14.25" customHeight="1">
+      <c r="A10" s="4" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>844</v>
+      </c>
+      <c r="C12" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>846</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>847</v>
+      </c>
+      <c r="E13" s="134" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="305" t="s">
+        <v>849</v>
+      </c>
+      <c r="E14" s="134" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>851</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>853</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>854</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E13" r:id="rId1" xr:uid="{3BD14087-096D-4B95-8D2A-BB6B2E6ECB04}"/>
+    <hyperlink ref="E14" r:id="rId2" xr:uid="{9746E316-C540-456C-8DB2-33AE97228441}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EDA9B0-1F64-43EA-B8A8-B58E6C73D378}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="83.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="46.140625" customWidth="1"/>
+    <col min="4" max="4" width="70.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15.75">
+      <c r="A1" s="5" t="s">
+        <v>701</v>
+      </c>
+      <c r="B1" t="s">
+        <v>702</v>
+      </c>
+      <c r="C1" t="s">
+        <v>703</v>
+      </c>
+      <c r="D1" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A2" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="B2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C2" s="124" t="s">
+        <v>707</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A3" t="s">
+        <v>709</v>
+      </c>
+      <c r="B3" t="s">
+        <v>710</v>
+      </c>
+      <c r="C3" s="306" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="D4" s="307" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="C5" s="125" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B6" t="s">
+        <v>719</v>
+      </c>
+      <c r="C6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>720</v>
+      </c>
+      <c r="B7" t="s">
+        <v>721</v>
+      </c>
+      <c r="C7" s="123" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>723</v>
+      </c>
+      <c r="B8" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>725</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{36F730E6-D2FB-4DE8-A8CA-115837D74B28}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30105"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3319" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15BAE4B1-9525-44BD-BBF2-8273753356D0}"/>
+  <xr:revisionPtr revIDLastSave="3320" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16ACF7C3-03DE-4470-8B23-F4A31228EBD7}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2165,81 +2165,6 @@
     <t>V2 HDC Buddy_1x.stl</t>
   </si>
   <si>
-    <t>Things still to do</t>
-  </si>
-  <si>
-    <t>owner</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>options</t>
-  </si>
-  <si>
-    <t>Find HT magnets for door ( might have to make a holder for SMCO's instead of pot magnets)</t>
-  </si>
-  <si>
-    <t>mark/Roy</t>
-  </si>
-  <si>
-    <t>going to use Nynodinum for now</t>
-  </si>
-  <si>
-    <t>20mm neodynium POT magnet in the oven at 115C for 2 hours it seems ok,</t>
-  </si>
-  <si>
-    <t>Test new Chamber Heater &amp; Fan</t>
-  </si>
-  <si>
-    <t>Roy</t>
-  </si>
-  <si>
-    <t>WIP</t>
-  </si>
-  <si>
-    <t>Mark to Find HT Fan for chamber heater or use external motor as per Roys previous design.</t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80mm 24v dc,  testing  with other fans </t>
-  </si>
-  <si>
-    <t>https://www.aliexpress.com/item/1005008197099809.html</t>
-  </si>
-  <si>
-    <t>make a list of basic macros</t>
-  </si>
-  <si>
-    <t>WIP need to confirm a few</t>
-  </si>
-  <si>
-    <t>make a basic config which boards ?</t>
-  </si>
-  <si>
-    <t>M/R</t>
-  </si>
-  <si>
-    <t>workout a way to get esp32 programmed easierly</t>
-  </si>
-  <si>
-    <t>Chris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3rd may Mark/chris  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">front door BOM and Drawings </t>
-  </si>
-  <si>
-    <t>R/M</t>
-  </si>
-  <si>
-    <t>finally finish the Hardware BOM when all above done</t>
-  </si>
-  <si>
     <t>Function</t>
   </si>
   <si>
@@ -2540,769 +2465,172 @@
     <t>TPU</t>
   </si>
   <si>
-    <t>Quantity M</t>
-  </si>
-  <si>
-    <t>Column2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPDM foam </t>
-  </si>
-  <si>
-    <t>5M</t>
-  </si>
-  <si>
-    <t>Door seal / Dry Box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">local hardware store </t>
-  </si>
-  <si>
-    <t>EPDM profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Square </t>
-  </si>
-  <si>
-    <t>Engineers square</t>
-  </si>
-  <si>
-    <t>Allen keys 1.27,2,3,4,mm 2.5mm ball ended</t>
-  </si>
-  <si>
-    <t xml:space="preserve">steel Rule or  Equiverlant </t>
-  </si>
-  <si>
-    <t xml:space="preserve">G or F clamp </t>
-  </si>
-  <si>
-    <t xml:space="preserve">gust for putting the frame together </t>
-  </si>
-  <si>
-    <t>Spanner  AF 7mm,</t>
-  </si>
-  <si>
-    <t>Drill bits mm  5,4,3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">solder iron and solder </t>
-  </si>
-  <si>
-    <t xml:space="preserve">crimp tool for  control board connection </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taps M6 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">calipers </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recomend Shahe </t>
-  </si>
-  <si>
-    <t>Allen Key short shank 2.5mmfor moth end</t>
-  </si>
-  <si>
-    <t>used on screws on moth end</t>
-  </si>
-  <si>
-    <t>https://www.aliexpress.com/item/1005009139855730.html?</t>
-  </si>
-  <si>
-    <t>Unclog Pin Specially Design </t>
-  </si>
-  <si>
-    <t>https://www.aliexpress.com/item/1005002948629438.html?spm=a2g0o.order_list.order_list_main.192.45b518027U4htK</t>
-  </si>
-  <si>
-    <t>Philips No. 2   ( screws in GX20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Good wire strippers  for the High temperature cable </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lead/Tin Sloder 60/40 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">This will make the soldering much easier </t>
-  </si>
-  <si>
-    <t>New  features and upgrades on the Valkyrie V2  HT 100+</t>
-  </si>
-  <si>
-    <t>Tool Head upgrades</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water flow monitoring with alarm </t>
-  </si>
-  <si>
-    <t>The Hot end now water cooled</t>
-  </si>
-  <si>
-    <t>Part cooling is now recycling the chamber hot air with a powerfull 0.76^3M/min</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filament buffer added increase in max volumectric flow rate </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Quick tool head disconnect (5 minutes to change over ) </t>
-  </si>
-  <si>
-    <t>Chamber upgrades</t>
-  </si>
-  <si>
-    <t>Chamber now has an active ?W heater to 100C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dry box temperature now up to 90C </t>
-  </si>
-  <si>
-    <t>Motion system  upgrade</t>
-  </si>
-  <si>
-    <t>x axis now has pre load to get more accurate nozzle control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Idleler bearings  updated to larger diamenter for longer life and less play </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belts now 1.5mm pitch to help with reducing artifcats </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A,B setepper motors are now upgraded to higherer current and long shafts with top bearing support </t>
-  </si>
-  <si>
-    <t>MGN carr's now all  metal  rated  to 120C</t>
-  </si>
-  <si>
-    <t>Auto z offset ajustment for nozzel height</t>
-  </si>
-  <si>
-    <t>Other improvements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High  temperature SmCo  Magnectics inseted into the printer  </t>
-  </si>
-  <si>
-    <t>Connectors added to the Dry box drawer and heated bed for easy servicing</t>
-  </si>
-  <si>
-    <t>Many updates to printer macros to improve performance</t>
-  </si>
-  <si>
-    <t>Specifications</t>
-  </si>
-  <si>
-    <t>Valkyrie V1</t>
-  </si>
-  <si>
-    <t>Valkyrie V2</t>
-  </si>
-  <si>
-    <t>Hevort</t>
-  </si>
-  <si>
-    <t>Voron 2.4</t>
-  </si>
-  <si>
-    <t>RatRig V3</t>
-  </si>
-  <si>
-    <t>BNC3D Epsilon</t>
-  </si>
-  <si>
-    <t>22 Idex V3</t>
-  </si>
-  <si>
-    <t>number of extruders</t>
-  </si>
-  <si>
-    <t>Idex</t>
-  </si>
-  <si>
-    <t>Max print speed</t>
-  </si>
-  <si>
-    <t>500mm/s</t>
-  </si>
-  <si>
-    <t>500 mm/s</t>
-  </si>
-  <si>
-    <t>Max extruder Tempreature</t>
-  </si>
-  <si>
-    <t>245 std, 290 HT</t>
-  </si>
-  <si>
-    <t>500C</t>
-  </si>
-  <si>
-    <t>Max Bed Tempreature deg C</t>
-  </si>
-  <si>
-    <t>120C</t>
-  </si>
-  <si>
-    <t>150C</t>
-  </si>
-  <si>
-    <t>250C</t>
-  </si>
-  <si>
-    <t>Max chamber Temperatue</t>
-  </si>
-  <si>
-    <t>100/active</t>
-  </si>
-  <si>
-    <t>Print Volume X,Y,Z</t>
-  </si>
-  <si>
-    <t>300x300x2xx</t>
-  </si>
-  <si>
-    <t>300x300x300</t>
-  </si>
-  <si>
-    <t>300 to 500 cubed</t>
-  </si>
-  <si>
-    <t>3 sizes, 250,300,350 cubed</t>
-  </si>
-  <si>
-    <t>3 sizes, 300,400,500 cubed</t>
-  </si>
-  <si>
-    <t>420*300*400</t>
-  </si>
-  <si>
-    <t>350 x350 x450</t>
-  </si>
-  <si>
-    <t>self leving bed</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>High-Performance Filaments with HDT  (2026 Reference)</t>
+  </si>
+  <si>
+    <t>Note: The values maybe different depending on the brands - Check</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Hr</t>
+  </si>
+  <si>
+    <t>UnAnnealed</t>
+  </si>
+  <si>
+    <t>Annealed</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Filament Name</t>
+  </si>
+  <si>
+    <t>Build Sheet</t>
+  </si>
+  <si>
+    <t>Cooling Fan Speed</t>
+  </si>
+  <si>
+    <t>Tg</t>
+  </si>
+  <si>
+    <t>Nozzle Temp</t>
+  </si>
+  <si>
+    <t>Bed Temp</t>
+  </si>
+  <si>
+    <t>Chamber Temp</t>
+  </si>
+  <si>
+    <t>Drying Temp</t>
+  </si>
+  <si>
+    <t>Drying Time</t>
+  </si>
+  <si>
+    <t>HDT</t>
+  </si>
+  <si>
+    <t>HDT Annealed</t>
+  </si>
+  <si>
+    <t>Bending Modulus MPa</t>
+  </si>
+  <si>
+    <t>PEI/Glass</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>ASA</t>
+  </si>
+  <si>
+    <t>CPE</t>
+  </si>
+  <si>
+    <t>PEI</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>HIPS</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>NON</t>
-  </si>
-  <si>
-    <t>3 point lead screw</t>
-  </si>
-  <si>
-    <t>build plate</t>
-  </si>
-  <si>
-    <t>builders choice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">builder choice </t>
-  </si>
-  <si>
-    <t>energetic PEI magnectic</t>
-  </si>
-  <si>
-    <t>FlexPlate Set - Powder Coated PEI</t>
-  </si>
-  <si>
-    <t>carbon/Glass</t>
-  </si>
-  <si>
-    <t>Bed</t>
-  </si>
-  <si>
-    <t>8mm Aluminium cast 8053 / insulated</t>
-  </si>
-  <si>
-    <t>8mm Aluminium cast 8053 with SmCo magnets</t>
-  </si>
-  <si>
-    <t>builders choiice</t>
-  </si>
-  <si>
-    <t>aluminium plate Rolled / uninsulated</t>
-  </si>
-  <si>
-    <t>6mm cast aluminium tooling plate</t>
-  </si>
-  <si>
-    <t>Glass Build Plate</t>
-  </si>
-  <si>
-    <t>build surface screw fasteners</t>
-  </si>
-  <si>
-    <t>bed probe</t>
-  </si>
-  <si>
-    <t>custom</t>
-  </si>
-  <si>
-    <t>Bltouch</t>
-  </si>
-  <si>
-    <t>inductive</t>
-  </si>
-  <si>
-    <t>BL touch</t>
-  </si>
-  <si>
-    <t>control board</t>
-  </si>
-  <si>
-    <t>Duet 6hc / octopus pro</t>
-  </si>
-  <si>
-    <t>Duet 6HC</t>
-  </si>
-  <si>
-    <t>DuetWifi + Duex5</t>
-  </si>
-  <si>
-    <t>SKR1.4/Spider</t>
-  </si>
-  <si>
-    <t>Duet3mini + Mini2+ or Duet3 6ch or SK pro 1.2</t>
-  </si>
-  <si>
-    <t>Duet 3, 3HC Expansion Board</t>
-  </si>
-  <si>
-    <t>Voltage AC</t>
-  </si>
-  <si>
-    <t>110/230</t>
-  </si>
-  <si>
-    <t>115 or 230</t>
-  </si>
-  <si>
-    <t>84 to 240</t>
-  </si>
-  <si>
-    <t>Enclosure type</t>
-  </si>
-  <si>
-    <t>PIR skined in ACM</t>
-  </si>
-  <si>
-    <t>DiBond</t>
-  </si>
-  <si>
-    <t>acrylic</t>
-  </si>
-  <si>
-    <t>4mm polycarbonate</t>
-  </si>
-  <si>
-    <t>steel and acrylic</t>
-  </si>
-  <si>
-    <t>insulation and steel</t>
-  </si>
-  <si>
-    <t>Filament Runout Sensor</t>
-  </si>
-  <si>
-    <t>Part cooling</t>
-  </si>
-  <si>
-    <t>air /5015 fan 4.5CFM</t>
-  </si>
-  <si>
-    <t>air/Robo fan 26CFM</t>
-  </si>
-  <si>
-    <t>compressor</t>
-  </si>
-  <si>
-    <t>fan</t>
-  </si>
-  <si>
-    <t>air 5015</t>
-  </si>
-  <si>
-    <t>extruder cooling</t>
-  </si>
-  <si>
-    <t>air</t>
-  </si>
-  <si>
-    <t>Water</t>
-  </si>
-  <si>
-    <t>water</t>
-  </si>
-  <si>
-    <t>Belt size A/B</t>
-  </si>
-  <si>
-    <t>9mm/2mm pitch</t>
-  </si>
-  <si>
-    <t>9mm/2.0mm pitch</t>
-  </si>
-  <si>
-    <t>6mm std ,9mm HT(mellow)</t>
-  </si>
-  <si>
-    <t>9mm</t>
-  </si>
-  <si>
-    <t>9mm Belts</t>
-  </si>
-  <si>
-    <t>12mm kevlar</t>
-  </si>
-  <si>
-    <t>Z Axis</t>
-  </si>
-  <si>
-    <t>9mm belts</t>
-  </si>
-  <si>
-    <t>lead screw</t>
-  </si>
-  <si>
-    <t>Belt 6 or 9mm</t>
-  </si>
-  <si>
-    <t>lead screw T8 x8</t>
-  </si>
-  <si>
-    <t>Position Accuracy/resolution</t>
-  </si>
-  <si>
-    <t>X/Y: 12.5 μm, Z: 3.125 μm</t>
-  </si>
-  <si>
-    <t>X/Y:10.0 μm, Z: 2.5 μm</t>
-  </si>
-  <si>
-    <t>X/Y: 1.25µm Z: 1µm</t>
-  </si>
-  <si>
-    <t>X/Y: 10 μm, Z: 7 μm</t>
-  </si>
-  <si>
-    <t>Filter</t>
-  </si>
-  <si>
-    <t>Non</t>
-  </si>
-  <si>
-    <t>non</t>
-  </si>
-  <si>
-    <t>H13 HEPA filter, Active Carbon filter</t>
-  </si>
-  <si>
-    <t>Optional HEPA + Active Carbon Filter System (sold separately)</t>
-  </si>
-  <si>
-    <t>Filament Box</t>
-  </si>
-  <si>
-    <t>humidity &amp; tempreature 1kg roll 70C</t>
-  </si>
-  <si>
-    <t>humidity &amp; tempreature 1kg roll 90C</t>
-  </si>
-  <si>
-    <t>humidity control 5 rolls</t>
-  </si>
-  <si>
-    <t>extra</t>
-  </si>
-  <si>
-    <t>Built in UPS</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>Raspberry Pi</t>
-  </si>
-  <si>
-    <t>Print Resoloution layer height</t>
-  </si>
-  <si>
-    <t>Screen</t>
-  </si>
-  <si>
-    <t>option , new Duet release soon</t>
-  </si>
-  <si>
-    <t>yes type?</t>
-  </si>
-  <si>
-    <t>touch 5"</t>
-  </si>
-  <si>
-    <t>Controller Firmware</t>
-  </si>
-  <si>
-    <t>REPRAP</t>
-  </si>
-  <si>
-    <t>klipper/Marrlin</t>
-  </si>
-  <si>
-    <t>Slicer</t>
-  </si>
-  <si>
-    <t>Any</t>
-  </si>
-  <si>
-    <t>any</t>
-  </si>
-  <si>
-    <t>CURA</t>
-  </si>
-  <si>
-    <t>Bodum or direct drive</t>
-  </si>
-  <si>
-    <t>direct</t>
-  </si>
-  <si>
-    <t>Direct plus Filament buffer</t>
-  </si>
-  <si>
-    <t>builder choice</t>
-  </si>
-  <si>
-    <t>bodun</t>
-  </si>
-  <si>
-    <t>Direct</t>
-  </si>
-  <si>
-    <t>Extruder</t>
-  </si>
-  <si>
-    <t>BTT H2V2S</t>
-  </si>
-  <si>
-    <t>BTT H2V2</t>
-  </si>
-  <si>
-    <t>LGX Pro High-Temp</t>
-  </si>
-  <si>
-    <t>connectivity WIFI USB</t>
-  </si>
-  <si>
-    <t>wifi/LAN</t>
-  </si>
-  <si>
-    <t>Wifi &amp; LAN</t>
-  </si>
-  <si>
-    <t>internal light</t>
-  </si>
-  <si>
-    <t>LED</t>
-  </si>
-  <si>
-    <t>Blue LED</t>
-  </si>
-  <si>
-    <t>RGB</t>
-  </si>
-  <si>
-    <t>Hot end</t>
-  </si>
-  <si>
-    <t>Solid copper</t>
-  </si>
-  <si>
-    <t>Solid Copper</t>
-  </si>
-  <si>
-    <t>Std E3D clone</t>
-  </si>
-  <si>
-    <t>e3D</t>
-  </si>
-  <si>
-    <t>Slice Engineering Copperhead</t>
-  </si>
-  <si>
-    <t>Price Approximately USA $</t>
-  </si>
-  <si>
-    <t>~2000</t>
-  </si>
-  <si>
-    <t>~2400</t>
-  </si>
-  <si>
-    <t>filament Dia</t>
-  </si>
-  <si>
-    <t>High-Performance Filaments with HDT  (2026 Reference)</t>
-  </si>
-  <si>
-    <t>Note: The values maybe different depending on the brands - Check</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Hr</t>
-  </si>
-  <si>
-    <t>UnAnnealed</t>
-  </si>
-  <si>
-    <t>Annealed</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Filament Name</t>
-  </si>
-  <si>
-    <t>Build Sheet</t>
-  </si>
-  <si>
-    <t>Cooling Fan Speed</t>
-  </si>
-  <si>
-    <t>Tg</t>
-  </si>
-  <si>
-    <t>Nozzle Temp</t>
-  </si>
-  <si>
-    <t>Bed Temp</t>
-  </si>
-  <si>
-    <t>Chamber Temp</t>
-  </si>
-  <si>
-    <t>Drying Temp</t>
-  </si>
-  <si>
-    <t>Drying Time</t>
-  </si>
-  <si>
-    <t>Bending Modulus MPa</t>
-  </si>
-  <si>
-    <t>PEI</t>
-  </si>
-  <si>
-    <t>Low</t>
+    <t>PA 6</t>
+  </si>
+  <si>
+    <t>G10/FR4</t>
+  </si>
+  <si>
+    <t>PA ePA CF</t>
+  </si>
+  <si>
+    <t>PA12 CF</t>
+  </si>
+  <si>
+    <t>PA12 GF</t>
+  </si>
+  <si>
+    <t>PA6 GF</t>
+  </si>
+  <si>
+    <t>PC</t>
+  </si>
+  <si>
+    <t>PC + ABS</t>
+  </si>
+  <si>
+    <t>PC + ASA</t>
+  </si>
+  <si>
+    <t>PC BambuLab</t>
+  </si>
+  <si>
+    <t>PC Blend CF Prusa</t>
+  </si>
+  <si>
+    <t>PC BLEND LCF*</t>
+  </si>
+  <si>
+    <t>PC CF/GF</t>
+  </si>
+  <si>
+    <t>PC Polymax</t>
+  </si>
+  <si>
+    <t>PEEK</t>
+  </si>
+  <si>
+    <t>CF/PEI</t>
+  </si>
+  <si>
+    <t>PEKK</t>
+  </si>
+  <si>
+    <t>PEKK CF</t>
+  </si>
+  <si>
+    <t>PET CF</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>PPS</t>
+  </si>
+  <si>
+    <t>PPSU</t>
+  </si>
+  <si>
+    <t>PC/PEI</t>
+  </si>
+  <si>
+    <t>PSU</t>
+  </si>
+  <si>
+    <t>FR4</t>
+  </si>
+  <si>
+    <t>PVDF</t>
+  </si>
+  <si>
+    <t>TPC FLEX</t>
   </si>
   <si>
     <t>ULTEM 1010</t>
   </si>
   <si>
-    <t>PC/PEI</t>
-  </si>
-  <si>
-    <t>PPSU</t>
-  </si>
-  <si>
-    <t>PC BLEND LCF*</t>
-  </si>
-  <si>
-    <t>PEKK</t>
-  </si>
-  <si>
-    <t>CF/PEI</t>
-  </si>
-  <si>
-    <t>PEKK CF</t>
-  </si>
-  <si>
     <t>ULTEM 9085</t>
-  </si>
-  <si>
-    <t>PSU</t>
-  </si>
-  <si>
-    <t>FR4</t>
-  </si>
-  <si>
-    <t>PVDF</t>
-  </si>
-  <si>
-    <t>PA 6</t>
-  </si>
-  <si>
-    <t>G10/FR4</t>
-  </si>
-  <si>
-    <t>PA6 GF</t>
-  </si>
-  <si>
-    <t>PEEK</t>
-  </si>
-  <si>
-    <t>PA12 CF</t>
-  </si>
-  <si>
-    <t>PA12 GF</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>PC CF/GF</t>
-  </si>
-  <si>
-    <t>PC + ABS</t>
-  </si>
-  <si>
-    <t>PC + ASA</t>
-  </si>
-  <si>
-    <t>TPC FLEX</t>
-  </si>
-  <si>
-    <t>Medium</t>
-  </si>
-  <si>
-    <t>PC Blend CF Prusa</t>
-  </si>
-  <si>
-    <t>PC Polymax</t>
-  </si>
-  <si>
-    <t>PC BambuLab</t>
-  </si>
-  <si>
-    <t>PET CF</t>
-  </si>
-  <si>
-    <t>PA ePA CF</t>
-  </si>
-  <si>
-    <t>PEI/Glass</t>
-  </si>
-  <si>
-    <t>ASA</t>
-  </si>
-  <si>
-    <t>PPS</t>
-  </si>
-  <si>
-    <t>HIPS</t>
-  </si>
-  <si>
-    <t>CPE</t>
-  </si>
-  <si>
-    <t>High</t>
   </si>
   <si>
     <t xml:space="preserve">*Add North </t>
@@ -3393,10 +2721,682 @@
     </r>
   </si>
   <si>
-    <t>HDT</t>
-  </si>
-  <si>
-    <t>HDT Annealed</t>
+    <t>New  features and upgrades on the Valkyrie V2  HT 100+</t>
+  </si>
+  <si>
+    <t>Tool Head upgrades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water flow monitoring with alarm </t>
+  </si>
+  <si>
+    <t>The Hot end now water cooled</t>
+  </si>
+  <si>
+    <t>Part cooling is now recycling the chamber hot air with a powerfull 0.76^3M/min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filament buffer added increase in max volumectric flow rate </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quick tool head disconnect (5 minutes to change over ) </t>
+  </si>
+  <si>
+    <t>Chamber upgrades</t>
+  </si>
+  <si>
+    <t>Chamber now has an active ?W heater to 100C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dry box temperature now up to 90C </t>
+  </si>
+  <si>
+    <t>Motion system  upgrade</t>
+  </si>
+  <si>
+    <t>x axis now has pre load to get more accurate nozzle control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idleler bearings  updated to larger diamenter for longer life and less play </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belts now 1.5mm pitch to help with reducing artifcats </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A,B setepper motors are now upgraded to higherer current and long shafts with top bearing support </t>
+  </si>
+  <si>
+    <t>MGN carr's now all  metal  rated  to 120C</t>
+  </si>
+  <si>
+    <t>Auto z offset ajustment for nozzel height</t>
+  </si>
+  <si>
+    <t>Other improvements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High  temperature SmCo  Magnectics inseted into the printer  </t>
+  </si>
+  <si>
+    <t>Connectors added to the Dry box drawer and heated bed for easy servicing</t>
+  </si>
+  <si>
+    <t>Many updates to printer macros to improve performance</t>
+  </si>
+  <si>
+    <t>Specifications</t>
+  </si>
+  <si>
+    <t>Valkyrie V1</t>
+  </si>
+  <si>
+    <t>Valkyrie V2</t>
+  </si>
+  <si>
+    <t>Hevort</t>
+  </si>
+  <si>
+    <t>Voron 2.4</t>
+  </si>
+  <si>
+    <t>RatRig V3</t>
+  </si>
+  <si>
+    <t>BNC3D Epsilon</t>
+  </si>
+  <si>
+    <t>22 Idex V3</t>
+  </si>
+  <si>
+    <t>number of extruders</t>
+  </si>
+  <si>
+    <t>Idex</t>
+  </si>
+  <si>
+    <t>Max print speed</t>
+  </si>
+  <si>
+    <t>500mm/s</t>
+  </si>
+  <si>
+    <t>500 mm/s</t>
+  </si>
+  <si>
+    <t>Max extruder Tempreature</t>
+  </si>
+  <si>
+    <t>245 std, 290 HT</t>
+  </si>
+  <si>
+    <t>500C</t>
+  </si>
+  <si>
+    <t>Max Bed Tempreature deg C</t>
+  </si>
+  <si>
+    <t>120C</t>
+  </si>
+  <si>
+    <t>150C</t>
+  </si>
+  <si>
+    <t>250C</t>
+  </si>
+  <si>
+    <t>Max chamber Temperatue</t>
+  </si>
+  <si>
+    <t>100/active</t>
+  </si>
+  <si>
+    <t>Print Volume X,Y,Z</t>
+  </si>
+  <si>
+    <t>300x300x2xx</t>
+  </si>
+  <si>
+    <t>300x300x300</t>
+  </si>
+  <si>
+    <t>300 to 500 cubed</t>
+  </si>
+  <si>
+    <t>3 sizes, 250,300,350 cubed</t>
+  </si>
+  <si>
+    <t>3 sizes, 300,400,500 cubed</t>
+  </si>
+  <si>
+    <t>420*300*400</t>
+  </si>
+  <si>
+    <t>350 x350 x450</t>
+  </si>
+  <si>
+    <t>self leving bed</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>NON</t>
+  </si>
+  <si>
+    <t>3 point lead screw</t>
+  </si>
+  <si>
+    <t>build plate</t>
+  </si>
+  <si>
+    <t>builders choice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">builder choice </t>
+  </si>
+  <si>
+    <t>energetic PEI magnectic</t>
+  </si>
+  <si>
+    <t>FlexPlate Set - Powder Coated PEI</t>
+  </si>
+  <si>
+    <t>carbon/Glass</t>
+  </si>
+  <si>
+    <t>Bed</t>
+  </si>
+  <si>
+    <t>8mm Aluminium cast 8053 / insulated</t>
+  </si>
+  <si>
+    <t>8mm Aluminium cast 8053 with SmCo magnets</t>
+  </si>
+  <si>
+    <t>builders choiice</t>
+  </si>
+  <si>
+    <t>aluminium plate Rolled / uninsulated</t>
+  </si>
+  <si>
+    <t>6mm cast aluminium tooling plate</t>
+  </si>
+  <si>
+    <t>Glass Build Plate</t>
+  </si>
+  <si>
+    <t>build surface screw fasteners</t>
+  </si>
+  <si>
+    <t>bed probe</t>
+  </si>
+  <si>
+    <t>custom</t>
+  </si>
+  <si>
+    <t>Bltouch</t>
+  </si>
+  <si>
+    <t>inductive</t>
+  </si>
+  <si>
+    <t>BL touch</t>
+  </si>
+  <si>
+    <t>control board</t>
+  </si>
+  <si>
+    <t>Duet 6hc / octopus pro</t>
+  </si>
+  <si>
+    <t>Duet 6HC</t>
+  </si>
+  <si>
+    <t>DuetWifi + Duex5</t>
+  </si>
+  <si>
+    <t>SKR1.4/Spider</t>
+  </si>
+  <si>
+    <t>Duet3mini + Mini2+ or Duet3 6ch or SK pro 1.2</t>
+  </si>
+  <si>
+    <t>Duet 3, 3HC Expansion Board</t>
+  </si>
+  <si>
+    <t>Voltage AC</t>
+  </si>
+  <si>
+    <t>110/230</t>
+  </si>
+  <si>
+    <t>115 or 230</t>
+  </si>
+  <si>
+    <t>84 to 240</t>
+  </si>
+  <si>
+    <t>Enclosure type</t>
+  </si>
+  <si>
+    <t>PIR skined in ACM</t>
+  </si>
+  <si>
+    <t>DiBond</t>
+  </si>
+  <si>
+    <t>acrylic</t>
+  </si>
+  <si>
+    <t>4mm polycarbonate</t>
+  </si>
+  <si>
+    <t>steel and acrylic</t>
+  </si>
+  <si>
+    <t>insulation and steel</t>
+  </si>
+  <si>
+    <t>Filament Runout Sensor</t>
+  </si>
+  <si>
+    <t>Part cooling</t>
+  </si>
+  <si>
+    <t>air /5015 fan 4.5CFM</t>
+  </si>
+  <si>
+    <t>air/Robo fan 26CFM</t>
+  </si>
+  <si>
+    <t>compressor</t>
+  </si>
+  <si>
+    <t>fan</t>
+  </si>
+  <si>
+    <t>air 5015</t>
+  </si>
+  <si>
+    <t>extruder cooling</t>
+  </si>
+  <si>
+    <t>air</t>
+  </si>
+  <si>
+    <t>Water</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>Belt size A/B</t>
+  </si>
+  <si>
+    <t>9mm/2mm pitch</t>
+  </si>
+  <si>
+    <t>9mm/2.0mm pitch</t>
+  </si>
+  <si>
+    <t>6mm std ,9mm HT(mellow)</t>
+  </si>
+  <si>
+    <t>9mm</t>
+  </si>
+  <si>
+    <t>9mm Belts</t>
+  </si>
+  <si>
+    <t>12mm kevlar</t>
+  </si>
+  <si>
+    <t>Z Axis</t>
+  </si>
+  <si>
+    <t>9mm belts</t>
+  </si>
+  <si>
+    <t>lead screw</t>
+  </si>
+  <si>
+    <t>Belt 6 or 9mm</t>
+  </si>
+  <si>
+    <t>lead screw T8 x8</t>
+  </si>
+  <si>
+    <t>Position Accuracy/resolution</t>
+  </si>
+  <si>
+    <t>X/Y: 12.5 μm, Z: 3.125 μm</t>
+  </si>
+  <si>
+    <t>X/Y:10.0 μm, Z: 2.5 μm</t>
+  </si>
+  <si>
+    <t>X/Y: 1.25µm Z: 1µm</t>
+  </si>
+  <si>
+    <t>X/Y: 10 μm, Z: 7 μm</t>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t>Non</t>
+  </si>
+  <si>
+    <t>non</t>
+  </si>
+  <si>
+    <t>H13 HEPA filter, Active Carbon filter</t>
+  </si>
+  <si>
+    <t>Optional HEPA + Active Carbon Filter System (sold separately)</t>
+  </si>
+  <si>
+    <t>Filament Box</t>
+  </si>
+  <si>
+    <t>humidity &amp; tempreature 1kg roll 70C</t>
+  </si>
+  <si>
+    <t>humidity &amp; tempreature 1kg roll 90C</t>
+  </si>
+  <si>
+    <t>humidity control 5 rolls</t>
+  </si>
+  <si>
+    <t>extra</t>
+  </si>
+  <si>
+    <t>Built in UPS</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>Raspberry Pi</t>
+  </si>
+  <si>
+    <t>Print Resoloution layer height</t>
+  </si>
+  <si>
+    <t>Screen</t>
+  </si>
+  <si>
+    <t>option , new Duet release soon</t>
+  </si>
+  <si>
+    <t>yes type?</t>
+  </si>
+  <si>
+    <t>touch 5"</t>
+  </si>
+  <si>
+    <t>Controller Firmware</t>
+  </si>
+  <si>
+    <t>REPRAP</t>
+  </si>
+  <si>
+    <t>klipper/Marrlin</t>
+  </si>
+  <si>
+    <t>Slicer</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>any</t>
+  </si>
+  <si>
+    <t>CURA</t>
+  </si>
+  <si>
+    <t>Bodum or direct drive</t>
+  </si>
+  <si>
+    <t>direct</t>
+  </si>
+  <si>
+    <t>Direct plus Filament buffer</t>
+  </si>
+  <si>
+    <t>builder choice</t>
+  </si>
+  <si>
+    <t>bodun</t>
+  </si>
+  <si>
+    <t>Direct</t>
+  </si>
+  <si>
+    <t>Extruder</t>
+  </si>
+  <si>
+    <t>BTT H2V2S</t>
+  </si>
+  <si>
+    <t>BTT H2V2</t>
+  </si>
+  <si>
+    <t>LGX Pro High-Temp</t>
+  </si>
+  <si>
+    <t>connectivity WIFI USB</t>
+  </si>
+  <si>
+    <t>wifi/LAN</t>
+  </si>
+  <si>
+    <t>Wifi &amp; LAN</t>
+  </si>
+  <si>
+    <t>internal light</t>
+  </si>
+  <si>
+    <t>LED</t>
+  </si>
+  <si>
+    <t>Blue LED</t>
+  </si>
+  <si>
+    <t>RGB</t>
+  </si>
+  <si>
+    <t>Hot end</t>
+  </si>
+  <si>
+    <t>Solid copper</t>
+  </si>
+  <si>
+    <t>Solid Copper</t>
+  </si>
+  <si>
+    <t>Std E3D clone</t>
+  </si>
+  <si>
+    <t>e3D</t>
+  </si>
+  <si>
+    <t>Slice Engineering Copperhead</t>
+  </si>
+  <si>
+    <t>Price Approximately USA $</t>
+  </si>
+  <si>
+    <t>~2000</t>
+  </si>
+  <si>
+    <t>~2400</t>
+  </si>
+  <si>
+    <t>filament Dia</t>
+  </si>
+  <si>
+    <t>Quantity M</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPDM foam </t>
+  </si>
+  <si>
+    <t>5M</t>
+  </si>
+  <si>
+    <t>Door seal / Dry Box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">local hardware store </t>
+  </si>
+  <si>
+    <t>EPDM profile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Square </t>
+  </si>
+  <si>
+    <t>Engineers square</t>
+  </si>
+  <si>
+    <t>Allen keys 1.27,2,3,4,mm 2.5mm ball ended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">steel Rule or  Equiverlant </t>
+  </si>
+  <si>
+    <t xml:space="preserve">G or F clamp </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gust for putting the frame together </t>
+  </si>
+  <si>
+    <t>Spanner  AF 7mm,</t>
+  </si>
+  <si>
+    <t>Drill bits mm  5,4,3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solder iron and solder </t>
+  </si>
+  <si>
+    <t xml:space="preserve">crimp tool for  control board connection </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taps M6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">calipers </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomend Shahe </t>
+  </si>
+  <si>
+    <t>Allen Key short shank 2.5mmfor moth end</t>
+  </si>
+  <si>
+    <t>used on screws on moth end</t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005009139855730.html?</t>
+  </si>
+  <si>
+    <t>Unclog Pin Specially Design </t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005002948629438.html?spm=a2g0o.order_list.order_list_main.192.45b518027U4htK</t>
+  </si>
+  <si>
+    <t>Philips No. 2   ( screws in GX20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Good wire strippers  for the High temperature cable </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lead/Tin Sloder 60/40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">This will make the soldering much easier </t>
+  </si>
+  <si>
+    <t>Things still to do</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>options</t>
+  </si>
+  <si>
+    <t>Find HT magnets for door ( might have to make a holder for SMCO's instead of pot magnets)</t>
+  </si>
+  <si>
+    <t>mark/Roy</t>
+  </si>
+  <si>
+    <t>going to use Nynodinum for now</t>
+  </si>
+  <si>
+    <t>20mm neodynium POT magnet in the oven at 115C for 2 hours it seems ok,</t>
+  </si>
+  <si>
+    <t>Test new Chamber Heater &amp; Fan</t>
+  </si>
+  <si>
+    <t>Roy</t>
+  </si>
+  <si>
+    <t>WIP</t>
+  </si>
+  <si>
+    <t>Mark to Find HT Fan for chamber heater or use external motor as per Roys previous design.</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80mm 24v dc,  testing  with other fans </t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005008197099809.html</t>
+  </si>
+  <si>
+    <t>make a list of basic macros</t>
+  </si>
+  <si>
+    <t>WIP need to confirm a few</t>
+  </si>
+  <si>
+    <t>make a basic config which boards ?</t>
+  </si>
+  <si>
+    <t>M/R</t>
+  </si>
+  <si>
+    <t>workout a way to get esp32 programmed easierly</t>
+  </si>
+  <si>
+    <t>Chris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3rd may Mark/chris  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">front door BOM and Drawings </t>
+  </si>
+  <si>
+    <t>R/M</t>
+  </si>
+  <si>
+    <t>finally finish the Hardware BOM when all above done</t>
   </si>
 </sst>
 </file>
@@ -3404,14 +3404,14 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
-    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
-    <numFmt numFmtId="169" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
-    <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* &quot;-&quot;??_ ;_-@_ "/>
+    <numFmt numFmtId="168" formatCode="_([$$-409]* #,##0_);_([$$-409]* \(#,##0\);_([$$-409]* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+    <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
   </numFmts>
   <fonts count="68">
     <font>
@@ -4196,7 +4196,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="315">
+  <cellXfs count="317">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2"/>
@@ -4223,7 +4223,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4263,10 +4263,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="19" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
@@ -4333,13 +4333,13 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="36" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4399,9 +4399,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -4412,7 +4412,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4460,7 +4460,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4548,7 +4548,7 @@
     <xf numFmtId="3" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4581,7 +4581,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="8" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
@@ -4603,7 +4603,7 @@
     <xf numFmtId="3" fontId="22" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="22" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
@@ -4619,7 +4619,7 @@
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -4666,7 +4666,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="6" fontId="3" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyProtection="1">
@@ -4850,7 +4850,7 @@
     <xf numFmtId="3" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4871,25 +4871,11 @@
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -4897,6 +4883,24 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5217,6 +5221,13 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
           <color indexed="64"/>
@@ -5256,13 +5267,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -5330,20 +5334,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="[h]:mm:ss;@"/>
+      <numFmt numFmtId="169" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="170" formatCode="[$]hh:mm;@" x16r2:formatCode16="[$-en-150,1]hh:mm;@"/>
+      <numFmt numFmtId="170" formatCode="[h]:mm:ss;@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
     </dxf>
     <dxf>
       <font>
@@ -5363,6 +5363,10 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5494,6 +5498,9 @@
       </font>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5510,9 +5517,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5571,6 +5575,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5587,9 +5594,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5648,6 +5652,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5664,9 +5671,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5725,6 +5729,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5741,9 +5748,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5802,6 +5806,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5818,9 +5825,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5879,6 +5883,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5895,9 +5902,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -5972,6 +5976,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -5988,9 +5995,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6049,6 +6053,9 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -6065,9 +6072,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <font>
@@ -6361,7 +6365,7 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6386,7 +6390,7 @@
         <name val="Calibri"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
+      <numFmt numFmtId="165" formatCode="_-[$$-409]* #,##0_ ;_-[$$-409]* \-#,##0\ ;_-[$$-409]* &quot;-&quot;_ ;_-@_ "/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -6461,6 +6465,13 @@
       </border>
     </dxf>
     <dxf>
+      <border>
+        <bottom style="medium">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <top style="medium">
           <color rgb="FF000000"/>
@@ -6479,13 +6490,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="medium">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <border>
@@ -7488,7 +7492,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M152" totalsRowShown="0" dataDxfId="101" headerRowBorderDxfId="102" tableBorderDxfId="100" headerRowCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{1DE5977A-0070-4907-B3F1-83B3E9D3EAF9}" name="Table1321" displayName="Table1321" ref="A1:M152" totalsRowShown="0" dataDxfId="102" headerRowBorderDxfId="100" tableBorderDxfId="101" headerRowCellStyle="Normal 2">
   <autoFilter ref="A1:M152" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}">
     <filterColumn colId="0">
       <filters>
@@ -7529,7 +7533,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E0A0C165-2589-4FA7-A356-93EEE88B2095}" name="Part name" totalsRowDxfId="35" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{49376C16-406D-4D5F-8B92-3BFE5FB962B9}" name="Description" totalsRowDxfId="34" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="33" totalsRowDxfId="32" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{6252F354-5A67-4DD7-A1AA-3DADB5EF6BF7}" name="BOM Quantity" dataDxfId="32" totalsRowDxfId="33" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7542,19 +7546,19 @@
     <sortCondition ref="A1:A91"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="28" totalsRowDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{C89F3025-C91C-4D89-A5CC-8772042DE324}" name="System" dataDxfId="29" totalsRowDxfId="30"/>
+    <tableColumn id="2" xr3:uid="{FCE9DC81-99C5-4DE1-AE60-3B3DE0EE8421}" name="Part" dataDxfId="27" totalsRowDxfId="28"/>
     <tableColumn id="3" xr3:uid="{6512942A-B4C3-4998-AA54-D3A429CF1394}" name="Meters"/>
     <tableColumn id="6" xr3:uid="{672D19F0-1E84-4954-AA80-1A756FF64B85}" name="Weight" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="25" totalsRowDxfId="24" dataCellStyle="Normal 7"/>
-    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="23" totalsRowDxfId="22" dataCellStyle="Normal 7">
+    <tableColumn id="11" xr3:uid="{B345B84F-64A2-4E92-BB95-3C9B14E2A5EA}" name="Items" totalsRowFunction="sum" dataDxfId="24" totalsRowDxfId="25" dataCellStyle="Normal 7"/>
+    <tableColumn id="4" xr3:uid="{8A449E36-4741-4576-8011-21C1B3D5DB29}" name="weight Tot" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="23" dataCellStyle="Normal 7">
       <calculatedColumnFormula>SUM(Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]])</calculatedColumnFormula>
       <totalsRowFormula>SUBTOTAL(109,Table6[weight Tot])&amp;"g"</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="21" totalsRowDxfId="20">
+    <tableColumn id="9" xr3:uid="{DF7CF065-4550-4DB7-B341-EF87320D0C8E}" name="Cost/part" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="21">
       <calculatedColumnFormula>$K$2/1000*Table6[[#This Row],[Weight]]*Table6[[#This Row],[Items]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="19" totalsRowDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{84F519DD-FB90-4299-8700-857D723260B1}" name="Time estimate" totalsRowFunction="sum" dataDxfId="18" totalsRowDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7617,7 +7621,7 @@
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}" name="Table14" displayName="Table14" ref="A4:L37" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13" headerRowCellStyle="Normal 12" dataCellStyle="Normal 12">
   <autoFilter ref="A4:L37" xr:uid="{3F10450C-E6FD-466B-B787-D7901F240217}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -7678,7 +7682,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C5533925-B810-4F05-9221-5D5DC08A3846}" name="Part name" totalsRowDxfId="77" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{13C33B91-92BB-4F0B-8B89-D7D5416E5479}" name="Description" totalsRowDxfId="76" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="75" totalsRowDxfId="74" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{684CEE11-8A68-45FD-871F-FFCFA808FEBD}" name="BOM Quantity" dataDxfId="74" totalsRowDxfId="75" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7693,7 +7697,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{0F292740-142C-4538-B6E0-04426284E315}" name="Part name" totalsRowDxfId="71" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{150C9F57-34E9-40EB-9D7E-4F2F4DC1A13F}" name="Description" totalsRowDxfId="70" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="69" totalsRowDxfId="68" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{A7D6434D-4498-49EB-9D73-D244744029D3}" name="BOM Quantity" dataDxfId="68" totalsRowDxfId="69" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7708,7 +7712,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{B397B237-34CC-4F05-A03A-172D9B10CC01}" name="Part name" totalsRowDxfId="65" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{A1AF3E5A-9878-43E6-8325-6EA13891B687}" name="Description" totalsRowDxfId="64" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="63" totalsRowDxfId="62" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{1585E650-1008-4DC9-8D1C-8F6E78001D58}" name="BOM Quantity" dataDxfId="62" totalsRowDxfId="63" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7723,7 +7727,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{1CE47076-A60D-4220-8B3D-C6D4BAFB1164}" name="Part name" totalsRowDxfId="59" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D41EBA7C-1A32-4553-871C-D0C5C96C9E90}" name="Description" totalsRowDxfId="58" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="57" totalsRowDxfId="56" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{1A8F0BE6-05F1-4339-9CFB-0F9B7B4E13D4}" name="BOM Quantity" dataDxfId="56" totalsRowDxfId="57" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7738,7 +7742,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FEDEBDB4-D2A0-4044-865C-6B89D3CC7592}" name="Part name" totalsRowDxfId="53" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{4C265877-F081-4975-80F2-6B962EBD7F5B}" name="Description" totalsRowDxfId="52" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="51" totalsRowDxfId="50" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{C58356B1-645B-4209-9365-0DE732AD7AAF}" name="BOM Quantity" dataDxfId="50" totalsRowDxfId="51" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7753,7 +7757,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3C370705-9D71-4B07-907E-72DEACEAFBA2}" name="Part name" totalsRowDxfId="47" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{D11DB86B-2519-40CE-A3B1-2DFF1E8D8BAF}" name="Description" totalsRowDxfId="46" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="45" totalsRowDxfId="44" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{030B0BC7-E7B6-43C0-9200-DE84B404D5FA}" name="BOM Quantity" dataDxfId="44" totalsRowDxfId="45" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7768,7 +7772,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D7153C23-8479-4254-BF69-2A4089CB71C0}" name="Part name" totalsRowDxfId="41" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
     <tableColumn id="7" xr3:uid="{5CF4E952-095C-46AE-A57F-99A26E57C478}" name="Description" totalsRowDxfId="40" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 2"/>
-    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="39" totalsRowDxfId="38" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
+    <tableColumn id="2" xr3:uid="{8AE4D1C0-7F70-4D1E-B6EC-42038CE642DF}" name="BOM Quantity" dataDxfId="38" totalsRowDxfId="39" dataCellStyle="Normal 2" totalsRowCellStyle="Normal 8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8037,7 +8041,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1">
+    <row r="2" spans="1:13">
       <c r="A2" s="15" t="s">
         <v>13</v>
       </c>
@@ -8071,7 +8075,7 @@
       <c r="L2" s="68"/>
       <c r="M2" s="129"/>
     </row>
-    <row r="3" spans="1:13" hidden="1">
+    <row r="3" spans="1:13">
       <c r="A3" s="15" t="s">
         <v>13</v>
       </c>
@@ -8105,7 +8109,7 @@
       <c r="L3" s="68"/>
       <c r="M3" s="129"/>
     </row>
-    <row r="4" spans="1:13" hidden="1">
+    <row r="4" spans="1:13">
       <c r="A4" s="15" t="s">
         <v>13</v>
       </c>
@@ -8138,7 +8142,7 @@
       <c r="L4" s="70"/>
       <c r="M4" s="129"/>
     </row>
-    <row r="5" spans="1:13" hidden="1">
+    <row r="5" spans="1:13">
       <c r="A5" s="15" t="s">
         <v>13</v>
       </c>
@@ -8172,7 +8176,7 @@
       <c r="L5" s="68"/>
       <c r="M5" s="129"/>
     </row>
-    <row r="6" spans="1:13" hidden="1">
+    <row r="6" spans="1:13">
       <c r="A6" s="15" t="s">
         <v>13</v>
       </c>
@@ -8206,7 +8210,7 @@
       <c r="L6" s="68"/>
       <c r="M6" s="129"/>
     </row>
-    <row r="7" spans="1:13" hidden="1">
+    <row r="7" spans="1:13">
       <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
@@ -8240,7 +8244,7 @@
       <c r="L7" s="68"/>
       <c r="M7" s="129"/>
     </row>
-    <row r="8" spans="1:13" hidden="1">
+    <row r="8" spans="1:13">
       <c r="A8" s="15" t="s">
         <v>13</v>
       </c>
@@ -8274,7 +8278,7 @@
       <c r="L8" s="68"/>
       <c r="M8" s="129"/>
     </row>
-    <row r="9" spans="1:13" hidden="1">
+    <row r="9" spans="1:13">
       <c r="A9" s="15" t="s">
         <v>13</v>
       </c>
@@ -8308,7 +8312,7 @@
       <c r="L9" s="68"/>
       <c r="M9" s="129"/>
     </row>
-    <row r="10" spans="1:13" hidden="1">
+    <row r="10" spans="1:13">
       <c r="A10" s="15" t="s">
         <v>13</v>
       </c>
@@ -8341,7 +8345,7 @@
       <c r="L10" s="70"/>
       <c r="M10" s="129"/>
     </row>
-    <row r="11" spans="1:13" hidden="1">
+    <row r="11" spans="1:13">
       <c r="A11" s="31" t="s">
         <v>37</v>
       </c>
@@ -8375,7 +8379,7 @@
       <c r="L11" s="68"/>
       <c r="M11" s="129"/>
     </row>
-    <row r="12" spans="1:13" hidden="1">
+    <row r="12" spans="1:13">
       <c r="A12" s="31" t="s">
         <v>37</v>
       </c>
@@ -8409,7 +8413,7 @@
       <c r="L12" s="68"/>
       <c r="M12" s="129"/>
     </row>
-    <row r="13" spans="1:13" hidden="1">
+    <row r="13" spans="1:13">
       <c r="A13" s="31" t="s">
         <v>37</v>
       </c>
@@ -8443,7 +8447,7 @@
       <c r="L13" s="68"/>
       <c r="M13" s="129"/>
     </row>
-    <row r="14" spans="1:13" hidden="1">
+    <row r="14" spans="1:13">
       <c r="A14" s="31" t="s">
         <v>37</v>
       </c>
@@ -8477,7 +8481,7 @@
       <c r="L14" s="68"/>
       <c r="M14" s="129"/>
     </row>
-    <row r="15" spans="1:13" hidden="1">
+    <row r="15" spans="1:13">
       <c r="A15" s="31" t="s">
         <v>37</v>
       </c>
@@ -8511,7 +8515,7 @@
       <c r="L15" s="68"/>
       <c r="M15" s="129"/>
     </row>
-    <row r="16" spans="1:13" hidden="1">
+    <row r="16" spans="1:13">
       <c r="A16" s="31" t="s">
         <v>37</v>
       </c>
@@ -8545,7 +8549,7 @@
       <c r="L16" s="68"/>
       <c r="M16" s="129"/>
     </row>
-    <row r="17" spans="1:13" hidden="1">
+    <row r="17" spans="1:13">
       <c r="A17" s="31" t="s">
         <v>37</v>
       </c>
@@ -8579,7 +8583,7 @@
       <c r="L17" s="68"/>
       <c r="M17" s="129"/>
     </row>
-    <row r="18" spans="1:13" hidden="1">
+    <row r="18" spans="1:13">
       <c r="A18" s="31" t="s">
         <v>37</v>
       </c>
@@ -8611,7 +8615,7 @@
       <c r="L18" s="68"/>
       <c r="M18" s="129"/>
     </row>
-    <row r="19" spans="1:13" hidden="1">
+    <row r="19" spans="1:13">
       <c r="A19" s="31" t="s">
         <v>37</v>
       </c>
@@ -8645,7 +8649,7 @@
       <c r="L19" s="68"/>
       <c r="M19" s="129"/>
     </row>
-    <row r="20" spans="1:13" hidden="1">
+    <row r="20" spans="1:13">
       <c r="A20" s="31" t="s">
         <v>37</v>
       </c>
@@ -8679,7 +8683,7 @@
       <c r="L20" s="68"/>
       <c r="M20" s="129"/>
     </row>
-    <row r="21" spans="1:13" hidden="1">
+    <row r="21" spans="1:13">
       <c r="A21" s="31" t="s">
         <v>37</v>
       </c>
@@ -8713,7 +8717,7 @@
       <c r="L21" s="68"/>
       <c r="M21" s="129"/>
     </row>
-    <row r="22" spans="1:13" hidden="1">
+    <row r="22" spans="1:13">
       <c r="A22" s="31" t="s">
         <v>37</v>
       </c>
@@ -8749,7 +8753,7 @@
       <c r="L22" s="68"/>
       <c r="M22" s="129"/>
     </row>
-    <row r="23" spans="1:13" hidden="1">
+    <row r="23" spans="1:13">
       <c r="A23" s="31" t="s">
         <v>37</v>
       </c>
@@ -8782,7 +8786,7 @@
       <c r="L23" s="68"/>
       <c r="M23" s="129"/>
     </row>
-    <row r="24" spans="1:13" hidden="1">
+    <row r="24" spans="1:13">
       <c r="A24" s="31" t="s">
         <v>37</v>
       </c>
@@ -8815,7 +8819,7 @@
       <c r="L24" s="68"/>
       <c r="M24" s="129"/>
     </row>
-    <row r="25" spans="1:13" hidden="1">
+    <row r="25" spans="1:13">
       <c r="A25" s="31" t="s">
         <v>37</v>
       </c>
@@ -8849,7 +8853,7 @@
       <c r="L25" s="68"/>
       <c r="M25" s="129"/>
     </row>
-    <row r="26" spans="1:13" hidden="1">
+    <row r="26" spans="1:13">
       <c r="A26" s="31" t="s">
         <v>37</v>
       </c>
@@ -8883,7 +8887,7 @@
       <c r="L26" s="68"/>
       <c r="M26" s="129"/>
     </row>
-    <row r="27" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:13" ht="15.75" customHeight="1">
       <c r="A27" s="16" t="s">
         <v>37</v>
       </c>
@@ -8917,7 +8921,7 @@
       <c r="L27" s="68"/>
       <c r="M27" s="129"/>
     </row>
-    <row r="28" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:13" ht="15.75" customHeight="1">
       <c r="A28" s="16" t="s">
         <v>37</v>
       </c>
@@ -8951,7 +8955,7 @@
       <c r="L28" s="68"/>
       <c r="M28" s="129"/>
     </row>
-    <row r="29" spans="1:13" ht="16.5" hidden="1" customHeight="1">
+    <row r="29" spans="1:13" ht="16.5" customHeight="1">
       <c r="A29" s="31" t="s">
         <v>37</v>
       </c>
@@ -8985,7 +8989,7 @@
       <c r="L29" s="68"/>
       <c r="M29" s="129"/>
     </row>
-    <row r="30" spans="1:13" ht="16.5" hidden="1" customHeight="1">
+    <row r="30" spans="1:13" ht="16.5" customHeight="1">
       <c r="A30" s="31" t="s">
         <v>37</v>
       </c>
@@ -9019,7 +9023,7 @@
       <c r="L30" s="68"/>
       <c r="M30" s="129"/>
     </row>
-    <row r="31" spans="1:13" hidden="1">
+    <row r="31" spans="1:13">
       <c r="A31" s="31" t="s">
         <v>37</v>
       </c>
@@ -9053,7 +9057,7 @@
       <c r="L31" s="68"/>
       <c r="M31" s="129"/>
     </row>
-    <row r="32" spans="1:13" hidden="1">
+    <row r="32" spans="1:13">
       <c r="A32" s="31" t="s">
         <v>37</v>
       </c>
@@ -9087,7 +9091,7 @@
       <c r="L32" s="68"/>
       <c r="M32" s="129"/>
     </row>
-    <row r="33" spans="1:13" hidden="1">
+    <row r="33" spans="1:13">
       <c r="A33" s="31" t="s">
         <v>37</v>
       </c>
@@ -9121,7 +9125,7 @@
       <c r="L33" s="68"/>
       <c r="M33" s="129"/>
     </row>
-    <row r="34" spans="1:13" hidden="1">
+    <row r="34" spans="1:13">
       <c r="A34" s="31" t="s">
         <v>37</v>
       </c>
@@ -9155,7 +9159,7 @@
       <c r="L34" s="68"/>
       <c r="M34" s="129"/>
     </row>
-    <row r="35" spans="1:13" hidden="1">
+    <row r="35" spans="1:13">
       <c r="A35" s="31" t="s">
         <v>37</v>
       </c>
@@ -9189,7 +9193,7 @@
       <c r="L35" s="68"/>
       <c r="M35" s="129"/>
     </row>
-    <row r="36" spans="1:13" hidden="1">
+    <row r="36" spans="1:13">
       <c r="A36" s="31" t="s">
         <v>37</v>
       </c>
@@ -9223,7 +9227,7 @@
       <c r="L36" s="68"/>
       <c r="M36" s="129"/>
     </row>
-    <row r="37" spans="1:13" hidden="1">
+    <row r="37" spans="1:13">
       <c r="A37" s="31" t="s">
         <v>37</v>
       </c>
@@ -9257,7 +9261,7 @@
       <c r="L37" s="68"/>
       <c r="M37" s="129"/>
     </row>
-    <row r="38" spans="1:13" hidden="1">
+    <row r="38" spans="1:13">
       <c r="A38" s="31" t="s">
         <v>37</v>
       </c>
@@ -9291,7 +9295,7 @@
       <c r="L38" s="68"/>
       <c r="M38" s="129"/>
     </row>
-    <row r="39" spans="1:13" hidden="1">
+    <row r="39" spans="1:13">
       <c r="A39" s="31" t="s">
         <v>37</v>
       </c>
@@ -9325,7 +9329,7 @@
       <c r="L39" s="68"/>
       <c r="M39" s="129"/>
     </row>
-    <row r="40" spans="1:13" hidden="1">
+    <row r="40" spans="1:13">
       <c r="A40" s="31" t="s">
         <v>37</v>
       </c>
@@ -9359,7 +9363,7 @@
       <c r="L40" s="68"/>
       <c r="M40" s="129"/>
     </row>
-    <row r="41" spans="1:13" hidden="1">
+    <row r="41" spans="1:13">
       <c r="A41" s="31" t="s">
         <v>37</v>
       </c>
@@ -9393,7 +9397,7 @@
       <c r="L41" s="68"/>
       <c r="M41" s="129"/>
     </row>
-    <row r="42" spans="1:13" hidden="1">
+    <row r="42" spans="1:13">
       <c r="A42" s="31" t="s">
         <v>37</v>
       </c>
@@ -9427,7 +9431,7 @@
       <c r="L42" s="68"/>
       <c r="M42" s="129"/>
     </row>
-    <row r="43" spans="1:13" hidden="1">
+    <row r="43" spans="1:13">
       <c r="A43" s="31" t="s">
         <v>37</v>
       </c>
@@ -9461,7 +9465,7 @@
       <c r="L43" s="68"/>
       <c r="M43" s="129"/>
     </row>
-    <row r="44" spans="1:13" hidden="1">
+    <row r="44" spans="1:13">
       <c r="A44" s="31" t="s">
         <v>37</v>
       </c>
@@ -9495,7 +9499,7 @@
       <c r="L44" s="68"/>
       <c r="M44" s="129"/>
     </row>
-    <row r="45" spans="1:13" hidden="1">
+    <row r="45" spans="1:13">
       <c r="A45" s="31" t="s">
         <v>37</v>
       </c>
@@ -9529,7 +9533,7 @@
       <c r="L45" s="68"/>
       <c r="M45" s="129"/>
     </row>
-    <row r="46" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:13" ht="15.75" customHeight="1">
       <c r="A46" s="31" t="s">
         <v>37</v>
       </c>
@@ -9563,7 +9567,7 @@
       <c r="L46" s="68"/>
       <c r="M46" s="129"/>
     </row>
-    <row r="47" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:13" ht="15.75" customHeight="1">
       <c r="A47" s="31" t="s">
         <v>37</v>
       </c>
@@ -9597,7 +9601,7 @@
       <c r="L47" s="68"/>
       <c r="M47" s="129"/>
     </row>
-    <row r="48" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:13" ht="15.75" customHeight="1">
       <c r="A48" s="31" t="s">
         <v>37</v>
       </c>
@@ -9631,7 +9635,7 @@
       <c r="L48" s="68"/>
       <c r="M48" s="129"/>
     </row>
-    <row r="49" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:13" ht="15.75" customHeight="1">
       <c r="A49" s="31" t="s">
         <v>37</v>
       </c>
@@ -9665,7 +9669,7 @@
       <c r="L49" s="68"/>
       <c r="M49" s="129"/>
     </row>
-    <row r="50" spans="1:13" hidden="1">
+    <row r="50" spans="1:13">
       <c r="A50" s="31" t="s">
         <v>37</v>
       </c>
@@ -9699,7 +9703,7 @@
       <c r="L50" s="68"/>
       <c r="M50" s="129"/>
     </row>
-    <row r="51" spans="1:13" hidden="1">
+    <row r="51" spans="1:13">
       <c r="A51" s="31" t="s">
         <v>37</v>
       </c>
@@ -9723,13 +9727,13 @@
       <c r="H51" s="152" t="s">
         <v>126</v>
       </c>
-      <c r="I51" s="308"/>
+      <c r="I51" s="312"/>
       <c r="J51" s="94"/>
       <c r="K51" s="10"/>
       <c r="L51" s="68"/>
       <c r="M51" s="129"/>
     </row>
-    <row r="52" spans="1:13" hidden="1">
+    <row r="52" spans="1:13">
       <c r="A52" s="31" t="s">
         <v>37</v>
       </c>
@@ -9753,13 +9757,13 @@
       <c r="H52" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="I52" s="308"/>
+      <c r="I52" s="312"/>
       <c r="J52" s="94"/>
       <c r="K52" s="10"/>
       <c r="L52" s="68"/>
       <c r="M52" s="129"/>
     </row>
-    <row r="53" spans="1:13" hidden="1">
+    <row r="53" spans="1:13">
       <c r="A53" s="31" t="s">
         <v>37</v>
       </c>
@@ -9793,7 +9797,7 @@
       <c r="L53" s="68"/>
       <c r="M53" s="129"/>
     </row>
-    <row r="54" spans="1:13" hidden="1">
+    <row r="54" spans="1:13">
       <c r="A54" s="31" t="s">
         <v>37</v>
       </c>
@@ -9827,7 +9831,7 @@
       <c r="L54" s="68"/>
       <c r="M54" s="129"/>
     </row>
-    <row r="55" spans="1:13" hidden="1">
+    <row r="55" spans="1:13">
       <c r="A55" s="31" t="s">
         <v>37</v>
       </c>
@@ -9861,7 +9865,7 @@
       <c r="L55" s="68"/>
       <c r="M55" s="129"/>
     </row>
-    <row r="56" spans="1:13" hidden="1">
+    <row r="56" spans="1:13">
       <c r="A56" s="31" t="s">
         <v>37</v>
       </c>
@@ -9895,7 +9899,7 @@
       <c r="L56" s="68"/>
       <c r="M56" s="129"/>
     </row>
-    <row r="57" spans="1:13" hidden="1">
+    <row r="57" spans="1:13">
       <c r="A57" s="16" t="s">
         <v>37</v>
       </c>
@@ -9929,7 +9933,7 @@
       <c r="L57" s="37"/>
       <c r="M57" s="129"/>
     </row>
-    <row r="58" spans="1:13" hidden="1">
+    <row r="58" spans="1:13">
       <c r="A58" s="31" t="s">
         <v>37</v>
       </c>
@@ -9963,7 +9967,7 @@
       <c r="L58" s="68"/>
       <c r="M58" s="129"/>
     </row>
-    <row r="59" spans="1:13" hidden="1">
+    <row r="59" spans="1:13">
       <c r="A59" s="31" t="s">
         <v>37</v>
       </c>
@@ -9995,7 +9999,7 @@
       <c r="L59" s="68"/>
       <c r="M59" s="129"/>
     </row>
-    <row r="60" spans="1:13" hidden="1">
+    <row r="60" spans="1:13">
       <c r="A60" s="31" t="s">
         <v>37</v>
       </c>
@@ -10029,7 +10033,7 @@
       <c r="L60" s="68"/>
       <c r="M60" s="129"/>
     </row>
-    <row r="61" spans="1:13" ht="17.25" hidden="1" customHeight="1">
+    <row r="61" spans="1:13" ht="17.25" customHeight="1">
       <c r="A61" s="31" t="s">
         <v>37</v>
       </c>
@@ -10065,7 +10069,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="17.25" hidden="1" customHeight="1">
+    <row r="62" spans="1:13" ht="17.25" customHeight="1">
       <c r="A62" s="31" t="s">
         <v>37</v>
       </c>
@@ -10097,7 +10101,7 @@
       <c r="L62" s="68"/>
       <c r="M62" s="129"/>
     </row>
-    <row r="63" spans="1:13" ht="15.75" hidden="1">
+    <row r="63" spans="1:13" ht="15.75">
       <c r="A63" s="31" t="s">
         <v>37</v>
       </c>
@@ -10117,7 +10121,7 @@
       <c r="H63" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="I63" s="308"/>
+      <c r="I63" s="312"/>
       <c r="J63" s="94"/>
       <c r="K63" s="10"/>
       <c r="L63" s="68"/>
@@ -10125,7 +10129,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1">
+    <row r="64" spans="1:13">
       <c r="A64" s="31" t="s">
         <v>37</v>
       </c>
@@ -10159,7 +10163,7 @@
       <c r="L64" s="68"/>
       <c r="M64" s="129"/>
     </row>
-    <row r="65" spans="1:13" hidden="1">
+    <row r="65" spans="1:13">
       <c r="A65" s="31" t="s">
         <v>160</v>
       </c>
@@ -10192,7 +10196,7 @@
       <c r="L65" s="68"/>
       <c r="M65" s="129"/>
     </row>
-    <row r="66" spans="1:13" hidden="1">
+    <row r="66" spans="1:13">
       <c r="A66" s="31" t="s">
         <v>160</v>
       </c>
@@ -10225,7 +10229,7 @@
       <c r="L66" s="70"/>
       <c r="M66" s="129"/>
     </row>
-    <row r="67" spans="1:13" hidden="1">
+    <row r="67" spans="1:13">
       <c r="A67" s="15" t="s">
         <v>160</v>
       </c>
@@ -10258,7 +10262,7 @@
       <c r="L67" s="68"/>
       <c r="M67" s="129"/>
     </row>
-    <row r="68" spans="1:13" hidden="1">
+    <row r="68" spans="1:13">
       <c r="A68" s="15" t="s">
         <v>160</v>
       </c>
@@ -10296,7 +10300,7 @@
       </c>
       <c r="M68" s="129"/>
     </row>
-    <row r="69" spans="1:13" hidden="1">
+    <row r="69" spans="1:13">
       <c r="A69" s="15" t="s">
         <v>160</v>
       </c>
@@ -10334,7 +10338,7 @@
       </c>
       <c r="M69" s="129"/>
     </row>
-    <row r="70" spans="1:13" hidden="1">
+    <row r="70" spans="1:13">
       <c r="A70" s="15" t="s">
         <v>160</v>
       </c>
@@ -10370,7 +10374,7 @@
       <c r="L70" s="68"/>
       <c r="M70" s="129"/>
     </row>
-    <row r="71" spans="1:13" hidden="1">
+    <row r="71" spans="1:13">
       <c r="A71" s="31" t="s">
         <v>160</v>
       </c>
@@ -10405,7 +10409,7 @@
       <c r="L71" s="68"/>
       <c r="M71" s="129"/>
     </row>
-    <row r="72" spans="1:13" hidden="1">
+    <row r="72" spans="1:13">
       <c r="A72" s="31" t="s">
         <v>160</v>
       </c>
@@ -10441,7 +10445,7 @@
       <c r="L72" s="70"/>
       <c r="M72" s="129"/>
     </row>
-    <row r="73" spans="1:13" hidden="1">
+    <row r="73" spans="1:13">
       <c r="A73" s="31" t="s">
         <v>160</v>
       </c>
@@ -10477,7 +10481,7 @@
       <c r="L73" s="68"/>
       <c r="M73" s="129"/>
     </row>
-    <row r="74" spans="1:13" hidden="1">
+    <row r="74" spans="1:13">
       <c r="A74" s="31" t="s">
         <v>160</v>
       </c>
@@ -10512,7 +10516,7 @@
       <c r="L74" s="68"/>
       <c r="M74" s="129"/>
     </row>
-    <row r="75" spans="1:13" hidden="1">
+    <row r="75" spans="1:13">
       <c r="A75" s="31" t="s">
         <v>160</v>
       </c>
@@ -10548,7 +10552,7 @@
       <c r="L75" s="68"/>
       <c r="M75" s="129"/>
     </row>
-    <row r="76" spans="1:13" hidden="1">
+    <row r="76" spans="1:13">
       <c r="A76" s="31" t="s">
         <v>160</v>
       </c>
@@ -10584,7 +10588,7 @@
       </c>
       <c r="M76" s="129"/>
     </row>
-    <row r="77" spans="1:13" hidden="1">
+    <row r="77" spans="1:13">
       <c r="A77" s="15" t="s">
         <v>160</v>
       </c>
@@ -10620,7 +10624,7 @@
       <c r="L77" s="68"/>
       <c r="M77" s="129"/>
     </row>
-    <row r="78" spans="1:13" hidden="1">
+    <row r="78" spans="1:13">
       <c r="A78" s="31" t="s">
         <v>160</v>
       </c>
@@ -10656,7 +10660,7 @@
       <c r="L78" s="68"/>
       <c r="M78" s="129"/>
     </row>
-    <row r="79" spans="1:13" hidden="1">
+    <row r="79" spans="1:13">
       <c r="A79" s="15" t="s">
         <v>160</v>
       </c>
@@ -10692,7 +10696,7 @@
       <c r="L79" s="70"/>
       <c r="M79" s="129"/>
     </row>
-    <row r="80" spans="1:13" hidden="1">
+    <row r="80" spans="1:13">
       <c r="A80" s="15" t="s">
         <v>160</v>
       </c>
@@ -10726,7 +10730,7 @@
       <c r="L80" s="68"/>
       <c r="M80" s="129"/>
     </row>
-    <row r="81" spans="1:13" hidden="1">
+    <row r="81" spans="1:13">
       <c r="A81" s="15" t="s">
         <v>160</v>
       </c>
@@ -10762,7 +10766,7 @@
       <c r="L81" s="68"/>
       <c r="M81" s="129"/>
     </row>
-    <row r="82" spans="1:13" hidden="1">
+    <row r="82" spans="1:13">
       <c r="A82" s="15" t="s">
         <v>160</v>
       </c>
@@ -10796,7 +10800,7 @@
       <c r="L82" s="68"/>
       <c r="M82" s="129"/>
     </row>
-    <row r="83" spans="1:13" ht="15.75" hidden="1" customHeight="1">
+    <row r="83" spans="1:13" ht="15.75" customHeight="1">
       <c r="A83" s="15" t="s">
         <v>160</v>
       </c>
@@ -10834,7 +10838,7 @@
       </c>
       <c r="M83" s="129"/>
     </row>
-    <row r="84" spans="1:13" hidden="1">
+    <row r="84" spans="1:13">
       <c r="A84" s="31" t="s">
         <v>160</v>
       </c>
@@ -10869,7 +10873,7 @@
       <c r="L84" s="70"/>
       <c r="M84" s="129"/>
     </row>
-    <row r="85" spans="1:13" hidden="1">
+    <row r="85" spans="1:13">
       <c r="A85" s="31" t="s">
         <v>160</v>
       </c>
@@ -10907,7 +10911,7 @@
       </c>
       <c r="M85" s="129"/>
     </row>
-    <row r="86" spans="1:13" hidden="1">
+    <row r="86" spans="1:13">
       <c r="A86" s="31" t="s">
         <v>160</v>
       </c>
@@ -10942,7 +10946,7 @@
       <c r="L86" s="70"/>
       <c r="M86" s="129"/>
     </row>
-    <row r="87" spans="1:13" hidden="1">
+    <row r="87" spans="1:13">
       <c r="A87" s="15" t="s">
         <v>160</v>
       </c>
@@ -10976,7 +10980,7 @@
       <c r="L87" s="68"/>
       <c r="M87" s="129"/>
     </row>
-    <row r="88" spans="1:13" hidden="1">
+    <row r="88" spans="1:13">
       <c r="A88" s="31" t="s">
         <v>160</v>
       </c>
@@ -11012,7 +11016,7 @@
       <c r="L88" s="68"/>
       <c r="M88" s="129"/>
     </row>
-    <row r="89" spans="1:13" hidden="1">
+    <row r="89" spans="1:13">
       <c r="A89" s="15" t="s">
         <v>160</v>
       </c>
@@ -11046,7 +11050,7 @@
       <c r="L89" s="68"/>
       <c r="M89" s="129"/>
     </row>
-    <row r="90" spans="1:13" hidden="1">
+    <row r="90" spans="1:13">
       <c r="A90" s="31" t="s">
         <v>160</v>
       </c>
@@ -11083,7 +11087,7 @@
       </c>
       <c r="M90" s="129"/>
     </row>
-    <row r="91" spans="1:13" hidden="1">
+    <row r="91" spans="1:13">
       <c r="A91" s="31" t="s">
         <v>160</v>
       </c>
@@ -11119,7 +11123,7 @@
       <c r="L91" s="70"/>
       <c r="M91" s="129"/>
     </row>
-    <row r="92" spans="1:13" hidden="1">
+    <row r="92" spans="1:13">
       <c r="A92" s="31" t="s">
         <v>160</v>
       </c>
@@ -11155,7 +11159,7 @@
       <c r="L92" s="70"/>
       <c r="M92" s="129"/>
     </row>
-    <row r="93" spans="1:13" hidden="1">
+    <row r="93" spans="1:13">
       <c r="A93" s="31" t="s">
         <v>160</v>
       </c>
@@ -11193,7 +11197,7 @@
       </c>
       <c r="M93" s="129"/>
     </row>
-    <row r="94" spans="1:13" hidden="1">
+    <row r="94" spans="1:13">
       <c r="A94" s="31" t="s">
         <v>160</v>
       </c>
@@ -11226,7 +11230,7 @@
       <c r="L94" s="68"/>
       <c r="M94" s="129"/>
     </row>
-    <row r="95" spans="1:13" hidden="1">
+    <row r="95" spans="1:13">
       <c r="A95" s="31" t="s">
         <v>160</v>
       </c>
@@ -11262,7 +11266,7 @@
       <c r="L95" s="70"/>
       <c r="M95" s="129"/>
     </row>
-    <row r="96" spans="1:13" hidden="1">
+    <row r="96" spans="1:13">
       <c r="A96" s="31" t="s">
         <v>160</v>
       </c>
@@ -11299,7 +11303,7 @@
       </c>
       <c r="M96" s="129"/>
     </row>
-    <row r="97" spans="1:13" hidden="1">
+    <row r="97" spans="1:13">
       <c r="A97" s="31" t="s">
         <v>160</v>
       </c>
@@ -11335,7 +11339,7 @@
       <c r="L97" s="68"/>
       <c r="M97" s="129"/>
     </row>
-    <row r="98" spans="1:13" hidden="1">
+    <row r="98" spans="1:13">
       <c r="A98" s="31" t="s">
         <v>160</v>
       </c>
@@ -11371,7 +11375,7 @@
       </c>
       <c r="M98" s="129"/>
     </row>
-    <row r="99" spans="1:13" hidden="1">
+    <row r="99" spans="1:13">
       <c r="A99" s="31" t="s">
         <v>160</v>
       </c>
@@ -11407,7 +11411,7 @@
       </c>
       <c r="M99" s="129"/>
     </row>
-    <row r="100" spans="1:13" hidden="1">
+    <row r="100" spans="1:13">
       <c r="A100" s="31" t="s">
         <v>160</v>
       </c>
@@ -11445,7 +11449,7 @@
       </c>
       <c r="M100" s="129"/>
     </row>
-    <row r="101" spans="1:13" hidden="1">
+    <row r="101" spans="1:13">
       <c r="A101" s="31" t="s">
         <v>160</v>
       </c>
@@ -11481,7 +11485,7 @@
       </c>
       <c r="M101" s="129"/>
     </row>
-    <row r="102" spans="1:13" hidden="1">
+    <row r="102" spans="1:13">
       <c r="A102" s="31" t="s">
         <v>160</v>
       </c>
@@ -11517,7 +11521,7 @@
       <c r="L102" s="68"/>
       <c r="M102" s="129"/>
     </row>
-    <row r="103" spans="1:13" s="301" customFormat="1" hidden="1">
+    <row r="103" spans="1:13" s="301" customFormat="1">
       <c r="A103" s="293" t="s">
         <v>160</v>
       </c>
@@ -11555,7 +11559,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="104" spans="1:13" s="301" customFormat="1" hidden="1">
+    <row r="104" spans="1:13" s="301" customFormat="1">
       <c r="A104" s="293" t="s">
         <v>160</v>
       </c>
@@ -11593,7 +11597,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="105" spans="1:13" hidden="1">
+    <row r="105" spans="1:13">
       <c r="A105" s="15" t="s">
         <v>160</v>
       </c>
@@ -11629,7 +11633,7 @@
       </c>
       <c r="M105" s="129"/>
     </row>
-    <row r="106" spans="1:13" hidden="1">
+    <row r="106" spans="1:13">
       <c r="A106" s="15" t="s">
         <v>246</v>
       </c>
@@ -11663,7 +11667,7 @@
       <c r="L106" s="68"/>
       <c r="M106" s="129"/>
     </row>
-    <row r="107" spans="1:13" hidden="1">
+    <row r="107" spans="1:13">
       <c r="A107" s="15" t="s">
         <v>246</v>
       </c>
@@ -11695,7 +11699,7 @@
       <c r="L107" s="68"/>
       <c r="M107" s="129"/>
     </row>
-    <row r="108" spans="1:13" hidden="1">
+    <row r="108" spans="1:13">
       <c r="A108" s="135" t="s">
         <v>246</v>
       </c>
@@ -11729,7 +11733,7 @@
       <c r="L108" s="137"/>
       <c r="M108" s="138"/>
     </row>
-    <row r="109" spans="1:13" hidden="1">
+    <row r="109" spans="1:13">
       <c r="A109" s="15" t="s">
         <v>246</v>
       </c>
@@ -11763,7 +11767,7 @@
       <c r="L109" s="68"/>
       <c r="M109" s="129"/>
     </row>
-    <row r="110" spans="1:13" hidden="1">
+    <row r="110" spans="1:13">
       <c r="A110" s="15" t="s">
         <v>246</v>
       </c>
@@ -11797,7 +11801,7 @@
       <c r="L110" s="68"/>
       <c r="M110" s="129"/>
     </row>
-    <row r="111" spans="1:13" hidden="1">
+    <row r="111" spans="1:13">
       <c r="A111" s="15" t="s">
         <v>258</v>
       </c>
@@ -11831,7 +11835,7 @@
       <c r="L111" s="68"/>
       <c r="M111" s="129"/>
     </row>
-    <row r="112" spans="1:13" hidden="1">
+    <row r="112" spans="1:13">
       <c r="A112" s="15" t="s">
         <v>258</v>
       </c>
@@ -11865,7 +11869,7 @@
       <c r="L112" s="68"/>
       <c r="M112" s="129"/>
     </row>
-    <row r="113" spans="1:13" hidden="1">
+    <row r="113" spans="1:13">
       <c r="A113" s="15" t="s">
         <v>258</v>
       </c>
@@ -11898,7 +11902,7 @@
       <c r="L113" s="68"/>
       <c r="M113" s="129"/>
     </row>
-    <row r="114" spans="1:13" hidden="1">
+    <row r="114" spans="1:13">
       <c r="A114" s="15" t="s">
         <v>258</v>
       </c>
@@ -13258,7 +13262,7 @@
       <c r="F153" s="34"/>
       <c r="G153" s="35">
         <f>SUBTOTAL(109,Table1321[*Cost Price $USD])</f>
-        <v>157.46</v>
+        <v>1597.5200000000002</v>
       </c>
       <c r="H153" s="196" t="s">
         <v>376</v>
@@ -15569,7 +15573,7 @@
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="309" t="s">
+      <c r="A93" s="313" t="s">
         <v>689</v>
       </c>
       <c r="B93" t="s">
@@ -15638,140 +15642,140 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>726</v>
+        <v>701</v>
       </c>
       <c r="B1" t="s">
-        <v>727</v>
+        <v>702</v>
       </c>
       <c r="C1" t="s">
         <v>378</v>
       </c>
       <c r="D1" t="s">
-        <v>728</v>
+        <v>703</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>729</v>
+        <v>704</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>730</v>
+        <v>705</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>731</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" t="s">
-        <v>732</v>
+        <v>707</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>733</v>
+        <v>708</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>734</v>
+        <v>709</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>735</v>
+        <v>710</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>736</v>
+        <v>711</v>
       </c>
       <c r="C4" t="s">
-        <v>737</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>738</v>
+        <v>713</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>739</v>
+        <v>714</v>
       </c>
       <c r="C5" t="s">
-        <v>740</v>
+        <v>715</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>741</v>
+        <v>716</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="12" customHeight="1">
       <c r="A6" t="s">
-        <v>742</v>
+        <v>717</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>743</v>
+        <v>718</v>
       </c>
       <c r="C6" t="s">
-        <v>744</v>
+        <v>719</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>745</v>
+        <v>720</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>746</v>
+        <v>721</v>
       </c>
       <c r="C7" t="s">
-        <v>747</v>
+        <v>722</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>748</v>
+        <v>723</v>
       </c>
       <c r="B8" s="203" t="s">
-        <v>749</v>
+        <v>724</v>
       </c>
       <c r="C8" t="s">
-        <v>750</v>
+        <v>725</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>751</v>
+        <v>726</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>752</v>
+        <v>727</v>
       </c>
       <c r="C9" t="s">
-        <v>753</v>
+        <v>728</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>754</v>
+        <v>729</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>755</v>
+        <v>730</v>
       </c>
       <c r="C10" t="s">
-        <v>756</v>
+        <v>731</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>757</v>
+        <v>732</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>758</v>
+        <v>733</v>
       </c>
       <c r="C11" t="s">
-        <v>759</v>
+        <v>734</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="251" t="s">
-        <v>760</v>
+        <v>735</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>761</v>
+        <v>736</v>
       </c>
       <c r="C12" t="s">
-        <v>762</v>
+        <v>737</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -15779,7 +15783,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>726</v>
+        <v>701</v>
       </c>
       <c r="B14" s="93" t="s">
         <v>661</v>
@@ -15793,151 +15797,151 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>763</v>
+        <v>738</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>764</v>
+        <v>739</v>
       </c>
       <c r="C15" t="s">
-        <v>765</v>
+        <v>740</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="B16" s="38" t="s">
-        <v>766</v>
+        <v>741</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>767</v>
+        <v>742</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="B17" s="38" t="s">
-        <v>768</v>
+        <v>743</v>
       </c>
       <c r="C17" t="s">
-        <v>769</v>
+        <v>744</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="B18" s="38" t="s">
-        <v>770</v>
+        <v>745</v>
       </c>
       <c r="C18" t="s">
-        <v>771</v>
+        <v>746</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="B19" s="38" t="s">
-        <v>772</v>
+        <v>747</v>
       </c>
       <c r="C19" t="s">
-        <v>773</v>
+        <v>748</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="38" t="s">
-        <v>774</v>
+        <v>749</v>
       </c>
       <c r="C20" t="s">
-        <v>775</v>
+        <v>750</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="B21" s="38" t="s">
-        <v>776</v>
+        <v>751</v>
       </c>
       <c r="C21" t="s">
-        <v>777</v>
+        <v>752</v>
       </c>
       <c r="D21" s="250" t="s">
-        <v>778</v>
+        <v>753</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>779</v>
+        <v>754</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>780</v>
+        <v>755</v>
       </c>
       <c r="C22" t="s">
-        <v>781</v>
+        <v>756</v>
       </c>
       <c r="D22" t="s">
-        <v>782</v>
+        <v>757</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="B23" s="38" t="s">
-        <v>783</v>
+        <v>758</v>
       </c>
       <c r="C23" t="s">
-        <v>784</v>
+        <v>759</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="B24" s="38" t="s">
-        <v>785</v>
+        <v>760</v>
       </c>
       <c r="C24" t="s">
-        <v>786</v>
+        <v>761</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="B25" s="38" t="s">
-        <v>787</v>
+        <v>762</v>
       </c>
       <c r="C25" t="s">
-        <v>788</v>
+        <v>763</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>789</v>
+        <v>764</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>790</v>
+        <v>765</v>
       </c>
       <c r="C26" t="s">
-        <v>791</v>
+        <v>766</v>
       </c>
       <c r="D26" t="s">
-        <v>792</v>
+        <v>767</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>793</v>
+        <v>768</v>
       </c>
       <c r="B27" s="38" t="s">
-        <v>794</v>
+        <v>769</v>
       </c>
       <c r="C27" t="s">
-        <v>795</v>
+        <v>770</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="B28" s="38" t="s">
-        <v>796</v>
+        <v>771</v>
       </c>
       <c r="C28" t="s">
-        <v>797</v>
+        <v>772</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="B29" s="38" t="s">
-        <v>798</v>
+        <v>773</v>
       </c>
       <c r="C29" t="s">
-        <v>799</v>
+        <v>774</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="B30" s="38" t="s">
-        <v>800</v>
+        <v>775</v>
       </c>
       <c r="C30" t="s">
-        <v>801</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -15948,10 +15952,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>802</v>
+        <v>777</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>803</v>
+        <v>778</v>
       </c>
       <c r="C33" t="s">
         <v>378</v>
@@ -15959,68 +15963,68 @@
     </row>
     <row r="34" spans="1:4">
       <c r="B34" t="s">
-        <v>804</v>
+        <v>779</v>
       </c>
       <c r="C34" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="B35" t="s">
-        <v>806</v>
+        <v>781</v>
       </c>
       <c r="C35" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="B36" t="s">
-        <v>807</v>
+        <v>782</v>
       </c>
       <c r="C36" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="B37" t="s">
-        <v>808</v>
+        <v>783</v>
       </c>
       <c r="C37" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="B39" t="s">
-        <v>809</v>
+        <v>784</v>
       </c>
       <c r="C39" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
       <c r="D39" t="s">
-        <v>810</v>
+        <v>785</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="D40" t="s">
-        <v>811</v>
+        <v>786</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="B41" t="s">
-        <v>812</v>
+        <v>787</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="B42" t="s">
-        <v>813</v>
+        <v>788</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>802</v>
+        <v>777</v>
       </c>
       <c r="B44" s="60" t="s">
-        <v>814</v>
+        <v>789</v>
       </c>
       <c r="C44" t="s">
         <v>378</v>
@@ -16028,82 +16032,82 @@
     </row>
     <row r="45" spans="1:4">
       <c r="B45" t="s">
-        <v>815</v>
+        <v>790</v>
       </c>
       <c r="C45" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="B46" t="s">
-        <v>816</v>
+        <v>791</v>
       </c>
       <c r="C46" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="B47" t="s">
-        <v>817</v>
+        <v>792</v>
       </c>
       <c r="C47" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="B48" t="s">
-        <v>818</v>
+        <v>793</v>
       </c>
       <c r="C48" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="49" spans="2:3">
       <c r="B49" t="s">
-        <v>819</v>
+        <v>794</v>
       </c>
       <c r="C49" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="50" spans="2:3">
       <c r="B50" t="s">
-        <v>820</v>
+        <v>795</v>
       </c>
       <c r="C50" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="51" spans="2:3">
       <c r="B51" t="s">
-        <v>821</v>
+        <v>796</v>
       </c>
       <c r="C51" t="s">
-        <v>822</v>
+        <v>797</v>
       </c>
     </row>
     <row r="52" spans="2:3">
       <c r="B52" t="s">
-        <v>823</v>
+        <v>798</v>
       </c>
       <c r="C52" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="53" spans="2:3">
       <c r="B53" t="s">
-        <v>824</v>
+        <v>799</v>
       </c>
       <c r="C53" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
     <row r="54" spans="2:3">
       <c r="B54" t="s">
-        <v>825</v>
+        <v>800</v>
       </c>
       <c r="C54" t="s">
-        <v>805</v>
+        <v>780</v>
       </c>
     </row>
   </sheetData>
@@ -16144,97 +16148,115 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1">
       <c r="A1" s="223" t="s">
-        <v>1028</v>
-      </c>
-      <c r="B1" s="220"/>
-      <c r="C1" s="220"/>
+        <v>801</v>
+      </c>
+      <c r="B1" s="309"/>
+      <c r="C1" s="309"/>
+      <c r="D1" s="309"/>
+      <c r="E1" s="309"/>
+      <c r="F1" s="309"/>
+      <c r="G1" s="309"/>
+      <c r="H1" s="309"/>
+      <c r="I1" s="309"/>
+      <c r="J1" s="309"/>
+      <c r="K1" s="309"/>
+      <c r="L1" s="309"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="224" t="s">
-        <v>1029</v>
-      </c>
-      <c r="B2" s="220"/>
-      <c r="C2" s="220"/>
+        <v>802</v>
+      </c>
+      <c r="B2" s="309"/>
+      <c r="C2" s="309"/>
+      <c r="D2" s="309"/>
+      <c r="E2" s="309"/>
+      <c r="F2" s="309"/>
+      <c r="G2" s="309"/>
+      <c r="H2" s="309"/>
+      <c r="I2" s="309"/>
+      <c r="J2" s="309"/>
+      <c r="K2" s="309"/>
+      <c r="L2" s="309"/>
     </row>
     <row r="3" spans="1:12" s="222" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="243"/>
       <c r="B3" s="244"/>
       <c r="C3" s="244"/>
       <c r="D3" s="226" t="s">
-        <v>1030</v>
+        <v>803</v>
       </c>
       <c r="E3" s="226" t="s">
-        <v>1030</v>
+        <v>803</v>
       </c>
       <c r="F3" s="226" t="s">
-        <v>1030</v>
+        <v>803</v>
       </c>
       <c r="G3" s="226" t="s">
-        <v>1030</v>
+        <v>803</v>
       </c>
       <c r="H3" s="226" t="s">
-        <v>1030</v>
+        <v>803</v>
       </c>
       <c r="I3" s="226" t="s">
-        <v>1031</v>
+        <v>804</v>
       </c>
       <c r="J3" s="249" t="s">
-        <v>1032</v>
+        <v>805</v>
       </c>
       <c r="K3" s="226" t="s">
-        <v>1033</v>
+        <v>806</v>
       </c>
       <c r="L3" s="228" t="s">
-        <v>1034</v>
+        <v>807</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="222" customFormat="1" ht="46.5" customHeight="1" thickBot="1">
       <c r="A4" s="242" t="s">
-        <v>1035</v>
+        <v>808</v>
       </c>
       <c r="B4" s="242" t="s">
-        <v>1036</v>
+        <v>809</v>
       </c>
       <c r="C4" s="242" t="s">
-        <v>1037</v>
+        <v>810</v>
       </c>
       <c r="D4" s="242" t="s">
-        <v>1038</v>
+        <v>811</v>
       </c>
       <c r="E4" s="242" t="s">
-        <v>1039</v>
+        <v>812</v>
       </c>
       <c r="F4" s="242" t="s">
-        <v>1040</v>
+        <v>813</v>
       </c>
       <c r="G4" s="242" t="s">
-        <v>1041</v>
+        <v>814</v>
       </c>
       <c r="H4" s="242" t="s">
-        <v>1042</v>
+        <v>815</v>
       </c>
       <c r="I4" s="242" t="s">
-        <v>1043</v>
+        <v>816</v>
       </c>
       <c r="J4" s="242" t="s">
-        <v>1091</v>
+        <v>817</v>
       </c>
       <c r="K4" s="242" t="s">
-        <v>1092</v>
+        <v>818</v>
       </c>
       <c r="L4" s="242" t="s">
-        <v>1044</v>
+        <v>819</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A5" s="245" t="s">
-        <v>816</v>
+        <v>791</v>
       </c>
       <c r="B5" s="238" t="s">
-        <v>1075</v>
+        <v>820</v>
       </c>
       <c r="C5" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D5" s="239">
         <v>105</v>
@@ -16266,13 +16288,13 @@
     </row>
     <row r="6" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A6" s="245" t="s">
-        <v>1076</v>
+        <v>822</v>
       </c>
       <c r="B6" s="238" t="s">
-        <v>1075</v>
+        <v>820</v>
       </c>
       <c r="C6" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D6" s="239">
         <v>105</v>
@@ -16304,13 +16326,13 @@
     </row>
     <row r="7" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A7" s="245" t="s">
-        <v>1079</v>
+        <v>823</v>
       </c>
       <c r="B7" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C7" s="239" t="s">
-        <v>1069</v>
+        <v>825</v>
       </c>
       <c r="D7" s="239">
         <v>90</v>
@@ -16342,10 +16364,10 @@
     </row>
     <row r="8" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A8" s="245" t="s">
-        <v>1078</v>
+        <v>826</v>
       </c>
       <c r="B8" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C8" s="239">
         <v>0</v>
@@ -16363,10 +16385,10 @@
         <v>50</v>
       </c>
       <c r="H8" s="239" t="s">
-        <v>908</v>
+        <v>827</v>
       </c>
       <c r="I8" s="240" t="s">
-        <v>908</v>
+        <v>827</v>
       </c>
       <c r="J8" s="239">
         <v>80</v>
@@ -16380,13 +16402,13 @@
     </row>
     <row r="9" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A9" s="237" t="s">
-        <v>1058</v>
+        <v>828</v>
       </c>
       <c r="B9" s="238" t="s">
-        <v>1059</v>
+        <v>829</v>
       </c>
       <c r="C9" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D9" s="239">
         <v>105</v>
@@ -16418,13 +16440,13 @@
     </row>
     <row r="10" spans="1:12" s="222" customFormat="1" ht="17.25" customHeight="1">
       <c r="A10" s="237" t="s">
-        <v>1074</v>
+        <v>830</v>
       </c>
       <c r="B10" s="238" t="s">
-        <v>1059</v>
+        <v>829</v>
       </c>
       <c r="C10" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D10" s="239">
         <v>60</v>
@@ -16456,13 +16478,13 @@
     </row>
     <row r="11" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A11" s="237" t="s">
-        <v>1062</v>
+        <v>831</v>
       </c>
       <c r="B11" s="238" t="s">
-        <v>1059</v>
+        <v>829</v>
       </c>
       <c r="C11" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D11" s="239">
         <v>60</v>
@@ -16494,13 +16516,13 @@
     </row>
     <row r="12" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A12" s="237" t="s">
-        <v>1063</v>
+        <v>832</v>
       </c>
       <c r="B12" s="238" t="s">
-        <v>1059</v>
+        <v>829</v>
       </c>
       <c r="C12" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D12" s="239">
         <v>60</v>
@@ -16532,13 +16554,13 @@
     </row>
     <row r="13" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A13" s="237" t="s">
-        <v>1060</v>
+        <v>833</v>
       </c>
       <c r="B13" s="238" t="s">
-        <v>1059</v>
+        <v>829</v>
       </c>
       <c r="C13" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D13" s="239">
         <v>70</v>
@@ -16570,10 +16592,10 @@
     </row>
     <row r="14" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A14" s="237" t="s">
-        <v>1064</v>
+        <v>834</v>
       </c>
       <c r="B14" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C14" s="239">
         <v>0</v>
@@ -16608,11 +16630,11 @@
     </row>
     <row r="15" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A15" s="245" t="s">
-        <v>1066</v>
+        <v>835</v>
       </c>
       <c r="B15" s="238"/>
       <c r="C15" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D15" s="239">
         <v>137</v>
@@ -16644,11 +16666,11 @@
     </row>
     <row r="16" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A16" s="245" t="s">
-        <v>1067</v>
+        <v>836</v>
       </c>
       <c r="B16" s="238"/>
       <c r="C16" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D16" s="239">
         <v>126</v>
@@ -16680,13 +16702,13 @@
     </row>
     <row r="17" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A17" s="237" t="s">
-        <v>1072</v>
+        <v>837</v>
       </c>
       <c r="B17" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C17" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D17" s="239">
         <v>145</v>
@@ -16718,13 +16740,13 @@
     </row>
     <row r="18" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A18" s="237" t="s">
-        <v>1070</v>
+        <v>838</v>
       </c>
       <c r="B18" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C18" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D18" s="239">
         <v>113</v>
@@ -16756,11 +16778,11 @@
     </row>
     <row r="19" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A19" s="237" t="s">
-        <v>1050</v>
+        <v>839</v>
       </c>
       <c r="B19" s="238"/>
       <c r="C19" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D19" s="239">
         <v>158</v>
@@ -16792,11 +16814,11 @@
     </row>
     <row r="20" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A20" s="237" t="s">
-        <v>1065</v>
+        <v>840</v>
       </c>
       <c r="B20" s="238"/>
       <c r="C20" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D20" s="239">
         <v>143</v>
@@ -16832,7 +16854,7 @@
       </c>
       <c r="B21" s="238"/>
       <c r="C21" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D21" s="239">
         <v>140</v>
@@ -16864,13 +16886,13 @@
     </row>
     <row r="22" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A22" s="237" t="s">
-        <v>1071</v>
+        <v>841</v>
       </c>
       <c r="B22" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C22" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D22" s="239">
         <v>113</v>
@@ -16902,13 +16924,13 @@
     </row>
     <row r="23" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A23" s="245" t="s">
-        <v>1061</v>
+        <v>842</v>
       </c>
       <c r="B23" s="238" t="s">
-        <v>1052</v>
+        <v>843</v>
       </c>
       <c r="C23" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D23" s="239">
         <v>143</v>
@@ -16940,13 +16962,13 @@
     </row>
     <row r="24" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="245" t="s">
-        <v>1051</v>
+        <v>844</v>
       </c>
       <c r="B24" s="238" t="s">
-        <v>1052</v>
+        <v>843</v>
       </c>
       <c r="C24" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D24" s="239">
         <v>165</v>
@@ -16978,13 +17000,13 @@
     </row>
     <row r="25" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="237" t="s">
-        <v>1053</v>
+        <v>845</v>
       </c>
       <c r="B25" s="238" t="s">
-        <v>1052</v>
+        <v>843</v>
       </c>
       <c r="C25" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D25" s="239">
         <v>165</v>
@@ -17016,13 +17038,13 @@
     </row>
     <row r="26" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A26" s="246" t="s">
-        <v>1073</v>
+        <v>846</v>
       </c>
       <c r="B26" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C26" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D26" s="239">
         <v>70</v>
@@ -17054,13 +17076,13 @@
     </row>
     <row r="27" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A27" s="245" t="s">
-        <v>817</v>
+        <v>792</v>
       </c>
       <c r="B27" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C27" s="239" t="s">
-        <v>1069</v>
+        <v>825</v>
       </c>
       <c r="D27" s="239">
         <v>80</v>
@@ -17092,13 +17114,13 @@
     </row>
     <row r="28" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A28" s="245" t="s">
-        <v>815</v>
+        <v>790</v>
       </c>
       <c r="B28" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C28" s="239" t="s">
-        <v>1080</v>
+        <v>847</v>
       </c>
       <c r="D28" s="239">
         <v>85</v>
@@ -17133,10 +17155,10 @@
         <v>676</v>
       </c>
       <c r="B29" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C29" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D29" s="239">
         <v>90</v>
@@ -17168,10 +17190,10 @@
     </row>
     <row r="30" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A30" s="245" t="s">
-        <v>1077</v>
+        <v>848</v>
       </c>
       <c r="B30" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C30" s="239">
         <v>0</v>
@@ -17209,7 +17231,7 @@
         <v>675</v>
       </c>
       <c r="B31" s="238" t="s">
-        <v>1045</v>
+        <v>824</v>
       </c>
       <c r="C31" s="239">
         <v>0</v>
@@ -17244,10 +17266,10 @@
     </row>
     <row r="32" spans="1:12" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A32" s="245" t="s">
-        <v>1049</v>
+        <v>849</v>
       </c>
       <c r="B32" s="238" t="s">
-        <v>1048</v>
+        <v>850</v>
       </c>
       <c r="C32" s="239">
         <v>0</v>
@@ -17282,10 +17304,10 @@
     </row>
     <row r="33" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A33" s="245" t="s">
-        <v>1055</v>
+        <v>851</v>
       </c>
       <c r="B33" s="238" t="s">
-        <v>1056</v>
+        <v>852</v>
       </c>
       <c r="C33" s="239">
         <v>0</v>
@@ -17317,14 +17339,15 @@
       <c r="L33" s="239">
         <v>2050</v>
       </c>
+      <c r="M33" s="307"/>
     </row>
     <row r="34" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A34" s="245" t="s">
-        <v>1057</v>
+        <v>853</v>
       </c>
       <c r="B34" s="238"/>
       <c r="C34" s="239" t="s">
-        <v>1046</v>
+        <v>821</v>
       </c>
       <c r="D34" s="239">
         <v>170</v>
@@ -17339,10 +17362,10 @@
         <v>100</v>
       </c>
       <c r="H34" s="239" t="s">
-        <v>908</v>
+        <v>827</v>
       </c>
       <c r="I34" s="240" t="s">
-        <v>908</v>
+        <v>827</v>
       </c>
       <c r="J34" s="239">
         <v>158</v>
@@ -17353,14 +17376,15 @@
       <c r="L34" s="239">
         <v>2100</v>
       </c>
+      <c r="M34" s="307"/>
     </row>
     <row r="35" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A35" s="245" t="s">
-        <v>1068</v>
+        <v>854</v>
       </c>
       <c r="B35" s="238"/>
       <c r="C35" s="239" t="s">
-        <v>1069</v>
+        <v>825</v>
       </c>
       <c r="D35" s="239">
         <v>80</v>
@@ -17389,13 +17413,14 @@
       <c r="L35" s="239">
         <v>100</v>
       </c>
+      <c r="M35" s="307"/>
     </row>
     <row r="36" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A36" s="237" t="s">
-        <v>1047</v>
+        <v>855</v>
       </c>
       <c r="B36" s="238" t="s">
-        <v>1048</v>
+        <v>850</v>
       </c>
       <c r="C36" s="239">
         <v>0</v>
@@ -17427,10 +17452,11 @@
       <c r="L36" s="239">
         <v>3000</v>
       </c>
+      <c r="M36" s="307"/>
     </row>
     <row r="37" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A37" s="237" t="s">
-        <v>1054</v>
+        <v>856</v>
       </c>
       <c r="B37" s="238"/>
       <c r="C37" s="239">
@@ -17463,102 +17489,159 @@
       <c r="L37" s="239">
         <v>2200</v>
       </c>
+      <c r="M37" s="307"/>
     </row>
     <row r="38" spans="1:13" s="222" customFormat="1" ht="15.75" customHeight="1">
       <c r="A38" s="227"/>
-      <c r="B38" s="311"/>
-      <c r="C38" s="311"/>
-      <c r="D38" s="312"/>
-      <c r="E38" s="312"/>
-      <c r="F38" s="312"/>
-      <c r="G38" s="312"/>
-      <c r="H38" s="312"/>
-      <c r="I38" s="312"/>
-      <c r="J38" s="312"/>
+      <c r="B38" s="310"/>
+      <c r="C38" s="310"/>
+      <c r="D38" s="314"/>
+      <c r="E38" s="314"/>
+      <c r="F38" s="314"/>
+      <c r="G38" s="314"/>
+      <c r="H38" s="314"/>
+      <c r="I38" s="314"/>
+      <c r="J38" s="314"/>
       <c r="K38" s="229"/>
       <c r="L38" s="229"/>
       <c r="M38" s="230"/>
     </row>
     <row r="39" spans="1:13" ht="15.75" customHeight="1">
       <c r="A39" s="225" t="s">
-        <v>1081</v>
-      </c>
-      <c r="B39" s="304"/>
-      <c r="C39" s="304"/>
+        <v>857</v>
+      </c>
+      <c r="B39" s="308"/>
+      <c r="C39" s="308"/>
+      <c r="D39" s="309"/>
+      <c r="E39" s="309"/>
+      <c r="F39" s="309"/>
+      <c r="G39" s="309"/>
+      <c r="H39" s="309"/>
+      <c r="I39" s="309"/>
+      <c r="J39" s="309"/>
       <c r="K39" s="231"/>
       <c r="L39" s="231"/>
       <c r="M39" s="232"/>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1">
-      <c r="B40" s="304"/>
-      <c r="C40" s="304"/>
+      <c r="B40" s="308"/>
+      <c r="C40" s="308"/>
+      <c r="D40" s="309"/>
+      <c r="E40" s="309"/>
+      <c r="F40" s="309"/>
+      <c r="G40" s="309"/>
+      <c r="H40" s="309"/>
+      <c r="I40" s="309"/>
+      <c r="J40" s="309"/>
       <c r="K40" s="231"/>
       <c r="L40" s="231"/>
       <c r="M40" s="232"/>
     </row>
     <row r="41" spans="1:13" ht="15.75" customHeight="1">
       <c r="A41" s="225" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B41" s="313"/>
-      <c r="C41" s="313"/>
-      <c r="D41" s="314"/>
-      <c r="E41" s="314"/>
-      <c r="F41" s="314"/>
-      <c r="G41" s="314"/>
-      <c r="H41" s="314"/>
-      <c r="I41" s="314"/>
-      <c r="J41" s="314"/>
-      <c r="K41" s="314"/>
+        <v>858</v>
+      </c>
+      <c r="B41" s="311"/>
+      <c r="C41" s="311"/>
+      <c r="D41" s="315"/>
+      <c r="E41" s="315"/>
+      <c r="F41" s="315"/>
+      <c r="G41" s="315"/>
+      <c r="H41" s="315"/>
+      <c r="I41" s="315"/>
+      <c r="J41" s="315"/>
+      <c r="K41" s="315"/>
+      <c r="L41" s="309"/>
       <c r="M41" s="232"/>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A42" s="304" t="s">
-        <v>1083</v>
-      </c>
-      <c r="B42" s="220"/>
-      <c r="C42" s="220"/>
+      <c r="A42" s="308" t="s">
+        <v>859</v>
+      </c>
+      <c r="B42" s="309"/>
+      <c r="C42" s="309"/>
+      <c r="D42" s="309"/>
+      <c r="E42" s="309"/>
+      <c r="F42" s="309"/>
+      <c r="G42" s="309"/>
+      <c r="H42" s="309"/>
+      <c r="I42" s="309"/>
       <c r="J42" s="231"/>
+      <c r="K42" s="309"/>
+      <c r="L42" s="309"/>
       <c r="M42" s="232"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A43" s="304" t="s">
-        <v>1084</v>
-      </c>
-      <c r="B43" s="220"/>
-      <c r="C43" s="220"/>
+      <c r="A43" s="308" t="s">
+        <v>860</v>
+      </c>
+      <c r="B43" s="309"/>
+      <c r="C43" s="309"/>
+      <c r="D43" s="309"/>
+      <c r="E43" s="309"/>
+      <c r="F43" s="309"/>
+      <c r="G43" s="309"/>
+      <c r="H43" s="309"/>
+      <c r="I43" s="309"/>
       <c r="J43" s="231"/>
+      <c r="K43" s="309"/>
+      <c r="L43" s="309"/>
       <c r="M43" s="232"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A44" s="304" t="s">
-        <v>1085</v>
-      </c>
-      <c r="B44" s="220"/>
-      <c r="C44" s="220"/>
+      <c r="A44" s="308" t="s">
+        <v>861</v>
+      </c>
+      <c r="B44" s="309"/>
+      <c r="C44" s="309"/>
+      <c r="D44" s="309"/>
+      <c r="E44" s="309"/>
+      <c r="F44" s="309"/>
+      <c r="G44" s="309"/>
+      <c r="H44" s="309"/>
+      <c r="I44" s="309"/>
+      <c r="J44" s="309"/>
+      <c r="K44" s="309"/>
+      <c r="L44" s="309"/>
       <c r="M44" s="232"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A45" s="304" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B45" s="220"/>
-      <c r="C45" s="220"/>
+      <c r="A45" s="308" t="s">
+        <v>862</v>
+      </c>
+      <c r="B45" s="309"/>
+      <c r="C45" s="309"/>
+      <c r="D45" s="309"/>
+      <c r="E45" s="309"/>
+      <c r="F45" s="309"/>
+      <c r="G45" s="309"/>
+      <c r="H45" s="309"/>
+      <c r="I45" s="309"/>
+      <c r="J45" s="309"/>
+      <c r="K45" s="309"/>
+      <c r="L45" s="309"/>
       <c r="M45" s="232"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A46" s="304" t="s">
-        <v>1087</v>
-      </c>
-      <c r="B46" s="220"/>
-      <c r="C46" s="220"/>
+      <c r="A46" s="308" t="s">
+        <v>863</v>
+      </c>
+      <c r="B46" s="309"/>
+      <c r="C46" s="309"/>
+      <c r="D46" s="309"/>
+      <c r="E46" s="309"/>
+      <c r="F46" s="309"/>
+      <c r="G46" s="309"/>
+      <c r="H46" s="309"/>
       <c r="I46" s="231"/>
       <c r="J46" s="231"/>
+      <c r="K46" s="309"/>
+      <c r="L46" s="309"/>
       <c r="M46" s="232"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
       <c r="A47" s="233" t="s">
-        <v>1088</v>
+        <v>864</v>
       </c>
       <c r="B47" s="233"/>
       <c r="C47" s="233"/>
@@ -17569,9 +17652,12 @@
       <c r="H47" s="233"/>
       <c r="I47" s="233"/>
       <c r="J47" s="233"/>
+      <c r="K47" s="309"/>
+      <c r="L47" s="309"/>
       <c r="M47" s="232"/>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D48" s="309"/>
       <c r="E48" s="236"/>
       <c r="F48" s="236"/>
       <c r="G48" s="236"/>
@@ -17584,8 +17670,9 @@
     </row>
     <row r="49" spans="1:13" ht="15.75" customHeight="1">
       <c r="A49" s="247" t="s">
-        <v>1089</v>
-      </c>
+        <v>865</v>
+      </c>
+      <c r="D49" s="309"/>
       <c r="E49" s="236"/>
       <c r="F49" s="236"/>
       <c r="G49" s="236"/>
@@ -17598,8 +17685,9 @@
     </row>
     <row r="50" spans="1:13" ht="15.75" customHeight="1">
       <c r="A50" s="247" t="s">
-        <v>1090</v>
-      </c>
+        <v>866</v>
+      </c>
+      <c r="D50" s="309"/>
       <c r="E50" s="236"/>
       <c r="F50" s="236"/>
       <c r="G50" s="236"/>
@@ -17611,7 +17699,8 @@
       <c r="M50" s="232"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A51" s="310"/>
+      <c r="A51" s="316"/>
+      <c r="D51" s="309"/>
       <c r="E51" s="236"/>
       <c r="F51" s="236"/>
       <c r="G51" s="236"/>
@@ -17624,6 +17713,7 @@
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1">
       <c r="A52" s="248"/>
+      <c r="D52" s="309"/>
       <c r="E52" s="236"/>
       <c r="F52" s="236"/>
       <c r="G52" s="236"/>
@@ -17635,6 +17725,7 @@
       <c r="M52" s="232"/>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D53" s="309"/>
       <c r="E53" s="236"/>
       <c r="F53" s="236"/>
       <c r="G53" s="236"/>
@@ -17646,6 +17737,7 @@
       <c r="M53" s="232"/>
     </row>
     <row r="54" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D54" s="309"/>
       <c r="E54" s="236"/>
       <c r="F54" s="236"/>
       <c r="G54" s="236"/>
@@ -17657,6 +17749,7 @@
       <c r="M54" s="232"/>
     </row>
     <row r="55" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D55" s="309"/>
       <c r="E55" s="236"/>
       <c r="F55" s="236"/>
       <c r="G55" s="236"/>
@@ -17668,6 +17761,7 @@
       <c r="M55" s="232"/>
     </row>
     <row r="56" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D56" s="309"/>
       <c r="E56" s="236"/>
       <c r="F56" s="236"/>
       <c r="G56" s="236"/>
@@ -17679,6 +17773,7 @@
       <c r="M56" s="232"/>
     </row>
     <row r="57" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D57" s="309"/>
       <c r="E57" s="236"/>
       <c r="F57" s="236"/>
       <c r="G57" s="236"/>
@@ -17690,6 +17785,7 @@
       <c r="M57" s="232"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D58" s="309"/>
       <c r="E58" s="236"/>
       <c r="F58" s="236"/>
       <c r="G58" s="236"/>
@@ -17701,6 +17797,7 @@
       <c r="M58" s="232"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D59" s="309"/>
       <c r="E59" s="236"/>
       <c r="F59" s="236"/>
       <c r="G59" s="236"/>
@@ -17712,6 +17809,7 @@
       <c r="M59" s="232"/>
     </row>
     <row r="60" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D60" s="309"/>
       <c r="E60" s="236"/>
       <c r="F60" s="236"/>
       <c r="G60" s="236"/>
@@ -17723,6 +17821,7 @@
       <c r="M60" s="232"/>
     </row>
     <row r="61" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D61" s="309"/>
       <c r="E61" s="236"/>
       <c r="F61" s="236"/>
       <c r="G61" s="236"/>
@@ -17734,6 +17833,7 @@
       <c r="M61" s="232"/>
     </row>
     <row r="62" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D62" s="309"/>
       <c r="E62" s="236"/>
       <c r="F62" s="236"/>
       <c r="G62" s="236"/>
@@ -17745,6 +17845,7 @@
       <c r="M62" s="232"/>
     </row>
     <row r="63" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D63" s="309"/>
       <c r="E63" s="236"/>
       <c r="F63" s="236"/>
       <c r="G63" s="236"/>
@@ -17756,6 +17857,7 @@
       <c r="M63" s="232"/>
     </row>
     <row r="64" spans="1:13" ht="15.75" customHeight="1">
+      <c r="D64" s="309"/>
       <c r="E64" s="236"/>
       <c r="F64" s="236"/>
       <c r="G64" s="236"/>
@@ -24835,7 +24937,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="205" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -24843,32 +24945,32 @@
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="206" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="207" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="205" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="205" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="205" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="205" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -24876,17 +24978,17 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="206" t="s">
-        <v>862</v>
+        <v>874</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11" s="207" t="s">
-        <v>863</v>
+        <v>875</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12" s="205" t="s">
-        <v>864</v>
+        <v>876</v>
       </c>
     </row>
     <row r="13" spans="1:1">
@@ -24894,37 +24996,37 @@
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="206" t="s">
-        <v>865</v>
+        <v>877</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="205" t="s">
-        <v>866</v>
+        <v>878</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="205" t="s">
-        <v>867</v>
+        <v>879</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="205" t="s">
-        <v>868</v>
+        <v>880</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="205" t="s">
-        <v>869</v>
+        <v>881</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="205" t="s">
-        <v>870</v>
+        <v>882</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="205" t="s">
-        <v>871</v>
+        <v>883</v>
       </c>
     </row>
     <row r="21" spans="1:1">
@@ -24932,22 +25034,22 @@
     </row>
     <row r="22" spans="1:1">
       <c r="A22" s="206" t="s">
-        <v>872</v>
+        <v>884</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="205" t="s">
-        <v>873</v>
+        <v>885</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="205" t="s">
-        <v>874</v>
+        <v>886</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="205" t="s">
-        <v>875</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>
@@ -24973,33 +25075,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="204" t="s">
-        <v>876</v>
+        <v>888</v>
       </c>
       <c r="B1" s="210" t="s">
-        <v>877</v>
+        <v>889</v>
       </c>
       <c r="C1" s="210" t="s">
-        <v>878</v>
+        <v>890</v>
       </c>
       <c r="D1" s="210" t="s">
-        <v>879</v>
+        <v>891</v>
       </c>
       <c r="E1" s="210" t="s">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="F1" s="210" t="s">
-        <v>881</v>
+        <v>893</v>
       </c>
       <c r="G1" s="209" t="s">
-        <v>882</v>
+        <v>894</v>
       </c>
       <c r="H1" s="208" t="s">
-        <v>883</v>
+        <v>895</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="204" t="s">
-        <v>884</v>
+        <v>896</v>
       </c>
       <c r="B2" s="210">
         <v>1</v>
@@ -25017,7 +25119,7 @@
         <v>1</v>
       </c>
       <c r="G2" s="209" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="H2" s="208">
         <v>2</v>
@@ -25025,30 +25127,30 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="204" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="B3" s="210" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="C3" s="210" t="s">
-        <v>888</v>
+        <v>900</v>
       </c>
       <c r="D3" s="219" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="E3" s="219" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
       <c r="F3" s="210" t="s">
         <v>156</v>
       </c>
       <c r="H3" s="208" t="s">
-        <v>887</v>
+        <v>899</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="204" t="s">
-        <v>889</v>
+        <v>901</v>
       </c>
       <c r="B4" s="210">
         <v>450</v>
@@ -25057,7 +25159,7 @@
         <v>450</v>
       </c>
       <c r="D4" s="210" t="s">
-        <v>890</v>
+        <v>902</v>
       </c>
       <c r="E4" s="210">
         <v>285</v>
@@ -25069,18 +25171,18 @@
         <v>300</v>
       </c>
       <c r="H4" s="208" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="204" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="B5" s="210" t="s">
-        <v>893</v>
+        <v>905</v>
       </c>
       <c r="C5" s="210" t="s">
-        <v>894</v>
+        <v>906</v>
       </c>
       <c r="D5" s="210">
         <v>150</v>
@@ -25095,12 +25197,12 @@
         <v>120</v>
       </c>
       <c r="H5" s="208" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="204" t="s">
-        <v>896</v>
+        <v>908</v>
       </c>
       <c r="B6" s="210">
         <v>80</v>
@@ -25121,168 +25223,168 @@
         <v>60</v>
       </c>
       <c r="H6" s="208" t="s">
-        <v>897</v>
+        <v>909</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="204" t="s">
-        <v>898</v>
+        <v>910</v>
       </c>
       <c r="B7" s="210" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="C7" s="210" t="s">
-        <v>900</v>
+        <v>912</v>
       </c>
       <c r="D7" s="210" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="E7" s="210" t="s">
-        <v>902</v>
+        <v>914</v>
       </c>
       <c r="F7" s="210" t="s">
-        <v>903</v>
+        <v>915</v>
       </c>
       <c r="G7" s="209" t="s">
-        <v>904</v>
+        <v>916</v>
       </c>
       <c r="H7" s="208" t="s">
-        <v>905</v>
+        <v>917</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="204" t="s">
-        <v>906</v>
+        <v>918</v>
       </c>
       <c r="B8" s="210" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C8" s="210" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="D8" s="210" t="s">
-        <v>908</v>
+        <v>827</v>
       </c>
       <c r="E8" s="210" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="F8" s="210" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="G8" s="209" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="H8" s="208" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="204" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
       <c r="B9" s="210" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="C9" s="210" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="D9" s="210" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="E9" s="210" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="F9" s="210" t="s">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="H9" s="208" t="s">
-        <v>916</v>
+        <v>927</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="204" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="B10" s="215" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="C10" s="215" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="D10" s="215" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="E10" s="215" t="s">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="F10" s="218" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="G10" s="217" t="s">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="H10" s="208" t="s">
-        <v>924</v>
+        <v>935</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="204" t="s">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="B11" s="210" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="C11" s="210" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="D11" s="210" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="E11" s="210" t="s">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="F11" s="210" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="G11" s="209" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="H11" s="208" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="17.25" customHeight="1">
       <c r="A12" s="216" t="s">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="B12" s="215" t="s">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="C12" s="215" t="s">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="D12" s="214" t="s">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="E12" s="215" t="s">
-        <v>934</v>
+        <v>945</v>
       </c>
       <c r="F12" s="214" t="s">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="H12" s="208" t="s">
-        <v>936</v>
+        <v>947</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="204" t="s">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="B13" s="210" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="C13" s="210" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="D13" s="210">
         <v>120</v>
@@ -25291,265 +25393,265 @@
         <v>156</v>
       </c>
       <c r="F13" s="210" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="G13" s="209" t="s">
-        <v>940</v>
+        <v>951</v>
       </c>
       <c r="H13" s="208" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="204" t="s">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="B14" s="210" t="s">
-        <v>942</v>
+        <v>953</v>
       </c>
       <c r="C14" s="210" t="s">
-        <v>942</v>
+        <v>953</v>
       </c>
       <c r="D14" s="210" t="s">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="E14" s="210" t="s">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="F14" s="210" t="s">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="G14" s="209" t="s">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="H14" s="208" t="s">
-        <v>947</v>
+        <v>958</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="213" t="s">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="B15" s="210" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="C15" s="210" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="H15" s="208" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="204" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="B16" s="210" t="s">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="C16" s="210" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="D16" s="210" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
       <c r="E16" s="210" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="F16" s="210" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="H16" s="208" t="s">
-        <v>954</v>
+        <v>965</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="204" t="s">
-        <v>955</v>
+        <v>966</v>
       </c>
       <c r="B17" s="210" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="C17" s="210" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="D17" s="210" t="s">
-        <v>958</v>
+        <v>969</v>
       </c>
       <c r="E17" s="210" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="F17" s="210" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="H17" s="208" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="204" t="s">
-        <v>959</v>
+        <v>970</v>
       </c>
       <c r="B18" s="210" t="s">
-        <v>960</v>
+        <v>971</v>
       </c>
       <c r="C18" s="210" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
       <c r="D18" s="210" t="s">
-        <v>962</v>
+        <v>973</v>
       </c>
       <c r="E18" s="210" t="s">
-        <v>963</v>
+        <v>974</v>
       </c>
       <c r="F18" s="210" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="H18" s="208" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="204" t="s">
-        <v>966</v>
+        <v>977</v>
       </c>
       <c r="B19" s="210" t="s">
-        <v>967</v>
+        <v>978</v>
       </c>
       <c r="C19" s="210" t="s">
-        <v>967</v>
+        <v>978</v>
       </c>
       <c r="D19" s="210" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="E19" s="210" t="s">
-        <v>969</v>
+        <v>980</v>
       </c>
       <c r="F19" s="210" t="s">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="G19" s="209" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="H19" s="209" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="213" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="B20" s="208" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
       <c r="C20" s="208" t="s">
-        <v>973</v>
+        <v>984</v>
       </c>
       <c r="G20" s="209" t="s">
-        <v>974</v>
+        <v>985</v>
       </c>
       <c r="H20" s="208" t="s">
-        <v>975</v>
+        <v>986</v>
       </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="204" t="s">
-        <v>976</v>
+        <v>987</v>
       </c>
       <c r="B21" s="210" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="C21" s="210" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="D21" s="210" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="E21" s="210" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="G21" s="212" t="s">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="H21" s="208" t="s">
-        <v>980</v>
+        <v>991</v>
       </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="204" t="s">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="B22" s="210" t="s">
-        <v>982</v>
+        <v>993</v>
       </c>
       <c r="C22" s="210" t="s">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="D22" s="210" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="E22" s="210" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="F22" s="210" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="G22" s="209" t="s">
-        <v>984</v>
+        <v>995</v>
       </c>
       <c r="H22" s="208" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="204" t="s">
-        <v>986</v>
+        <v>997</v>
       </c>
       <c r="B23" s="210" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="C23" s="210" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="D23" s="210" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="E23" s="210" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="F23" s="210" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="G23" s="209" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="H23" s="208" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="204" t="s">
+        <v>999</v>
+      </c>
+      <c r="B24" s="210" t="s">
         <v>988</v>
       </c>
-      <c r="B24" s="210" t="s">
-        <v>977</v>
-      </c>
       <c r="C24" s="210" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="D24" s="210" t="s">
         <v>156</v>
       </c>
       <c r="E24" s="210" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
       <c r="H24" s="208" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="204" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="B25" s="210">
         <v>0.05</v>
@@ -25572,194 +25674,194 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="204" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="B26" s="210" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="C26" s="210" t="s">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="D26" s="210" t="s">
         <v>156</v>
       </c>
       <c r="E26" s="210" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="G26" s="209" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="H26" s="208" t="s">
-        <v>907</v>
+        <v>919</v>
       </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="204" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
       <c r="B27" s="210" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="C27" s="210" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="D27" s="210" t="s">
         <v>156</v>
       </c>
       <c r="E27" s="210" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="H27" s="210" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="204" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="B28" s="210" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="C28" s="210" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="D28" s="210" t="s">
         <v>156</v>
       </c>
       <c r="E28" s="210" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="G28" s="210" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="H28" s="208" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="204" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="B29" s="210" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="C29" s="210" t="s">
-        <v>1003</v>
+        <v>1014</v>
       </c>
       <c r="D29" s="210" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="E29" s="210" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="G29" s="209" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
       <c r="H29" s="208" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="204" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="B30" s="210" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="C30" s="210" t="s">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="D30" s="210" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="E30" s="210" t="s">
         <v>156</v>
       </c>
       <c r="G30" s="209" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
       <c r="H30" s="208" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="204" t="s">
-        <v>1011</v>
+        <v>1022</v>
       </c>
       <c r="B31" s="210" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
       <c r="C31" s="210" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
       <c r="D31" s="210" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="E31" s="210" t="s">
         <v>156</v>
       </c>
       <c r="G31" s="209" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
       <c r="H31" s="210" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="204" t="s">
-        <v>1014</v>
+        <v>1025</v>
       </c>
       <c r="B32" s="210" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C32" s="210" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D32" s="210" t="s">
         <v>1015</v>
-      </c>
-      <c r="C32" s="210" t="s">
-        <v>1015</v>
-      </c>
-      <c r="D32" s="210" t="s">
-        <v>1004</v>
       </c>
       <c r="E32" s="210" t="s">
         <v>156</v>
       </c>
       <c r="G32" s="209" t="s">
-        <v>1016</v>
+        <v>1027</v>
       </c>
       <c r="H32" s="208" t="s">
-        <v>1017</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="204" t="s">
-        <v>1018</v>
+        <v>1029</v>
       </c>
       <c r="B33" s="210" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="C33" s="210" t="s">
-        <v>1020</v>
+        <v>1031</v>
       </c>
       <c r="D33" s="210" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
       <c r="E33" s="210" t="s">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="G33" s="209" t="s">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="H33" s="208" t="s">
-        <v>1023</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="204" t="s">
-        <v>1024</v>
+        <v>1035</v>
       </c>
       <c r="B34" s="210" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
       <c r="C34" s="210" t="s">
-        <v>1026</v>
+        <v>1037</v>
       </c>
       <c r="D34" s="210">
         <v>1000</v>
@@ -25779,7 +25881,7 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="204" t="s">
-        <v>1027</v>
+        <v>1038</v>
       </c>
       <c r="B35" s="210">
         <v>1.75</v>
@@ -25830,7 +25932,7 @@
         <v>377</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>826</v>
+        <v>1039</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>378</v>
@@ -25839,110 +25941,110 @@
         <v>8</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>827</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>828</v>
+        <v>1041</v>
       </c>
       <c r="B2" t="s">
-        <v>829</v>
+        <v>1042</v>
       </c>
       <c r="C2" t="s">
-        <v>830</v>
+        <v>1043</v>
       </c>
       <c r="D2" t="s">
-        <v>831</v>
+        <v>1044</v>
       </c>
       <c r="E2" s="109" t="s">
-        <v>832</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>833</v>
+        <v>1046</v>
       </c>
       <c r="C3" t="s">
-        <v>834</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>835</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>836</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" customHeight="1">
       <c r="A6" t="s">
-        <v>837</v>
+        <v>1050</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>838</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>839</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>840</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>841</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>842</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>843</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>844</v>
+        <v>1057</v>
       </c>
       <c r="C12" t="s">
-        <v>845</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>846</v>
+        <v>1059</v>
       </c>
       <c r="B13">
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>847</v>
+        <v>1060</v>
       </c>
       <c r="E13" s="134" t="s">
-        <v>848</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="305" t="s">
-        <v>849</v>
+      <c r="A14" s="304" t="s">
+        <v>1062</v>
       </c>
       <c r="E14" s="134" t="s">
-        <v>850</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>851</v>
+        <v>1064</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -25950,7 +26052,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>852</v>
+        <v>1065</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -25958,13 +26060,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>853</v>
+        <v>1066</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>854</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -25993,71 +26095,71 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="5" t="s">
-        <v>701</v>
+        <v>1068</v>
       </c>
       <c r="B1" t="s">
-        <v>702</v>
+        <v>1069</v>
       </c>
       <c r="C1" t="s">
-        <v>703</v>
+        <v>1070</v>
       </c>
       <c r="D1" t="s">
-        <v>704</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>705</v>
+        <v>1072</v>
       </c>
       <c r="B2" t="s">
-        <v>706</v>
+        <v>1073</v>
       </c>
       <c r="C2" s="124" t="s">
-        <v>707</v>
+        <v>1074</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>708</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>709</v>
+        <v>1076</v>
       </c>
       <c r="B3" t="s">
-        <v>710</v>
-      </c>
-      <c r="C3" s="306" t="s">
-        <v>711</v>
+        <v>1077</v>
+      </c>
+      <c r="C3" s="305" t="s">
+        <v>1078</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>712</v>
+        <v>1079</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>713</v>
+        <v>1080</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>714</v>
-      </c>
-      <c r="D4" s="307" t="s">
-        <v>715</v>
+        <v>1081</v>
+      </c>
+      <c r="D4" s="306" t="s">
+        <v>1082</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>716</v>
+        <v>1083</v>
       </c>
       <c r="C5" s="125" t="s">
-        <v>717</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>718</v>
+        <v>1085</v>
       </c>
       <c r="B6" t="s">
-        <v>719</v>
+        <v>1086</v>
       </c>
       <c r="C6" t="s">
         <v>527</v>
@@ -26065,26 +26167,26 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>720</v>
+        <v>1087</v>
       </c>
       <c r="B7" t="s">
-        <v>721</v>
+        <v>1088</v>
       </c>
       <c r="C7" s="123" t="s">
-        <v>722</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>723</v>
+        <v>1090</v>
       </c>
       <c r="B8" t="s">
-        <v>724</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>725</v>
+        <v>1092</v>
       </c>
     </row>
   </sheetData>

--- a/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
+++ b/V2 BETA/BOM/Valkyrie V2 HT100 BOM Beta.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3837cd5b4a1a02ac/Document Library/GitHub/Project-Valkyrie/V2 BETA/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3320" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16ACF7C3-03DE-4470-8B23-F4A31228EBD7}"/>
+  <xr:revisionPtr revIDLastSave="3326" documentId="8_{5107759B-8870-48A8-933E-C4A7F6F41B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0B7D310-E116-4041-959C-733200523DB3}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="16440" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PARTS LIST" sheetId="43" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1992" uniqueCount="1093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1994" uniqueCount="1095">
   <si>
     <t>Type</t>
   </si>
@@ -3279,7 +3279,7 @@
     <t>Spanner  AF 7mm,</t>
   </si>
   <si>
-    <t>Drill bits mm  5,4,3</t>
+    <t>Drill bits mm  6,5,4,3,4.2,</t>
   </si>
   <si>
     <t xml:space="preserve">solder iron and solder </t>
@@ -3322,6 +3322,12 @@
   </si>
   <si>
     <t xml:space="preserve">This will make the soldering much easier </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adhisive Heat sink compound </t>
+  </si>
+  <si>
+    <t>https://www.aliexpress.com/item/1005009582306904.html?</t>
   </si>
   <si>
     <t>Things still to do</t>
@@ -4879,27 +4885,27 @@
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="12" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="12" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="13">
@@ -9727,7 +9733,7 @@
       <c r="H51" s="152" t="s">
         <v>126</v>
       </c>
-      <c r="I51" s="312"/>
+      <c r="I51" s="314"/>
       <c r="J51" s="94"/>
       <c r="K51" s="10"/>
       <c r="L51" s="68"/>
@@ -9757,7 +9763,7 @@
       <c r="H52" s="152" t="s">
         <v>127</v>
       </c>
-      <c r="I52" s="312"/>
+      <c r="I52" s="314"/>
       <c r="J52" s="94"/>
       <c r="K52" s="10"/>
       <c r="L52" s="68"/>
@@ -10121,7 +10127,7 @@
       <c r="H63" s="133" t="s">
         <v>156</v>
       </c>
-      <c r="I63" s="312"/>
+      <c r="I63" s="314"/>
       <c r="J63" s="94"/>
       <c r="K63" s="10"/>
       <c r="L63" s="68"/>
@@ -15573,7 +15579,7 @@
       </c>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="313" t="s">
+      <c r="A93" s="315" t="s">
         <v>689</v>
       </c>
       <c r="B93" t="s">
@@ -16150,33 +16156,33 @@
       <c r="A1" s="223" t="s">
         <v>801</v>
       </c>
-      <c r="B1" s="309"/>
-      <c r="C1" s="309"/>
-      <c r="D1" s="309"/>
-      <c r="E1" s="309"/>
-      <c r="F1" s="309"/>
-      <c r="G1" s="309"/>
-      <c r="H1" s="309"/>
-      <c r="I1" s="309"/>
-      <c r="J1" s="309"/>
-      <c r="K1" s="309"/>
-      <c r="L1" s="309"/>
+      <c r="B1" s="308"/>
+      <c r="C1" s="308"/>
+      <c r="D1" s="308"/>
+      <c r="E1" s="308"/>
+      <c r="F1" s="308"/>
+      <c r="G1" s="308"/>
+      <c r="H1" s="308"/>
+      <c r="I1" s="308"/>
+      <c r="J1" s="308"/>
+      <c r="K1" s="308"/>
+      <c r="L1" s="308"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
       <c r="A2" s="224" t="s">
         <v>802</v>
       </c>
-      <c r="B2" s="309"/>
-      <c r="C2" s="309"/>
-      <c r="D2" s="309"/>
-      <c r="E2" s="309"/>
-      <c r="F2" s="309"/>
-      <c r="G2" s="309"/>
-      <c r="H2" s="309"/>
-      <c r="I2" s="309"/>
-      <c r="J2" s="309"/>
-      <c r="K2" s="309"/>
-      <c r="L2" s="309"/>
+      <c r="B2" s="308"/>
+      <c r="C2" s="308"/>
+      <c r="D2" s="308"/>
+      <c r="E2" s="308"/>
+      <c r="F2" s="308"/>
+      <c r="G2" s="308"/>
+      <c r="H2" s="308"/>
+      <c r="I2" s="308"/>
+      <c r="J2" s="308"/>
+      <c r="K2" s="308"/>
+      <c r="L2" s="308"/>
     </row>
     <row r="3" spans="1:12" s="222" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="243"/>
@@ -17495,13 +17501,13 @@
       <c r="A38" s="227"/>
       <c r="B38" s="310"/>
       <c r="C38" s="310"/>
-      <c r="D38" s="314"/>
-      <c r="E38" s="314"/>
-      <c r="F38" s="314"/>
-      <c r="G38" s="314"/>
-      <c r="H38" s="314"/>
-      <c r="I38" s="314"/>
-      <c r="J38" s="314"/>
+      <c r="D38" s="311"/>
+      <c r="E38" s="311"/>
+      <c r="F38" s="311"/>
+      <c r="G38" s="311"/>
+      <c r="H38" s="311"/>
+      <c r="I38" s="311"/>
+      <c r="J38" s="311"/>
       <c r="K38" s="229"/>
       <c r="L38" s="229"/>
       <c r="M38" s="230"/>
@@ -17510,29 +17516,29 @@
       <c r="A39" s="225" t="s">
         <v>857</v>
       </c>
-      <c r="B39" s="308"/>
-      <c r="C39" s="308"/>
-      <c r="D39" s="309"/>
-      <c r="E39" s="309"/>
-      <c r="F39" s="309"/>
-      <c r="G39" s="309"/>
-      <c r="H39" s="309"/>
-      <c r="I39" s="309"/>
-      <c r="J39" s="309"/>
+      <c r="B39" s="309"/>
+      <c r="C39" s="309"/>
+      <c r="D39" s="308"/>
+      <c r="E39" s="308"/>
+      <c r="F39" s="308"/>
+      <c r="G39" s="308"/>
+      <c r="H39" s="308"/>
+      <c r="I39" s="308"/>
+      <c r="J39" s="308"/>
       <c r="K39" s="231"/>
       <c r="L39" s="231"/>
       <c r="M39" s="232"/>
     </row>
     <row r="40" spans="1:13" ht="15.75" customHeight="1">
-      <c r="B40" s="308"/>
-      <c r="C40" s="308"/>
-      <c r="D40" s="309"/>
-      <c r="E40" s="309"/>
-      <c r="F40" s="309"/>
-      <c r="G40" s="309"/>
-      <c r="H40" s="309"/>
-      <c r="I40" s="309"/>
-      <c r="J40" s="309"/>
+      <c r="B40" s="309"/>
+      <c r="C40" s="309"/>
+      <c r="D40" s="308"/>
+      <c r="E40" s="308"/>
+      <c r="F40" s="308"/>
+      <c r="G40" s="308"/>
+      <c r="H40" s="308"/>
+      <c r="I40" s="308"/>
+      <c r="J40" s="308"/>
       <c r="K40" s="231"/>
       <c r="L40" s="231"/>
       <c r="M40" s="232"/>
@@ -17541,102 +17547,102 @@
       <c r="A41" s="225" t="s">
         <v>858</v>
       </c>
-      <c r="B41" s="311"/>
-      <c r="C41" s="311"/>
-      <c r="D41" s="315"/>
-      <c r="E41" s="315"/>
-      <c r="F41" s="315"/>
-      <c r="G41" s="315"/>
-      <c r="H41" s="315"/>
-      <c r="I41" s="315"/>
-      <c r="J41" s="315"/>
-      <c r="K41" s="315"/>
-      <c r="L41" s="309"/>
+      <c r="B41" s="312"/>
+      <c r="C41" s="312"/>
+      <c r="D41" s="313"/>
+      <c r="E41" s="313"/>
+      <c r="F41" s="313"/>
+      <c r="G41" s="313"/>
+      <c r="H41" s="313"/>
+      <c r="I41" s="313"/>
+      <c r="J41" s="313"/>
+      <c r="K41" s="313"/>
+      <c r="L41" s="308"/>
       <c r="M41" s="232"/>
     </row>
     <row r="42" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A42" s="308" t="s">
+      <c r="A42" s="309" t="s">
         <v>859</v>
       </c>
-      <c r="B42" s="309"/>
-      <c r="C42" s="309"/>
-      <c r="D42" s="309"/>
-      <c r="E42" s="309"/>
-      <c r="F42" s="309"/>
-      <c r="G42" s="309"/>
-      <c r="H42" s="309"/>
-      <c r="I42" s="309"/>
+      <c r="B42" s="308"/>
+      <c r="C42" s="308"/>
+      <c r="D42" s="308"/>
+      <c r="E42" s="308"/>
+      <c r="F42" s="308"/>
+      <c r="G42" s="308"/>
+      <c r="H42" s="308"/>
+      <c r="I42" s="308"/>
       <c r="J42" s="231"/>
-      <c r="K42" s="309"/>
-      <c r="L42" s="309"/>
+      <c r="K42" s="308"/>
+      <c r="L42" s="308"/>
       <c r="M42" s="232"/>
     </row>
     <row r="43" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A43" s="308" t="s">
+      <c r="A43" s="309" t="s">
         <v>860</v>
       </c>
-      <c r="B43" s="309"/>
-      <c r="C43" s="309"/>
-      <c r="D43" s="309"/>
-      <c r="E43" s="309"/>
-      <c r="F43" s="309"/>
-      <c r="G43" s="309"/>
-      <c r="H43" s="309"/>
-      <c r="I43" s="309"/>
+      <c r="B43" s="308"/>
+      <c r="C43" s="308"/>
+      <c r="D43" s="308"/>
+      <c r="E43" s="308"/>
+      <c r="F43" s="308"/>
+      <c r="G43" s="308"/>
+      <c r="H43" s="308"/>
+      <c r="I43" s="308"/>
       <c r="J43" s="231"/>
-      <c r="K43" s="309"/>
-      <c r="L43" s="309"/>
+      <c r="K43" s="308"/>
+      <c r="L43" s="308"/>
       <c r="M43" s="232"/>
     </row>
     <row r="44" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A44" s="308" t="s">
+      <c r="A44" s="309" t="s">
         <v>861</v>
       </c>
-      <c r="B44" s="309"/>
-      <c r="C44" s="309"/>
-      <c r="D44" s="309"/>
-      <c r="E44" s="309"/>
-      <c r="F44" s="309"/>
-      <c r="G44" s="309"/>
-      <c r="H44" s="309"/>
-      <c r="I44" s="309"/>
-      <c r="J44" s="309"/>
-      <c r="K44" s="309"/>
-      <c r="L44" s="309"/>
+      <c r="B44" s="308"/>
+      <c r="C44" s="308"/>
+      <c r="D44" s="308"/>
+      <c r="E44" s="308"/>
+      <c r="F44" s="308"/>
+      <c r="G44" s="308"/>
+      <c r="H44" s="308"/>
+      <c r="I44" s="308"/>
+      <c r="J44" s="308"/>
+      <c r="K44" s="308"/>
+      <c r="L44" s="308"/>
       <c r="M44" s="232"/>
     </row>
     <row r="45" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A45" s="308" t="s">
+      <c r="A45" s="309" t="s">
         <v>862</v>
       </c>
-      <c r="B45" s="309"/>
-      <c r="C45" s="309"/>
-      <c r="D45" s="309"/>
-      <c r="E45" s="309"/>
-      <c r="F45" s="309"/>
-      <c r="G45" s="309"/>
-      <c r="H45" s="309"/>
-      <c r="I45" s="309"/>
-      <c r="J45" s="309"/>
-      <c r="K45" s="309"/>
-      <c r="L45" s="309"/>
+      <c r="B45" s="308"/>
+      <c r="C45" s="308"/>
+      <c r="D45" s="308"/>
+      <c r="E45" s="308"/>
+      <c r="F45" s="308"/>
+      <c r="G45" s="308"/>
+      <c r="H45" s="308"/>
+      <c r="I45" s="308"/>
+      <c r="J45" s="308"/>
+      <c r="K45" s="308"/>
+      <c r="L45" s="308"/>
       <c r="M45" s="232"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" customHeight="1">
-      <c r="A46" s="308" t="s">
+      <c r="A46" s="309" t="s">
         <v>863</v>
       </c>
-      <c r="B46" s="309"/>
-      <c r="C46" s="309"/>
-      <c r="D46" s="309"/>
-      <c r="E46" s="309"/>
-      <c r="F46" s="309"/>
-      <c r="G46" s="309"/>
-      <c r="H46" s="309"/>
+      <c r="B46" s="308"/>
+      <c r="C46" s="308"/>
+      <c r="D46" s="308"/>
+      <c r="E46" s="308"/>
+      <c r="F46" s="308"/>
+      <c r="G46" s="308"/>
+      <c r="H46" s="308"/>
       <c r="I46" s="231"/>
       <c r="J46" s="231"/>
-      <c r="K46" s="309"/>
-      <c r="L46" s="309"/>
+      <c r="K46" s="308"/>
+      <c r="L46" s="308"/>
       <c r="M46" s="232"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" customHeight="1">
@@ -17652,12 +17658,12 @@
       <c r="H47" s="233"/>
       <c r="I47" s="233"/>
       <c r="J47" s="233"/>
-      <c r="K47" s="309"/>
-      <c r="L47" s="309"/>
+      <c r="K47" s="308"/>
+      <c r="L47" s="308"/>
       <c r="M47" s="232"/>
     </row>
     <row r="48" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D48" s="309"/>
+      <c r="D48" s="308"/>
       <c r="E48" s="236"/>
       <c r="F48" s="236"/>
       <c r="G48" s="236"/>
@@ -17672,7 +17678,7 @@
       <c r="A49" s="247" t="s">
         <v>865</v>
       </c>
-      <c r="D49" s="309"/>
+      <c r="D49" s="308"/>
       <c r="E49" s="236"/>
       <c r="F49" s="236"/>
       <c r="G49" s="236"/>
@@ -17687,7 +17693,7 @@
       <c r="A50" s="247" t="s">
         <v>866</v>
       </c>
-      <c r="D50" s="309"/>
+      <c r="D50" s="308"/>
       <c r="E50" s="236"/>
       <c r="F50" s="236"/>
       <c r="G50" s="236"/>
@@ -17700,7 +17706,7 @@
     </row>
     <row r="51" spans="1:13" ht="15.75" customHeight="1">
       <c r="A51" s="316"/>
-      <c r="D51" s="309"/>
+      <c r="D51" s="308"/>
       <c r="E51" s="236"/>
       <c r="F51" s="236"/>
       <c r="G51" s="236"/>
@@ -17713,7 +17719,7 @@
     </row>
     <row r="52" spans="1:13" ht="15.75" customHeight="1">
       <c r="A52" s="248"/>
-      <c r="D52" s="309"/>
+      <c r="D52" s="308"/>
       <c r="E52" s="236"/>
       <c r="F52" s="236"/>
       <c r="G52" s="236"/>
@@ -17725,7 +17731,7 @@
       <c r="M52" s="232"/>
     </row>
     <row r="53" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D53" s="309"/>
+      <c r="D53" s="308"/>
       <c r="E53" s="236"/>
       <c r="F53" s="236"/>
       <c r="G53" s="236"/>
@@ -17737,7 +17743,7 @@
       <c r="M53" s="232"/>
     </row>
     <row r="54" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D54" s="309"/>
+      <c r="D54" s="308"/>
       <c r="E54" s="236"/>
       <c r="F54" s="236"/>
       <c r="G54" s="236"/>
@@ -17749,7 +17755,7 @@
       <c r="M54" s="232"/>
     </row>
     <row r="55" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D55" s="309"/>
+      <c r="D55" s="308"/>
       <c r="E55" s="236"/>
       <c r="F55" s="236"/>
       <c r="G55" s="236"/>
@@ -17761,7 +17767,7 @@
       <c r="M55" s="232"/>
     </row>
     <row r="56" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D56" s="309"/>
+      <c r="D56" s="308"/>
       <c r="E56" s="236"/>
       <c r="F56" s="236"/>
       <c r="G56" s="236"/>
@@ -17773,7 +17779,7 @@
       <c r="M56" s="232"/>
     </row>
     <row r="57" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D57" s="309"/>
+      <c r="D57" s="308"/>
       <c r="E57" s="236"/>
       <c r="F57" s="236"/>
       <c r="G57" s="236"/>
@@ -17785,7 +17791,7 @@
       <c r="M57" s="232"/>
     </row>
     <row r="58" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D58" s="309"/>
+      <c r="D58" s="308"/>
       <c r="E58" s="236"/>
       <c r="F58" s="236"/>
       <c r="G58" s="236"/>
@@ -17797,7 +17803,7 @@
       <c r="M58" s="232"/>
     </row>
     <row r="59" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D59" s="309"/>
+      <c r="D59" s="308"/>
       <c r="E59" s="236"/>
       <c r="F59" s="236"/>
       <c r="G59" s="236"/>
@@ -17809,7 +17815,7 @@
       <c r="M59" s="232"/>
     </row>
     <row r="60" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D60" s="309"/>
+      <c r="D60" s="308"/>
       <c r="E60" s="236"/>
       <c r="F60" s="236"/>
       <c r="G60" s="236"/>
@@ -17821,7 +17827,7 @@
       <c r="M60" s="232"/>
     </row>
     <row r="61" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D61" s="309"/>
+      <c r="D61" s="308"/>
       <c r="E61" s="236"/>
       <c r="F61" s="236"/>
       <c r="G61" s="236"/>
@@ -17833,7 +17839,7 @@
       <c r="M61" s="232"/>
     </row>
     <row r="62" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D62" s="309"/>
+      <c r="D62" s="308"/>
       <c r="E62" s="236"/>
       <c r="F62" s="236"/>
       <c r="G62" s="236"/>
@@ -17845,7 +17851,7 @@
       <c r="M62" s="232"/>
     </row>
     <row r="63" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D63" s="309"/>
+      <c r="D63" s="308"/>
       <c r="E63" s="236"/>
       <c r="F63" s="236"/>
       <c r="G63" s="236"/>
@@ -17857,7 +17863,7 @@
       <c r="M63" s="232"/>
     </row>
     <row r="64" spans="1:13" ht="15.75" customHeight="1">
-      <c r="D64" s="309"/>
+      <c r="D64" s="308"/>
       <c r="E64" s="236"/>
       <c r="F64" s="236"/>
       <c r="G64" s="236"/>
@@ -25917,7 +25923,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617F1214-FEDF-4959-B6B1-8C60CA48A0FC}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="51.42578125" customWidth="1"/>
@@ -26069,13 +26075,25 @@
         <v>1067</v>
       </c>
     </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="E18" s="134" t="s">
+        <v>1069</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E13" r:id="rId1" xr:uid="{3BD14087-096D-4B95-8D2A-BB6B2E6ECB04}"/>
     <hyperlink ref="E14" r:id="rId2" xr:uid="{9746E316-C540-456C-8DB2-33AE97228441}"/>
+    <hyperlink ref="E18" r:id="rId3" xr:uid="{30922808-7B02-4131-A1BA-A1959F68CDAC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -26095,71 +26113,71 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15.75">
       <c r="A1" s="5" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B1" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C1" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="D1" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="20.25" customHeight="1">
       <c r="A2" s="4" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B2" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C2" s="124" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1">
       <c r="A3" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B3" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C3" s="305" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="6" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="D4" s="306" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C5" s="125" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="B6" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C6" t="s">
         <v>527</v>
@@ -26167,26 +26185,26 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B7" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C7" s="123" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B8" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
     </row>
   </sheetData>
